--- a/Case Size.xlsx
+++ b/Case Size.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
+  <workbookPr defaultThemeVersion="202300"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maa00\Downloads\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF6FA16F-5ACE-4224-8EE6-63A9936AD59B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="19416" windowHeight="11496"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -13,7 +19,20 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$2:$J$2</definedName>
   </definedNames>
-  <calcPr calcId="145621"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -633,11 +652,6 @@
     <t>125 gms Scented Candle</t>
   </si>
   <si>
-    <t xml:space="preserve">20 candles unsencted 
-Extended Burn Time: Each 4-inch tall unscented candle burns continuously for up to 2 hours.
-</t>
-  </si>
-  <si>
     <r>
       <t>Regular CONE</t>
     </r>
@@ -654,11 +668,15 @@
   <si>
     <t>6 hexa pack in packet</t>
   </si>
+  <si>
+    <t>20 candles unsencted 
+Extended Burn Time: Each 4-inch tall unscented candle burns continuously for up to 2 hours.</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
   <numFmts count="4">
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="164" formatCode="0.000"/>
@@ -6088,7 +6106,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="72">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -6259,17 +6277,8 @@
     <xf numFmtId="0" fontId="37" fillId="26" borderId="139" xfId="3031" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="27" borderId="135" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="31" fillId="0" borderId="135" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="26" borderId="139" xfId="3031" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="26" borderId="139" xfId="3031" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="36" fillId="27" borderId="139" xfId="3031" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -6277,3059 +6286,3053 @@
     <xf numFmtId="0" fontId="37" fillId="27" borderId="139" xfId="3031" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="27" borderId="139" xfId="3031" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="38" fillId="0" borderId="139" xfId="3031" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="27" borderId="139" xfId="3031" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="27" borderId="139" xfId="3031" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="27" borderId="139" xfId="3031" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="166" fontId="37" fillId="27" borderId="139" xfId="3031" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="135" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="27" borderId="135" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3033">
-    <cellStyle name="20% - Accent1 10" xfId="5"/>
-    <cellStyle name="20% - Accent1 11" xfId="6"/>
-    <cellStyle name="20% - Accent1 12" xfId="7"/>
-    <cellStyle name="20% - Accent1 13" xfId="8"/>
-    <cellStyle name="20% - Accent1 14" xfId="9"/>
-    <cellStyle name="20% - Accent1 15" xfId="10"/>
-    <cellStyle name="20% - Accent1 16" xfId="11"/>
-    <cellStyle name="20% - Accent1 2" xfId="12"/>
-    <cellStyle name="20% - Accent1 3" xfId="13"/>
-    <cellStyle name="20% - Accent1 4" xfId="14"/>
-    <cellStyle name="20% - Accent1 5" xfId="15"/>
-    <cellStyle name="20% - Accent1 6" xfId="16"/>
-    <cellStyle name="20% - Accent1 7" xfId="17"/>
-    <cellStyle name="20% - Accent1 8" xfId="18"/>
-    <cellStyle name="20% - Accent1 9" xfId="19"/>
-    <cellStyle name="20% - Accent2 10" xfId="20"/>
-    <cellStyle name="20% - Accent2 11" xfId="21"/>
-    <cellStyle name="20% - Accent2 12" xfId="22"/>
-    <cellStyle name="20% - Accent2 13" xfId="23"/>
-    <cellStyle name="20% - Accent2 14" xfId="24"/>
-    <cellStyle name="20% - Accent2 15" xfId="25"/>
-    <cellStyle name="20% - Accent2 16" xfId="26"/>
-    <cellStyle name="20% - Accent2 2" xfId="27"/>
-    <cellStyle name="20% - Accent2 3" xfId="28"/>
-    <cellStyle name="20% - Accent2 4" xfId="29"/>
-    <cellStyle name="20% - Accent2 5" xfId="30"/>
-    <cellStyle name="20% - Accent2 6" xfId="31"/>
-    <cellStyle name="20% - Accent2 7" xfId="32"/>
-    <cellStyle name="20% - Accent2 8" xfId="33"/>
-    <cellStyle name="20% - Accent2 9" xfId="34"/>
-    <cellStyle name="20% - Accent3 10" xfId="35"/>
-    <cellStyle name="20% - Accent3 11" xfId="36"/>
-    <cellStyle name="20% - Accent3 12" xfId="37"/>
-    <cellStyle name="20% - Accent3 13" xfId="38"/>
-    <cellStyle name="20% - Accent3 14" xfId="39"/>
-    <cellStyle name="20% - Accent3 15" xfId="40"/>
-    <cellStyle name="20% - Accent3 16" xfId="41"/>
-    <cellStyle name="20% - Accent3 2" xfId="42"/>
-    <cellStyle name="20% - Accent3 3" xfId="43"/>
-    <cellStyle name="20% - Accent3 4" xfId="44"/>
-    <cellStyle name="20% - Accent3 5" xfId="45"/>
-    <cellStyle name="20% - Accent3 6" xfId="46"/>
-    <cellStyle name="20% - Accent3 7" xfId="47"/>
-    <cellStyle name="20% - Accent3 8" xfId="48"/>
-    <cellStyle name="20% - Accent3 9" xfId="49"/>
-    <cellStyle name="20% - Accent4 10" xfId="50"/>
-    <cellStyle name="20% - Accent4 11" xfId="51"/>
-    <cellStyle name="20% - Accent4 12" xfId="52"/>
-    <cellStyle name="20% - Accent4 13" xfId="53"/>
-    <cellStyle name="20% - Accent4 14" xfId="54"/>
-    <cellStyle name="20% - Accent4 15" xfId="55"/>
-    <cellStyle name="20% - Accent4 16" xfId="56"/>
-    <cellStyle name="20% - Accent4 2" xfId="57"/>
-    <cellStyle name="20% - Accent4 3" xfId="58"/>
-    <cellStyle name="20% - Accent4 4" xfId="59"/>
-    <cellStyle name="20% - Accent4 5" xfId="60"/>
-    <cellStyle name="20% - Accent4 6" xfId="61"/>
-    <cellStyle name="20% - Accent4 7" xfId="62"/>
-    <cellStyle name="20% - Accent4 8" xfId="63"/>
-    <cellStyle name="20% - Accent4 9" xfId="64"/>
-    <cellStyle name="20% - Accent5 10" xfId="65"/>
-    <cellStyle name="20% - Accent5 11" xfId="66"/>
-    <cellStyle name="20% - Accent5 12" xfId="67"/>
-    <cellStyle name="20% - Accent5 13" xfId="68"/>
-    <cellStyle name="20% - Accent5 14" xfId="69"/>
-    <cellStyle name="20% - Accent5 15" xfId="70"/>
-    <cellStyle name="20% - Accent5 16" xfId="71"/>
-    <cellStyle name="20% - Accent5 2" xfId="72"/>
-    <cellStyle name="20% - Accent5 3" xfId="73"/>
-    <cellStyle name="20% - Accent5 4" xfId="74"/>
-    <cellStyle name="20% - Accent5 5" xfId="75"/>
-    <cellStyle name="20% - Accent5 6" xfId="76"/>
-    <cellStyle name="20% - Accent5 7" xfId="77"/>
-    <cellStyle name="20% - Accent5 8" xfId="78"/>
-    <cellStyle name="20% - Accent5 9" xfId="79"/>
-    <cellStyle name="20% - Accent6 10" xfId="80"/>
-    <cellStyle name="20% - Accent6 11" xfId="81"/>
-    <cellStyle name="20% - Accent6 12" xfId="82"/>
-    <cellStyle name="20% - Accent6 13" xfId="83"/>
-    <cellStyle name="20% - Accent6 14" xfId="84"/>
-    <cellStyle name="20% - Accent6 15" xfId="85"/>
-    <cellStyle name="20% - Accent6 16" xfId="86"/>
-    <cellStyle name="20% - Accent6 2" xfId="87"/>
-    <cellStyle name="20% - Accent6 3" xfId="88"/>
-    <cellStyle name="20% - Accent6 4" xfId="89"/>
-    <cellStyle name="20% - Accent6 5" xfId="90"/>
-    <cellStyle name="20% - Accent6 6" xfId="91"/>
-    <cellStyle name="20% - Accent6 7" xfId="92"/>
-    <cellStyle name="20% - Accent6 8" xfId="93"/>
-    <cellStyle name="20% - Accent6 9" xfId="94"/>
-    <cellStyle name="40% - Accent1 10" xfId="95"/>
-    <cellStyle name="40% - Accent1 11" xfId="96"/>
-    <cellStyle name="40% - Accent1 12" xfId="97"/>
-    <cellStyle name="40% - Accent1 13" xfId="98"/>
-    <cellStyle name="40% - Accent1 14" xfId="99"/>
-    <cellStyle name="40% - Accent1 15" xfId="100"/>
-    <cellStyle name="40% - Accent1 16" xfId="101"/>
-    <cellStyle name="40% - Accent1 2" xfId="102"/>
-    <cellStyle name="40% - Accent1 3" xfId="103"/>
-    <cellStyle name="40% - Accent1 4" xfId="104"/>
-    <cellStyle name="40% - Accent1 5" xfId="105"/>
-    <cellStyle name="40% - Accent1 6" xfId="106"/>
-    <cellStyle name="40% - Accent1 7" xfId="107"/>
-    <cellStyle name="40% - Accent1 8" xfId="108"/>
-    <cellStyle name="40% - Accent1 9" xfId="109"/>
-    <cellStyle name="40% - Accent2 10" xfId="110"/>
-    <cellStyle name="40% - Accent2 11" xfId="111"/>
-    <cellStyle name="40% - Accent2 12" xfId="112"/>
-    <cellStyle name="40% - Accent2 13" xfId="113"/>
-    <cellStyle name="40% - Accent2 14" xfId="114"/>
-    <cellStyle name="40% - Accent2 15" xfId="115"/>
-    <cellStyle name="40% - Accent2 16" xfId="116"/>
-    <cellStyle name="40% - Accent2 2" xfId="117"/>
-    <cellStyle name="40% - Accent2 3" xfId="118"/>
-    <cellStyle name="40% - Accent2 4" xfId="119"/>
-    <cellStyle name="40% - Accent2 5" xfId="120"/>
-    <cellStyle name="40% - Accent2 6" xfId="121"/>
-    <cellStyle name="40% - Accent2 7" xfId="122"/>
-    <cellStyle name="40% - Accent2 8" xfId="123"/>
-    <cellStyle name="40% - Accent2 9" xfId="124"/>
-    <cellStyle name="40% - Accent3 10" xfId="125"/>
-    <cellStyle name="40% - Accent3 11" xfId="126"/>
-    <cellStyle name="40% - Accent3 12" xfId="127"/>
-    <cellStyle name="40% - Accent3 13" xfId="128"/>
-    <cellStyle name="40% - Accent3 14" xfId="129"/>
-    <cellStyle name="40% - Accent3 15" xfId="130"/>
-    <cellStyle name="40% - Accent3 16" xfId="131"/>
-    <cellStyle name="40% - Accent3 2" xfId="132"/>
-    <cellStyle name="40% - Accent3 3" xfId="133"/>
-    <cellStyle name="40% - Accent3 4" xfId="134"/>
-    <cellStyle name="40% - Accent3 5" xfId="135"/>
-    <cellStyle name="40% - Accent3 6" xfId="136"/>
-    <cellStyle name="40% - Accent3 7" xfId="137"/>
-    <cellStyle name="40% - Accent3 8" xfId="138"/>
-    <cellStyle name="40% - Accent3 9" xfId="139"/>
-    <cellStyle name="40% - Accent4 10" xfId="140"/>
-    <cellStyle name="40% - Accent4 11" xfId="141"/>
-    <cellStyle name="40% - Accent4 12" xfId="142"/>
-    <cellStyle name="40% - Accent4 13" xfId="143"/>
-    <cellStyle name="40% - Accent4 14" xfId="144"/>
-    <cellStyle name="40% - Accent4 15" xfId="145"/>
-    <cellStyle name="40% - Accent4 16" xfId="146"/>
-    <cellStyle name="40% - Accent4 2" xfId="147"/>
-    <cellStyle name="40% - Accent4 3" xfId="148"/>
-    <cellStyle name="40% - Accent4 4" xfId="149"/>
-    <cellStyle name="40% - Accent4 5" xfId="150"/>
-    <cellStyle name="40% - Accent4 6" xfId="151"/>
-    <cellStyle name="40% - Accent4 7" xfId="152"/>
-    <cellStyle name="40% - Accent4 8" xfId="153"/>
-    <cellStyle name="40% - Accent4 9" xfId="154"/>
-    <cellStyle name="40% - Accent5 10" xfId="155"/>
-    <cellStyle name="40% - Accent5 11" xfId="156"/>
-    <cellStyle name="40% - Accent5 12" xfId="157"/>
-    <cellStyle name="40% - Accent5 13" xfId="158"/>
-    <cellStyle name="40% - Accent5 14" xfId="159"/>
-    <cellStyle name="40% - Accent5 15" xfId="160"/>
-    <cellStyle name="40% - Accent5 16" xfId="161"/>
-    <cellStyle name="40% - Accent5 2" xfId="162"/>
-    <cellStyle name="40% - Accent5 3" xfId="163"/>
-    <cellStyle name="40% - Accent5 4" xfId="164"/>
-    <cellStyle name="40% - Accent5 5" xfId="165"/>
-    <cellStyle name="40% - Accent5 6" xfId="166"/>
-    <cellStyle name="40% - Accent5 7" xfId="167"/>
-    <cellStyle name="40% - Accent5 8" xfId="168"/>
-    <cellStyle name="40% - Accent5 9" xfId="169"/>
-    <cellStyle name="40% - Accent6 10" xfId="170"/>
-    <cellStyle name="40% - Accent6 11" xfId="171"/>
-    <cellStyle name="40% - Accent6 12" xfId="172"/>
-    <cellStyle name="40% - Accent6 13" xfId="173"/>
-    <cellStyle name="40% - Accent6 14" xfId="174"/>
-    <cellStyle name="40% - Accent6 15" xfId="175"/>
-    <cellStyle name="40% - Accent6 16" xfId="176"/>
-    <cellStyle name="40% - Accent6 2" xfId="177"/>
-    <cellStyle name="40% - Accent6 3" xfId="178"/>
-    <cellStyle name="40% - Accent6 4" xfId="179"/>
-    <cellStyle name="40% - Accent6 5" xfId="180"/>
-    <cellStyle name="40% - Accent6 6" xfId="181"/>
-    <cellStyle name="40% - Accent6 7" xfId="182"/>
-    <cellStyle name="40% - Accent6 8" xfId="183"/>
-    <cellStyle name="40% - Accent6 9" xfId="184"/>
-    <cellStyle name="60% - Accent1 10" xfId="185"/>
-    <cellStyle name="60% - Accent1 11" xfId="186"/>
-    <cellStyle name="60% - Accent1 12" xfId="187"/>
-    <cellStyle name="60% - Accent1 13" xfId="188"/>
-    <cellStyle name="60% - Accent1 14" xfId="189"/>
-    <cellStyle name="60% - Accent1 15" xfId="190"/>
-    <cellStyle name="60% - Accent1 16" xfId="191"/>
-    <cellStyle name="60% - Accent1 2" xfId="192"/>
-    <cellStyle name="60% - Accent1 3" xfId="193"/>
-    <cellStyle name="60% - Accent1 4" xfId="194"/>
-    <cellStyle name="60% - Accent1 5" xfId="195"/>
-    <cellStyle name="60% - Accent1 6" xfId="196"/>
-    <cellStyle name="60% - Accent1 7" xfId="197"/>
-    <cellStyle name="60% - Accent1 8" xfId="198"/>
-    <cellStyle name="60% - Accent1 9" xfId="199"/>
-    <cellStyle name="60% - Accent2 10" xfId="200"/>
-    <cellStyle name="60% - Accent2 11" xfId="201"/>
-    <cellStyle name="60% - Accent2 12" xfId="202"/>
-    <cellStyle name="60% - Accent2 13" xfId="203"/>
-    <cellStyle name="60% - Accent2 14" xfId="204"/>
-    <cellStyle name="60% - Accent2 15" xfId="205"/>
-    <cellStyle name="60% - Accent2 16" xfId="206"/>
-    <cellStyle name="60% - Accent2 2" xfId="207"/>
-    <cellStyle name="60% - Accent2 3" xfId="208"/>
-    <cellStyle name="60% - Accent2 4" xfId="209"/>
-    <cellStyle name="60% - Accent2 5" xfId="210"/>
-    <cellStyle name="60% - Accent2 6" xfId="211"/>
-    <cellStyle name="60% - Accent2 7" xfId="212"/>
-    <cellStyle name="60% - Accent2 8" xfId="213"/>
-    <cellStyle name="60% - Accent2 9" xfId="214"/>
-    <cellStyle name="60% - Accent3 10" xfId="215"/>
-    <cellStyle name="60% - Accent3 11" xfId="216"/>
-    <cellStyle name="60% - Accent3 12" xfId="217"/>
-    <cellStyle name="60% - Accent3 13" xfId="218"/>
-    <cellStyle name="60% - Accent3 14" xfId="219"/>
-    <cellStyle name="60% - Accent3 15" xfId="220"/>
-    <cellStyle name="60% - Accent3 16" xfId="221"/>
-    <cellStyle name="60% - Accent3 2" xfId="222"/>
-    <cellStyle name="60% - Accent3 3" xfId="223"/>
-    <cellStyle name="60% - Accent3 4" xfId="224"/>
-    <cellStyle name="60% - Accent3 5" xfId="225"/>
-    <cellStyle name="60% - Accent3 6" xfId="226"/>
-    <cellStyle name="60% - Accent3 7" xfId="227"/>
-    <cellStyle name="60% - Accent3 8" xfId="228"/>
-    <cellStyle name="60% - Accent3 9" xfId="229"/>
-    <cellStyle name="60% - Accent4 10" xfId="230"/>
-    <cellStyle name="60% - Accent4 11" xfId="231"/>
-    <cellStyle name="60% - Accent4 12" xfId="232"/>
-    <cellStyle name="60% - Accent4 13" xfId="233"/>
-    <cellStyle name="60% - Accent4 14" xfId="234"/>
-    <cellStyle name="60% - Accent4 15" xfId="235"/>
-    <cellStyle name="60% - Accent4 16" xfId="236"/>
-    <cellStyle name="60% - Accent4 2" xfId="237"/>
-    <cellStyle name="60% - Accent4 3" xfId="238"/>
-    <cellStyle name="60% - Accent4 4" xfId="239"/>
-    <cellStyle name="60% - Accent4 5" xfId="240"/>
-    <cellStyle name="60% - Accent4 6" xfId="241"/>
-    <cellStyle name="60% - Accent4 7" xfId="242"/>
-    <cellStyle name="60% - Accent4 8" xfId="243"/>
-    <cellStyle name="60% - Accent4 9" xfId="244"/>
-    <cellStyle name="60% - Accent5 10" xfId="245"/>
-    <cellStyle name="60% - Accent5 11" xfId="246"/>
-    <cellStyle name="60% - Accent5 12" xfId="247"/>
-    <cellStyle name="60% - Accent5 13" xfId="248"/>
-    <cellStyle name="60% - Accent5 14" xfId="249"/>
-    <cellStyle name="60% - Accent5 15" xfId="250"/>
-    <cellStyle name="60% - Accent5 16" xfId="251"/>
-    <cellStyle name="60% - Accent5 2" xfId="252"/>
-    <cellStyle name="60% - Accent5 3" xfId="253"/>
-    <cellStyle name="60% - Accent5 4" xfId="254"/>
-    <cellStyle name="60% - Accent5 5" xfId="255"/>
-    <cellStyle name="60% - Accent5 6" xfId="256"/>
-    <cellStyle name="60% - Accent5 7" xfId="257"/>
-    <cellStyle name="60% - Accent5 8" xfId="258"/>
-    <cellStyle name="60% - Accent5 9" xfId="259"/>
-    <cellStyle name="60% - Accent6 10" xfId="260"/>
-    <cellStyle name="60% - Accent6 11" xfId="261"/>
-    <cellStyle name="60% - Accent6 12" xfId="262"/>
-    <cellStyle name="60% - Accent6 13" xfId="263"/>
-    <cellStyle name="60% - Accent6 14" xfId="264"/>
-    <cellStyle name="60% - Accent6 15" xfId="265"/>
-    <cellStyle name="60% - Accent6 16" xfId="266"/>
-    <cellStyle name="60% - Accent6 2" xfId="267"/>
-    <cellStyle name="60% - Accent6 3" xfId="268"/>
-    <cellStyle name="60% - Accent6 4" xfId="269"/>
-    <cellStyle name="60% - Accent6 5" xfId="270"/>
-    <cellStyle name="60% - Accent6 6" xfId="271"/>
-    <cellStyle name="60% - Accent6 7" xfId="272"/>
-    <cellStyle name="60% - Accent6 8" xfId="273"/>
-    <cellStyle name="60% - Accent6 9" xfId="274"/>
-    <cellStyle name="Accent1 10" xfId="275"/>
-    <cellStyle name="Accent1 11" xfId="276"/>
-    <cellStyle name="Accent1 12" xfId="277"/>
-    <cellStyle name="Accent1 13" xfId="278"/>
-    <cellStyle name="Accent1 14" xfId="279"/>
-    <cellStyle name="Accent1 15" xfId="280"/>
-    <cellStyle name="Accent1 16" xfId="281"/>
-    <cellStyle name="Accent1 2" xfId="282"/>
-    <cellStyle name="Accent1 3" xfId="283"/>
-    <cellStyle name="Accent1 4" xfId="284"/>
-    <cellStyle name="Accent1 5" xfId="285"/>
-    <cellStyle name="Accent1 6" xfId="286"/>
-    <cellStyle name="Accent1 7" xfId="287"/>
-    <cellStyle name="Accent1 8" xfId="288"/>
-    <cellStyle name="Accent1 9" xfId="289"/>
-    <cellStyle name="Accent2 10" xfId="290"/>
-    <cellStyle name="Accent2 11" xfId="291"/>
-    <cellStyle name="Accent2 12" xfId="292"/>
-    <cellStyle name="Accent2 13" xfId="293"/>
-    <cellStyle name="Accent2 14" xfId="294"/>
-    <cellStyle name="Accent2 15" xfId="295"/>
-    <cellStyle name="Accent2 16" xfId="296"/>
-    <cellStyle name="Accent2 2" xfId="297"/>
-    <cellStyle name="Accent2 3" xfId="298"/>
-    <cellStyle name="Accent2 4" xfId="299"/>
-    <cellStyle name="Accent2 5" xfId="300"/>
-    <cellStyle name="Accent2 6" xfId="301"/>
-    <cellStyle name="Accent2 7" xfId="302"/>
-    <cellStyle name="Accent2 8" xfId="303"/>
-    <cellStyle name="Accent2 9" xfId="304"/>
-    <cellStyle name="Accent3 10" xfId="305"/>
-    <cellStyle name="Accent3 11" xfId="306"/>
-    <cellStyle name="Accent3 12" xfId="307"/>
-    <cellStyle name="Accent3 13" xfId="308"/>
-    <cellStyle name="Accent3 14" xfId="309"/>
-    <cellStyle name="Accent3 15" xfId="310"/>
-    <cellStyle name="Accent3 16" xfId="311"/>
-    <cellStyle name="Accent3 2" xfId="312"/>
-    <cellStyle name="Accent3 3" xfId="313"/>
-    <cellStyle name="Accent3 4" xfId="314"/>
-    <cellStyle name="Accent3 5" xfId="315"/>
-    <cellStyle name="Accent3 6" xfId="316"/>
-    <cellStyle name="Accent3 7" xfId="317"/>
-    <cellStyle name="Accent3 8" xfId="318"/>
-    <cellStyle name="Accent3 9" xfId="319"/>
-    <cellStyle name="Accent4 10" xfId="320"/>
-    <cellStyle name="Accent4 11" xfId="321"/>
-    <cellStyle name="Accent4 12" xfId="322"/>
-    <cellStyle name="Accent4 13" xfId="323"/>
-    <cellStyle name="Accent4 14" xfId="324"/>
-    <cellStyle name="Accent4 15" xfId="325"/>
-    <cellStyle name="Accent4 16" xfId="326"/>
-    <cellStyle name="Accent4 2" xfId="327"/>
-    <cellStyle name="Accent4 3" xfId="328"/>
-    <cellStyle name="Accent4 4" xfId="329"/>
-    <cellStyle name="Accent4 5" xfId="330"/>
-    <cellStyle name="Accent4 6" xfId="331"/>
-    <cellStyle name="Accent4 7" xfId="332"/>
-    <cellStyle name="Accent4 8" xfId="333"/>
-    <cellStyle name="Accent4 9" xfId="334"/>
-    <cellStyle name="Accent5 10" xfId="335"/>
-    <cellStyle name="Accent5 11" xfId="336"/>
-    <cellStyle name="Accent5 12" xfId="337"/>
-    <cellStyle name="Accent5 13" xfId="338"/>
-    <cellStyle name="Accent5 14" xfId="339"/>
-    <cellStyle name="Accent5 15" xfId="340"/>
-    <cellStyle name="Accent5 16" xfId="341"/>
-    <cellStyle name="Accent5 2" xfId="342"/>
-    <cellStyle name="Accent5 3" xfId="343"/>
-    <cellStyle name="Accent5 4" xfId="344"/>
-    <cellStyle name="Accent5 5" xfId="345"/>
-    <cellStyle name="Accent5 6" xfId="346"/>
-    <cellStyle name="Accent5 7" xfId="347"/>
-    <cellStyle name="Accent5 8" xfId="348"/>
-    <cellStyle name="Accent5 9" xfId="349"/>
-    <cellStyle name="Accent6 10" xfId="350"/>
-    <cellStyle name="Accent6 11" xfId="351"/>
-    <cellStyle name="Accent6 12" xfId="352"/>
-    <cellStyle name="Accent6 13" xfId="353"/>
-    <cellStyle name="Accent6 14" xfId="354"/>
-    <cellStyle name="Accent6 15" xfId="355"/>
-    <cellStyle name="Accent6 16" xfId="356"/>
-    <cellStyle name="Accent6 2" xfId="357"/>
-    <cellStyle name="Accent6 3" xfId="358"/>
-    <cellStyle name="Accent6 4" xfId="359"/>
-    <cellStyle name="Accent6 5" xfId="360"/>
-    <cellStyle name="Accent6 6" xfId="361"/>
-    <cellStyle name="Accent6 7" xfId="362"/>
-    <cellStyle name="Accent6 8" xfId="363"/>
-    <cellStyle name="Accent6 9" xfId="364"/>
-    <cellStyle name="Bad 10" xfId="365"/>
-    <cellStyle name="Bad 11" xfId="366"/>
-    <cellStyle name="Bad 12" xfId="367"/>
-    <cellStyle name="Bad 13" xfId="368"/>
-    <cellStyle name="Bad 14" xfId="369"/>
-    <cellStyle name="Bad 15" xfId="370"/>
-    <cellStyle name="Bad 16" xfId="371"/>
-    <cellStyle name="Bad 2" xfId="372"/>
-    <cellStyle name="Bad 3" xfId="373"/>
-    <cellStyle name="Bad 4" xfId="374"/>
-    <cellStyle name="Bad 5" xfId="375"/>
-    <cellStyle name="Bad 6" xfId="376"/>
-    <cellStyle name="Bad 7" xfId="377"/>
-    <cellStyle name="Bad 8" xfId="378"/>
-    <cellStyle name="Bad 9" xfId="379"/>
-    <cellStyle name="Calculation 10" xfId="380"/>
-    <cellStyle name="Calculation 10 10" xfId="955"/>
-    <cellStyle name="Calculation 10 11" xfId="830"/>
-    <cellStyle name="Calculation 10 12" xfId="970"/>
-    <cellStyle name="Calculation 10 13" xfId="815"/>
-    <cellStyle name="Calculation 10 14" xfId="986"/>
-    <cellStyle name="Calculation 10 15" xfId="891"/>
-    <cellStyle name="Calculation 10 16" xfId="1001"/>
-    <cellStyle name="Calculation 10 17" xfId="786"/>
-    <cellStyle name="Calculation 10 18" xfId="1030"/>
-    <cellStyle name="Calculation 10 19" xfId="771"/>
-    <cellStyle name="Calculation 10 2" xfId="895"/>
-    <cellStyle name="Calculation 10 20" xfId="1254"/>
-    <cellStyle name="Calculation 10 21" xfId="742"/>
-    <cellStyle name="Calculation 10 22" xfId="1086"/>
-    <cellStyle name="Calculation 10 23" xfId="1484"/>
-    <cellStyle name="Calculation 10 24" xfId="985"/>
-    <cellStyle name="Calculation 10 25" xfId="1635"/>
-    <cellStyle name="Calculation 10 26" xfId="1709"/>
-    <cellStyle name="Calculation 10 27" xfId="1785"/>
-    <cellStyle name="Calculation 10 28" xfId="1850"/>
-    <cellStyle name="Calculation 10 29" xfId="1914"/>
-    <cellStyle name="Calculation 10 3" xfId="888"/>
-    <cellStyle name="Calculation 10 30" xfId="1707"/>
-    <cellStyle name="Calculation 10 31" xfId="894"/>
-    <cellStyle name="Calculation 10 32" xfId="1848"/>
-    <cellStyle name="Calculation 10 4" xfId="911"/>
-    <cellStyle name="Calculation 10 5" xfId="890"/>
-    <cellStyle name="Calculation 10 6" xfId="910"/>
-    <cellStyle name="Calculation 10 7" xfId="860"/>
-    <cellStyle name="Calculation 10 8" xfId="940"/>
-    <cellStyle name="Calculation 10 9" xfId="845"/>
-    <cellStyle name="Calculation 11" xfId="381"/>
-    <cellStyle name="Calculation 11 10" xfId="956"/>
-    <cellStyle name="Calculation 11 11" xfId="829"/>
-    <cellStyle name="Calculation 11 12" xfId="971"/>
-    <cellStyle name="Calculation 11 13" xfId="814"/>
-    <cellStyle name="Calculation 11 14" xfId="987"/>
-    <cellStyle name="Calculation 11 15" xfId="800"/>
-    <cellStyle name="Calculation 11 16" xfId="1002"/>
-    <cellStyle name="Calculation 11 17" xfId="785"/>
-    <cellStyle name="Calculation 11 18" xfId="1031"/>
-    <cellStyle name="Calculation 11 19" xfId="770"/>
-    <cellStyle name="Calculation 11 2" xfId="896"/>
-    <cellStyle name="Calculation 11 20" xfId="1059"/>
-    <cellStyle name="Calculation 11 21" xfId="1332"/>
-    <cellStyle name="Calculation 11 22" xfId="1255"/>
-    <cellStyle name="Calculation 11 23" xfId="699"/>
-    <cellStyle name="Calculation 11 24" xfId="673"/>
-    <cellStyle name="Calculation 11 25" xfId="1214"/>
-    <cellStyle name="Calculation 11 26" xfId="1291"/>
-    <cellStyle name="Calculation 11 27" xfId="1368"/>
-    <cellStyle name="Calculation 11 28" xfId="1444"/>
-    <cellStyle name="Calculation 11 29" xfId="1519"/>
-    <cellStyle name="Calculation 11 3" xfId="887"/>
-    <cellStyle name="Calculation 11 30" xfId="1596"/>
-    <cellStyle name="Calculation 11 31" xfId="893"/>
-    <cellStyle name="Calculation 11 32" xfId="1746"/>
-    <cellStyle name="Calculation 11 4" xfId="912"/>
-    <cellStyle name="Calculation 11 5" xfId="889"/>
-    <cellStyle name="Calculation 11 6" xfId="926"/>
-    <cellStyle name="Calculation 11 7" xfId="859"/>
-    <cellStyle name="Calculation 11 8" xfId="941"/>
-    <cellStyle name="Calculation 11 9" xfId="844"/>
-    <cellStyle name="Calculation 12" xfId="382"/>
-    <cellStyle name="Calculation 12 10" xfId="957"/>
-    <cellStyle name="Calculation 12 11" xfId="828"/>
-    <cellStyle name="Calculation 12 12" xfId="972"/>
-    <cellStyle name="Calculation 12 13" xfId="813"/>
-    <cellStyle name="Calculation 12 14" xfId="988"/>
-    <cellStyle name="Calculation 12 15" xfId="799"/>
-    <cellStyle name="Calculation 12 16" xfId="1003"/>
-    <cellStyle name="Calculation 12 17" xfId="784"/>
-    <cellStyle name="Calculation 12 18" xfId="1032"/>
-    <cellStyle name="Calculation 12 19" xfId="769"/>
-    <cellStyle name="Calculation 12 2" xfId="897"/>
-    <cellStyle name="Calculation 12 20" xfId="1060"/>
-    <cellStyle name="Calculation 12 21" xfId="726"/>
-    <cellStyle name="Calculation 12 22" xfId="1087"/>
-    <cellStyle name="Calculation 12 23" xfId="1333"/>
-    <cellStyle name="Calculation 12 24" xfId="1410"/>
-    <cellStyle name="Calculation 12 25" xfId="1485"/>
-    <cellStyle name="Calculation 12 26" xfId="1561"/>
-    <cellStyle name="Calculation 12 27" xfId="1636"/>
-    <cellStyle name="Calculation 12 28" xfId="1710"/>
-    <cellStyle name="Calculation 12 29" xfId="1786"/>
-    <cellStyle name="Calculation 12 3" xfId="886"/>
-    <cellStyle name="Calculation 12 30" xfId="1597"/>
-    <cellStyle name="Calculation 12 31" xfId="892"/>
-    <cellStyle name="Calculation 12 32" xfId="1747"/>
-    <cellStyle name="Calculation 12 4" xfId="913"/>
-    <cellStyle name="Calculation 12 5" xfId="873"/>
-    <cellStyle name="Calculation 12 6" xfId="927"/>
-    <cellStyle name="Calculation 12 7" xfId="858"/>
-    <cellStyle name="Calculation 12 8" xfId="942"/>
-    <cellStyle name="Calculation 12 9" xfId="843"/>
-    <cellStyle name="Calculation 13" xfId="383"/>
-    <cellStyle name="Calculation 13 10" xfId="958"/>
-    <cellStyle name="Calculation 13 11" xfId="827"/>
-    <cellStyle name="Calculation 13 12" xfId="973"/>
-    <cellStyle name="Calculation 13 13" xfId="812"/>
-    <cellStyle name="Calculation 13 14" xfId="989"/>
-    <cellStyle name="Calculation 13 15" xfId="798"/>
-    <cellStyle name="Calculation 13 16" xfId="1004"/>
-    <cellStyle name="Calculation 13 17" xfId="783"/>
-    <cellStyle name="Calculation 13 18" xfId="1033"/>
-    <cellStyle name="Calculation 13 19" xfId="1181"/>
-    <cellStyle name="Calculation 13 2" xfId="898"/>
-    <cellStyle name="Calculation 13 20" xfId="1061"/>
-    <cellStyle name="Calculation 13 21" xfId="725"/>
-    <cellStyle name="Calculation 13 22" xfId="1088"/>
-    <cellStyle name="Calculation 13 23" xfId="698"/>
-    <cellStyle name="Calculation 13 24" xfId="1143"/>
-    <cellStyle name="Calculation 13 25" xfId="1215"/>
-    <cellStyle name="Calculation 13 26" xfId="1292"/>
-    <cellStyle name="Calculation 13 27" xfId="1369"/>
-    <cellStyle name="Calculation 13 28" xfId="1445"/>
-    <cellStyle name="Calculation 13 29" xfId="1520"/>
-    <cellStyle name="Calculation 13 3" xfId="885"/>
-    <cellStyle name="Calculation 13 30" xfId="1598"/>
-    <cellStyle name="Calculation 13 31" xfId="714"/>
-    <cellStyle name="Calculation 13 32" xfId="1748"/>
-    <cellStyle name="Calculation 13 4" xfId="914"/>
-    <cellStyle name="Calculation 13 5" xfId="872"/>
-    <cellStyle name="Calculation 13 6" xfId="928"/>
-    <cellStyle name="Calculation 13 7" xfId="857"/>
-    <cellStyle name="Calculation 13 8" xfId="943"/>
-    <cellStyle name="Calculation 13 9" xfId="842"/>
-    <cellStyle name="Calculation 14" xfId="384"/>
-    <cellStyle name="Calculation 14 10" xfId="959"/>
-    <cellStyle name="Calculation 14 11" xfId="826"/>
-    <cellStyle name="Calculation 14 12" xfId="974"/>
-    <cellStyle name="Calculation 14 13" xfId="811"/>
-    <cellStyle name="Calculation 14 14" xfId="990"/>
-    <cellStyle name="Calculation 14 15" xfId="797"/>
-    <cellStyle name="Calculation 14 16" xfId="1005"/>
-    <cellStyle name="Calculation 14 17" xfId="782"/>
-    <cellStyle name="Calculation 14 18" xfId="1034"/>
-    <cellStyle name="Calculation 14 19" xfId="753"/>
-    <cellStyle name="Calculation 14 2" xfId="899"/>
-    <cellStyle name="Calculation 14 20" xfId="1062"/>
-    <cellStyle name="Calculation 14 21" xfId="724"/>
-    <cellStyle name="Calculation 14 22" xfId="1089"/>
-    <cellStyle name="Calculation 14 23" xfId="697"/>
-    <cellStyle name="Calculation 14 24" xfId="1144"/>
-    <cellStyle name="Calculation 14 25" xfId="1330"/>
-    <cellStyle name="Calculation 14 26" xfId="1407"/>
-    <cellStyle name="Calculation 14 27" xfId="1482"/>
-    <cellStyle name="Calculation 14 28" xfId="1558"/>
-    <cellStyle name="Calculation 14 29" xfId="1633"/>
-    <cellStyle name="Calculation 14 3" xfId="884"/>
-    <cellStyle name="Calculation 14 30" xfId="1599"/>
-    <cellStyle name="Calculation 14 31" xfId="1669"/>
-    <cellStyle name="Calculation 14 32" xfId="1749"/>
-    <cellStyle name="Calculation 14 4" xfId="915"/>
-    <cellStyle name="Calculation 14 5" xfId="871"/>
-    <cellStyle name="Calculation 14 6" xfId="929"/>
-    <cellStyle name="Calculation 14 7" xfId="856"/>
-    <cellStyle name="Calculation 14 8" xfId="944"/>
-    <cellStyle name="Calculation 14 9" xfId="841"/>
-    <cellStyle name="Calculation 15" xfId="385"/>
-    <cellStyle name="Calculation 15 10" xfId="960"/>
-    <cellStyle name="Calculation 15 11" xfId="825"/>
-    <cellStyle name="Calculation 15 12" xfId="975"/>
-    <cellStyle name="Calculation 15 13" xfId="810"/>
-    <cellStyle name="Calculation 15 14" xfId="991"/>
-    <cellStyle name="Calculation 15 15" xfId="796"/>
-    <cellStyle name="Calculation 15 16" xfId="1006"/>
-    <cellStyle name="Calculation 15 17" xfId="781"/>
-    <cellStyle name="Calculation 15 18" xfId="1035"/>
-    <cellStyle name="Calculation 15 19" xfId="752"/>
-    <cellStyle name="Calculation 15 2" xfId="900"/>
-    <cellStyle name="Calculation 15 20" xfId="1063"/>
-    <cellStyle name="Calculation 15 21" xfId="1182"/>
-    <cellStyle name="Calculation 15 22" xfId="1090"/>
-    <cellStyle name="Calculation 15 23" xfId="696"/>
-    <cellStyle name="Calculation 15 24" xfId="1252"/>
-    <cellStyle name="Calculation 15 25" xfId="1216"/>
-    <cellStyle name="Calculation 15 26" xfId="1293"/>
-    <cellStyle name="Calculation 15 27" xfId="1370"/>
-    <cellStyle name="Calculation 15 28" xfId="1446"/>
-    <cellStyle name="Calculation 15 29" xfId="1521"/>
-    <cellStyle name="Calculation 15 3" xfId="883"/>
-    <cellStyle name="Calculation 15 30" xfId="1600"/>
-    <cellStyle name="Calculation 15 31" xfId="1670"/>
-    <cellStyle name="Calculation 15 32" xfId="1750"/>
-    <cellStyle name="Calculation 15 4" xfId="916"/>
-    <cellStyle name="Calculation 15 5" xfId="870"/>
-    <cellStyle name="Calculation 15 6" xfId="930"/>
-    <cellStyle name="Calculation 15 7" xfId="855"/>
-    <cellStyle name="Calculation 15 8" xfId="945"/>
-    <cellStyle name="Calculation 15 9" xfId="840"/>
-    <cellStyle name="Calculation 16" xfId="386"/>
-    <cellStyle name="Calculation 16 10" xfId="961"/>
-    <cellStyle name="Calculation 16 11" xfId="824"/>
-    <cellStyle name="Calculation 16 12" xfId="976"/>
-    <cellStyle name="Calculation 16 13" xfId="809"/>
-    <cellStyle name="Calculation 16 14" xfId="992"/>
-    <cellStyle name="Calculation 16 15" xfId="795"/>
-    <cellStyle name="Calculation 16 16" xfId="1007"/>
-    <cellStyle name="Calculation 16 17" xfId="780"/>
-    <cellStyle name="Calculation 16 18" xfId="1036"/>
-    <cellStyle name="Calculation 16 19" xfId="751"/>
-    <cellStyle name="Calculation 16 2" xfId="901"/>
-    <cellStyle name="Calculation 16 20" xfId="1064"/>
-    <cellStyle name="Calculation 16 21" xfId="723"/>
-    <cellStyle name="Calculation 16 22" xfId="1091"/>
-    <cellStyle name="Calculation 16 23" xfId="1179"/>
-    <cellStyle name="Calculation 16 24" xfId="1145"/>
-    <cellStyle name="Calculation 16 25" xfId="1217"/>
-    <cellStyle name="Calculation 16 26" xfId="1294"/>
-    <cellStyle name="Calculation 16 27" xfId="1371"/>
-    <cellStyle name="Calculation 16 28" xfId="1447"/>
-    <cellStyle name="Calculation 16 29" xfId="1522"/>
-    <cellStyle name="Calculation 16 3" xfId="882"/>
-    <cellStyle name="Calculation 16 30" xfId="1601"/>
-    <cellStyle name="Calculation 16 31" xfId="1915"/>
-    <cellStyle name="Calculation 16 32" xfId="1751"/>
-    <cellStyle name="Calculation 16 4" xfId="917"/>
-    <cellStyle name="Calculation 16 5" xfId="869"/>
-    <cellStyle name="Calculation 16 6" xfId="931"/>
-    <cellStyle name="Calculation 16 7" xfId="854"/>
-    <cellStyle name="Calculation 16 8" xfId="946"/>
-    <cellStyle name="Calculation 16 9" xfId="839"/>
-    <cellStyle name="Calculation 2" xfId="387"/>
-    <cellStyle name="Calculation 2 10" xfId="962"/>
-    <cellStyle name="Calculation 2 11" xfId="823"/>
-    <cellStyle name="Calculation 2 12" xfId="977"/>
-    <cellStyle name="Calculation 2 13" xfId="808"/>
-    <cellStyle name="Calculation 2 14" xfId="993"/>
-    <cellStyle name="Calculation 2 15" xfId="794"/>
-    <cellStyle name="Calculation 2 16" xfId="1008"/>
-    <cellStyle name="Calculation 2 17" xfId="779"/>
-    <cellStyle name="Calculation 2 18" xfId="1037"/>
-    <cellStyle name="Calculation 2 19" xfId="750"/>
-    <cellStyle name="Calculation 2 2" xfId="902"/>
-    <cellStyle name="Calculation 2 20" xfId="1065"/>
-    <cellStyle name="Calculation 2 21" xfId="722"/>
-    <cellStyle name="Calculation 2 22" xfId="1092"/>
-    <cellStyle name="Calculation 2 23" xfId="695"/>
-    <cellStyle name="Calculation 2 24" xfId="1146"/>
-    <cellStyle name="Calculation 2 25" xfId="1218"/>
-    <cellStyle name="Calculation 2 26" xfId="1295"/>
-    <cellStyle name="Calculation 2 27" xfId="1372"/>
-    <cellStyle name="Calculation 2 28" xfId="1448"/>
-    <cellStyle name="Calculation 2 29" xfId="1523"/>
-    <cellStyle name="Calculation 2 3" xfId="881"/>
-    <cellStyle name="Calculation 2 30" xfId="1602"/>
-    <cellStyle name="Calculation 2 31" xfId="1671"/>
-    <cellStyle name="Calculation 2 32" xfId="1752"/>
-    <cellStyle name="Calculation 2 4" xfId="918"/>
-    <cellStyle name="Calculation 2 5" xfId="868"/>
-    <cellStyle name="Calculation 2 6" xfId="932"/>
-    <cellStyle name="Calculation 2 7" xfId="853"/>
-    <cellStyle name="Calculation 2 8" xfId="947"/>
-    <cellStyle name="Calculation 2 9" xfId="838"/>
-    <cellStyle name="Calculation 3" xfId="388"/>
-    <cellStyle name="Calculation 3 10" xfId="963"/>
-    <cellStyle name="Calculation 3 11" xfId="822"/>
-    <cellStyle name="Calculation 3 12" xfId="978"/>
-    <cellStyle name="Calculation 3 13" xfId="807"/>
-    <cellStyle name="Calculation 3 14" xfId="994"/>
-    <cellStyle name="Calculation 3 15" xfId="793"/>
-    <cellStyle name="Calculation 3 16" xfId="1009"/>
-    <cellStyle name="Calculation 3 17" xfId="778"/>
-    <cellStyle name="Calculation 3 18" xfId="1038"/>
-    <cellStyle name="Calculation 3 19" xfId="749"/>
-    <cellStyle name="Calculation 3 2" xfId="903"/>
-    <cellStyle name="Calculation 3 20" xfId="1066"/>
-    <cellStyle name="Calculation 3 21" xfId="721"/>
-    <cellStyle name="Calculation 3 22" xfId="1093"/>
-    <cellStyle name="Calculation 3 23" xfId="694"/>
-    <cellStyle name="Calculation 3 24" xfId="1147"/>
-    <cellStyle name="Calculation 3 25" xfId="1219"/>
-    <cellStyle name="Calculation 3 26" xfId="1296"/>
-    <cellStyle name="Calculation 3 27" xfId="1373"/>
-    <cellStyle name="Calculation 3 28" xfId="1449"/>
-    <cellStyle name="Calculation 3 29" xfId="1524"/>
-    <cellStyle name="Calculation 3 3" xfId="880"/>
-    <cellStyle name="Calculation 3 30" xfId="1603"/>
-    <cellStyle name="Calculation 3 31" xfId="1783"/>
-    <cellStyle name="Calculation 3 32" xfId="1753"/>
-    <cellStyle name="Calculation 3 4" xfId="919"/>
-    <cellStyle name="Calculation 3 5" xfId="867"/>
-    <cellStyle name="Calculation 3 6" xfId="933"/>
-    <cellStyle name="Calculation 3 7" xfId="852"/>
-    <cellStyle name="Calculation 3 8" xfId="948"/>
-    <cellStyle name="Calculation 3 9" xfId="837"/>
-    <cellStyle name="Calculation 4" xfId="389"/>
-    <cellStyle name="Calculation 4 10" xfId="964"/>
-    <cellStyle name="Calculation 4 11" xfId="821"/>
-    <cellStyle name="Calculation 4 12" xfId="979"/>
-    <cellStyle name="Calculation 4 13" xfId="806"/>
-    <cellStyle name="Calculation 4 14" xfId="995"/>
-    <cellStyle name="Calculation 4 15" xfId="792"/>
-    <cellStyle name="Calculation 4 16" xfId="1010"/>
-    <cellStyle name="Calculation 4 17" xfId="777"/>
-    <cellStyle name="Calculation 4 18" xfId="1039"/>
-    <cellStyle name="Calculation 4 19" xfId="748"/>
-    <cellStyle name="Calculation 4 2" xfId="904"/>
-    <cellStyle name="Calculation 4 20" xfId="1067"/>
-    <cellStyle name="Calculation 4 21" xfId="720"/>
-    <cellStyle name="Calculation 4 22" xfId="1094"/>
-    <cellStyle name="Calculation 4 23" xfId="693"/>
-    <cellStyle name="Calculation 4 24" xfId="1148"/>
-    <cellStyle name="Calculation 4 25" xfId="1220"/>
-    <cellStyle name="Calculation 4 26" xfId="1297"/>
-    <cellStyle name="Calculation 4 27" xfId="1374"/>
-    <cellStyle name="Calculation 4 28" xfId="1450"/>
-    <cellStyle name="Calculation 4 29" xfId="1525"/>
-    <cellStyle name="Calculation 4 3" xfId="879"/>
-    <cellStyle name="Calculation 4 30" xfId="1849"/>
-    <cellStyle name="Calculation 4 31" xfId="1672"/>
-    <cellStyle name="Calculation 4 32" xfId="1754"/>
-    <cellStyle name="Calculation 4 4" xfId="920"/>
-    <cellStyle name="Calculation 4 5" xfId="866"/>
-    <cellStyle name="Calculation 4 6" xfId="934"/>
-    <cellStyle name="Calculation 4 7" xfId="851"/>
-    <cellStyle name="Calculation 4 8" xfId="949"/>
-    <cellStyle name="Calculation 4 9" xfId="836"/>
-    <cellStyle name="Calculation 5" xfId="390"/>
-    <cellStyle name="Calculation 5 10" xfId="965"/>
-    <cellStyle name="Calculation 5 11" xfId="820"/>
-    <cellStyle name="Calculation 5 12" xfId="980"/>
-    <cellStyle name="Calculation 5 13" xfId="805"/>
-    <cellStyle name="Calculation 5 14" xfId="996"/>
-    <cellStyle name="Calculation 5 15" xfId="791"/>
-    <cellStyle name="Calculation 5 16" xfId="1011"/>
-    <cellStyle name="Calculation 5 17" xfId="776"/>
-    <cellStyle name="Calculation 5 18" xfId="1040"/>
-    <cellStyle name="Calculation 5 19" xfId="747"/>
-    <cellStyle name="Calculation 5 2" xfId="905"/>
-    <cellStyle name="Calculation 5 20" xfId="672"/>
-    <cellStyle name="Calculation 5 21" xfId="719"/>
-    <cellStyle name="Calculation 5 22" xfId="674"/>
-    <cellStyle name="Calculation 5 23" xfId="692"/>
-    <cellStyle name="Calculation 5 24" xfId="1149"/>
-    <cellStyle name="Calculation 5 25" xfId="1221"/>
-    <cellStyle name="Calculation 5 26" xfId="1298"/>
-    <cellStyle name="Calculation 5 27" xfId="1375"/>
-    <cellStyle name="Calculation 5 28" xfId="1451"/>
-    <cellStyle name="Calculation 5 29" xfId="1526"/>
-    <cellStyle name="Calculation 5 3" xfId="878"/>
-    <cellStyle name="Calculation 5 30" xfId="1706"/>
-    <cellStyle name="Calculation 5 31" xfId="1673"/>
-    <cellStyle name="Calculation 5 32" xfId="1976"/>
-    <cellStyle name="Calculation 5 4" xfId="921"/>
-    <cellStyle name="Calculation 5 5" xfId="865"/>
-    <cellStyle name="Calculation 5 6" xfId="935"/>
-    <cellStyle name="Calculation 5 7" xfId="850"/>
-    <cellStyle name="Calculation 5 8" xfId="950"/>
-    <cellStyle name="Calculation 5 9" xfId="835"/>
-    <cellStyle name="Calculation 6" xfId="391"/>
-    <cellStyle name="Calculation 6 10" xfId="966"/>
-    <cellStyle name="Calculation 6 11" xfId="819"/>
-    <cellStyle name="Calculation 6 12" xfId="981"/>
-    <cellStyle name="Calculation 6 13" xfId="804"/>
-    <cellStyle name="Calculation 6 14" xfId="997"/>
-    <cellStyle name="Calculation 6 15" xfId="790"/>
-    <cellStyle name="Calculation 6 16" xfId="1012"/>
-    <cellStyle name="Calculation 6 17" xfId="775"/>
-    <cellStyle name="Calculation 6 18" xfId="1041"/>
-    <cellStyle name="Calculation 6 19" xfId="746"/>
-    <cellStyle name="Calculation 6 2" xfId="906"/>
-    <cellStyle name="Calculation 6 20" xfId="1069"/>
-    <cellStyle name="Calculation 6 21" xfId="718"/>
-    <cellStyle name="Calculation 6 22" xfId="1095"/>
-    <cellStyle name="Calculation 6 23" xfId="691"/>
-    <cellStyle name="Calculation 6 24" xfId="1150"/>
-    <cellStyle name="Calculation 6 25" xfId="1222"/>
-    <cellStyle name="Calculation 6 26" xfId="1299"/>
-    <cellStyle name="Calculation 6 27" xfId="1376"/>
-    <cellStyle name="Calculation 6 28" xfId="1452"/>
-    <cellStyle name="Calculation 6 29" xfId="1527"/>
-    <cellStyle name="Calculation 6 3" xfId="877"/>
-    <cellStyle name="Calculation 6 30" xfId="1605"/>
-    <cellStyle name="Calculation 6 31" xfId="1674"/>
-    <cellStyle name="Calculation 6 32" xfId="1755"/>
-    <cellStyle name="Calculation 6 4" xfId="922"/>
-    <cellStyle name="Calculation 6 5" xfId="864"/>
-    <cellStyle name="Calculation 6 6" xfId="936"/>
-    <cellStyle name="Calculation 6 7" xfId="849"/>
-    <cellStyle name="Calculation 6 8" xfId="951"/>
-    <cellStyle name="Calculation 6 9" xfId="834"/>
-    <cellStyle name="Calculation 7" xfId="392"/>
-    <cellStyle name="Calculation 7 10" xfId="967"/>
-    <cellStyle name="Calculation 7 11" xfId="818"/>
-    <cellStyle name="Calculation 7 12" xfId="982"/>
-    <cellStyle name="Calculation 7 13" xfId="803"/>
-    <cellStyle name="Calculation 7 14" xfId="998"/>
-    <cellStyle name="Calculation 7 15" xfId="789"/>
-    <cellStyle name="Calculation 7 16" xfId="671"/>
-    <cellStyle name="Calculation 7 17" xfId="774"/>
-    <cellStyle name="Calculation 7 18" xfId="1042"/>
-    <cellStyle name="Calculation 7 19" xfId="745"/>
-    <cellStyle name="Calculation 7 2" xfId="907"/>
-    <cellStyle name="Calculation 7 20" xfId="1070"/>
-    <cellStyle name="Calculation 7 21" xfId="717"/>
-    <cellStyle name="Calculation 7 22" xfId="1253"/>
-    <cellStyle name="Calculation 7 23" xfId="690"/>
-    <cellStyle name="Calculation 7 24" xfId="1151"/>
-    <cellStyle name="Calculation 7 25" xfId="1223"/>
-    <cellStyle name="Calculation 7 26" xfId="1300"/>
-    <cellStyle name="Calculation 7 27" xfId="1377"/>
-    <cellStyle name="Calculation 7 28" xfId="1453"/>
-    <cellStyle name="Calculation 7 29" xfId="1528"/>
-    <cellStyle name="Calculation 7 3" xfId="876"/>
-    <cellStyle name="Calculation 7 30" xfId="2100"/>
-    <cellStyle name="Calculation 7 31" xfId="1675"/>
-    <cellStyle name="Calculation 7 32" xfId="2226"/>
-    <cellStyle name="Calculation 7 4" xfId="923"/>
-    <cellStyle name="Calculation 7 5" xfId="863"/>
-    <cellStyle name="Calculation 7 6" xfId="937"/>
-    <cellStyle name="Calculation 7 7" xfId="848"/>
-    <cellStyle name="Calculation 7 8" xfId="952"/>
-    <cellStyle name="Calculation 7 9" xfId="833"/>
-    <cellStyle name="Calculation 8" xfId="393"/>
-    <cellStyle name="Calculation 8 10" xfId="968"/>
-    <cellStyle name="Calculation 8 11" xfId="817"/>
-    <cellStyle name="Calculation 8 12" xfId="983"/>
-    <cellStyle name="Calculation 8 13" xfId="802"/>
-    <cellStyle name="Calculation 8 14" xfId="999"/>
-    <cellStyle name="Calculation 8 15" xfId="788"/>
-    <cellStyle name="Calculation 8 16" xfId="1028"/>
-    <cellStyle name="Calculation 8 17" xfId="773"/>
-    <cellStyle name="Calculation 8 18" xfId="1043"/>
-    <cellStyle name="Calculation 8 19" xfId="744"/>
-    <cellStyle name="Calculation 8 2" xfId="908"/>
-    <cellStyle name="Calculation 8 20" xfId="1071"/>
-    <cellStyle name="Calculation 8 21" xfId="716"/>
-    <cellStyle name="Calculation 8 22" xfId="1560"/>
-    <cellStyle name="Calculation 8 23" xfId="1331"/>
-    <cellStyle name="Calculation 8 24" xfId="1408"/>
-    <cellStyle name="Calculation 8 25" xfId="1483"/>
-    <cellStyle name="Calculation 8 26" xfId="1559"/>
-    <cellStyle name="Calculation 8 27" xfId="1634"/>
-    <cellStyle name="Calculation 8 28" xfId="1708"/>
-    <cellStyle name="Calculation 8 29" xfId="1784"/>
-    <cellStyle name="Calculation 8 3" xfId="875"/>
-    <cellStyle name="Calculation 8 30" xfId="1745"/>
-    <cellStyle name="Calculation 8 31" xfId="1676"/>
-    <cellStyle name="Calculation 8 32" xfId="1885"/>
-    <cellStyle name="Calculation 8 4" xfId="924"/>
-    <cellStyle name="Calculation 8 5" xfId="862"/>
-    <cellStyle name="Calculation 8 6" xfId="938"/>
-    <cellStyle name="Calculation 8 7" xfId="847"/>
-    <cellStyle name="Calculation 8 8" xfId="953"/>
-    <cellStyle name="Calculation 8 9" xfId="832"/>
-    <cellStyle name="Calculation 9" xfId="394"/>
-    <cellStyle name="Calculation 9 10" xfId="969"/>
-    <cellStyle name="Calculation 9 11" xfId="816"/>
-    <cellStyle name="Calculation 9 12" xfId="984"/>
-    <cellStyle name="Calculation 9 13" xfId="801"/>
-    <cellStyle name="Calculation 9 14" xfId="1000"/>
-    <cellStyle name="Calculation 9 15" xfId="787"/>
-    <cellStyle name="Calculation 9 16" xfId="1029"/>
-    <cellStyle name="Calculation 9 17" xfId="772"/>
-    <cellStyle name="Calculation 9 18" xfId="1044"/>
-    <cellStyle name="Calculation 9 19" xfId="743"/>
-    <cellStyle name="Calculation 9 2" xfId="909"/>
-    <cellStyle name="Calculation 9 20" xfId="1409"/>
-    <cellStyle name="Calculation 9 21" xfId="715"/>
-    <cellStyle name="Calculation 9 22" xfId="1142"/>
-    <cellStyle name="Calculation 9 23" xfId="688"/>
-    <cellStyle name="Calculation 9 24" xfId="1168"/>
-    <cellStyle name="Calculation 9 25" xfId="1329"/>
-    <cellStyle name="Calculation 9 26" xfId="1406"/>
-    <cellStyle name="Calculation 9 27" xfId="1481"/>
-    <cellStyle name="Calculation 9 28" xfId="1557"/>
-    <cellStyle name="Calculation 9 29" xfId="2039"/>
-    <cellStyle name="Calculation 9 3" xfId="874"/>
-    <cellStyle name="Calculation 9 30" xfId="1977"/>
-    <cellStyle name="Calculation 9 31" xfId="1677"/>
-    <cellStyle name="Calculation 9 32" xfId="2101"/>
-    <cellStyle name="Calculation 9 4" xfId="925"/>
-    <cellStyle name="Calculation 9 5" xfId="861"/>
-    <cellStyle name="Calculation 9 6" xfId="939"/>
-    <cellStyle name="Calculation 9 7" xfId="846"/>
-    <cellStyle name="Calculation 9 8" xfId="954"/>
-    <cellStyle name="Calculation 9 9" xfId="831"/>
-    <cellStyle name="Check Cell 10" xfId="395"/>
-    <cellStyle name="Check Cell 11" xfId="396"/>
-    <cellStyle name="Check Cell 12" xfId="397"/>
-    <cellStyle name="Check Cell 13" xfId="398"/>
-    <cellStyle name="Check Cell 14" xfId="399"/>
-    <cellStyle name="Check Cell 15" xfId="400"/>
-    <cellStyle name="Check Cell 16" xfId="401"/>
-    <cellStyle name="Check Cell 2" xfId="402"/>
-    <cellStyle name="Check Cell 3" xfId="403"/>
-    <cellStyle name="Check Cell 4" xfId="404"/>
-    <cellStyle name="Check Cell 5" xfId="405"/>
-    <cellStyle name="Check Cell 6" xfId="406"/>
-    <cellStyle name="Check Cell 7" xfId="407"/>
-    <cellStyle name="Check Cell 8" xfId="408"/>
-    <cellStyle name="Check Cell 9" xfId="409"/>
-    <cellStyle name="Comma 2" xfId="3030"/>
-    <cellStyle name="Explanatory Text 10" xfId="410"/>
-    <cellStyle name="Explanatory Text 11" xfId="411"/>
-    <cellStyle name="Explanatory Text 12" xfId="412"/>
-    <cellStyle name="Explanatory Text 13" xfId="413"/>
-    <cellStyle name="Explanatory Text 14" xfId="414"/>
-    <cellStyle name="Explanatory Text 15" xfId="415"/>
-    <cellStyle name="Explanatory Text 16" xfId="416"/>
-    <cellStyle name="Explanatory Text 2" xfId="417"/>
-    <cellStyle name="Explanatory Text 3" xfId="418"/>
-    <cellStyle name="Explanatory Text 4" xfId="419"/>
-    <cellStyle name="Explanatory Text 5" xfId="420"/>
-    <cellStyle name="Explanatory Text 6" xfId="421"/>
-    <cellStyle name="Explanatory Text 7" xfId="422"/>
-    <cellStyle name="Explanatory Text 8" xfId="423"/>
-    <cellStyle name="Explanatory Text 9" xfId="424"/>
-    <cellStyle name="Good 10" xfId="425"/>
-    <cellStyle name="Good 11" xfId="426"/>
-    <cellStyle name="Good 12" xfId="427"/>
-    <cellStyle name="Good 13" xfId="428"/>
-    <cellStyle name="Good 14" xfId="429"/>
-    <cellStyle name="Good 15" xfId="430"/>
-    <cellStyle name="Good 16" xfId="431"/>
-    <cellStyle name="Good 2" xfId="432"/>
-    <cellStyle name="Good 3" xfId="433"/>
-    <cellStyle name="Good 4" xfId="434"/>
-    <cellStyle name="Good 5" xfId="435"/>
-    <cellStyle name="Good 6" xfId="436"/>
-    <cellStyle name="Good 7" xfId="437"/>
-    <cellStyle name="Good 8" xfId="438"/>
-    <cellStyle name="Good 9" xfId="439"/>
-    <cellStyle name="Heading 1 10" xfId="440"/>
-    <cellStyle name="Heading 1 11" xfId="441"/>
-    <cellStyle name="Heading 1 12" xfId="442"/>
-    <cellStyle name="Heading 1 13" xfId="443"/>
-    <cellStyle name="Heading 1 14" xfId="444"/>
-    <cellStyle name="Heading 1 15" xfId="445"/>
-    <cellStyle name="Heading 1 16" xfId="446"/>
-    <cellStyle name="Heading 1 2" xfId="447"/>
-    <cellStyle name="Heading 1 3" xfId="448"/>
-    <cellStyle name="Heading 1 4" xfId="449"/>
-    <cellStyle name="Heading 1 5" xfId="450"/>
-    <cellStyle name="Heading 1 6" xfId="451"/>
-    <cellStyle name="Heading 1 7" xfId="452"/>
-    <cellStyle name="Heading 1 8" xfId="453"/>
-    <cellStyle name="Heading 1 9" xfId="454"/>
-    <cellStyle name="Heading 2 10" xfId="455"/>
-    <cellStyle name="Heading 2 11" xfId="456"/>
-    <cellStyle name="Heading 2 12" xfId="457"/>
-    <cellStyle name="Heading 2 13" xfId="458"/>
-    <cellStyle name="Heading 2 14" xfId="459"/>
-    <cellStyle name="Heading 2 15" xfId="460"/>
-    <cellStyle name="Heading 2 16" xfId="461"/>
-    <cellStyle name="Heading 2 2" xfId="462"/>
-    <cellStyle name="Heading 2 3" xfId="463"/>
-    <cellStyle name="Heading 2 4" xfId="464"/>
-    <cellStyle name="Heading 2 5" xfId="465"/>
-    <cellStyle name="Heading 2 6" xfId="466"/>
-    <cellStyle name="Heading 2 7" xfId="467"/>
-    <cellStyle name="Heading 2 8" xfId="468"/>
-    <cellStyle name="Heading 2 9" xfId="469"/>
-    <cellStyle name="Heading 3 10" xfId="470"/>
-    <cellStyle name="Heading 3 11" xfId="471"/>
-    <cellStyle name="Heading 3 12" xfId="472"/>
-    <cellStyle name="Heading 3 13" xfId="473"/>
-    <cellStyle name="Heading 3 14" xfId="474"/>
-    <cellStyle name="Heading 3 15" xfId="475"/>
-    <cellStyle name="Heading 3 16" xfId="476"/>
-    <cellStyle name="Heading 3 2" xfId="477"/>
-    <cellStyle name="Heading 3 3" xfId="478"/>
-    <cellStyle name="Heading 3 4" xfId="479"/>
-    <cellStyle name="Heading 3 5" xfId="480"/>
-    <cellStyle name="Heading 3 6" xfId="481"/>
-    <cellStyle name="Heading 3 7" xfId="482"/>
-    <cellStyle name="Heading 3 8" xfId="483"/>
-    <cellStyle name="Heading 3 9" xfId="484"/>
-    <cellStyle name="Heading 4 10" xfId="485"/>
-    <cellStyle name="Heading 4 11" xfId="486"/>
-    <cellStyle name="Heading 4 12" xfId="487"/>
-    <cellStyle name="Heading 4 13" xfId="488"/>
-    <cellStyle name="Heading 4 14" xfId="489"/>
-    <cellStyle name="Heading 4 15" xfId="490"/>
-    <cellStyle name="Heading 4 16" xfId="491"/>
-    <cellStyle name="Heading 4 2" xfId="492"/>
-    <cellStyle name="Heading 4 3" xfId="493"/>
-    <cellStyle name="Heading 4 4" xfId="494"/>
-    <cellStyle name="Heading 4 5" xfId="495"/>
-    <cellStyle name="Heading 4 6" xfId="496"/>
-    <cellStyle name="Heading 4 7" xfId="497"/>
-    <cellStyle name="Heading 4 8" xfId="498"/>
-    <cellStyle name="Heading 4 9" xfId="499"/>
-    <cellStyle name="Input 10" xfId="500"/>
-    <cellStyle name="Input 10 10" xfId="1251"/>
-    <cellStyle name="Input 10 11" xfId="1225"/>
-    <cellStyle name="Input 10 12" xfId="1302"/>
-    <cellStyle name="Input 10 13" xfId="1379"/>
-    <cellStyle name="Input 10 14" xfId="1455"/>
-    <cellStyle name="Input 10 15" xfId="1632"/>
-    <cellStyle name="Input 10 16" xfId="1606"/>
-    <cellStyle name="Input 10 17" xfId="1782"/>
-    <cellStyle name="Input 10 18" xfId="1756"/>
-    <cellStyle name="Input 10 19" xfId="1913"/>
-    <cellStyle name="Input 10 2" xfId="1013"/>
-    <cellStyle name="Input 10 20" xfId="1887"/>
-    <cellStyle name="Input 10 21" xfId="1949"/>
-    <cellStyle name="Input 10 22" xfId="2013"/>
-    <cellStyle name="Input 10 23" xfId="2074"/>
-    <cellStyle name="Input 10 24" xfId="2225"/>
-    <cellStyle name="Input 10 25" xfId="2199"/>
-    <cellStyle name="Input 10 26" xfId="2469"/>
-    <cellStyle name="Input 10 27" xfId="2320"/>
-    <cellStyle name="Input 10 28" xfId="2380"/>
-    <cellStyle name="Input 10 29" xfId="2443"/>
-    <cellStyle name="Input 10 3" xfId="768"/>
-    <cellStyle name="Input 10 30" xfId="2518"/>
-    <cellStyle name="Input 10 31" xfId="2561"/>
-    <cellStyle name="Input 10 32" xfId="2640"/>
-    <cellStyle name="Input 10 4" xfId="1045"/>
-    <cellStyle name="Input 10 5" xfId="741"/>
-    <cellStyle name="Input 10 6" xfId="1072"/>
-    <cellStyle name="Input 10 7" xfId="1180"/>
-    <cellStyle name="Input 10 8" xfId="1097"/>
-    <cellStyle name="Input 10 9" xfId="687"/>
-    <cellStyle name="Input 11" xfId="501"/>
-    <cellStyle name="Input 11 10" xfId="1169"/>
-    <cellStyle name="Input 11 11" xfId="1226"/>
-    <cellStyle name="Input 11 12" xfId="1303"/>
-    <cellStyle name="Input 11 13" xfId="1380"/>
-    <cellStyle name="Input 11 14" xfId="1471"/>
-    <cellStyle name="Input 11 15" xfId="1530"/>
-    <cellStyle name="Input 11 16" xfId="1622"/>
-    <cellStyle name="Input 11 17" xfId="1679"/>
-    <cellStyle name="Input 11 18" xfId="1772"/>
-    <cellStyle name="Input 11 19" xfId="1820"/>
-    <cellStyle name="Input 11 2" xfId="1014"/>
-    <cellStyle name="Input 11 20" xfId="1903"/>
-    <cellStyle name="Input 11 21" xfId="1950"/>
-    <cellStyle name="Input 11 22" xfId="2029"/>
-    <cellStyle name="Input 11 23" xfId="2090"/>
-    <cellStyle name="Input 11 24" xfId="2137"/>
-    <cellStyle name="Input 11 25" xfId="2215"/>
-    <cellStyle name="Input 11 26" xfId="2259"/>
-    <cellStyle name="Input 11 27" xfId="2336"/>
-    <cellStyle name="Input 11 28" xfId="2468"/>
-    <cellStyle name="Input 11 29" xfId="2459"/>
-    <cellStyle name="Input 11 3" xfId="767"/>
-    <cellStyle name="Input 11 30" xfId="2519"/>
-    <cellStyle name="Input 11 31" xfId="2562"/>
-    <cellStyle name="Input 11 32" xfId="2641"/>
-    <cellStyle name="Input 11 4" xfId="1046"/>
-    <cellStyle name="Input 11 5" xfId="740"/>
-    <cellStyle name="Input 11 6" xfId="1073"/>
-    <cellStyle name="Input 11 7" xfId="712"/>
-    <cellStyle name="Input 11 8" xfId="1098"/>
-    <cellStyle name="Input 11 9" xfId="1178"/>
-    <cellStyle name="Input 12" xfId="502"/>
-    <cellStyle name="Input 12 10" xfId="1170"/>
-    <cellStyle name="Input 12 11" xfId="1227"/>
-    <cellStyle name="Input 12 12" xfId="1304"/>
-    <cellStyle name="Input 12 13" xfId="1396"/>
-    <cellStyle name="Input 12 14" xfId="1472"/>
-    <cellStyle name="Input 12 15" xfId="1531"/>
-    <cellStyle name="Input 12 16" xfId="1623"/>
-    <cellStyle name="Input 12 17" xfId="1680"/>
-    <cellStyle name="Input 12 18" xfId="1773"/>
-    <cellStyle name="Input 12 19" xfId="1821"/>
-    <cellStyle name="Input 12 2" xfId="1015"/>
-    <cellStyle name="Input 12 20" xfId="1904"/>
-    <cellStyle name="Input 12 21" xfId="1951"/>
-    <cellStyle name="Input 12 22" xfId="2030"/>
-    <cellStyle name="Input 12 23" xfId="2091"/>
-    <cellStyle name="Input 12 24" xfId="2138"/>
-    <cellStyle name="Input 12 25" xfId="2216"/>
-    <cellStyle name="Input 12 26" xfId="2260"/>
-    <cellStyle name="Input 12 27" xfId="2337"/>
-    <cellStyle name="Input 12 28" xfId="2381"/>
-    <cellStyle name="Input 12 29" xfId="2460"/>
-    <cellStyle name="Input 12 3" xfId="766"/>
-    <cellStyle name="Input 12 30" xfId="2520"/>
-    <cellStyle name="Input 12 31" xfId="2747"/>
-    <cellStyle name="Input 12 32" xfId="2642"/>
-    <cellStyle name="Input 12 4" xfId="1047"/>
-    <cellStyle name="Input 12 5" xfId="739"/>
-    <cellStyle name="Input 12 6" xfId="1074"/>
-    <cellStyle name="Input 12 7" xfId="711"/>
-    <cellStyle name="Input 12 8" xfId="1099"/>
-    <cellStyle name="Input 12 9" xfId="686"/>
-    <cellStyle name="Input 13" xfId="503"/>
-    <cellStyle name="Input 13 10" xfId="1171"/>
-    <cellStyle name="Input 13 11" xfId="1228"/>
-    <cellStyle name="Input 13 12" xfId="1320"/>
-    <cellStyle name="Input 13 13" xfId="1397"/>
-    <cellStyle name="Input 13 14" xfId="1473"/>
-    <cellStyle name="Input 13 15" xfId="1547"/>
-    <cellStyle name="Input 13 16" xfId="1624"/>
-    <cellStyle name="Input 13 17" xfId="1696"/>
-    <cellStyle name="Input 13 18" xfId="1774"/>
-    <cellStyle name="Input 13 19" xfId="1837"/>
-    <cellStyle name="Input 13 2" xfId="1016"/>
-    <cellStyle name="Input 13 20" xfId="1905"/>
-    <cellStyle name="Input 13 21" xfId="1967"/>
-    <cellStyle name="Input 13 22" xfId="2031"/>
-    <cellStyle name="Input 13 23" xfId="2092"/>
-    <cellStyle name="Input 13 24" xfId="2154"/>
-    <cellStyle name="Input 13 25" xfId="2217"/>
-    <cellStyle name="Input 13 26" xfId="2276"/>
-    <cellStyle name="Input 13 27" xfId="2338"/>
-    <cellStyle name="Input 13 28" xfId="2397"/>
-    <cellStyle name="Input 13 29" xfId="2461"/>
-    <cellStyle name="Input 13 3" xfId="765"/>
-    <cellStyle name="Input 13 30" xfId="2502"/>
-    <cellStyle name="Input 13 31" xfId="2648"/>
-    <cellStyle name="Input 13 32" xfId="2624"/>
-    <cellStyle name="Input 13 4" xfId="1048"/>
-    <cellStyle name="Input 13 5" xfId="738"/>
-    <cellStyle name="Input 13 6" xfId="1075"/>
-    <cellStyle name="Input 13 7" xfId="710"/>
-    <cellStyle name="Input 13 8" xfId="1100"/>
-    <cellStyle name="Input 13 9" xfId="685"/>
-    <cellStyle name="Input 14" xfId="504"/>
-    <cellStyle name="Input 14 10" xfId="1172"/>
-    <cellStyle name="Input 14 11" xfId="1244"/>
-    <cellStyle name="Input 14 12" xfId="1321"/>
-    <cellStyle name="Input 14 13" xfId="1398"/>
-    <cellStyle name="Input 14 14" xfId="1474"/>
-    <cellStyle name="Input 14 15" xfId="1548"/>
-    <cellStyle name="Input 14 16" xfId="1625"/>
-    <cellStyle name="Input 14 17" xfId="1697"/>
-    <cellStyle name="Input 14 18" xfId="1775"/>
-    <cellStyle name="Input 14 19" xfId="1838"/>
-    <cellStyle name="Input 14 2" xfId="1017"/>
-    <cellStyle name="Input 14 20" xfId="1906"/>
-    <cellStyle name="Input 14 21" xfId="1968"/>
-    <cellStyle name="Input 14 22" xfId="2032"/>
-    <cellStyle name="Input 14 23" xfId="2093"/>
-    <cellStyle name="Input 14 24" xfId="2155"/>
-    <cellStyle name="Input 14 25" xfId="2218"/>
-    <cellStyle name="Input 14 26" xfId="2277"/>
-    <cellStyle name="Input 14 27" xfId="2339"/>
-    <cellStyle name="Input 14 28" xfId="2398"/>
-    <cellStyle name="Input 14 29" xfId="2462"/>
-    <cellStyle name="Input 14 3" xfId="764"/>
-    <cellStyle name="Input 14 30" xfId="2521"/>
-    <cellStyle name="Input 14 31" xfId="2564"/>
-    <cellStyle name="Input 14 32" xfId="2643"/>
-    <cellStyle name="Input 14 4" xfId="1049"/>
-    <cellStyle name="Input 14 5" xfId="737"/>
-    <cellStyle name="Input 14 6" xfId="1076"/>
-    <cellStyle name="Input 14 7" xfId="709"/>
-    <cellStyle name="Input 14 8" xfId="1101"/>
-    <cellStyle name="Input 14 9" xfId="684"/>
-    <cellStyle name="Input 15" xfId="505"/>
-    <cellStyle name="Input 15 10" xfId="1173"/>
-    <cellStyle name="Input 15 11" xfId="1245"/>
-    <cellStyle name="Input 15 12" xfId="1322"/>
-    <cellStyle name="Input 15 13" xfId="1399"/>
-    <cellStyle name="Input 15 14" xfId="1475"/>
-    <cellStyle name="Input 15 15" xfId="1549"/>
-    <cellStyle name="Input 15 16" xfId="1626"/>
-    <cellStyle name="Input 15 17" xfId="1698"/>
-    <cellStyle name="Input 15 18" xfId="1776"/>
-    <cellStyle name="Input 15 19" xfId="1839"/>
-    <cellStyle name="Input 15 2" xfId="1018"/>
-    <cellStyle name="Input 15 20" xfId="1907"/>
-    <cellStyle name="Input 15 21" xfId="1969"/>
-    <cellStyle name="Input 15 22" xfId="2033"/>
-    <cellStyle name="Input 15 23" xfId="2094"/>
-    <cellStyle name="Input 15 24" xfId="2156"/>
-    <cellStyle name="Input 15 25" xfId="2219"/>
-    <cellStyle name="Input 15 26" xfId="2278"/>
-    <cellStyle name="Input 15 27" xfId="2340"/>
-    <cellStyle name="Input 15 28" xfId="2399"/>
-    <cellStyle name="Input 15 29" xfId="2463"/>
-    <cellStyle name="Input 15 3" xfId="763"/>
-    <cellStyle name="Input 15 30" xfId="2522"/>
-    <cellStyle name="Input 15 31" xfId="2565"/>
-    <cellStyle name="Input 15 32" xfId="2644"/>
-    <cellStyle name="Input 15 4" xfId="1050"/>
-    <cellStyle name="Input 15 5" xfId="736"/>
-    <cellStyle name="Input 15 6" xfId="1068"/>
-    <cellStyle name="Input 15 7" xfId="708"/>
-    <cellStyle name="Input 15 8" xfId="1102"/>
-    <cellStyle name="Input 15 9" xfId="683"/>
-    <cellStyle name="Input 16" xfId="506"/>
-    <cellStyle name="Input 16 10" xfId="1174"/>
-    <cellStyle name="Input 16 11" xfId="1246"/>
-    <cellStyle name="Input 16 12" xfId="1323"/>
-    <cellStyle name="Input 16 13" xfId="1400"/>
-    <cellStyle name="Input 16 14" xfId="1454"/>
-    <cellStyle name="Input 16 15" xfId="1550"/>
-    <cellStyle name="Input 16 16" xfId="1604"/>
-    <cellStyle name="Input 16 17" xfId="1699"/>
-    <cellStyle name="Input 16 18" xfId="1777"/>
-    <cellStyle name="Input 16 19" xfId="1840"/>
-    <cellStyle name="Input 16 2" xfId="1019"/>
-    <cellStyle name="Input 16 20" xfId="1908"/>
-    <cellStyle name="Input 16 21" xfId="1970"/>
-    <cellStyle name="Input 16 22" xfId="2012"/>
-    <cellStyle name="Input 16 23" xfId="2073"/>
-    <cellStyle name="Input 16 24" xfId="2157"/>
-    <cellStyle name="Input 16 25" xfId="2198"/>
-    <cellStyle name="Input 16 26" xfId="2279"/>
-    <cellStyle name="Input 16 27" xfId="2341"/>
-    <cellStyle name="Input 16 28" xfId="2400"/>
-    <cellStyle name="Input 16 29" xfId="2464"/>
-    <cellStyle name="Input 16 3" xfId="762"/>
-    <cellStyle name="Input 16 30" xfId="2523"/>
-    <cellStyle name="Input 16 31" xfId="2581"/>
-    <cellStyle name="Input 16 32" xfId="2645"/>
-    <cellStyle name="Input 16 4" xfId="1051"/>
-    <cellStyle name="Input 16 5" xfId="735"/>
-    <cellStyle name="Input 16 6" xfId="1077"/>
-    <cellStyle name="Input 16 7" xfId="707"/>
-    <cellStyle name="Input 16 8" xfId="1103"/>
-    <cellStyle name="Input 16 9" xfId="682"/>
-    <cellStyle name="Input 2" xfId="507"/>
-    <cellStyle name="Input 2 10" xfId="1152"/>
-    <cellStyle name="Input 2 11" xfId="1224"/>
-    <cellStyle name="Input 2 12" xfId="1301"/>
-    <cellStyle name="Input 2 13" xfId="1378"/>
-    <cellStyle name="Input 2 14" xfId="1476"/>
-    <cellStyle name="Input 2 15" xfId="1551"/>
-    <cellStyle name="Input 2 16" xfId="1627"/>
-    <cellStyle name="Input 2 17" xfId="1700"/>
-    <cellStyle name="Input 2 18" xfId="1847"/>
-    <cellStyle name="Input 2 19" xfId="1819"/>
-    <cellStyle name="Input 2 2" xfId="1020"/>
-    <cellStyle name="Input 2 20" xfId="1886"/>
-    <cellStyle name="Input 2 21" xfId="1948"/>
-    <cellStyle name="Input 2 22" xfId="2034"/>
-    <cellStyle name="Input 2 23" xfId="2095"/>
-    <cellStyle name="Input 2 24" xfId="2158"/>
-    <cellStyle name="Input 2 25" xfId="2220"/>
-    <cellStyle name="Input 2 26" xfId="2280"/>
-    <cellStyle name="Input 2 27" xfId="2407"/>
-    <cellStyle name="Input 2 28" xfId="2379"/>
-    <cellStyle name="Input 2 29" xfId="2442"/>
-    <cellStyle name="Input 2 3" xfId="761"/>
-    <cellStyle name="Input 2 30" xfId="2524"/>
-    <cellStyle name="Input 2 31" xfId="2582"/>
-    <cellStyle name="Input 2 32" xfId="2646"/>
-    <cellStyle name="Input 2 4" xfId="1052"/>
-    <cellStyle name="Input 2 5" xfId="734"/>
-    <cellStyle name="Input 2 6" xfId="1078"/>
-    <cellStyle name="Input 2 7" xfId="706"/>
-    <cellStyle name="Input 2 8" xfId="1104"/>
-    <cellStyle name="Input 2 9" xfId="689"/>
-    <cellStyle name="Input 3" xfId="508"/>
-    <cellStyle name="Input 3 10" xfId="1175"/>
-    <cellStyle name="Input 3 11" xfId="1247"/>
-    <cellStyle name="Input 3 12" xfId="1324"/>
-    <cellStyle name="Input 3 13" xfId="1401"/>
-    <cellStyle name="Input 3 14" xfId="1477"/>
-    <cellStyle name="Input 3 15" xfId="1529"/>
-    <cellStyle name="Input 3 16" xfId="1628"/>
-    <cellStyle name="Input 3 17" xfId="1678"/>
-    <cellStyle name="Input 3 18" xfId="1778"/>
-    <cellStyle name="Input 3 19" xfId="1841"/>
-    <cellStyle name="Input 3 2" xfId="1021"/>
-    <cellStyle name="Input 3 20" xfId="1909"/>
-    <cellStyle name="Input 3 21" xfId="1971"/>
-    <cellStyle name="Input 3 22" xfId="2035"/>
-    <cellStyle name="Input 3 23" xfId="2096"/>
-    <cellStyle name="Input 3 24" xfId="2136"/>
-    <cellStyle name="Input 3 25" xfId="2221"/>
-    <cellStyle name="Input 3 26" xfId="2281"/>
-    <cellStyle name="Input 3 27" xfId="2342"/>
-    <cellStyle name="Input 3 28" xfId="2401"/>
-    <cellStyle name="Input 3 29" xfId="2465"/>
-    <cellStyle name="Input 3 3" xfId="760"/>
-    <cellStyle name="Input 3 30" xfId="2525"/>
-    <cellStyle name="Input 3 31" xfId="2583"/>
-    <cellStyle name="Input 3 32" xfId="2647"/>
-    <cellStyle name="Input 3 4" xfId="1053"/>
-    <cellStyle name="Input 3 5" xfId="733"/>
-    <cellStyle name="Input 3 6" xfId="1079"/>
-    <cellStyle name="Input 3 7" xfId="705"/>
-    <cellStyle name="Input 3 8" xfId="1096"/>
-    <cellStyle name="Input 3 9" xfId="681"/>
-    <cellStyle name="Input 4" xfId="509"/>
-    <cellStyle name="Input 4 10" xfId="1176"/>
-    <cellStyle name="Input 4 11" xfId="1248"/>
-    <cellStyle name="Input 4 12" xfId="1325"/>
-    <cellStyle name="Input 4 13" xfId="1402"/>
-    <cellStyle name="Input 4 14" xfId="1478"/>
-    <cellStyle name="Input 4 15" xfId="1552"/>
-    <cellStyle name="Input 4 16" xfId="1629"/>
-    <cellStyle name="Input 4 17" xfId="1701"/>
-    <cellStyle name="Input 4 18" xfId="1779"/>
-    <cellStyle name="Input 4 19" xfId="1842"/>
-    <cellStyle name="Input 4 2" xfId="1022"/>
-    <cellStyle name="Input 4 20" xfId="1910"/>
-    <cellStyle name="Input 4 21" xfId="1972"/>
-    <cellStyle name="Input 4 22" xfId="2036"/>
-    <cellStyle name="Input 4 23" xfId="2097"/>
-    <cellStyle name="Input 4 24" xfId="2159"/>
-    <cellStyle name="Input 4 25" xfId="2222"/>
-    <cellStyle name="Input 4 26" xfId="2346"/>
-    <cellStyle name="Input 4 27" xfId="2343"/>
-    <cellStyle name="Input 4 28" xfId="2402"/>
-    <cellStyle name="Input 4 29" xfId="2466"/>
-    <cellStyle name="Input 4 3" xfId="759"/>
-    <cellStyle name="Input 4 30" xfId="2620"/>
-    <cellStyle name="Input 4 31" xfId="2584"/>
-    <cellStyle name="Input 4 32" xfId="2727"/>
-    <cellStyle name="Input 4 4" xfId="1054"/>
-    <cellStyle name="Input 4 5" xfId="732"/>
-    <cellStyle name="Input 4 6" xfId="1080"/>
-    <cellStyle name="Input 4 7" xfId="713"/>
-    <cellStyle name="Input 4 8" xfId="1105"/>
-    <cellStyle name="Input 4 9" xfId="680"/>
-    <cellStyle name="Input 5" xfId="510"/>
-    <cellStyle name="Input 5 10" xfId="1177"/>
-    <cellStyle name="Input 5 11" xfId="1249"/>
-    <cellStyle name="Input 5 12" xfId="1326"/>
-    <cellStyle name="Input 5 13" xfId="1403"/>
-    <cellStyle name="Input 5 14" xfId="1479"/>
-    <cellStyle name="Input 5 15" xfId="1553"/>
-    <cellStyle name="Input 5 16" xfId="1630"/>
-    <cellStyle name="Input 5 17" xfId="1702"/>
-    <cellStyle name="Input 5 18" xfId="1780"/>
-    <cellStyle name="Input 5 19" xfId="1843"/>
-    <cellStyle name="Input 5 2" xfId="1023"/>
-    <cellStyle name="Input 5 20" xfId="1911"/>
-    <cellStyle name="Input 5 21" xfId="1973"/>
-    <cellStyle name="Input 5 22" xfId="2037"/>
-    <cellStyle name="Input 5 23" xfId="2098"/>
-    <cellStyle name="Input 5 24" xfId="2160"/>
-    <cellStyle name="Input 5 25" xfId="2223"/>
-    <cellStyle name="Input 5 26" xfId="2282"/>
-    <cellStyle name="Input 5 27" xfId="2344"/>
-    <cellStyle name="Input 5 28" xfId="2403"/>
-    <cellStyle name="Input 5 29" xfId="2467"/>
-    <cellStyle name="Input 5 3" xfId="758"/>
-    <cellStyle name="Input 5 30" xfId="2621"/>
-    <cellStyle name="Input 5 31" xfId="2585"/>
-    <cellStyle name="Input 5 32" xfId="2728"/>
-    <cellStyle name="Input 5 4" xfId="1055"/>
-    <cellStyle name="Input 5 5" xfId="731"/>
-    <cellStyle name="Input 5 6" xfId="1081"/>
-    <cellStyle name="Input 5 7" xfId="704"/>
-    <cellStyle name="Input 5 8" xfId="1106"/>
-    <cellStyle name="Input 5 9" xfId="679"/>
-    <cellStyle name="Input 6" xfId="511"/>
-    <cellStyle name="Input 6 10" xfId="1256"/>
-    <cellStyle name="Input 6 11" xfId="1250"/>
-    <cellStyle name="Input 6 12" xfId="1327"/>
-    <cellStyle name="Input 6 13" xfId="1404"/>
-    <cellStyle name="Input 6 14" xfId="1480"/>
-    <cellStyle name="Input 6 15" xfId="1554"/>
-    <cellStyle name="Input 6 16" xfId="1631"/>
-    <cellStyle name="Input 6 17" xfId="1703"/>
-    <cellStyle name="Input 6 18" xfId="1781"/>
-    <cellStyle name="Input 6 19" xfId="1844"/>
-    <cellStyle name="Input 6 2" xfId="1024"/>
-    <cellStyle name="Input 6 20" xfId="1912"/>
-    <cellStyle name="Input 6 21" xfId="1974"/>
-    <cellStyle name="Input 6 22" xfId="2038"/>
-    <cellStyle name="Input 6 23" xfId="2099"/>
-    <cellStyle name="Input 6 24" xfId="2161"/>
-    <cellStyle name="Input 6 25" xfId="2224"/>
-    <cellStyle name="Input 6 26" xfId="2283"/>
-    <cellStyle name="Input 6 27" xfId="2345"/>
-    <cellStyle name="Input 6 28" xfId="2404"/>
-    <cellStyle name="Input 6 29" xfId="2526"/>
-    <cellStyle name="Input 6 3" xfId="757"/>
-    <cellStyle name="Input 6 30" xfId="2622"/>
-    <cellStyle name="Input 6 31" xfId="2563"/>
-    <cellStyle name="Input 6 32" xfId="2729"/>
-    <cellStyle name="Input 6 4" xfId="1056"/>
-    <cellStyle name="Input 6 5" xfId="730"/>
-    <cellStyle name="Input 6 6" xfId="1082"/>
-    <cellStyle name="Input 6 7" xfId="703"/>
-    <cellStyle name="Input 6 8" xfId="1138"/>
-    <cellStyle name="Input 6 9" xfId="678"/>
-    <cellStyle name="Input 7" xfId="512"/>
-    <cellStyle name="Input 7 10" xfId="1257"/>
-    <cellStyle name="Input 7 11" xfId="1334"/>
-    <cellStyle name="Input 7 12" xfId="1328"/>
-    <cellStyle name="Input 7 13" xfId="1405"/>
-    <cellStyle name="Input 7 14" xfId="1593"/>
-    <cellStyle name="Input 7 15" xfId="1555"/>
-    <cellStyle name="Input 7 16" xfId="1742"/>
-    <cellStyle name="Input 7 17" xfId="1704"/>
-    <cellStyle name="Input 7 18" xfId="1882"/>
-    <cellStyle name="Input 7 19" xfId="1845"/>
-    <cellStyle name="Input 7 2" xfId="1025"/>
-    <cellStyle name="Input 7 20" xfId="1978"/>
-    <cellStyle name="Input 7 21" xfId="1975"/>
-    <cellStyle name="Input 7 22" xfId="2133"/>
-    <cellStyle name="Input 7 23" xfId="2195"/>
-    <cellStyle name="Input 7 24" xfId="2162"/>
-    <cellStyle name="Input 7 25" xfId="2317"/>
-    <cellStyle name="Input 7 26" xfId="2284"/>
-    <cellStyle name="Input 7 27" xfId="2439"/>
-    <cellStyle name="Input 7 28" xfId="2405"/>
-    <cellStyle name="Input 7 29" xfId="2527"/>
-    <cellStyle name="Input 7 3" xfId="756"/>
-    <cellStyle name="Input 7 30" xfId="2795"/>
-    <cellStyle name="Input 7 31" xfId="2586"/>
-    <cellStyle name="Input 7 32" xfId="2730"/>
-    <cellStyle name="Input 7 4" xfId="1057"/>
-    <cellStyle name="Input 7 5" xfId="729"/>
-    <cellStyle name="Input 7 6" xfId="1083"/>
-    <cellStyle name="Input 7 7" xfId="702"/>
-    <cellStyle name="Input 7 8" xfId="1139"/>
-    <cellStyle name="Input 7 9" xfId="677"/>
-    <cellStyle name="Input 8" xfId="513"/>
-    <cellStyle name="Input 8 10" xfId="1258"/>
-    <cellStyle name="Input 8 11" xfId="1366"/>
-    <cellStyle name="Input 8 12" xfId="1442"/>
-    <cellStyle name="Input 8 13" xfId="1517"/>
-    <cellStyle name="Input 8 14" xfId="1594"/>
-    <cellStyle name="Input 8 15" xfId="1556"/>
-    <cellStyle name="Input 8 16" xfId="1743"/>
-    <cellStyle name="Input 8 17" xfId="1705"/>
-    <cellStyle name="Input 8 18" xfId="1883"/>
-    <cellStyle name="Input 8 19" xfId="1846"/>
-    <cellStyle name="Input 8 2" xfId="1026"/>
-    <cellStyle name="Input 8 20" xfId="2010"/>
-    <cellStyle name="Input 8 21" xfId="2071"/>
-    <cellStyle name="Input 8 22" xfId="2134"/>
-    <cellStyle name="Input 8 23" xfId="2196"/>
-    <cellStyle name="Input 8 24" xfId="2163"/>
-    <cellStyle name="Input 8 25" xfId="2318"/>
-    <cellStyle name="Input 8 26" xfId="2285"/>
-    <cellStyle name="Input 8 27" xfId="2440"/>
-    <cellStyle name="Input 8 28" xfId="2406"/>
-    <cellStyle name="Input 8 29" xfId="2559"/>
-    <cellStyle name="Input 8 3" xfId="755"/>
-    <cellStyle name="Input 8 30" xfId="2623"/>
-    <cellStyle name="Input 8 31" xfId="2587"/>
-    <cellStyle name="Input 8 32" xfId="2794"/>
-    <cellStyle name="Input 8 4" xfId="670"/>
-    <cellStyle name="Input 8 5" xfId="728"/>
-    <cellStyle name="Input 8 6" xfId="1084"/>
-    <cellStyle name="Input 8 7" xfId="701"/>
-    <cellStyle name="Input 8 8" xfId="1140"/>
-    <cellStyle name="Input 8 9" xfId="676"/>
-    <cellStyle name="Input 9" xfId="514"/>
-    <cellStyle name="Input 9 10" xfId="1290"/>
-    <cellStyle name="Input 9 11" xfId="1367"/>
-    <cellStyle name="Input 9 12" xfId="1443"/>
-    <cellStyle name="Input 9 13" xfId="1518"/>
-    <cellStyle name="Input 9 14" xfId="1595"/>
-    <cellStyle name="Input 9 15" xfId="1668"/>
-    <cellStyle name="Input 9 16" xfId="1744"/>
-    <cellStyle name="Input 9 17" xfId="1818"/>
-    <cellStyle name="Input 9 18" xfId="1884"/>
-    <cellStyle name="Input 9 19" xfId="1947"/>
-    <cellStyle name="Input 9 2" xfId="1027"/>
-    <cellStyle name="Input 9 20" xfId="2011"/>
-    <cellStyle name="Input 9 21" xfId="2072"/>
-    <cellStyle name="Input 9 22" xfId="2135"/>
-    <cellStyle name="Input 9 23" xfId="2197"/>
-    <cellStyle name="Input 9 24" xfId="2258"/>
-    <cellStyle name="Input 9 25" xfId="2319"/>
-    <cellStyle name="Input 9 26" xfId="2378"/>
-    <cellStyle name="Input 9 27" xfId="2441"/>
-    <cellStyle name="Input 9 28" xfId="2470"/>
-    <cellStyle name="Input 9 29" xfId="2560"/>
-    <cellStyle name="Input 9 3" xfId="754"/>
-    <cellStyle name="Input 9 30" xfId="2695"/>
-    <cellStyle name="Input 9 31" xfId="2588"/>
-    <cellStyle name="Input 9 32" xfId="2731"/>
-    <cellStyle name="Input 9 4" xfId="1058"/>
-    <cellStyle name="Input 9 5" xfId="727"/>
-    <cellStyle name="Input 9 6" xfId="1085"/>
-    <cellStyle name="Input 9 7" xfId="700"/>
-    <cellStyle name="Input 9 8" xfId="1141"/>
-    <cellStyle name="Input 9 9" xfId="675"/>
-    <cellStyle name="Linked Cell 10" xfId="515"/>
-    <cellStyle name="Linked Cell 11" xfId="516"/>
-    <cellStyle name="Linked Cell 12" xfId="517"/>
-    <cellStyle name="Linked Cell 13" xfId="518"/>
-    <cellStyle name="Linked Cell 14" xfId="519"/>
-    <cellStyle name="Linked Cell 15" xfId="520"/>
-    <cellStyle name="Linked Cell 16" xfId="521"/>
-    <cellStyle name="Linked Cell 2" xfId="522"/>
-    <cellStyle name="Linked Cell 3" xfId="523"/>
-    <cellStyle name="Linked Cell 4" xfId="524"/>
-    <cellStyle name="Linked Cell 5" xfId="525"/>
-    <cellStyle name="Linked Cell 6" xfId="526"/>
-    <cellStyle name="Linked Cell 7" xfId="527"/>
-    <cellStyle name="Linked Cell 8" xfId="528"/>
-    <cellStyle name="Linked Cell 9" xfId="529"/>
-    <cellStyle name="Neutral 10" xfId="530"/>
-    <cellStyle name="Neutral 11" xfId="531"/>
-    <cellStyle name="Neutral 12" xfId="532"/>
-    <cellStyle name="Neutral 13" xfId="533"/>
-    <cellStyle name="Neutral 14" xfId="534"/>
-    <cellStyle name="Neutral 15" xfId="535"/>
-    <cellStyle name="Neutral 16" xfId="536"/>
-    <cellStyle name="Neutral 2" xfId="537"/>
-    <cellStyle name="Neutral 3" xfId="538"/>
-    <cellStyle name="Neutral 4" xfId="539"/>
-    <cellStyle name="Neutral 5" xfId="540"/>
-    <cellStyle name="Neutral 6" xfId="541"/>
-    <cellStyle name="Neutral 7" xfId="542"/>
-    <cellStyle name="Neutral 8" xfId="543"/>
-    <cellStyle name="Neutral 9" xfId="544"/>
+    <cellStyle name="20% - Accent1 10" xfId="5" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
+    <cellStyle name="20% - Accent1 11" xfId="6" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="20% - Accent1 12" xfId="7" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
+    <cellStyle name="20% - Accent1 13" xfId="8" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
+    <cellStyle name="20% - Accent1 14" xfId="9" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
+    <cellStyle name="20% - Accent1 15" xfId="10" xr:uid="{00000000-0005-0000-0000-000005000000}"/>
+    <cellStyle name="20% - Accent1 16" xfId="11" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
+    <cellStyle name="20% - Accent1 2" xfId="12" xr:uid="{00000000-0005-0000-0000-000007000000}"/>
+    <cellStyle name="20% - Accent1 3" xfId="13" xr:uid="{00000000-0005-0000-0000-000008000000}"/>
+    <cellStyle name="20% - Accent1 4" xfId="14" xr:uid="{00000000-0005-0000-0000-000009000000}"/>
+    <cellStyle name="20% - Accent1 5" xfId="15" xr:uid="{00000000-0005-0000-0000-00000A000000}"/>
+    <cellStyle name="20% - Accent1 6" xfId="16" xr:uid="{00000000-0005-0000-0000-00000B000000}"/>
+    <cellStyle name="20% - Accent1 7" xfId="17" xr:uid="{00000000-0005-0000-0000-00000C000000}"/>
+    <cellStyle name="20% - Accent1 8" xfId="18" xr:uid="{00000000-0005-0000-0000-00000D000000}"/>
+    <cellStyle name="20% - Accent1 9" xfId="19" xr:uid="{00000000-0005-0000-0000-00000E000000}"/>
+    <cellStyle name="20% - Accent2 10" xfId="20" xr:uid="{00000000-0005-0000-0000-00000F000000}"/>
+    <cellStyle name="20% - Accent2 11" xfId="21" xr:uid="{00000000-0005-0000-0000-000010000000}"/>
+    <cellStyle name="20% - Accent2 12" xfId="22" xr:uid="{00000000-0005-0000-0000-000011000000}"/>
+    <cellStyle name="20% - Accent2 13" xfId="23" xr:uid="{00000000-0005-0000-0000-000012000000}"/>
+    <cellStyle name="20% - Accent2 14" xfId="24" xr:uid="{00000000-0005-0000-0000-000013000000}"/>
+    <cellStyle name="20% - Accent2 15" xfId="25" xr:uid="{00000000-0005-0000-0000-000014000000}"/>
+    <cellStyle name="20% - Accent2 16" xfId="26" xr:uid="{00000000-0005-0000-0000-000015000000}"/>
+    <cellStyle name="20% - Accent2 2" xfId="27" xr:uid="{00000000-0005-0000-0000-000016000000}"/>
+    <cellStyle name="20% - Accent2 3" xfId="28" xr:uid="{00000000-0005-0000-0000-000017000000}"/>
+    <cellStyle name="20% - Accent2 4" xfId="29" xr:uid="{00000000-0005-0000-0000-000018000000}"/>
+    <cellStyle name="20% - Accent2 5" xfId="30" xr:uid="{00000000-0005-0000-0000-000019000000}"/>
+    <cellStyle name="20% - Accent2 6" xfId="31" xr:uid="{00000000-0005-0000-0000-00001A000000}"/>
+    <cellStyle name="20% - Accent2 7" xfId="32" xr:uid="{00000000-0005-0000-0000-00001B000000}"/>
+    <cellStyle name="20% - Accent2 8" xfId="33" xr:uid="{00000000-0005-0000-0000-00001C000000}"/>
+    <cellStyle name="20% - Accent2 9" xfId="34" xr:uid="{00000000-0005-0000-0000-00001D000000}"/>
+    <cellStyle name="20% - Accent3 10" xfId="35" xr:uid="{00000000-0005-0000-0000-00001E000000}"/>
+    <cellStyle name="20% - Accent3 11" xfId="36" xr:uid="{00000000-0005-0000-0000-00001F000000}"/>
+    <cellStyle name="20% - Accent3 12" xfId="37" xr:uid="{00000000-0005-0000-0000-000020000000}"/>
+    <cellStyle name="20% - Accent3 13" xfId="38" xr:uid="{00000000-0005-0000-0000-000021000000}"/>
+    <cellStyle name="20% - Accent3 14" xfId="39" xr:uid="{00000000-0005-0000-0000-000022000000}"/>
+    <cellStyle name="20% - Accent3 15" xfId="40" xr:uid="{00000000-0005-0000-0000-000023000000}"/>
+    <cellStyle name="20% - Accent3 16" xfId="41" xr:uid="{00000000-0005-0000-0000-000024000000}"/>
+    <cellStyle name="20% - Accent3 2" xfId="42" xr:uid="{00000000-0005-0000-0000-000025000000}"/>
+    <cellStyle name="20% - Accent3 3" xfId="43" xr:uid="{00000000-0005-0000-0000-000026000000}"/>
+    <cellStyle name="20% - Accent3 4" xfId="44" xr:uid="{00000000-0005-0000-0000-000027000000}"/>
+    <cellStyle name="20% - Accent3 5" xfId="45" xr:uid="{00000000-0005-0000-0000-000028000000}"/>
+    <cellStyle name="20% - Accent3 6" xfId="46" xr:uid="{00000000-0005-0000-0000-000029000000}"/>
+    <cellStyle name="20% - Accent3 7" xfId="47" xr:uid="{00000000-0005-0000-0000-00002A000000}"/>
+    <cellStyle name="20% - Accent3 8" xfId="48" xr:uid="{00000000-0005-0000-0000-00002B000000}"/>
+    <cellStyle name="20% - Accent3 9" xfId="49" xr:uid="{00000000-0005-0000-0000-00002C000000}"/>
+    <cellStyle name="20% - Accent4 10" xfId="50" xr:uid="{00000000-0005-0000-0000-00002D000000}"/>
+    <cellStyle name="20% - Accent4 11" xfId="51" xr:uid="{00000000-0005-0000-0000-00002E000000}"/>
+    <cellStyle name="20% - Accent4 12" xfId="52" xr:uid="{00000000-0005-0000-0000-00002F000000}"/>
+    <cellStyle name="20% - Accent4 13" xfId="53" xr:uid="{00000000-0005-0000-0000-000030000000}"/>
+    <cellStyle name="20% - Accent4 14" xfId="54" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
+    <cellStyle name="20% - Accent4 15" xfId="55" xr:uid="{00000000-0005-0000-0000-000032000000}"/>
+    <cellStyle name="20% - Accent4 16" xfId="56" xr:uid="{00000000-0005-0000-0000-000033000000}"/>
+    <cellStyle name="20% - Accent4 2" xfId="57" xr:uid="{00000000-0005-0000-0000-000034000000}"/>
+    <cellStyle name="20% - Accent4 3" xfId="58" xr:uid="{00000000-0005-0000-0000-000035000000}"/>
+    <cellStyle name="20% - Accent4 4" xfId="59" xr:uid="{00000000-0005-0000-0000-000036000000}"/>
+    <cellStyle name="20% - Accent4 5" xfId="60" xr:uid="{00000000-0005-0000-0000-000037000000}"/>
+    <cellStyle name="20% - Accent4 6" xfId="61" xr:uid="{00000000-0005-0000-0000-000038000000}"/>
+    <cellStyle name="20% - Accent4 7" xfId="62" xr:uid="{00000000-0005-0000-0000-000039000000}"/>
+    <cellStyle name="20% - Accent4 8" xfId="63" xr:uid="{00000000-0005-0000-0000-00003A000000}"/>
+    <cellStyle name="20% - Accent4 9" xfId="64" xr:uid="{00000000-0005-0000-0000-00003B000000}"/>
+    <cellStyle name="20% - Accent5 10" xfId="65" xr:uid="{00000000-0005-0000-0000-00003C000000}"/>
+    <cellStyle name="20% - Accent5 11" xfId="66" xr:uid="{00000000-0005-0000-0000-00003D000000}"/>
+    <cellStyle name="20% - Accent5 12" xfId="67" xr:uid="{00000000-0005-0000-0000-00003E000000}"/>
+    <cellStyle name="20% - Accent5 13" xfId="68" xr:uid="{00000000-0005-0000-0000-00003F000000}"/>
+    <cellStyle name="20% - Accent5 14" xfId="69" xr:uid="{00000000-0005-0000-0000-000040000000}"/>
+    <cellStyle name="20% - Accent5 15" xfId="70" xr:uid="{00000000-0005-0000-0000-000041000000}"/>
+    <cellStyle name="20% - Accent5 16" xfId="71" xr:uid="{00000000-0005-0000-0000-000042000000}"/>
+    <cellStyle name="20% - Accent5 2" xfId="72" xr:uid="{00000000-0005-0000-0000-000043000000}"/>
+    <cellStyle name="20% - Accent5 3" xfId="73" xr:uid="{00000000-0005-0000-0000-000044000000}"/>
+    <cellStyle name="20% - Accent5 4" xfId="74" xr:uid="{00000000-0005-0000-0000-000045000000}"/>
+    <cellStyle name="20% - Accent5 5" xfId="75" xr:uid="{00000000-0005-0000-0000-000046000000}"/>
+    <cellStyle name="20% - Accent5 6" xfId="76" xr:uid="{00000000-0005-0000-0000-000047000000}"/>
+    <cellStyle name="20% - Accent5 7" xfId="77" xr:uid="{00000000-0005-0000-0000-000048000000}"/>
+    <cellStyle name="20% - Accent5 8" xfId="78" xr:uid="{00000000-0005-0000-0000-000049000000}"/>
+    <cellStyle name="20% - Accent5 9" xfId="79" xr:uid="{00000000-0005-0000-0000-00004A000000}"/>
+    <cellStyle name="20% - Accent6 10" xfId="80" xr:uid="{00000000-0005-0000-0000-00004B000000}"/>
+    <cellStyle name="20% - Accent6 11" xfId="81" xr:uid="{00000000-0005-0000-0000-00004C000000}"/>
+    <cellStyle name="20% - Accent6 12" xfId="82" xr:uid="{00000000-0005-0000-0000-00004D000000}"/>
+    <cellStyle name="20% - Accent6 13" xfId="83" xr:uid="{00000000-0005-0000-0000-00004E000000}"/>
+    <cellStyle name="20% - Accent6 14" xfId="84" xr:uid="{00000000-0005-0000-0000-00004F000000}"/>
+    <cellStyle name="20% - Accent6 15" xfId="85" xr:uid="{00000000-0005-0000-0000-000050000000}"/>
+    <cellStyle name="20% - Accent6 16" xfId="86" xr:uid="{00000000-0005-0000-0000-000051000000}"/>
+    <cellStyle name="20% - Accent6 2" xfId="87" xr:uid="{00000000-0005-0000-0000-000052000000}"/>
+    <cellStyle name="20% - Accent6 3" xfId="88" xr:uid="{00000000-0005-0000-0000-000053000000}"/>
+    <cellStyle name="20% - Accent6 4" xfId="89" xr:uid="{00000000-0005-0000-0000-000054000000}"/>
+    <cellStyle name="20% - Accent6 5" xfId="90" xr:uid="{00000000-0005-0000-0000-000055000000}"/>
+    <cellStyle name="20% - Accent6 6" xfId="91" xr:uid="{00000000-0005-0000-0000-000056000000}"/>
+    <cellStyle name="20% - Accent6 7" xfId="92" xr:uid="{00000000-0005-0000-0000-000057000000}"/>
+    <cellStyle name="20% - Accent6 8" xfId="93" xr:uid="{00000000-0005-0000-0000-000058000000}"/>
+    <cellStyle name="20% - Accent6 9" xfId="94" xr:uid="{00000000-0005-0000-0000-000059000000}"/>
+    <cellStyle name="40% - Accent1 10" xfId="95" xr:uid="{00000000-0005-0000-0000-00005A000000}"/>
+    <cellStyle name="40% - Accent1 11" xfId="96" xr:uid="{00000000-0005-0000-0000-00005B000000}"/>
+    <cellStyle name="40% - Accent1 12" xfId="97" xr:uid="{00000000-0005-0000-0000-00005C000000}"/>
+    <cellStyle name="40% - Accent1 13" xfId="98" xr:uid="{00000000-0005-0000-0000-00005D000000}"/>
+    <cellStyle name="40% - Accent1 14" xfId="99" xr:uid="{00000000-0005-0000-0000-00005E000000}"/>
+    <cellStyle name="40% - Accent1 15" xfId="100" xr:uid="{00000000-0005-0000-0000-00005F000000}"/>
+    <cellStyle name="40% - Accent1 16" xfId="101" xr:uid="{00000000-0005-0000-0000-000060000000}"/>
+    <cellStyle name="40% - Accent1 2" xfId="102" xr:uid="{00000000-0005-0000-0000-000061000000}"/>
+    <cellStyle name="40% - Accent1 3" xfId="103" xr:uid="{00000000-0005-0000-0000-000062000000}"/>
+    <cellStyle name="40% - Accent1 4" xfId="104" xr:uid="{00000000-0005-0000-0000-000063000000}"/>
+    <cellStyle name="40% - Accent1 5" xfId="105" xr:uid="{00000000-0005-0000-0000-000064000000}"/>
+    <cellStyle name="40% - Accent1 6" xfId="106" xr:uid="{00000000-0005-0000-0000-000065000000}"/>
+    <cellStyle name="40% - Accent1 7" xfId="107" xr:uid="{00000000-0005-0000-0000-000066000000}"/>
+    <cellStyle name="40% - Accent1 8" xfId="108" xr:uid="{00000000-0005-0000-0000-000067000000}"/>
+    <cellStyle name="40% - Accent1 9" xfId="109" xr:uid="{00000000-0005-0000-0000-000068000000}"/>
+    <cellStyle name="40% - Accent2 10" xfId="110" xr:uid="{00000000-0005-0000-0000-000069000000}"/>
+    <cellStyle name="40% - Accent2 11" xfId="111" xr:uid="{00000000-0005-0000-0000-00006A000000}"/>
+    <cellStyle name="40% - Accent2 12" xfId="112" xr:uid="{00000000-0005-0000-0000-00006B000000}"/>
+    <cellStyle name="40% - Accent2 13" xfId="113" xr:uid="{00000000-0005-0000-0000-00006C000000}"/>
+    <cellStyle name="40% - Accent2 14" xfId="114" xr:uid="{00000000-0005-0000-0000-00006D000000}"/>
+    <cellStyle name="40% - Accent2 15" xfId="115" xr:uid="{00000000-0005-0000-0000-00006E000000}"/>
+    <cellStyle name="40% - Accent2 16" xfId="116" xr:uid="{00000000-0005-0000-0000-00006F000000}"/>
+    <cellStyle name="40% - Accent2 2" xfId="117" xr:uid="{00000000-0005-0000-0000-000070000000}"/>
+    <cellStyle name="40% - Accent2 3" xfId="118" xr:uid="{00000000-0005-0000-0000-000071000000}"/>
+    <cellStyle name="40% - Accent2 4" xfId="119" xr:uid="{00000000-0005-0000-0000-000072000000}"/>
+    <cellStyle name="40% - Accent2 5" xfId="120" xr:uid="{00000000-0005-0000-0000-000073000000}"/>
+    <cellStyle name="40% - Accent2 6" xfId="121" xr:uid="{00000000-0005-0000-0000-000074000000}"/>
+    <cellStyle name="40% - Accent2 7" xfId="122" xr:uid="{00000000-0005-0000-0000-000075000000}"/>
+    <cellStyle name="40% - Accent2 8" xfId="123" xr:uid="{00000000-0005-0000-0000-000076000000}"/>
+    <cellStyle name="40% - Accent2 9" xfId="124" xr:uid="{00000000-0005-0000-0000-000077000000}"/>
+    <cellStyle name="40% - Accent3 10" xfId="125" xr:uid="{00000000-0005-0000-0000-000078000000}"/>
+    <cellStyle name="40% - Accent3 11" xfId="126" xr:uid="{00000000-0005-0000-0000-000079000000}"/>
+    <cellStyle name="40% - Accent3 12" xfId="127" xr:uid="{00000000-0005-0000-0000-00007A000000}"/>
+    <cellStyle name="40% - Accent3 13" xfId="128" xr:uid="{00000000-0005-0000-0000-00007B000000}"/>
+    <cellStyle name="40% - Accent3 14" xfId="129" xr:uid="{00000000-0005-0000-0000-00007C000000}"/>
+    <cellStyle name="40% - Accent3 15" xfId="130" xr:uid="{00000000-0005-0000-0000-00007D000000}"/>
+    <cellStyle name="40% - Accent3 16" xfId="131" xr:uid="{00000000-0005-0000-0000-00007E000000}"/>
+    <cellStyle name="40% - Accent3 2" xfId="132" xr:uid="{00000000-0005-0000-0000-00007F000000}"/>
+    <cellStyle name="40% - Accent3 3" xfId="133" xr:uid="{00000000-0005-0000-0000-000080000000}"/>
+    <cellStyle name="40% - Accent3 4" xfId="134" xr:uid="{00000000-0005-0000-0000-000081000000}"/>
+    <cellStyle name="40% - Accent3 5" xfId="135" xr:uid="{00000000-0005-0000-0000-000082000000}"/>
+    <cellStyle name="40% - Accent3 6" xfId="136" xr:uid="{00000000-0005-0000-0000-000083000000}"/>
+    <cellStyle name="40% - Accent3 7" xfId="137" xr:uid="{00000000-0005-0000-0000-000084000000}"/>
+    <cellStyle name="40% - Accent3 8" xfId="138" xr:uid="{00000000-0005-0000-0000-000085000000}"/>
+    <cellStyle name="40% - Accent3 9" xfId="139" xr:uid="{00000000-0005-0000-0000-000086000000}"/>
+    <cellStyle name="40% - Accent4 10" xfId="140" xr:uid="{00000000-0005-0000-0000-000087000000}"/>
+    <cellStyle name="40% - Accent4 11" xfId="141" xr:uid="{00000000-0005-0000-0000-000088000000}"/>
+    <cellStyle name="40% - Accent4 12" xfId="142" xr:uid="{00000000-0005-0000-0000-000089000000}"/>
+    <cellStyle name="40% - Accent4 13" xfId="143" xr:uid="{00000000-0005-0000-0000-00008A000000}"/>
+    <cellStyle name="40% - Accent4 14" xfId="144" xr:uid="{00000000-0005-0000-0000-00008B000000}"/>
+    <cellStyle name="40% - Accent4 15" xfId="145" xr:uid="{00000000-0005-0000-0000-00008C000000}"/>
+    <cellStyle name="40% - Accent4 16" xfId="146" xr:uid="{00000000-0005-0000-0000-00008D000000}"/>
+    <cellStyle name="40% - Accent4 2" xfId="147" xr:uid="{00000000-0005-0000-0000-00008E000000}"/>
+    <cellStyle name="40% - Accent4 3" xfId="148" xr:uid="{00000000-0005-0000-0000-00008F000000}"/>
+    <cellStyle name="40% - Accent4 4" xfId="149" xr:uid="{00000000-0005-0000-0000-000090000000}"/>
+    <cellStyle name="40% - Accent4 5" xfId="150" xr:uid="{00000000-0005-0000-0000-000091000000}"/>
+    <cellStyle name="40% - Accent4 6" xfId="151" xr:uid="{00000000-0005-0000-0000-000092000000}"/>
+    <cellStyle name="40% - Accent4 7" xfId="152" xr:uid="{00000000-0005-0000-0000-000093000000}"/>
+    <cellStyle name="40% - Accent4 8" xfId="153" xr:uid="{00000000-0005-0000-0000-000094000000}"/>
+    <cellStyle name="40% - Accent4 9" xfId="154" xr:uid="{00000000-0005-0000-0000-000095000000}"/>
+    <cellStyle name="40% - Accent5 10" xfId="155" xr:uid="{00000000-0005-0000-0000-000096000000}"/>
+    <cellStyle name="40% - Accent5 11" xfId="156" xr:uid="{00000000-0005-0000-0000-000097000000}"/>
+    <cellStyle name="40% - Accent5 12" xfId="157" xr:uid="{00000000-0005-0000-0000-000098000000}"/>
+    <cellStyle name="40% - Accent5 13" xfId="158" xr:uid="{00000000-0005-0000-0000-000099000000}"/>
+    <cellStyle name="40% - Accent5 14" xfId="159" xr:uid="{00000000-0005-0000-0000-00009A000000}"/>
+    <cellStyle name="40% - Accent5 15" xfId="160" xr:uid="{00000000-0005-0000-0000-00009B000000}"/>
+    <cellStyle name="40% - Accent5 16" xfId="161" xr:uid="{00000000-0005-0000-0000-00009C000000}"/>
+    <cellStyle name="40% - Accent5 2" xfId="162" xr:uid="{00000000-0005-0000-0000-00009D000000}"/>
+    <cellStyle name="40% - Accent5 3" xfId="163" xr:uid="{00000000-0005-0000-0000-00009E000000}"/>
+    <cellStyle name="40% - Accent5 4" xfId="164" xr:uid="{00000000-0005-0000-0000-00009F000000}"/>
+    <cellStyle name="40% - Accent5 5" xfId="165" xr:uid="{00000000-0005-0000-0000-0000A0000000}"/>
+    <cellStyle name="40% - Accent5 6" xfId="166" xr:uid="{00000000-0005-0000-0000-0000A1000000}"/>
+    <cellStyle name="40% - Accent5 7" xfId="167" xr:uid="{00000000-0005-0000-0000-0000A2000000}"/>
+    <cellStyle name="40% - Accent5 8" xfId="168" xr:uid="{00000000-0005-0000-0000-0000A3000000}"/>
+    <cellStyle name="40% - Accent5 9" xfId="169" xr:uid="{00000000-0005-0000-0000-0000A4000000}"/>
+    <cellStyle name="40% - Accent6 10" xfId="170" xr:uid="{00000000-0005-0000-0000-0000A5000000}"/>
+    <cellStyle name="40% - Accent6 11" xfId="171" xr:uid="{00000000-0005-0000-0000-0000A6000000}"/>
+    <cellStyle name="40% - Accent6 12" xfId="172" xr:uid="{00000000-0005-0000-0000-0000A7000000}"/>
+    <cellStyle name="40% - Accent6 13" xfId="173" xr:uid="{00000000-0005-0000-0000-0000A8000000}"/>
+    <cellStyle name="40% - Accent6 14" xfId="174" xr:uid="{00000000-0005-0000-0000-0000A9000000}"/>
+    <cellStyle name="40% - Accent6 15" xfId="175" xr:uid="{00000000-0005-0000-0000-0000AA000000}"/>
+    <cellStyle name="40% - Accent6 16" xfId="176" xr:uid="{00000000-0005-0000-0000-0000AB000000}"/>
+    <cellStyle name="40% - Accent6 2" xfId="177" xr:uid="{00000000-0005-0000-0000-0000AC000000}"/>
+    <cellStyle name="40% - Accent6 3" xfId="178" xr:uid="{00000000-0005-0000-0000-0000AD000000}"/>
+    <cellStyle name="40% - Accent6 4" xfId="179" xr:uid="{00000000-0005-0000-0000-0000AE000000}"/>
+    <cellStyle name="40% - Accent6 5" xfId="180" xr:uid="{00000000-0005-0000-0000-0000AF000000}"/>
+    <cellStyle name="40% - Accent6 6" xfId="181" xr:uid="{00000000-0005-0000-0000-0000B0000000}"/>
+    <cellStyle name="40% - Accent6 7" xfId="182" xr:uid="{00000000-0005-0000-0000-0000B1000000}"/>
+    <cellStyle name="40% - Accent6 8" xfId="183" xr:uid="{00000000-0005-0000-0000-0000B2000000}"/>
+    <cellStyle name="40% - Accent6 9" xfId="184" xr:uid="{00000000-0005-0000-0000-0000B3000000}"/>
+    <cellStyle name="60% - Accent1 10" xfId="185" xr:uid="{00000000-0005-0000-0000-0000B4000000}"/>
+    <cellStyle name="60% - Accent1 11" xfId="186" xr:uid="{00000000-0005-0000-0000-0000B5000000}"/>
+    <cellStyle name="60% - Accent1 12" xfId="187" xr:uid="{00000000-0005-0000-0000-0000B6000000}"/>
+    <cellStyle name="60% - Accent1 13" xfId="188" xr:uid="{00000000-0005-0000-0000-0000B7000000}"/>
+    <cellStyle name="60% - Accent1 14" xfId="189" xr:uid="{00000000-0005-0000-0000-0000B8000000}"/>
+    <cellStyle name="60% - Accent1 15" xfId="190" xr:uid="{00000000-0005-0000-0000-0000B9000000}"/>
+    <cellStyle name="60% - Accent1 16" xfId="191" xr:uid="{00000000-0005-0000-0000-0000BA000000}"/>
+    <cellStyle name="60% - Accent1 2" xfId="192" xr:uid="{00000000-0005-0000-0000-0000BB000000}"/>
+    <cellStyle name="60% - Accent1 3" xfId="193" xr:uid="{00000000-0005-0000-0000-0000BC000000}"/>
+    <cellStyle name="60% - Accent1 4" xfId="194" xr:uid="{00000000-0005-0000-0000-0000BD000000}"/>
+    <cellStyle name="60% - Accent1 5" xfId="195" xr:uid="{00000000-0005-0000-0000-0000BE000000}"/>
+    <cellStyle name="60% - Accent1 6" xfId="196" xr:uid="{00000000-0005-0000-0000-0000BF000000}"/>
+    <cellStyle name="60% - Accent1 7" xfId="197" xr:uid="{00000000-0005-0000-0000-0000C0000000}"/>
+    <cellStyle name="60% - Accent1 8" xfId="198" xr:uid="{00000000-0005-0000-0000-0000C1000000}"/>
+    <cellStyle name="60% - Accent1 9" xfId="199" xr:uid="{00000000-0005-0000-0000-0000C2000000}"/>
+    <cellStyle name="60% - Accent2 10" xfId="200" xr:uid="{00000000-0005-0000-0000-0000C3000000}"/>
+    <cellStyle name="60% - Accent2 11" xfId="201" xr:uid="{00000000-0005-0000-0000-0000C4000000}"/>
+    <cellStyle name="60% - Accent2 12" xfId="202" xr:uid="{00000000-0005-0000-0000-0000C5000000}"/>
+    <cellStyle name="60% - Accent2 13" xfId="203" xr:uid="{00000000-0005-0000-0000-0000C6000000}"/>
+    <cellStyle name="60% - Accent2 14" xfId="204" xr:uid="{00000000-0005-0000-0000-0000C7000000}"/>
+    <cellStyle name="60% - Accent2 15" xfId="205" xr:uid="{00000000-0005-0000-0000-0000C8000000}"/>
+    <cellStyle name="60% - Accent2 16" xfId="206" xr:uid="{00000000-0005-0000-0000-0000C9000000}"/>
+    <cellStyle name="60% - Accent2 2" xfId="207" xr:uid="{00000000-0005-0000-0000-0000CA000000}"/>
+    <cellStyle name="60% - Accent2 3" xfId="208" xr:uid="{00000000-0005-0000-0000-0000CB000000}"/>
+    <cellStyle name="60% - Accent2 4" xfId="209" xr:uid="{00000000-0005-0000-0000-0000CC000000}"/>
+    <cellStyle name="60% - Accent2 5" xfId="210" xr:uid="{00000000-0005-0000-0000-0000CD000000}"/>
+    <cellStyle name="60% - Accent2 6" xfId="211" xr:uid="{00000000-0005-0000-0000-0000CE000000}"/>
+    <cellStyle name="60% - Accent2 7" xfId="212" xr:uid="{00000000-0005-0000-0000-0000CF000000}"/>
+    <cellStyle name="60% - Accent2 8" xfId="213" xr:uid="{00000000-0005-0000-0000-0000D0000000}"/>
+    <cellStyle name="60% - Accent2 9" xfId="214" xr:uid="{00000000-0005-0000-0000-0000D1000000}"/>
+    <cellStyle name="60% - Accent3 10" xfId="215" xr:uid="{00000000-0005-0000-0000-0000D2000000}"/>
+    <cellStyle name="60% - Accent3 11" xfId="216" xr:uid="{00000000-0005-0000-0000-0000D3000000}"/>
+    <cellStyle name="60% - Accent3 12" xfId="217" xr:uid="{00000000-0005-0000-0000-0000D4000000}"/>
+    <cellStyle name="60% - Accent3 13" xfId="218" xr:uid="{00000000-0005-0000-0000-0000D5000000}"/>
+    <cellStyle name="60% - Accent3 14" xfId="219" xr:uid="{00000000-0005-0000-0000-0000D6000000}"/>
+    <cellStyle name="60% - Accent3 15" xfId="220" xr:uid="{00000000-0005-0000-0000-0000D7000000}"/>
+    <cellStyle name="60% - Accent3 16" xfId="221" xr:uid="{00000000-0005-0000-0000-0000D8000000}"/>
+    <cellStyle name="60% - Accent3 2" xfId="222" xr:uid="{00000000-0005-0000-0000-0000D9000000}"/>
+    <cellStyle name="60% - Accent3 3" xfId="223" xr:uid="{00000000-0005-0000-0000-0000DA000000}"/>
+    <cellStyle name="60% - Accent3 4" xfId="224" xr:uid="{00000000-0005-0000-0000-0000DB000000}"/>
+    <cellStyle name="60% - Accent3 5" xfId="225" xr:uid="{00000000-0005-0000-0000-0000DC000000}"/>
+    <cellStyle name="60% - Accent3 6" xfId="226" xr:uid="{00000000-0005-0000-0000-0000DD000000}"/>
+    <cellStyle name="60% - Accent3 7" xfId="227" xr:uid="{00000000-0005-0000-0000-0000DE000000}"/>
+    <cellStyle name="60% - Accent3 8" xfId="228" xr:uid="{00000000-0005-0000-0000-0000DF000000}"/>
+    <cellStyle name="60% - Accent3 9" xfId="229" xr:uid="{00000000-0005-0000-0000-0000E0000000}"/>
+    <cellStyle name="60% - Accent4 10" xfId="230" xr:uid="{00000000-0005-0000-0000-0000E1000000}"/>
+    <cellStyle name="60% - Accent4 11" xfId="231" xr:uid="{00000000-0005-0000-0000-0000E2000000}"/>
+    <cellStyle name="60% - Accent4 12" xfId="232" xr:uid="{00000000-0005-0000-0000-0000E3000000}"/>
+    <cellStyle name="60% - Accent4 13" xfId="233" xr:uid="{00000000-0005-0000-0000-0000E4000000}"/>
+    <cellStyle name="60% - Accent4 14" xfId="234" xr:uid="{00000000-0005-0000-0000-0000E5000000}"/>
+    <cellStyle name="60% - Accent4 15" xfId="235" xr:uid="{00000000-0005-0000-0000-0000E6000000}"/>
+    <cellStyle name="60% - Accent4 16" xfId="236" xr:uid="{00000000-0005-0000-0000-0000E7000000}"/>
+    <cellStyle name="60% - Accent4 2" xfId="237" xr:uid="{00000000-0005-0000-0000-0000E8000000}"/>
+    <cellStyle name="60% - Accent4 3" xfId="238" xr:uid="{00000000-0005-0000-0000-0000E9000000}"/>
+    <cellStyle name="60% - Accent4 4" xfId="239" xr:uid="{00000000-0005-0000-0000-0000EA000000}"/>
+    <cellStyle name="60% - Accent4 5" xfId="240" xr:uid="{00000000-0005-0000-0000-0000EB000000}"/>
+    <cellStyle name="60% - Accent4 6" xfId="241" xr:uid="{00000000-0005-0000-0000-0000EC000000}"/>
+    <cellStyle name="60% - Accent4 7" xfId="242" xr:uid="{00000000-0005-0000-0000-0000ED000000}"/>
+    <cellStyle name="60% - Accent4 8" xfId="243" xr:uid="{00000000-0005-0000-0000-0000EE000000}"/>
+    <cellStyle name="60% - Accent4 9" xfId="244" xr:uid="{00000000-0005-0000-0000-0000EF000000}"/>
+    <cellStyle name="60% - Accent5 10" xfId="245" xr:uid="{00000000-0005-0000-0000-0000F0000000}"/>
+    <cellStyle name="60% - Accent5 11" xfId="246" xr:uid="{00000000-0005-0000-0000-0000F1000000}"/>
+    <cellStyle name="60% - Accent5 12" xfId="247" xr:uid="{00000000-0005-0000-0000-0000F2000000}"/>
+    <cellStyle name="60% - Accent5 13" xfId="248" xr:uid="{00000000-0005-0000-0000-0000F3000000}"/>
+    <cellStyle name="60% - Accent5 14" xfId="249" xr:uid="{00000000-0005-0000-0000-0000F4000000}"/>
+    <cellStyle name="60% - Accent5 15" xfId="250" xr:uid="{00000000-0005-0000-0000-0000F5000000}"/>
+    <cellStyle name="60% - Accent5 16" xfId="251" xr:uid="{00000000-0005-0000-0000-0000F6000000}"/>
+    <cellStyle name="60% - Accent5 2" xfId="252" xr:uid="{00000000-0005-0000-0000-0000F7000000}"/>
+    <cellStyle name="60% - Accent5 3" xfId="253" xr:uid="{00000000-0005-0000-0000-0000F8000000}"/>
+    <cellStyle name="60% - Accent5 4" xfId="254" xr:uid="{00000000-0005-0000-0000-0000F9000000}"/>
+    <cellStyle name="60% - Accent5 5" xfId="255" xr:uid="{00000000-0005-0000-0000-0000FA000000}"/>
+    <cellStyle name="60% - Accent5 6" xfId="256" xr:uid="{00000000-0005-0000-0000-0000FB000000}"/>
+    <cellStyle name="60% - Accent5 7" xfId="257" xr:uid="{00000000-0005-0000-0000-0000FC000000}"/>
+    <cellStyle name="60% - Accent5 8" xfId="258" xr:uid="{00000000-0005-0000-0000-0000FD000000}"/>
+    <cellStyle name="60% - Accent5 9" xfId="259" xr:uid="{00000000-0005-0000-0000-0000FE000000}"/>
+    <cellStyle name="60% - Accent6 10" xfId="260" xr:uid="{00000000-0005-0000-0000-0000FF000000}"/>
+    <cellStyle name="60% - Accent6 11" xfId="261" xr:uid="{00000000-0005-0000-0000-000000010000}"/>
+    <cellStyle name="60% - Accent6 12" xfId="262" xr:uid="{00000000-0005-0000-0000-000001010000}"/>
+    <cellStyle name="60% - Accent6 13" xfId="263" xr:uid="{00000000-0005-0000-0000-000002010000}"/>
+    <cellStyle name="60% - Accent6 14" xfId="264" xr:uid="{00000000-0005-0000-0000-000003010000}"/>
+    <cellStyle name="60% - Accent6 15" xfId="265" xr:uid="{00000000-0005-0000-0000-000004010000}"/>
+    <cellStyle name="60% - Accent6 16" xfId="266" xr:uid="{00000000-0005-0000-0000-000005010000}"/>
+    <cellStyle name="60% - Accent6 2" xfId="267" xr:uid="{00000000-0005-0000-0000-000006010000}"/>
+    <cellStyle name="60% - Accent6 3" xfId="268" xr:uid="{00000000-0005-0000-0000-000007010000}"/>
+    <cellStyle name="60% - Accent6 4" xfId="269" xr:uid="{00000000-0005-0000-0000-000008010000}"/>
+    <cellStyle name="60% - Accent6 5" xfId="270" xr:uid="{00000000-0005-0000-0000-000009010000}"/>
+    <cellStyle name="60% - Accent6 6" xfId="271" xr:uid="{00000000-0005-0000-0000-00000A010000}"/>
+    <cellStyle name="60% - Accent6 7" xfId="272" xr:uid="{00000000-0005-0000-0000-00000B010000}"/>
+    <cellStyle name="60% - Accent6 8" xfId="273" xr:uid="{00000000-0005-0000-0000-00000C010000}"/>
+    <cellStyle name="60% - Accent6 9" xfId="274" xr:uid="{00000000-0005-0000-0000-00000D010000}"/>
+    <cellStyle name="Accent1 10" xfId="275" xr:uid="{00000000-0005-0000-0000-00000E010000}"/>
+    <cellStyle name="Accent1 11" xfId="276" xr:uid="{00000000-0005-0000-0000-00000F010000}"/>
+    <cellStyle name="Accent1 12" xfId="277" xr:uid="{00000000-0005-0000-0000-000010010000}"/>
+    <cellStyle name="Accent1 13" xfId="278" xr:uid="{00000000-0005-0000-0000-000011010000}"/>
+    <cellStyle name="Accent1 14" xfId="279" xr:uid="{00000000-0005-0000-0000-000012010000}"/>
+    <cellStyle name="Accent1 15" xfId="280" xr:uid="{00000000-0005-0000-0000-000013010000}"/>
+    <cellStyle name="Accent1 16" xfId="281" xr:uid="{00000000-0005-0000-0000-000014010000}"/>
+    <cellStyle name="Accent1 2" xfId="282" xr:uid="{00000000-0005-0000-0000-000015010000}"/>
+    <cellStyle name="Accent1 3" xfId="283" xr:uid="{00000000-0005-0000-0000-000016010000}"/>
+    <cellStyle name="Accent1 4" xfId="284" xr:uid="{00000000-0005-0000-0000-000017010000}"/>
+    <cellStyle name="Accent1 5" xfId="285" xr:uid="{00000000-0005-0000-0000-000018010000}"/>
+    <cellStyle name="Accent1 6" xfId="286" xr:uid="{00000000-0005-0000-0000-000019010000}"/>
+    <cellStyle name="Accent1 7" xfId="287" xr:uid="{00000000-0005-0000-0000-00001A010000}"/>
+    <cellStyle name="Accent1 8" xfId="288" xr:uid="{00000000-0005-0000-0000-00001B010000}"/>
+    <cellStyle name="Accent1 9" xfId="289" xr:uid="{00000000-0005-0000-0000-00001C010000}"/>
+    <cellStyle name="Accent2 10" xfId="290" xr:uid="{00000000-0005-0000-0000-00001D010000}"/>
+    <cellStyle name="Accent2 11" xfId="291" xr:uid="{00000000-0005-0000-0000-00001E010000}"/>
+    <cellStyle name="Accent2 12" xfId="292" xr:uid="{00000000-0005-0000-0000-00001F010000}"/>
+    <cellStyle name="Accent2 13" xfId="293" xr:uid="{00000000-0005-0000-0000-000020010000}"/>
+    <cellStyle name="Accent2 14" xfId="294" xr:uid="{00000000-0005-0000-0000-000021010000}"/>
+    <cellStyle name="Accent2 15" xfId="295" xr:uid="{00000000-0005-0000-0000-000022010000}"/>
+    <cellStyle name="Accent2 16" xfId="296" xr:uid="{00000000-0005-0000-0000-000023010000}"/>
+    <cellStyle name="Accent2 2" xfId="297" xr:uid="{00000000-0005-0000-0000-000024010000}"/>
+    <cellStyle name="Accent2 3" xfId="298" xr:uid="{00000000-0005-0000-0000-000025010000}"/>
+    <cellStyle name="Accent2 4" xfId="299" xr:uid="{00000000-0005-0000-0000-000026010000}"/>
+    <cellStyle name="Accent2 5" xfId="300" xr:uid="{00000000-0005-0000-0000-000027010000}"/>
+    <cellStyle name="Accent2 6" xfId="301" xr:uid="{00000000-0005-0000-0000-000028010000}"/>
+    <cellStyle name="Accent2 7" xfId="302" xr:uid="{00000000-0005-0000-0000-000029010000}"/>
+    <cellStyle name="Accent2 8" xfId="303" xr:uid="{00000000-0005-0000-0000-00002A010000}"/>
+    <cellStyle name="Accent2 9" xfId="304" xr:uid="{00000000-0005-0000-0000-00002B010000}"/>
+    <cellStyle name="Accent3 10" xfId="305" xr:uid="{00000000-0005-0000-0000-00002C010000}"/>
+    <cellStyle name="Accent3 11" xfId="306" xr:uid="{00000000-0005-0000-0000-00002D010000}"/>
+    <cellStyle name="Accent3 12" xfId="307" xr:uid="{00000000-0005-0000-0000-00002E010000}"/>
+    <cellStyle name="Accent3 13" xfId="308" xr:uid="{00000000-0005-0000-0000-00002F010000}"/>
+    <cellStyle name="Accent3 14" xfId="309" xr:uid="{00000000-0005-0000-0000-000030010000}"/>
+    <cellStyle name="Accent3 15" xfId="310" xr:uid="{00000000-0005-0000-0000-000031010000}"/>
+    <cellStyle name="Accent3 16" xfId="311" xr:uid="{00000000-0005-0000-0000-000032010000}"/>
+    <cellStyle name="Accent3 2" xfId="312" xr:uid="{00000000-0005-0000-0000-000033010000}"/>
+    <cellStyle name="Accent3 3" xfId="313" xr:uid="{00000000-0005-0000-0000-000034010000}"/>
+    <cellStyle name="Accent3 4" xfId="314" xr:uid="{00000000-0005-0000-0000-000035010000}"/>
+    <cellStyle name="Accent3 5" xfId="315" xr:uid="{00000000-0005-0000-0000-000036010000}"/>
+    <cellStyle name="Accent3 6" xfId="316" xr:uid="{00000000-0005-0000-0000-000037010000}"/>
+    <cellStyle name="Accent3 7" xfId="317" xr:uid="{00000000-0005-0000-0000-000038010000}"/>
+    <cellStyle name="Accent3 8" xfId="318" xr:uid="{00000000-0005-0000-0000-000039010000}"/>
+    <cellStyle name="Accent3 9" xfId="319" xr:uid="{00000000-0005-0000-0000-00003A010000}"/>
+    <cellStyle name="Accent4 10" xfId="320" xr:uid="{00000000-0005-0000-0000-00003B010000}"/>
+    <cellStyle name="Accent4 11" xfId="321" xr:uid="{00000000-0005-0000-0000-00003C010000}"/>
+    <cellStyle name="Accent4 12" xfId="322" xr:uid="{00000000-0005-0000-0000-00003D010000}"/>
+    <cellStyle name="Accent4 13" xfId="323" xr:uid="{00000000-0005-0000-0000-00003E010000}"/>
+    <cellStyle name="Accent4 14" xfId="324" xr:uid="{00000000-0005-0000-0000-00003F010000}"/>
+    <cellStyle name="Accent4 15" xfId="325" xr:uid="{00000000-0005-0000-0000-000040010000}"/>
+    <cellStyle name="Accent4 16" xfId="326" xr:uid="{00000000-0005-0000-0000-000041010000}"/>
+    <cellStyle name="Accent4 2" xfId="327" xr:uid="{00000000-0005-0000-0000-000042010000}"/>
+    <cellStyle name="Accent4 3" xfId="328" xr:uid="{00000000-0005-0000-0000-000043010000}"/>
+    <cellStyle name="Accent4 4" xfId="329" xr:uid="{00000000-0005-0000-0000-000044010000}"/>
+    <cellStyle name="Accent4 5" xfId="330" xr:uid="{00000000-0005-0000-0000-000045010000}"/>
+    <cellStyle name="Accent4 6" xfId="331" xr:uid="{00000000-0005-0000-0000-000046010000}"/>
+    <cellStyle name="Accent4 7" xfId="332" xr:uid="{00000000-0005-0000-0000-000047010000}"/>
+    <cellStyle name="Accent4 8" xfId="333" xr:uid="{00000000-0005-0000-0000-000048010000}"/>
+    <cellStyle name="Accent4 9" xfId="334" xr:uid="{00000000-0005-0000-0000-000049010000}"/>
+    <cellStyle name="Accent5 10" xfId="335" xr:uid="{00000000-0005-0000-0000-00004A010000}"/>
+    <cellStyle name="Accent5 11" xfId="336" xr:uid="{00000000-0005-0000-0000-00004B010000}"/>
+    <cellStyle name="Accent5 12" xfId="337" xr:uid="{00000000-0005-0000-0000-00004C010000}"/>
+    <cellStyle name="Accent5 13" xfId="338" xr:uid="{00000000-0005-0000-0000-00004D010000}"/>
+    <cellStyle name="Accent5 14" xfId="339" xr:uid="{00000000-0005-0000-0000-00004E010000}"/>
+    <cellStyle name="Accent5 15" xfId="340" xr:uid="{00000000-0005-0000-0000-00004F010000}"/>
+    <cellStyle name="Accent5 16" xfId="341" xr:uid="{00000000-0005-0000-0000-000050010000}"/>
+    <cellStyle name="Accent5 2" xfId="342" xr:uid="{00000000-0005-0000-0000-000051010000}"/>
+    <cellStyle name="Accent5 3" xfId="343" xr:uid="{00000000-0005-0000-0000-000052010000}"/>
+    <cellStyle name="Accent5 4" xfId="344" xr:uid="{00000000-0005-0000-0000-000053010000}"/>
+    <cellStyle name="Accent5 5" xfId="345" xr:uid="{00000000-0005-0000-0000-000054010000}"/>
+    <cellStyle name="Accent5 6" xfId="346" xr:uid="{00000000-0005-0000-0000-000055010000}"/>
+    <cellStyle name="Accent5 7" xfId="347" xr:uid="{00000000-0005-0000-0000-000056010000}"/>
+    <cellStyle name="Accent5 8" xfId="348" xr:uid="{00000000-0005-0000-0000-000057010000}"/>
+    <cellStyle name="Accent5 9" xfId="349" xr:uid="{00000000-0005-0000-0000-000058010000}"/>
+    <cellStyle name="Accent6 10" xfId="350" xr:uid="{00000000-0005-0000-0000-000059010000}"/>
+    <cellStyle name="Accent6 11" xfId="351" xr:uid="{00000000-0005-0000-0000-00005A010000}"/>
+    <cellStyle name="Accent6 12" xfId="352" xr:uid="{00000000-0005-0000-0000-00005B010000}"/>
+    <cellStyle name="Accent6 13" xfId="353" xr:uid="{00000000-0005-0000-0000-00005C010000}"/>
+    <cellStyle name="Accent6 14" xfId="354" xr:uid="{00000000-0005-0000-0000-00005D010000}"/>
+    <cellStyle name="Accent6 15" xfId="355" xr:uid="{00000000-0005-0000-0000-00005E010000}"/>
+    <cellStyle name="Accent6 16" xfId="356" xr:uid="{00000000-0005-0000-0000-00005F010000}"/>
+    <cellStyle name="Accent6 2" xfId="357" xr:uid="{00000000-0005-0000-0000-000060010000}"/>
+    <cellStyle name="Accent6 3" xfId="358" xr:uid="{00000000-0005-0000-0000-000061010000}"/>
+    <cellStyle name="Accent6 4" xfId="359" xr:uid="{00000000-0005-0000-0000-000062010000}"/>
+    <cellStyle name="Accent6 5" xfId="360" xr:uid="{00000000-0005-0000-0000-000063010000}"/>
+    <cellStyle name="Accent6 6" xfId="361" xr:uid="{00000000-0005-0000-0000-000064010000}"/>
+    <cellStyle name="Accent6 7" xfId="362" xr:uid="{00000000-0005-0000-0000-000065010000}"/>
+    <cellStyle name="Accent6 8" xfId="363" xr:uid="{00000000-0005-0000-0000-000066010000}"/>
+    <cellStyle name="Accent6 9" xfId="364" xr:uid="{00000000-0005-0000-0000-000067010000}"/>
+    <cellStyle name="Bad 10" xfId="365" xr:uid="{00000000-0005-0000-0000-000068010000}"/>
+    <cellStyle name="Bad 11" xfId="366" xr:uid="{00000000-0005-0000-0000-000069010000}"/>
+    <cellStyle name="Bad 12" xfId="367" xr:uid="{00000000-0005-0000-0000-00006A010000}"/>
+    <cellStyle name="Bad 13" xfId="368" xr:uid="{00000000-0005-0000-0000-00006B010000}"/>
+    <cellStyle name="Bad 14" xfId="369" xr:uid="{00000000-0005-0000-0000-00006C010000}"/>
+    <cellStyle name="Bad 15" xfId="370" xr:uid="{00000000-0005-0000-0000-00006D010000}"/>
+    <cellStyle name="Bad 16" xfId="371" xr:uid="{00000000-0005-0000-0000-00006E010000}"/>
+    <cellStyle name="Bad 2" xfId="372" xr:uid="{00000000-0005-0000-0000-00006F010000}"/>
+    <cellStyle name="Bad 3" xfId="373" xr:uid="{00000000-0005-0000-0000-000070010000}"/>
+    <cellStyle name="Bad 4" xfId="374" xr:uid="{00000000-0005-0000-0000-000071010000}"/>
+    <cellStyle name="Bad 5" xfId="375" xr:uid="{00000000-0005-0000-0000-000072010000}"/>
+    <cellStyle name="Bad 6" xfId="376" xr:uid="{00000000-0005-0000-0000-000073010000}"/>
+    <cellStyle name="Bad 7" xfId="377" xr:uid="{00000000-0005-0000-0000-000074010000}"/>
+    <cellStyle name="Bad 8" xfId="378" xr:uid="{00000000-0005-0000-0000-000075010000}"/>
+    <cellStyle name="Bad 9" xfId="379" xr:uid="{00000000-0005-0000-0000-000076010000}"/>
+    <cellStyle name="Calculation 10" xfId="380" xr:uid="{00000000-0005-0000-0000-000077010000}"/>
+    <cellStyle name="Calculation 10 10" xfId="955" xr:uid="{00000000-0005-0000-0000-000078010000}"/>
+    <cellStyle name="Calculation 10 11" xfId="830" xr:uid="{00000000-0005-0000-0000-000079010000}"/>
+    <cellStyle name="Calculation 10 12" xfId="970" xr:uid="{00000000-0005-0000-0000-00007A010000}"/>
+    <cellStyle name="Calculation 10 13" xfId="815" xr:uid="{00000000-0005-0000-0000-00007B010000}"/>
+    <cellStyle name="Calculation 10 14" xfId="986" xr:uid="{00000000-0005-0000-0000-00007C010000}"/>
+    <cellStyle name="Calculation 10 15" xfId="891" xr:uid="{00000000-0005-0000-0000-00007D010000}"/>
+    <cellStyle name="Calculation 10 16" xfId="1001" xr:uid="{00000000-0005-0000-0000-00007E010000}"/>
+    <cellStyle name="Calculation 10 17" xfId="786" xr:uid="{00000000-0005-0000-0000-00007F010000}"/>
+    <cellStyle name="Calculation 10 18" xfId="1030" xr:uid="{00000000-0005-0000-0000-000080010000}"/>
+    <cellStyle name="Calculation 10 19" xfId="771" xr:uid="{00000000-0005-0000-0000-000081010000}"/>
+    <cellStyle name="Calculation 10 2" xfId="895" xr:uid="{00000000-0005-0000-0000-000082010000}"/>
+    <cellStyle name="Calculation 10 20" xfId="1254" xr:uid="{00000000-0005-0000-0000-000083010000}"/>
+    <cellStyle name="Calculation 10 21" xfId="742" xr:uid="{00000000-0005-0000-0000-000084010000}"/>
+    <cellStyle name="Calculation 10 22" xfId="1086" xr:uid="{00000000-0005-0000-0000-000085010000}"/>
+    <cellStyle name="Calculation 10 23" xfId="1484" xr:uid="{00000000-0005-0000-0000-000086010000}"/>
+    <cellStyle name="Calculation 10 24" xfId="985" xr:uid="{00000000-0005-0000-0000-000087010000}"/>
+    <cellStyle name="Calculation 10 25" xfId="1635" xr:uid="{00000000-0005-0000-0000-000088010000}"/>
+    <cellStyle name="Calculation 10 26" xfId="1709" xr:uid="{00000000-0005-0000-0000-000089010000}"/>
+    <cellStyle name="Calculation 10 27" xfId="1785" xr:uid="{00000000-0005-0000-0000-00008A010000}"/>
+    <cellStyle name="Calculation 10 28" xfId="1850" xr:uid="{00000000-0005-0000-0000-00008B010000}"/>
+    <cellStyle name="Calculation 10 29" xfId="1914" xr:uid="{00000000-0005-0000-0000-00008C010000}"/>
+    <cellStyle name="Calculation 10 3" xfId="888" xr:uid="{00000000-0005-0000-0000-00008D010000}"/>
+    <cellStyle name="Calculation 10 30" xfId="1707" xr:uid="{00000000-0005-0000-0000-00008E010000}"/>
+    <cellStyle name="Calculation 10 31" xfId="894" xr:uid="{00000000-0005-0000-0000-00008F010000}"/>
+    <cellStyle name="Calculation 10 32" xfId="1848" xr:uid="{00000000-0005-0000-0000-000090010000}"/>
+    <cellStyle name="Calculation 10 4" xfId="911" xr:uid="{00000000-0005-0000-0000-000091010000}"/>
+    <cellStyle name="Calculation 10 5" xfId="890" xr:uid="{00000000-0005-0000-0000-000092010000}"/>
+    <cellStyle name="Calculation 10 6" xfId="910" xr:uid="{00000000-0005-0000-0000-000093010000}"/>
+    <cellStyle name="Calculation 10 7" xfId="860" xr:uid="{00000000-0005-0000-0000-000094010000}"/>
+    <cellStyle name="Calculation 10 8" xfId="940" xr:uid="{00000000-0005-0000-0000-000095010000}"/>
+    <cellStyle name="Calculation 10 9" xfId="845" xr:uid="{00000000-0005-0000-0000-000096010000}"/>
+    <cellStyle name="Calculation 11" xfId="381" xr:uid="{00000000-0005-0000-0000-000097010000}"/>
+    <cellStyle name="Calculation 11 10" xfId="956" xr:uid="{00000000-0005-0000-0000-000098010000}"/>
+    <cellStyle name="Calculation 11 11" xfId="829" xr:uid="{00000000-0005-0000-0000-000099010000}"/>
+    <cellStyle name="Calculation 11 12" xfId="971" xr:uid="{00000000-0005-0000-0000-00009A010000}"/>
+    <cellStyle name="Calculation 11 13" xfId="814" xr:uid="{00000000-0005-0000-0000-00009B010000}"/>
+    <cellStyle name="Calculation 11 14" xfId="987" xr:uid="{00000000-0005-0000-0000-00009C010000}"/>
+    <cellStyle name="Calculation 11 15" xfId="800" xr:uid="{00000000-0005-0000-0000-00009D010000}"/>
+    <cellStyle name="Calculation 11 16" xfId="1002" xr:uid="{00000000-0005-0000-0000-00009E010000}"/>
+    <cellStyle name="Calculation 11 17" xfId="785" xr:uid="{00000000-0005-0000-0000-00009F010000}"/>
+    <cellStyle name="Calculation 11 18" xfId="1031" xr:uid="{00000000-0005-0000-0000-0000A0010000}"/>
+    <cellStyle name="Calculation 11 19" xfId="770" xr:uid="{00000000-0005-0000-0000-0000A1010000}"/>
+    <cellStyle name="Calculation 11 2" xfId="896" xr:uid="{00000000-0005-0000-0000-0000A2010000}"/>
+    <cellStyle name="Calculation 11 20" xfId="1059" xr:uid="{00000000-0005-0000-0000-0000A3010000}"/>
+    <cellStyle name="Calculation 11 21" xfId="1332" xr:uid="{00000000-0005-0000-0000-0000A4010000}"/>
+    <cellStyle name="Calculation 11 22" xfId="1255" xr:uid="{00000000-0005-0000-0000-0000A5010000}"/>
+    <cellStyle name="Calculation 11 23" xfId="699" xr:uid="{00000000-0005-0000-0000-0000A6010000}"/>
+    <cellStyle name="Calculation 11 24" xfId="673" xr:uid="{00000000-0005-0000-0000-0000A7010000}"/>
+    <cellStyle name="Calculation 11 25" xfId="1214" xr:uid="{00000000-0005-0000-0000-0000A8010000}"/>
+    <cellStyle name="Calculation 11 26" xfId="1291" xr:uid="{00000000-0005-0000-0000-0000A9010000}"/>
+    <cellStyle name="Calculation 11 27" xfId="1368" xr:uid="{00000000-0005-0000-0000-0000AA010000}"/>
+    <cellStyle name="Calculation 11 28" xfId="1444" xr:uid="{00000000-0005-0000-0000-0000AB010000}"/>
+    <cellStyle name="Calculation 11 29" xfId="1519" xr:uid="{00000000-0005-0000-0000-0000AC010000}"/>
+    <cellStyle name="Calculation 11 3" xfId="887" xr:uid="{00000000-0005-0000-0000-0000AD010000}"/>
+    <cellStyle name="Calculation 11 30" xfId="1596" xr:uid="{00000000-0005-0000-0000-0000AE010000}"/>
+    <cellStyle name="Calculation 11 31" xfId="893" xr:uid="{00000000-0005-0000-0000-0000AF010000}"/>
+    <cellStyle name="Calculation 11 32" xfId="1746" xr:uid="{00000000-0005-0000-0000-0000B0010000}"/>
+    <cellStyle name="Calculation 11 4" xfId="912" xr:uid="{00000000-0005-0000-0000-0000B1010000}"/>
+    <cellStyle name="Calculation 11 5" xfId="889" xr:uid="{00000000-0005-0000-0000-0000B2010000}"/>
+    <cellStyle name="Calculation 11 6" xfId="926" xr:uid="{00000000-0005-0000-0000-0000B3010000}"/>
+    <cellStyle name="Calculation 11 7" xfId="859" xr:uid="{00000000-0005-0000-0000-0000B4010000}"/>
+    <cellStyle name="Calculation 11 8" xfId="941" xr:uid="{00000000-0005-0000-0000-0000B5010000}"/>
+    <cellStyle name="Calculation 11 9" xfId="844" xr:uid="{00000000-0005-0000-0000-0000B6010000}"/>
+    <cellStyle name="Calculation 12" xfId="382" xr:uid="{00000000-0005-0000-0000-0000B7010000}"/>
+    <cellStyle name="Calculation 12 10" xfId="957" xr:uid="{00000000-0005-0000-0000-0000B8010000}"/>
+    <cellStyle name="Calculation 12 11" xfId="828" xr:uid="{00000000-0005-0000-0000-0000B9010000}"/>
+    <cellStyle name="Calculation 12 12" xfId="972" xr:uid="{00000000-0005-0000-0000-0000BA010000}"/>
+    <cellStyle name="Calculation 12 13" xfId="813" xr:uid="{00000000-0005-0000-0000-0000BB010000}"/>
+    <cellStyle name="Calculation 12 14" xfId="988" xr:uid="{00000000-0005-0000-0000-0000BC010000}"/>
+    <cellStyle name="Calculation 12 15" xfId="799" xr:uid="{00000000-0005-0000-0000-0000BD010000}"/>
+    <cellStyle name="Calculation 12 16" xfId="1003" xr:uid="{00000000-0005-0000-0000-0000BE010000}"/>
+    <cellStyle name="Calculation 12 17" xfId="784" xr:uid="{00000000-0005-0000-0000-0000BF010000}"/>
+    <cellStyle name="Calculation 12 18" xfId="1032" xr:uid="{00000000-0005-0000-0000-0000C0010000}"/>
+    <cellStyle name="Calculation 12 19" xfId="769" xr:uid="{00000000-0005-0000-0000-0000C1010000}"/>
+    <cellStyle name="Calculation 12 2" xfId="897" xr:uid="{00000000-0005-0000-0000-0000C2010000}"/>
+    <cellStyle name="Calculation 12 20" xfId="1060" xr:uid="{00000000-0005-0000-0000-0000C3010000}"/>
+    <cellStyle name="Calculation 12 21" xfId="726" xr:uid="{00000000-0005-0000-0000-0000C4010000}"/>
+    <cellStyle name="Calculation 12 22" xfId="1087" xr:uid="{00000000-0005-0000-0000-0000C5010000}"/>
+    <cellStyle name="Calculation 12 23" xfId="1333" xr:uid="{00000000-0005-0000-0000-0000C6010000}"/>
+    <cellStyle name="Calculation 12 24" xfId="1410" xr:uid="{00000000-0005-0000-0000-0000C7010000}"/>
+    <cellStyle name="Calculation 12 25" xfId="1485" xr:uid="{00000000-0005-0000-0000-0000C8010000}"/>
+    <cellStyle name="Calculation 12 26" xfId="1561" xr:uid="{00000000-0005-0000-0000-0000C9010000}"/>
+    <cellStyle name="Calculation 12 27" xfId="1636" xr:uid="{00000000-0005-0000-0000-0000CA010000}"/>
+    <cellStyle name="Calculation 12 28" xfId="1710" xr:uid="{00000000-0005-0000-0000-0000CB010000}"/>
+    <cellStyle name="Calculation 12 29" xfId="1786" xr:uid="{00000000-0005-0000-0000-0000CC010000}"/>
+    <cellStyle name="Calculation 12 3" xfId="886" xr:uid="{00000000-0005-0000-0000-0000CD010000}"/>
+    <cellStyle name="Calculation 12 30" xfId="1597" xr:uid="{00000000-0005-0000-0000-0000CE010000}"/>
+    <cellStyle name="Calculation 12 31" xfId="892" xr:uid="{00000000-0005-0000-0000-0000CF010000}"/>
+    <cellStyle name="Calculation 12 32" xfId="1747" xr:uid="{00000000-0005-0000-0000-0000D0010000}"/>
+    <cellStyle name="Calculation 12 4" xfId="913" xr:uid="{00000000-0005-0000-0000-0000D1010000}"/>
+    <cellStyle name="Calculation 12 5" xfId="873" xr:uid="{00000000-0005-0000-0000-0000D2010000}"/>
+    <cellStyle name="Calculation 12 6" xfId="927" xr:uid="{00000000-0005-0000-0000-0000D3010000}"/>
+    <cellStyle name="Calculation 12 7" xfId="858" xr:uid="{00000000-0005-0000-0000-0000D4010000}"/>
+    <cellStyle name="Calculation 12 8" xfId="942" xr:uid="{00000000-0005-0000-0000-0000D5010000}"/>
+    <cellStyle name="Calculation 12 9" xfId="843" xr:uid="{00000000-0005-0000-0000-0000D6010000}"/>
+    <cellStyle name="Calculation 13" xfId="383" xr:uid="{00000000-0005-0000-0000-0000D7010000}"/>
+    <cellStyle name="Calculation 13 10" xfId="958" xr:uid="{00000000-0005-0000-0000-0000D8010000}"/>
+    <cellStyle name="Calculation 13 11" xfId="827" xr:uid="{00000000-0005-0000-0000-0000D9010000}"/>
+    <cellStyle name="Calculation 13 12" xfId="973" xr:uid="{00000000-0005-0000-0000-0000DA010000}"/>
+    <cellStyle name="Calculation 13 13" xfId="812" xr:uid="{00000000-0005-0000-0000-0000DB010000}"/>
+    <cellStyle name="Calculation 13 14" xfId="989" xr:uid="{00000000-0005-0000-0000-0000DC010000}"/>
+    <cellStyle name="Calculation 13 15" xfId="798" xr:uid="{00000000-0005-0000-0000-0000DD010000}"/>
+    <cellStyle name="Calculation 13 16" xfId="1004" xr:uid="{00000000-0005-0000-0000-0000DE010000}"/>
+    <cellStyle name="Calculation 13 17" xfId="783" xr:uid="{00000000-0005-0000-0000-0000DF010000}"/>
+    <cellStyle name="Calculation 13 18" xfId="1033" xr:uid="{00000000-0005-0000-0000-0000E0010000}"/>
+    <cellStyle name="Calculation 13 19" xfId="1181" xr:uid="{00000000-0005-0000-0000-0000E1010000}"/>
+    <cellStyle name="Calculation 13 2" xfId="898" xr:uid="{00000000-0005-0000-0000-0000E2010000}"/>
+    <cellStyle name="Calculation 13 20" xfId="1061" xr:uid="{00000000-0005-0000-0000-0000E3010000}"/>
+    <cellStyle name="Calculation 13 21" xfId="725" xr:uid="{00000000-0005-0000-0000-0000E4010000}"/>
+    <cellStyle name="Calculation 13 22" xfId="1088" xr:uid="{00000000-0005-0000-0000-0000E5010000}"/>
+    <cellStyle name="Calculation 13 23" xfId="698" xr:uid="{00000000-0005-0000-0000-0000E6010000}"/>
+    <cellStyle name="Calculation 13 24" xfId="1143" xr:uid="{00000000-0005-0000-0000-0000E7010000}"/>
+    <cellStyle name="Calculation 13 25" xfId="1215" xr:uid="{00000000-0005-0000-0000-0000E8010000}"/>
+    <cellStyle name="Calculation 13 26" xfId="1292" xr:uid="{00000000-0005-0000-0000-0000E9010000}"/>
+    <cellStyle name="Calculation 13 27" xfId="1369" xr:uid="{00000000-0005-0000-0000-0000EA010000}"/>
+    <cellStyle name="Calculation 13 28" xfId="1445" xr:uid="{00000000-0005-0000-0000-0000EB010000}"/>
+    <cellStyle name="Calculation 13 29" xfId="1520" xr:uid="{00000000-0005-0000-0000-0000EC010000}"/>
+    <cellStyle name="Calculation 13 3" xfId="885" xr:uid="{00000000-0005-0000-0000-0000ED010000}"/>
+    <cellStyle name="Calculation 13 30" xfId="1598" xr:uid="{00000000-0005-0000-0000-0000EE010000}"/>
+    <cellStyle name="Calculation 13 31" xfId="714" xr:uid="{00000000-0005-0000-0000-0000EF010000}"/>
+    <cellStyle name="Calculation 13 32" xfId="1748" xr:uid="{00000000-0005-0000-0000-0000F0010000}"/>
+    <cellStyle name="Calculation 13 4" xfId="914" xr:uid="{00000000-0005-0000-0000-0000F1010000}"/>
+    <cellStyle name="Calculation 13 5" xfId="872" xr:uid="{00000000-0005-0000-0000-0000F2010000}"/>
+    <cellStyle name="Calculation 13 6" xfId="928" xr:uid="{00000000-0005-0000-0000-0000F3010000}"/>
+    <cellStyle name="Calculation 13 7" xfId="857" xr:uid="{00000000-0005-0000-0000-0000F4010000}"/>
+    <cellStyle name="Calculation 13 8" xfId="943" xr:uid="{00000000-0005-0000-0000-0000F5010000}"/>
+    <cellStyle name="Calculation 13 9" xfId="842" xr:uid="{00000000-0005-0000-0000-0000F6010000}"/>
+    <cellStyle name="Calculation 14" xfId="384" xr:uid="{00000000-0005-0000-0000-0000F7010000}"/>
+    <cellStyle name="Calculation 14 10" xfId="959" xr:uid="{00000000-0005-0000-0000-0000F8010000}"/>
+    <cellStyle name="Calculation 14 11" xfId="826" xr:uid="{00000000-0005-0000-0000-0000F9010000}"/>
+    <cellStyle name="Calculation 14 12" xfId="974" xr:uid="{00000000-0005-0000-0000-0000FA010000}"/>
+    <cellStyle name="Calculation 14 13" xfId="811" xr:uid="{00000000-0005-0000-0000-0000FB010000}"/>
+    <cellStyle name="Calculation 14 14" xfId="990" xr:uid="{00000000-0005-0000-0000-0000FC010000}"/>
+    <cellStyle name="Calculation 14 15" xfId="797" xr:uid="{00000000-0005-0000-0000-0000FD010000}"/>
+    <cellStyle name="Calculation 14 16" xfId="1005" xr:uid="{00000000-0005-0000-0000-0000FE010000}"/>
+    <cellStyle name="Calculation 14 17" xfId="782" xr:uid="{00000000-0005-0000-0000-0000FF010000}"/>
+    <cellStyle name="Calculation 14 18" xfId="1034" xr:uid="{00000000-0005-0000-0000-000000020000}"/>
+    <cellStyle name="Calculation 14 19" xfId="753" xr:uid="{00000000-0005-0000-0000-000001020000}"/>
+    <cellStyle name="Calculation 14 2" xfId="899" xr:uid="{00000000-0005-0000-0000-000002020000}"/>
+    <cellStyle name="Calculation 14 20" xfId="1062" xr:uid="{00000000-0005-0000-0000-000003020000}"/>
+    <cellStyle name="Calculation 14 21" xfId="724" xr:uid="{00000000-0005-0000-0000-000004020000}"/>
+    <cellStyle name="Calculation 14 22" xfId="1089" xr:uid="{00000000-0005-0000-0000-000005020000}"/>
+    <cellStyle name="Calculation 14 23" xfId="697" xr:uid="{00000000-0005-0000-0000-000006020000}"/>
+    <cellStyle name="Calculation 14 24" xfId="1144" xr:uid="{00000000-0005-0000-0000-000007020000}"/>
+    <cellStyle name="Calculation 14 25" xfId="1330" xr:uid="{00000000-0005-0000-0000-000008020000}"/>
+    <cellStyle name="Calculation 14 26" xfId="1407" xr:uid="{00000000-0005-0000-0000-000009020000}"/>
+    <cellStyle name="Calculation 14 27" xfId="1482" xr:uid="{00000000-0005-0000-0000-00000A020000}"/>
+    <cellStyle name="Calculation 14 28" xfId="1558" xr:uid="{00000000-0005-0000-0000-00000B020000}"/>
+    <cellStyle name="Calculation 14 29" xfId="1633" xr:uid="{00000000-0005-0000-0000-00000C020000}"/>
+    <cellStyle name="Calculation 14 3" xfId="884" xr:uid="{00000000-0005-0000-0000-00000D020000}"/>
+    <cellStyle name="Calculation 14 30" xfId="1599" xr:uid="{00000000-0005-0000-0000-00000E020000}"/>
+    <cellStyle name="Calculation 14 31" xfId="1669" xr:uid="{00000000-0005-0000-0000-00000F020000}"/>
+    <cellStyle name="Calculation 14 32" xfId="1749" xr:uid="{00000000-0005-0000-0000-000010020000}"/>
+    <cellStyle name="Calculation 14 4" xfId="915" xr:uid="{00000000-0005-0000-0000-000011020000}"/>
+    <cellStyle name="Calculation 14 5" xfId="871" xr:uid="{00000000-0005-0000-0000-000012020000}"/>
+    <cellStyle name="Calculation 14 6" xfId="929" xr:uid="{00000000-0005-0000-0000-000013020000}"/>
+    <cellStyle name="Calculation 14 7" xfId="856" xr:uid="{00000000-0005-0000-0000-000014020000}"/>
+    <cellStyle name="Calculation 14 8" xfId="944" xr:uid="{00000000-0005-0000-0000-000015020000}"/>
+    <cellStyle name="Calculation 14 9" xfId="841" xr:uid="{00000000-0005-0000-0000-000016020000}"/>
+    <cellStyle name="Calculation 15" xfId="385" xr:uid="{00000000-0005-0000-0000-000017020000}"/>
+    <cellStyle name="Calculation 15 10" xfId="960" xr:uid="{00000000-0005-0000-0000-000018020000}"/>
+    <cellStyle name="Calculation 15 11" xfId="825" xr:uid="{00000000-0005-0000-0000-000019020000}"/>
+    <cellStyle name="Calculation 15 12" xfId="975" xr:uid="{00000000-0005-0000-0000-00001A020000}"/>
+    <cellStyle name="Calculation 15 13" xfId="810" xr:uid="{00000000-0005-0000-0000-00001B020000}"/>
+    <cellStyle name="Calculation 15 14" xfId="991" xr:uid="{00000000-0005-0000-0000-00001C020000}"/>
+    <cellStyle name="Calculation 15 15" xfId="796" xr:uid="{00000000-0005-0000-0000-00001D020000}"/>
+    <cellStyle name="Calculation 15 16" xfId="1006" xr:uid="{00000000-0005-0000-0000-00001E020000}"/>
+    <cellStyle name="Calculation 15 17" xfId="781" xr:uid="{00000000-0005-0000-0000-00001F020000}"/>
+    <cellStyle name="Calculation 15 18" xfId="1035" xr:uid="{00000000-0005-0000-0000-000020020000}"/>
+    <cellStyle name="Calculation 15 19" xfId="752" xr:uid="{00000000-0005-0000-0000-000021020000}"/>
+    <cellStyle name="Calculation 15 2" xfId="900" xr:uid="{00000000-0005-0000-0000-000022020000}"/>
+    <cellStyle name="Calculation 15 20" xfId="1063" xr:uid="{00000000-0005-0000-0000-000023020000}"/>
+    <cellStyle name="Calculation 15 21" xfId="1182" xr:uid="{00000000-0005-0000-0000-000024020000}"/>
+    <cellStyle name="Calculation 15 22" xfId="1090" xr:uid="{00000000-0005-0000-0000-000025020000}"/>
+    <cellStyle name="Calculation 15 23" xfId="696" xr:uid="{00000000-0005-0000-0000-000026020000}"/>
+    <cellStyle name="Calculation 15 24" xfId="1252" xr:uid="{00000000-0005-0000-0000-000027020000}"/>
+    <cellStyle name="Calculation 15 25" xfId="1216" xr:uid="{00000000-0005-0000-0000-000028020000}"/>
+    <cellStyle name="Calculation 15 26" xfId="1293" xr:uid="{00000000-0005-0000-0000-000029020000}"/>
+    <cellStyle name="Calculation 15 27" xfId="1370" xr:uid="{00000000-0005-0000-0000-00002A020000}"/>
+    <cellStyle name="Calculation 15 28" xfId="1446" xr:uid="{00000000-0005-0000-0000-00002B020000}"/>
+    <cellStyle name="Calculation 15 29" xfId="1521" xr:uid="{00000000-0005-0000-0000-00002C020000}"/>
+    <cellStyle name="Calculation 15 3" xfId="883" xr:uid="{00000000-0005-0000-0000-00002D020000}"/>
+    <cellStyle name="Calculation 15 30" xfId="1600" xr:uid="{00000000-0005-0000-0000-00002E020000}"/>
+    <cellStyle name="Calculation 15 31" xfId="1670" xr:uid="{00000000-0005-0000-0000-00002F020000}"/>
+    <cellStyle name="Calculation 15 32" xfId="1750" xr:uid="{00000000-0005-0000-0000-000030020000}"/>
+    <cellStyle name="Calculation 15 4" xfId="916" xr:uid="{00000000-0005-0000-0000-000031020000}"/>
+    <cellStyle name="Calculation 15 5" xfId="870" xr:uid="{00000000-0005-0000-0000-000032020000}"/>
+    <cellStyle name="Calculation 15 6" xfId="930" xr:uid="{00000000-0005-0000-0000-000033020000}"/>
+    <cellStyle name="Calculation 15 7" xfId="855" xr:uid="{00000000-0005-0000-0000-000034020000}"/>
+    <cellStyle name="Calculation 15 8" xfId="945" xr:uid="{00000000-0005-0000-0000-000035020000}"/>
+    <cellStyle name="Calculation 15 9" xfId="840" xr:uid="{00000000-0005-0000-0000-000036020000}"/>
+    <cellStyle name="Calculation 16" xfId="386" xr:uid="{00000000-0005-0000-0000-000037020000}"/>
+    <cellStyle name="Calculation 16 10" xfId="961" xr:uid="{00000000-0005-0000-0000-000038020000}"/>
+    <cellStyle name="Calculation 16 11" xfId="824" xr:uid="{00000000-0005-0000-0000-000039020000}"/>
+    <cellStyle name="Calculation 16 12" xfId="976" xr:uid="{00000000-0005-0000-0000-00003A020000}"/>
+    <cellStyle name="Calculation 16 13" xfId="809" xr:uid="{00000000-0005-0000-0000-00003B020000}"/>
+    <cellStyle name="Calculation 16 14" xfId="992" xr:uid="{00000000-0005-0000-0000-00003C020000}"/>
+    <cellStyle name="Calculation 16 15" xfId="795" xr:uid="{00000000-0005-0000-0000-00003D020000}"/>
+    <cellStyle name="Calculation 16 16" xfId="1007" xr:uid="{00000000-0005-0000-0000-00003E020000}"/>
+    <cellStyle name="Calculation 16 17" xfId="780" xr:uid="{00000000-0005-0000-0000-00003F020000}"/>
+    <cellStyle name="Calculation 16 18" xfId="1036" xr:uid="{00000000-0005-0000-0000-000040020000}"/>
+    <cellStyle name="Calculation 16 19" xfId="751" xr:uid="{00000000-0005-0000-0000-000041020000}"/>
+    <cellStyle name="Calculation 16 2" xfId="901" xr:uid="{00000000-0005-0000-0000-000042020000}"/>
+    <cellStyle name="Calculation 16 20" xfId="1064" xr:uid="{00000000-0005-0000-0000-000043020000}"/>
+    <cellStyle name="Calculation 16 21" xfId="723" xr:uid="{00000000-0005-0000-0000-000044020000}"/>
+    <cellStyle name="Calculation 16 22" xfId="1091" xr:uid="{00000000-0005-0000-0000-000045020000}"/>
+    <cellStyle name="Calculation 16 23" xfId="1179" xr:uid="{00000000-0005-0000-0000-000046020000}"/>
+    <cellStyle name="Calculation 16 24" xfId="1145" xr:uid="{00000000-0005-0000-0000-000047020000}"/>
+    <cellStyle name="Calculation 16 25" xfId="1217" xr:uid="{00000000-0005-0000-0000-000048020000}"/>
+    <cellStyle name="Calculation 16 26" xfId="1294" xr:uid="{00000000-0005-0000-0000-000049020000}"/>
+    <cellStyle name="Calculation 16 27" xfId="1371" xr:uid="{00000000-0005-0000-0000-00004A020000}"/>
+    <cellStyle name="Calculation 16 28" xfId="1447" xr:uid="{00000000-0005-0000-0000-00004B020000}"/>
+    <cellStyle name="Calculation 16 29" xfId="1522" xr:uid="{00000000-0005-0000-0000-00004C020000}"/>
+    <cellStyle name="Calculation 16 3" xfId="882" xr:uid="{00000000-0005-0000-0000-00004D020000}"/>
+    <cellStyle name="Calculation 16 30" xfId="1601" xr:uid="{00000000-0005-0000-0000-00004E020000}"/>
+    <cellStyle name="Calculation 16 31" xfId="1915" xr:uid="{00000000-0005-0000-0000-00004F020000}"/>
+    <cellStyle name="Calculation 16 32" xfId="1751" xr:uid="{00000000-0005-0000-0000-000050020000}"/>
+    <cellStyle name="Calculation 16 4" xfId="917" xr:uid="{00000000-0005-0000-0000-000051020000}"/>
+    <cellStyle name="Calculation 16 5" xfId="869" xr:uid="{00000000-0005-0000-0000-000052020000}"/>
+    <cellStyle name="Calculation 16 6" xfId="931" xr:uid="{00000000-0005-0000-0000-000053020000}"/>
+    <cellStyle name="Calculation 16 7" xfId="854" xr:uid="{00000000-0005-0000-0000-000054020000}"/>
+    <cellStyle name="Calculation 16 8" xfId="946" xr:uid="{00000000-0005-0000-0000-000055020000}"/>
+    <cellStyle name="Calculation 16 9" xfId="839" xr:uid="{00000000-0005-0000-0000-000056020000}"/>
+    <cellStyle name="Calculation 2" xfId="387" xr:uid="{00000000-0005-0000-0000-000057020000}"/>
+    <cellStyle name="Calculation 2 10" xfId="962" xr:uid="{00000000-0005-0000-0000-000058020000}"/>
+    <cellStyle name="Calculation 2 11" xfId="823" xr:uid="{00000000-0005-0000-0000-000059020000}"/>
+    <cellStyle name="Calculation 2 12" xfId="977" xr:uid="{00000000-0005-0000-0000-00005A020000}"/>
+    <cellStyle name="Calculation 2 13" xfId="808" xr:uid="{00000000-0005-0000-0000-00005B020000}"/>
+    <cellStyle name="Calculation 2 14" xfId="993" xr:uid="{00000000-0005-0000-0000-00005C020000}"/>
+    <cellStyle name="Calculation 2 15" xfId="794" xr:uid="{00000000-0005-0000-0000-00005D020000}"/>
+    <cellStyle name="Calculation 2 16" xfId="1008" xr:uid="{00000000-0005-0000-0000-00005E020000}"/>
+    <cellStyle name="Calculation 2 17" xfId="779" xr:uid="{00000000-0005-0000-0000-00005F020000}"/>
+    <cellStyle name="Calculation 2 18" xfId="1037" xr:uid="{00000000-0005-0000-0000-000060020000}"/>
+    <cellStyle name="Calculation 2 19" xfId="750" xr:uid="{00000000-0005-0000-0000-000061020000}"/>
+    <cellStyle name="Calculation 2 2" xfId="902" xr:uid="{00000000-0005-0000-0000-000062020000}"/>
+    <cellStyle name="Calculation 2 20" xfId="1065" xr:uid="{00000000-0005-0000-0000-000063020000}"/>
+    <cellStyle name="Calculation 2 21" xfId="722" xr:uid="{00000000-0005-0000-0000-000064020000}"/>
+    <cellStyle name="Calculation 2 22" xfId="1092" xr:uid="{00000000-0005-0000-0000-000065020000}"/>
+    <cellStyle name="Calculation 2 23" xfId="695" xr:uid="{00000000-0005-0000-0000-000066020000}"/>
+    <cellStyle name="Calculation 2 24" xfId="1146" xr:uid="{00000000-0005-0000-0000-000067020000}"/>
+    <cellStyle name="Calculation 2 25" xfId="1218" xr:uid="{00000000-0005-0000-0000-000068020000}"/>
+    <cellStyle name="Calculation 2 26" xfId="1295" xr:uid="{00000000-0005-0000-0000-000069020000}"/>
+    <cellStyle name="Calculation 2 27" xfId="1372" xr:uid="{00000000-0005-0000-0000-00006A020000}"/>
+    <cellStyle name="Calculation 2 28" xfId="1448" xr:uid="{00000000-0005-0000-0000-00006B020000}"/>
+    <cellStyle name="Calculation 2 29" xfId="1523" xr:uid="{00000000-0005-0000-0000-00006C020000}"/>
+    <cellStyle name="Calculation 2 3" xfId="881" xr:uid="{00000000-0005-0000-0000-00006D020000}"/>
+    <cellStyle name="Calculation 2 30" xfId="1602" xr:uid="{00000000-0005-0000-0000-00006E020000}"/>
+    <cellStyle name="Calculation 2 31" xfId="1671" xr:uid="{00000000-0005-0000-0000-00006F020000}"/>
+    <cellStyle name="Calculation 2 32" xfId="1752" xr:uid="{00000000-0005-0000-0000-000070020000}"/>
+    <cellStyle name="Calculation 2 4" xfId="918" xr:uid="{00000000-0005-0000-0000-000071020000}"/>
+    <cellStyle name="Calculation 2 5" xfId="868" xr:uid="{00000000-0005-0000-0000-000072020000}"/>
+    <cellStyle name="Calculation 2 6" xfId="932" xr:uid="{00000000-0005-0000-0000-000073020000}"/>
+    <cellStyle name="Calculation 2 7" xfId="853" xr:uid="{00000000-0005-0000-0000-000074020000}"/>
+    <cellStyle name="Calculation 2 8" xfId="947" xr:uid="{00000000-0005-0000-0000-000075020000}"/>
+    <cellStyle name="Calculation 2 9" xfId="838" xr:uid="{00000000-0005-0000-0000-000076020000}"/>
+    <cellStyle name="Calculation 3" xfId="388" xr:uid="{00000000-0005-0000-0000-000077020000}"/>
+    <cellStyle name="Calculation 3 10" xfId="963" xr:uid="{00000000-0005-0000-0000-000078020000}"/>
+    <cellStyle name="Calculation 3 11" xfId="822" xr:uid="{00000000-0005-0000-0000-000079020000}"/>
+    <cellStyle name="Calculation 3 12" xfId="978" xr:uid="{00000000-0005-0000-0000-00007A020000}"/>
+    <cellStyle name="Calculation 3 13" xfId="807" xr:uid="{00000000-0005-0000-0000-00007B020000}"/>
+    <cellStyle name="Calculation 3 14" xfId="994" xr:uid="{00000000-0005-0000-0000-00007C020000}"/>
+    <cellStyle name="Calculation 3 15" xfId="793" xr:uid="{00000000-0005-0000-0000-00007D020000}"/>
+    <cellStyle name="Calculation 3 16" xfId="1009" xr:uid="{00000000-0005-0000-0000-00007E020000}"/>
+    <cellStyle name="Calculation 3 17" xfId="778" xr:uid="{00000000-0005-0000-0000-00007F020000}"/>
+    <cellStyle name="Calculation 3 18" xfId="1038" xr:uid="{00000000-0005-0000-0000-000080020000}"/>
+    <cellStyle name="Calculation 3 19" xfId="749" xr:uid="{00000000-0005-0000-0000-000081020000}"/>
+    <cellStyle name="Calculation 3 2" xfId="903" xr:uid="{00000000-0005-0000-0000-000082020000}"/>
+    <cellStyle name="Calculation 3 20" xfId="1066" xr:uid="{00000000-0005-0000-0000-000083020000}"/>
+    <cellStyle name="Calculation 3 21" xfId="721" xr:uid="{00000000-0005-0000-0000-000084020000}"/>
+    <cellStyle name="Calculation 3 22" xfId="1093" xr:uid="{00000000-0005-0000-0000-000085020000}"/>
+    <cellStyle name="Calculation 3 23" xfId="694" xr:uid="{00000000-0005-0000-0000-000086020000}"/>
+    <cellStyle name="Calculation 3 24" xfId="1147" xr:uid="{00000000-0005-0000-0000-000087020000}"/>
+    <cellStyle name="Calculation 3 25" xfId="1219" xr:uid="{00000000-0005-0000-0000-000088020000}"/>
+    <cellStyle name="Calculation 3 26" xfId="1296" xr:uid="{00000000-0005-0000-0000-000089020000}"/>
+    <cellStyle name="Calculation 3 27" xfId="1373" xr:uid="{00000000-0005-0000-0000-00008A020000}"/>
+    <cellStyle name="Calculation 3 28" xfId="1449" xr:uid="{00000000-0005-0000-0000-00008B020000}"/>
+    <cellStyle name="Calculation 3 29" xfId="1524" xr:uid="{00000000-0005-0000-0000-00008C020000}"/>
+    <cellStyle name="Calculation 3 3" xfId="880" xr:uid="{00000000-0005-0000-0000-00008D020000}"/>
+    <cellStyle name="Calculation 3 30" xfId="1603" xr:uid="{00000000-0005-0000-0000-00008E020000}"/>
+    <cellStyle name="Calculation 3 31" xfId="1783" xr:uid="{00000000-0005-0000-0000-00008F020000}"/>
+    <cellStyle name="Calculation 3 32" xfId="1753" xr:uid="{00000000-0005-0000-0000-000090020000}"/>
+    <cellStyle name="Calculation 3 4" xfId="919" xr:uid="{00000000-0005-0000-0000-000091020000}"/>
+    <cellStyle name="Calculation 3 5" xfId="867" xr:uid="{00000000-0005-0000-0000-000092020000}"/>
+    <cellStyle name="Calculation 3 6" xfId="933" xr:uid="{00000000-0005-0000-0000-000093020000}"/>
+    <cellStyle name="Calculation 3 7" xfId="852" xr:uid="{00000000-0005-0000-0000-000094020000}"/>
+    <cellStyle name="Calculation 3 8" xfId="948" xr:uid="{00000000-0005-0000-0000-000095020000}"/>
+    <cellStyle name="Calculation 3 9" xfId="837" xr:uid="{00000000-0005-0000-0000-000096020000}"/>
+    <cellStyle name="Calculation 4" xfId="389" xr:uid="{00000000-0005-0000-0000-000097020000}"/>
+    <cellStyle name="Calculation 4 10" xfId="964" xr:uid="{00000000-0005-0000-0000-000098020000}"/>
+    <cellStyle name="Calculation 4 11" xfId="821" xr:uid="{00000000-0005-0000-0000-000099020000}"/>
+    <cellStyle name="Calculation 4 12" xfId="979" xr:uid="{00000000-0005-0000-0000-00009A020000}"/>
+    <cellStyle name="Calculation 4 13" xfId="806" xr:uid="{00000000-0005-0000-0000-00009B020000}"/>
+    <cellStyle name="Calculation 4 14" xfId="995" xr:uid="{00000000-0005-0000-0000-00009C020000}"/>
+    <cellStyle name="Calculation 4 15" xfId="792" xr:uid="{00000000-0005-0000-0000-00009D020000}"/>
+    <cellStyle name="Calculation 4 16" xfId="1010" xr:uid="{00000000-0005-0000-0000-00009E020000}"/>
+    <cellStyle name="Calculation 4 17" xfId="777" xr:uid="{00000000-0005-0000-0000-00009F020000}"/>
+    <cellStyle name="Calculation 4 18" xfId="1039" xr:uid="{00000000-0005-0000-0000-0000A0020000}"/>
+    <cellStyle name="Calculation 4 19" xfId="748" xr:uid="{00000000-0005-0000-0000-0000A1020000}"/>
+    <cellStyle name="Calculation 4 2" xfId="904" xr:uid="{00000000-0005-0000-0000-0000A2020000}"/>
+    <cellStyle name="Calculation 4 20" xfId="1067" xr:uid="{00000000-0005-0000-0000-0000A3020000}"/>
+    <cellStyle name="Calculation 4 21" xfId="720" xr:uid="{00000000-0005-0000-0000-0000A4020000}"/>
+    <cellStyle name="Calculation 4 22" xfId="1094" xr:uid="{00000000-0005-0000-0000-0000A5020000}"/>
+    <cellStyle name="Calculation 4 23" xfId="693" xr:uid="{00000000-0005-0000-0000-0000A6020000}"/>
+    <cellStyle name="Calculation 4 24" xfId="1148" xr:uid="{00000000-0005-0000-0000-0000A7020000}"/>
+    <cellStyle name="Calculation 4 25" xfId="1220" xr:uid="{00000000-0005-0000-0000-0000A8020000}"/>
+    <cellStyle name="Calculation 4 26" xfId="1297" xr:uid="{00000000-0005-0000-0000-0000A9020000}"/>
+    <cellStyle name="Calculation 4 27" xfId="1374" xr:uid="{00000000-0005-0000-0000-0000AA020000}"/>
+    <cellStyle name="Calculation 4 28" xfId="1450" xr:uid="{00000000-0005-0000-0000-0000AB020000}"/>
+    <cellStyle name="Calculation 4 29" xfId="1525" xr:uid="{00000000-0005-0000-0000-0000AC020000}"/>
+    <cellStyle name="Calculation 4 3" xfId="879" xr:uid="{00000000-0005-0000-0000-0000AD020000}"/>
+    <cellStyle name="Calculation 4 30" xfId="1849" xr:uid="{00000000-0005-0000-0000-0000AE020000}"/>
+    <cellStyle name="Calculation 4 31" xfId="1672" xr:uid="{00000000-0005-0000-0000-0000AF020000}"/>
+    <cellStyle name="Calculation 4 32" xfId="1754" xr:uid="{00000000-0005-0000-0000-0000B0020000}"/>
+    <cellStyle name="Calculation 4 4" xfId="920" xr:uid="{00000000-0005-0000-0000-0000B1020000}"/>
+    <cellStyle name="Calculation 4 5" xfId="866" xr:uid="{00000000-0005-0000-0000-0000B2020000}"/>
+    <cellStyle name="Calculation 4 6" xfId="934" xr:uid="{00000000-0005-0000-0000-0000B3020000}"/>
+    <cellStyle name="Calculation 4 7" xfId="851" xr:uid="{00000000-0005-0000-0000-0000B4020000}"/>
+    <cellStyle name="Calculation 4 8" xfId="949" xr:uid="{00000000-0005-0000-0000-0000B5020000}"/>
+    <cellStyle name="Calculation 4 9" xfId="836" xr:uid="{00000000-0005-0000-0000-0000B6020000}"/>
+    <cellStyle name="Calculation 5" xfId="390" xr:uid="{00000000-0005-0000-0000-0000B7020000}"/>
+    <cellStyle name="Calculation 5 10" xfId="965" xr:uid="{00000000-0005-0000-0000-0000B8020000}"/>
+    <cellStyle name="Calculation 5 11" xfId="820" xr:uid="{00000000-0005-0000-0000-0000B9020000}"/>
+    <cellStyle name="Calculation 5 12" xfId="980" xr:uid="{00000000-0005-0000-0000-0000BA020000}"/>
+    <cellStyle name="Calculation 5 13" xfId="805" xr:uid="{00000000-0005-0000-0000-0000BB020000}"/>
+    <cellStyle name="Calculation 5 14" xfId="996" xr:uid="{00000000-0005-0000-0000-0000BC020000}"/>
+    <cellStyle name="Calculation 5 15" xfId="791" xr:uid="{00000000-0005-0000-0000-0000BD020000}"/>
+    <cellStyle name="Calculation 5 16" xfId="1011" xr:uid="{00000000-0005-0000-0000-0000BE020000}"/>
+    <cellStyle name="Calculation 5 17" xfId="776" xr:uid="{00000000-0005-0000-0000-0000BF020000}"/>
+    <cellStyle name="Calculation 5 18" xfId="1040" xr:uid="{00000000-0005-0000-0000-0000C0020000}"/>
+    <cellStyle name="Calculation 5 19" xfId="747" xr:uid="{00000000-0005-0000-0000-0000C1020000}"/>
+    <cellStyle name="Calculation 5 2" xfId="905" xr:uid="{00000000-0005-0000-0000-0000C2020000}"/>
+    <cellStyle name="Calculation 5 20" xfId="672" xr:uid="{00000000-0005-0000-0000-0000C3020000}"/>
+    <cellStyle name="Calculation 5 21" xfId="719" xr:uid="{00000000-0005-0000-0000-0000C4020000}"/>
+    <cellStyle name="Calculation 5 22" xfId="674" xr:uid="{00000000-0005-0000-0000-0000C5020000}"/>
+    <cellStyle name="Calculation 5 23" xfId="692" xr:uid="{00000000-0005-0000-0000-0000C6020000}"/>
+    <cellStyle name="Calculation 5 24" xfId="1149" xr:uid="{00000000-0005-0000-0000-0000C7020000}"/>
+    <cellStyle name="Calculation 5 25" xfId="1221" xr:uid="{00000000-0005-0000-0000-0000C8020000}"/>
+    <cellStyle name="Calculation 5 26" xfId="1298" xr:uid="{00000000-0005-0000-0000-0000C9020000}"/>
+    <cellStyle name="Calculation 5 27" xfId="1375" xr:uid="{00000000-0005-0000-0000-0000CA020000}"/>
+    <cellStyle name="Calculation 5 28" xfId="1451" xr:uid="{00000000-0005-0000-0000-0000CB020000}"/>
+    <cellStyle name="Calculation 5 29" xfId="1526" xr:uid="{00000000-0005-0000-0000-0000CC020000}"/>
+    <cellStyle name="Calculation 5 3" xfId="878" xr:uid="{00000000-0005-0000-0000-0000CD020000}"/>
+    <cellStyle name="Calculation 5 30" xfId="1706" xr:uid="{00000000-0005-0000-0000-0000CE020000}"/>
+    <cellStyle name="Calculation 5 31" xfId="1673" xr:uid="{00000000-0005-0000-0000-0000CF020000}"/>
+    <cellStyle name="Calculation 5 32" xfId="1976" xr:uid="{00000000-0005-0000-0000-0000D0020000}"/>
+    <cellStyle name="Calculation 5 4" xfId="921" xr:uid="{00000000-0005-0000-0000-0000D1020000}"/>
+    <cellStyle name="Calculation 5 5" xfId="865" xr:uid="{00000000-0005-0000-0000-0000D2020000}"/>
+    <cellStyle name="Calculation 5 6" xfId="935" xr:uid="{00000000-0005-0000-0000-0000D3020000}"/>
+    <cellStyle name="Calculation 5 7" xfId="850" xr:uid="{00000000-0005-0000-0000-0000D4020000}"/>
+    <cellStyle name="Calculation 5 8" xfId="950" xr:uid="{00000000-0005-0000-0000-0000D5020000}"/>
+    <cellStyle name="Calculation 5 9" xfId="835" xr:uid="{00000000-0005-0000-0000-0000D6020000}"/>
+    <cellStyle name="Calculation 6" xfId="391" xr:uid="{00000000-0005-0000-0000-0000D7020000}"/>
+    <cellStyle name="Calculation 6 10" xfId="966" xr:uid="{00000000-0005-0000-0000-0000D8020000}"/>
+    <cellStyle name="Calculation 6 11" xfId="819" xr:uid="{00000000-0005-0000-0000-0000D9020000}"/>
+    <cellStyle name="Calculation 6 12" xfId="981" xr:uid="{00000000-0005-0000-0000-0000DA020000}"/>
+    <cellStyle name="Calculation 6 13" xfId="804" xr:uid="{00000000-0005-0000-0000-0000DB020000}"/>
+    <cellStyle name="Calculation 6 14" xfId="997" xr:uid="{00000000-0005-0000-0000-0000DC020000}"/>
+    <cellStyle name="Calculation 6 15" xfId="790" xr:uid="{00000000-0005-0000-0000-0000DD020000}"/>
+    <cellStyle name="Calculation 6 16" xfId="1012" xr:uid="{00000000-0005-0000-0000-0000DE020000}"/>
+    <cellStyle name="Calculation 6 17" xfId="775" xr:uid="{00000000-0005-0000-0000-0000DF020000}"/>
+    <cellStyle name="Calculation 6 18" xfId="1041" xr:uid="{00000000-0005-0000-0000-0000E0020000}"/>
+    <cellStyle name="Calculation 6 19" xfId="746" xr:uid="{00000000-0005-0000-0000-0000E1020000}"/>
+    <cellStyle name="Calculation 6 2" xfId="906" xr:uid="{00000000-0005-0000-0000-0000E2020000}"/>
+    <cellStyle name="Calculation 6 20" xfId="1069" xr:uid="{00000000-0005-0000-0000-0000E3020000}"/>
+    <cellStyle name="Calculation 6 21" xfId="718" xr:uid="{00000000-0005-0000-0000-0000E4020000}"/>
+    <cellStyle name="Calculation 6 22" xfId="1095" xr:uid="{00000000-0005-0000-0000-0000E5020000}"/>
+    <cellStyle name="Calculation 6 23" xfId="691" xr:uid="{00000000-0005-0000-0000-0000E6020000}"/>
+    <cellStyle name="Calculation 6 24" xfId="1150" xr:uid="{00000000-0005-0000-0000-0000E7020000}"/>
+    <cellStyle name="Calculation 6 25" xfId="1222" xr:uid="{00000000-0005-0000-0000-0000E8020000}"/>
+    <cellStyle name="Calculation 6 26" xfId="1299" xr:uid="{00000000-0005-0000-0000-0000E9020000}"/>
+    <cellStyle name="Calculation 6 27" xfId="1376" xr:uid="{00000000-0005-0000-0000-0000EA020000}"/>
+    <cellStyle name="Calculation 6 28" xfId="1452" xr:uid="{00000000-0005-0000-0000-0000EB020000}"/>
+    <cellStyle name="Calculation 6 29" xfId="1527" xr:uid="{00000000-0005-0000-0000-0000EC020000}"/>
+    <cellStyle name="Calculation 6 3" xfId="877" xr:uid="{00000000-0005-0000-0000-0000ED020000}"/>
+    <cellStyle name="Calculation 6 30" xfId="1605" xr:uid="{00000000-0005-0000-0000-0000EE020000}"/>
+    <cellStyle name="Calculation 6 31" xfId="1674" xr:uid="{00000000-0005-0000-0000-0000EF020000}"/>
+    <cellStyle name="Calculation 6 32" xfId="1755" xr:uid="{00000000-0005-0000-0000-0000F0020000}"/>
+    <cellStyle name="Calculation 6 4" xfId="922" xr:uid="{00000000-0005-0000-0000-0000F1020000}"/>
+    <cellStyle name="Calculation 6 5" xfId="864" xr:uid="{00000000-0005-0000-0000-0000F2020000}"/>
+    <cellStyle name="Calculation 6 6" xfId="936" xr:uid="{00000000-0005-0000-0000-0000F3020000}"/>
+    <cellStyle name="Calculation 6 7" xfId="849" xr:uid="{00000000-0005-0000-0000-0000F4020000}"/>
+    <cellStyle name="Calculation 6 8" xfId="951" xr:uid="{00000000-0005-0000-0000-0000F5020000}"/>
+    <cellStyle name="Calculation 6 9" xfId="834" xr:uid="{00000000-0005-0000-0000-0000F6020000}"/>
+    <cellStyle name="Calculation 7" xfId="392" xr:uid="{00000000-0005-0000-0000-0000F7020000}"/>
+    <cellStyle name="Calculation 7 10" xfId="967" xr:uid="{00000000-0005-0000-0000-0000F8020000}"/>
+    <cellStyle name="Calculation 7 11" xfId="818" xr:uid="{00000000-0005-0000-0000-0000F9020000}"/>
+    <cellStyle name="Calculation 7 12" xfId="982" xr:uid="{00000000-0005-0000-0000-0000FA020000}"/>
+    <cellStyle name="Calculation 7 13" xfId="803" xr:uid="{00000000-0005-0000-0000-0000FB020000}"/>
+    <cellStyle name="Calculation 7 14" xfId="998" xr:uid="{00000000-0005-0000-0000-0000FC020000}"/>
+    <cellStyle name="Calculation 7 15" xfId="789" xr:uid="{00000000-0005-0000-0000-0000FD020000}"/>
+    <cellStyle name="Calculation 7 16" xfId="671" xr:uid="{00000000-0005-0000-0000-0000FE020000}"/>
+    <cellStyle name="Calculation 7 17" xfId="774" xr:uid="{00000000-0005-0000-0000-0000FF020000}"/>
+    <cellStyle name="Calculation 7 18" xfId="1042" xr:uid="{00000000-0005-0000-0000-000000030000}"/>
+    <cellStyle name="Calculation 7 19" xfId="745" xr:uid="{00000000-0005-0000-0000-000001030000}"/>
+    <cellStyle name="Calculation 7 2" xfId="907" xr:uid="{00000000-0005-0000-0000-000002030000}"/>
+    <cellStyle name="Calculation 7 20" xfId="1070" xr:uid="{00000000-0005-0000-0000-000003030000}"/>
+    <cellStyle name="Calculation 7 21" xfId="717" xr:uid="{00000000-0005-0000-0000-000004030000}"/>
+    <cellStyle name="Calculation 7 22" xfId="1253" xr:uid="{00000000-0005-0000-0000-000005030000}"/>
+    <cellStyle name="Calculation 7 23" xfId="690" xr:uid="{00000000-0005-0000-0000-000006030000}"/>
+    <cellStyle name="Calculation 7 24" xfId="1151" xr:uid="{00000000-0005-0000-0000-000007030000}"/>
+    <cellStyle name="Calculation 7 25" xfId="1223" xr:uid="{00000000-0005-0000-0000-000008030000}"/>
+    <cellStyle name="Calculation 7 26" xfId="1300" xr:uid="{00000000-0005-0000-0000-000009030000}"/>
+    <cellStyle name="Calculation 7 27" xfId="1377" xr:uid="{00000000-0005-0000-0000-00000A030000}"/>
+    <cellStyle name="Calculation 7 28" xfId="1453" xr:uid="{00000000-0005-0000-0000-00000B030000}"/>
+    <cellStyle name="Calculation 7 29" xfId="1528" xr:uid="{00000000-0005-0000-0000-00000C030000}"/>
+    <cellStyle name="Calculation 7 3" xfId="876" xr:uid="{00000000-0005-0000-0000-00000D030000}"/>
+    <cellStyle name="Calculation 7 30" xfId="2100" xr:uid="{00000000-0005-0000-0000-00000E030000}"/>
+    <cellStyle name="Calculation 7 31" xfId="1675" xr:uid="{00000000-0005-0000-0000-00000F030000}"/>
+    <cellStyle name="Calculation 7 32" xfId="2226" xr:uid="{00000000-0005-0000-0000-000010030000}"/>
+    <cellStyle name="Calculation 7 4" xfId="923" xr:uid="{00000000-0005-0000-0000-000011030000}"/>
+    <cellStyle name="Calculation 7 5" xfId="863" xr:uid="{00000000-0005-0000-0000-000012030000}"/>
+    <cellStyle name="Calculation 7 6" xfId="937" xr:uid="{00000000-0005-0000-0000-000013030000}"/>
+    <cellStyle name="Calculation 7 7" xfId="848" xr:uid="{00000000-0005-0000-0000-000014030000}"/>
+    <cellStyle name="Calculation 7 8" xfId="952" xr:uid="{00000000-0005-0000-0000-000015030000}"/>
+    <cellStyle name="Calculation 7 9" xfId="833" xr:uid="{00000000-0005-0000-0000-000016030000}"/>
+    <cellStyle name="Calculation 8" xfId="393" xr:uid="{00000000-0005-0000-0000-000017030000}"/>
+    <cellStyle name="Calculation 8 10" xfId="968" xr:uid="{00000000-0005-0000-0000-000018030000}"/>
+    <cellStyle name="Calculation 8 11" xfId="817" xr:uid="{00000000-0005-0000-0000-000019030000}"/>
+    <cellStyle name="Calculation 8 12" xfId="983" xr:uid="{00000000-0005-0000-0000-00001A030000}"/>
+    <cellStyle name="Calculation 8 13" xfId="802" xr:uid="{00000000-0005-0000-0000-00001B030000}"/>
+    <cellStyle name="Calculation 8 14" xfId="999" xr:uid="{00000000-0005-0000-0000-00001C030000}"/>
+    <cellStyle name="Calculation 8 15" xfId="788" xr:uid="{00000000-0005-0000-0000-00001D030000}"/>
+    <cellStyle name="Calculation 8 16" xfId="1028" xr:uid="{00000000-0005-0000-0000-00001E030000}"/>
+    <cellStyle name="Calculation 8 17" xfId="773" xr:uid="{00000000-0005-0000-0000-00001F030000}"/>
+    <cellStyle name="Calculation 8 18" xfId="1043" xr:uid="{00000000-0005-0000-0000-000020030000}"/>
+    <cellStyle name="Calculation 8 19" xfId="744" xr:uid="{00000000-0005-0000-0000-000021030000}"/>
+    <cellStyle name="Calculation 8 2" xfId="908" xr:uid="{00000000-0005-0000-0000-000022030000}"/>
+    <cellStyle name="Calculation 8 20" xfId="1071" xr:uid="{00000000-0005-0000-0000-000023030000}"/>
+    <cellStyle name="Calculation 8 21" xfId="716" xr:uid="{00000000-0005-0000-0000-000024030000}"/>
+    <cellStyle name="Calculation 8 22" xfId="1560" xr:uid="{00000000-0005-0000-0000-000025030000}"/>
+    <cellStyle name="Calculation 8 23" xfId="1331" xr:uid="{00000000-0005-0000-0000-000026030000}"/>
+    <cellStyle name="Calculation 8 24" xfId="1408" xr:uid="{00000000-0005-0000-0000-000027030000}"/>
+    <cellStyle name="Calculation 8 25" xfId="1483" xr:uid="{00000000-0005-0000-0000-000028030000}"/>
+    <cellStyle name="Calculation 8 26" xfId="1559" xr:uid="{00000000-0005-0000-0000-000029030000}"/>
+    <cellStyle name="Calculation 8 27" xfId="1634" xr:uid="{00000000-0005-0000-0000-00002A030000}"/>
+    <cellStyle name="Calculation 8 28" xfId="1708" xr:uid="{00000000-0005-0000-0000-00002B030000}"/>
+    <cellStyle name="Calculation 8 29" xfId="1784" xr:uid="{00000000-0005-0000-0000-00002C030000}"/>
+    <cellStyle name="Calculation 8 3" xfId="875" xr:uid="{00000000-0005-0000-0000-00002D030000}"/>
+    <cellStyle name="Calculation 8 30" xfId="1745" xr:uid="{00000000-0005-0000-0000-00002E030000}"/>
+    <cellStyle name="Calculation 8 31" xfId="1676" xr:uid="{00000000-0005-0000-0000-00002F030000}"/>
+    <cellStyle name="Calculation 8 32" xfId="1885" xr:uid="{00000000-0005-0000-0000-000030030000}"/>
+    <cellStyle name="Calculation 8 4" xfId="924" xr:uid="{00000000-0005-0000-0000-000031030000}"/>
+    <cellStyle name="Calculation 8 5" xfId="862" xr:uid="{00000000-0005-0000-0000-000032030000}"/>
+    <cellStyle name="Calculation 8 6" xfId="938" xr:uid="{00000000-0005-0000-0000-000033030000}"/>
+    <cellStyle name="Calculation 8 7" xfId="847" xr:uid="{00000000-0005-0000-0000-000034030000}"/>
+    <cellStyle name="Calculation 8 8" xfId="953" xr:uid="{00000000-0005-0000-0000-000035030000}"/>
+    <cellStyle name="Calculation 8 9" xfId="832" xr:uid="{00000000-0005-0000-0000-000036030000}"/>
+    <cellStyle name="Calculation 9" xfId="394" xr:uid="{00000000-0005-0000-0000-000037030000}"/>
+    <cellStyle name="Calculation 9 10" xfId="969" xr:uid="{00000000-0005-0000-0000-000038030000}"/>
+    <cellStyle name="Calculation 9 11" xfId="816" xr:uid="{00000000-0005-0000-0000-000039030000}"/>
+    <cellStyle name="Calculation 9 12" xfId="984" xr:uid="{00000000-0005-0000-0000-00003A030000}"/>
+    <cellStyle name="Calculation 9 13" xfId="801" xr:uid="{00000000-0005-0000-0000-00003B030000}"/>
+    <cellStyle name="Calculation 9 14" xfId="1000" xr:uid="{00000000-0005-0000-0000-00003C030000}"/>
+    <cellStyle name="Calculation 9 15" xfId="787" xr:uid="{00000000-0005-0000-0000-00003D030000}"/>
+    <cellStyle name="Calculation 9 16" xfId="1029" xr:uid="{00000000-0005-0000-0000-00003E030000}"/>
+    <cellStyle name="Calculation 9 17" xfId="772" xr:uid="{00000000-0005-0000-0000-00003F030000}"/>
+    <cellStyle name="Calculation 9 18" xfId="1044" xr:uid="{00000000-0005-0000-0000-000040030000}"/>
+    <cellStyle name="Calculation 9 19" xfId="743" xr:uid="{00000000-0005-0000-0000-000041030000}"/>
+    <cellStyle name="Calculation 9 2" xfId="909" xr:uid="{00000000-0005-0000-0000-000042030000}"/>
+    <cellStyle name="Calculation 9 20" xfId="1409" xr:uid="{00000000-0005-0000-0000-000043030000}"/>
+    <cellStyle name="Calculation 9 21" xfId="715" xr:uid="{00000000-0005-0000-0000-000044030000}"/>
+    <cellStyle name="Calculation 9 22" xfId="1142" xr:uid="{00000000-0005-0000-0000-000045030000}"/>
+    <cellStyle name="Calculation 9 23" xfId="688" xr:uid="{00000000-0005-0000-0000-000046030000}"/>
+    <cellStyle name="Calculation 9 24" xfId="1168" xr:uid="{00000000-0005-0000-0000-000047030000}"/>
+    <cellStyle name="Calculation 9 25" xfId="1329" xr:uid="{00000000-0005-0000-0000-000048030000}"/>
+    <cellStyle name="Calculation 9 26" xfId="1406" xr:uid="{00000000-0005-0000-0000-000049030000}"/>
+    <cellStyle name="Calculation 9 27" xfId="1481" xr:uid="{00000000-0005-0000-0000-00004A030000}"/>
+    <cellStyle name="Calculation 9 28" xfId="1557" xr:uid="{00000000-0005-0000-0000-00004B030000}"/>
+    <cellStyle name="Calculation 9 29" xfId="2039" xr:uid="{00000000-0005-0000-0000-00004C030000}"/>
+    <cellStyle name="Calculation 9 3" xfId="874" xr:uid="{00000000-0005-0000-0000-00004D030000}"/>
+    <cellStyle name="Calculation 9 30" xfId="1977" xr:uid="{00000000-0005-0000-0000-00004E030000}"/>
+    <cellStyle name="Calculation 9 31" xfId="1677" xr:uid="{00000000-0005-0000-0000-00004F030000}"/>
+    <cellStyle name="Calculation 9 32" xfId="2101" xr:uid="{00000000-0005-0000-0000-000050030000}"/>
+    <cellStyle name="Calculation 9 4" xfId="925" xr:uid="{00000000-0005-0000-0000-000051030000}"/>
+    <cellStyle name="Calculation 9 5" xfId="861" xr:uid="{00000000-0005-0000-0000-000052030000}"/>
+    <cellStyle name="Calculation 9 6" xfId="939" xr:uid="{00000000-0005-0000-0000-000053030000}"/>
+    <cellStyle name="Calculation 9 7" xfId="846" xr:uid="{00000000-0005-0000-0000-000054030000}"/>
+    <cellStyle name="Calculation 9 8" xfId="954" xr:uid="{00000000-0005-0000-0000-000055030000}"/>
+    <cellStyle name="Calculation 9 9" xfId="831" xr:uid="{00000000-0005-0000-0000-000056030000}"/>
+    <cellStyle name="Check Cell 10" xfId="395" xr:uid="{00000000-0005-0000-0000-000057030000}"/>
+    <cellStyle name="Check Cell 11" xfId="396" xr:uid="{00000000-0005-0000-0000-000058030000}"/>
+    <cellStyle name="Check Cell 12" xfId="397" xr:uid="{00000000-0005-0000-0000-000059030000}"/>
+    <cellStyle name="Check Cell 13" xfId="398" xr:uid="{00000000-0005-0000-0000-00005A030000}"/>
+    <cellStyle name="Check Cell 14" xfId="399" xr:uid="{00000000-0005-0000-0000-00005B030000}"/>
+    <cellStyle name="Check Cell 15" xfId="400" xr:uid="{00000000-0005-0000-0000-00005C030000}"/>
+    <cellStyle name="Check Cell 16" xfId="401" xr:uid="{00000000-0005-0000-0000-00005D030000}"/>
+    <cellStyle name="Check Cell 2" xfId="402" xr:uid="{00000000-0005-0000-0000-00005E030000}"/>
+    <cellStyle name="Check Cell 3" xfId="403" xr:uid="{00000000-0005-0000-0000-00005F030000}"/>
+    <cellStyle name="Check Cell 4" xfId="404" xr:uid="{00000000-0005-0000-0000-000060030000}"/>
+    <cellStyle name="Check Cell 5" xfId="405" xr:uid="{00000000-0005-0000-0000-000061030000}"/>
+    <cellStyle name="Check Cell 6" xfId="406" xr:uid="{00000000-0005-0000-0000-000062030000}"/>
+    <cellStyle name="Check Cell 7" xfId="407" xr:uid="{00000000-0005-0000-0000-000063030000}"/>
+    <cellStyle name="Check Cell 8" xfId="408" xr:uid="{00000000-0005-0000-0000-000064030000}"/>
+    <cellStyle name="Check Cell 9" xfId="409" xr:uid="{00000000-0005-0000-0000-000065030000}"/>
+    <cellStyle name="Comma 2" xfId="3030" xr:uid="{00000000-0005-0000-0000-000066030000}"/>
+    <cellStyle name="Explanatory Text 10" xfId="410" xr:uid="{00000000-0005-0000-0000-000067030000}"/>
+    <cellStyle name="Explanatory Text 11" xfId="411" xr:uid="{00000000-0005-0000-0000-000068030000}"/>
+    <cellStyle name="Explanatory Text 12" xfId="412" xr:uid="{00000000-0005-0000-0000-000069030000}"/>
+    <cellStyle name="Explanatory Text 13" xfId="413" xr:uid="{00000000-0005-0000-0000-00006A030000}"/>
+    <cellStyle name="Explanatory Text 14" xfId="414" xr:uid="{00000000-0005-0000-0000-00006B030000}"/>
+    <cellStyle name="Explanatory Text 15" xfId="415" xr:uid="{00000000-0005-0000-0000-00006C030000}"/>
+    <cellStyle name="Explanatory Text 16" xfId="416" xr:uid="{00000000-0005-0000-0000-00006D030000}"/>
+    <cellStyle name="Explanatory Text 2" xfId="417" xr:uid="{00000000-0005-0000-0000-00006E030000}"/>
+    <cellStyle name="Explanatory Text 3" xfId="418" xr:uid="{00000000-0005-0000-0000-00006F030000}"/>
+    <cellStyle name="Explanatory Text 4" xfId="419" xr:uid="{00000000-0005-0000-0000-000070030000}"/>
+    <cellStyle name="Explanatory Text 5" xfId="420" xr:uid="{00000000-0005-0000-0000-000071030000}"/>
+    <cellStyle name="Explanatory Text 6" xfId="421" xr:uid="{00000000-0005-0000-0000-000072030000}"/>
+    <cellStyle name="Explanatory Text 7" xfId="422" xr:uid="{00000000-0005-0000-0000-000073030000}"/>
+    <cellStyle name="Explanatory Text 8" xfId="423" xr:uid="{00000000-0005-0000-0000-000074030000}"/>
+    <cellStyle name="Explanatory Text 9" xfId="424" xr:uid="{00000000-0005-0000-0000-000075030000}"/>
+    <cellStyle name="Good 10" xfId="425" xr:uid="{00000000-0005-0000-0000-000076030000}"/>
+    <cellStyle name="Good 11" xfId="426" xr:uid="{00000000-0005-0000-0000-000077030000}"/>
+    <cellStyle name="Good 12" xfId="427" xr:uid="{00000000-0005-0000-0000-000078030000}"/>
+    <cellStyle name="Good 13" xfId="428" xr:uid="{00000000-0005-0000-0000-000079030000}"/>
+    <cellStyle name="Good 14" xfId="429" xr:uid="{00000000-0005-0000-0000-00007A030000}"/>
+    <cellStyle name="Good 15" xfId="430" xr:uid="{00000000-0005-0000-0000-00007B030000}"/>
+    <cellStyle name="Good 16" xfId="431" xr:uid="{00000000-0005-0000-0000-00007C030000}"/>
+    <cellStyle name="Good 2" xfId="432" xr:uid="{00000000-0005-0000-0000-00007D030000}"/>
+    <cellStyle name="Good 3" xfId="433" xr:uid="{00000000-0005-0000-0000-00007E030000}"/>
+    <cellStyle name="Good 4" xfId="434" xr:uid="{00000000-0005-0000-0000-00007F030000}"/>
+    <cellStyle name="Good 5" xfId="435" xr:uid="{00000000-0005-0000-0000-000080030000}"/>
+    <cellStyle name="Good 6" xfId="436" xr:uid="{00000000-0005-0000-0000-000081030000}"/>
+    <cellStyle name="Good 7" xfId="437" xr:uid="{00000000-0005-0000-0000-000082030000}"/>
+    <cellStyle name="Good 8" xfId="438" xr:uid="{00000000-0005-0000-0000-000083030000}"/>
+    <cellStyle name="Good 9" xfId="439" xr:uid="{00000000-0005-0000-0000-000084030000}"/>
+    <cellStyle name="Heading 1 10" xfId="440" xr:uid="{00000000-0005-0000-0000-000085030000}"/>
+    <cellStyle name="Heading 1 11" xfId="441" xr:uid="{00000000-0005-0000-0000-000086030000}"/>
+    <cellStyle name="Heading 1 12" xfId="442" xr:uid="{00000000-0005-0000-0000-000087030000}"/>
+    <cellStyle name="Heading 1 13" xfId="443" xr:uid="{00000000-0005-0000-0000-000088030000}"/>
+    <cellStyle name="Heading 1 14" xfId="444" xr:uid="{00000000-0005-0000-0000-000089030000}"/>
+    <cellStyle name="Heading 1 15" xfId="445" xr:uid="{00000000-0005-0000-0000-00008A030000}"/>
+    <cellStyle name="Heading 1 16" xfId="446" xr:uid="{00000000-0005-0000-0000-00008B030000}"/>
+    <cellStyle name="Heading 1 2" xfId="447" xr:uid="{00000000-0005-0000-0000-00008C030000}"/>
+    <cellStyle name="Heading 1 3" xfId="448" xr:uid="{00000000-0005-0000-0000-00008D030000}"/>
+    <cellStyle name="Heading 1 4" xfId="449" xr:uid="{00000000-0005-0000-0000-00008E030000}"/>
+    <cellStyle name="Heading 1 5" xfId="450" xr:uid="{00000000-0005-0000-0000-00008F030000}"/>
+    <cellStyle name="Heading 1 6" xfId="451" xr:uid="{00000000-0005-0000-0000-000090030000}"/>
+    <cellStyle name="Heading 1 7" xfId="452" xr:uid="{00000000-0005-0000-0000-000091030000}"/>
+    <cellStyle name="Heading 1 8" xfId="453" xr:uid="{00000000-0005-0000-0000-000092030000}"/>
+    <cellStyle name="Heading 1 9" xfId="454" xr:uid="{00000000-0005-0000-0000-000093030000}"/>
+    <cellStyle name="Heading 2 10" xfId="455" xr:uid="{00000000-0005-0000-0000-000094030000}"/>
+    <cellStyle name="Heading 2 11" xfId="456" xr:uid="{00000000-0005-0000-0000-000095030000}"/>
+    <cellStyle name="Heading 2 12" xfId="457" xr:uid="{00000000-0005-0000-0000-000096030000}"/>
+    <cellStyle name="Heading 2 13" xfId="458" xr:uid="{00000000-0005-0000-0000-000097030000}"/>
+    <cellStyle name="Heading 2 14" xfId="459" xr:uid="{00000000-0005-0000-0000-000098030000}"/>
+    <cellStyle name="Heading 2 15" xfId="460" xr:uid="{00000000-0005-0000-0000-000099030000}"/>
+    <cellStyle name="Heading 2 16" xfId="461" xr:uid="{00000000-0005-0000-0000-00009A030000}"/>
+    <cellStyle name="Heading 2 2" xfId="462" xr:uid="{00000000-0005-0000-0000-00009B030000}"/>
+    <cellStyle name="Heading 2 3" xfId="463" xr:uid="{00000000-0005-0000-0000-00009C030000}"/>
+    <cellStyle name="Heading 2 4" xfId="464" xr:uid="{00000000-0005-0000-0000-00009D030000}"/>
+    <cellStyle name="Heading 2 5" xfId="465" xr:uid="{00000000-0005-0000-0000-00009E030000}"/>
+    <cellStyle name="Heading 2 6" xfId="466" xr:uid="{00000000-0005-0000-0000-00009F030000}"/>
+    <cellStyle name="Heading 2 7" xfId="467" xr:uid="{00000000-0005-0000-0000-0000A0030000}"/>
+    <cellStyle name="Heading 2 8" xfId="468" xr:uid="{00000000-0005-0000-0000-0000A1030000}"/>
+    <cellStyle name="Heading 2 9" xfId="469" xr:uid="{00000000-0005-0000-0000-0000A2030000}"/>
+    <cellStyle name="Heading 3 10" xfId="470" xr:uid="{00000000-0005-0000-0000-0000A3030000}"/>
+    <cellStyle name="Heading 3 11" xfId="471" xr:uid="{00000000-0005-0000-0000-0000A4030000}"/>
+    <cellStyle name="Heading 3 12" xfId="472" xr:uid="{00000000-0005-0000-0000-0000A5030000}"/>
+    <cellStyle name="Heading 3 13" xfId="473" xr:uid="{00000000-0005-0000-0000-0000A6030000}"/>
+    <cellStyle name="Heading 3 14" xfId="474" xr:uid="{00000000-0005-0000-0000-0000A7030000}"/>
+    <cellStyle name="Heading 3 15" xfId="475" xr:uid="{00000000-0005-0000-0000-0000A8030000}"/>
+    <cellStyle name="Heading 3 16" xfId="476" xr:uid="{00000000-0005-0000-0000-0000A9030000}"/>
+    <cellStyle name="Heading 3 2" xfId="477" xr:uid="{00000000-0005-0000-0000-0000AA030000}"/>
+    <cellStyle name="Heading 3 3" xfId="478" xr:uid="{00000000-0005-0000-0000-0000AB030000}"/>
+    <cellStyle name="Heading 3 4" xfId="479" xr:uid="{00000000-0005-0000-0000-0000AC030000}"/>
+    <cellStyle name="Heading 3 5" xfId="480" xr:uid="{00000000-0005-0000-0000-0000AD030000}"/>
+    <cellStyle name="Heading 3 6" xfId="481" xr:uid="{00000000-0005-0000-0000-0000AE030000}"/>
+    <cellStyle name="Heading 3 7" xfId="482" xr:uid="{00000000-0005-0000-0000-0000AF030000}"/>
+    <cellStyle name="Heading 3 8" xfId="483" xr:uid="{00000000-0005-0000-0000-0000B0030000}"/>
+    <cellStyle name="Heading 3 9" xfId="484" xr:uid="{00000000-0005-0000-0000-0000B1030000}"/>
+    <cellStyle name="Heading 4 10" xfId="485" xr:uid="{00000000-0005-0000-0000-0000B2030000}"/>
+    <cellStyle name="Heading 4 11" xfId="486" xr:uid="{00000000-0005-0000-0000-0000B3030000}"/>
+    <cellStyle name="Heading 4 12" xfId="487" xr:uid="{00000000-0005-0000-0000-0000B4030000}"/>
+    <cellStyle name="Heading 4 13" xfId="488" xr:uid="{00000000-0005-0000-0000-0000B5030000}"/>
+    <cellStyle name="Heading 4 14" xfId="489" xr:uid="{00000000-0005-0000-0000-0000B6030000}"/>
+    <cellStyle name="Heading 4 15" xfId="490" xr:uid="{00000000-0005-0000-0000-0000B7030000}"/>
+    <cellStyle name="Heading 4 16" xfId="491" xr:uid="{00000000-0005-0000-0000-0000B8030000}"/>
+    <cellStyle name="Heading 4 2" xfId="492" xr:uid="{00000000-0005-0000-0000-0000B9030000}"/>
+    <cellStyle name="Heading 4 3" xfId="493" xr:uid="{00000000-0005-0000-0000-0000BA030000}"/>
+    <cellStyle name="Heading 4 4" xfId="494" xr:uid="{00000000-0005-0000-0000-0000BB030000}"/>
+    <cellStyle name="Heading 4 5" xfId="495" xr:uid="{00000000-0005-0000-0000-0000BC030000}"/>
+    <cellStyle name="Heading 4 6" xfId="496" xr:uid="{00000000-0005-0000-0000-0000BD030000}"/>
+    <cellStyle name="Heading 4 7" xfId="497" xr:uid="{00000000-0005-0000-0000-0000BE030000}"/>
+    <cellStyle name="Heading 4 8" xfId="498" xr:uid="{00000000-0005-0000-0000-0000BF030000}"/>
+    <cellStyle name="Heading 4 9" xfId="499" xr:uid="{00000000-0005-0000-0000-0000C0030000}"/>
+    <cellStyle name="Input 10" xfId="500" xr:uid="{00000000-0005-0000-0000-0000C1030000}"/>
+    <cellStyle name="Input 10 10" xfId="1251" xr:uid="{00000000-0005-0000-0000-0000C2030000}"/>
+    <cellStyle name="Input 10 11" xfId="1225" xr:uid="{00000000-0005-0000-0000-0000C3030000}"/>
+    <cellStyle name="Input 10 12" xfId="1302" xr:uid="{00000000-0005-0000-0000-0000C4030000}"/>
+    <cellStyle name="Input 10 13" xfId="1379" xr:uid="{00000000-0005-0000-0000-0000C5030000}"/>
+    <cellStyle name="Input 10 14" xfId="1455" xr:uid="{00000000-0005-0000-0000-0000C6030000}"/>
+    <cellStyle name="Input 10 15" xfId="1632" xr:uid="{00000000-0005-0000-0000-0000C7030000}"/>
+    <cellStyle name="Input 10 16" xfId="1606" xr:uid="{00000000-0005-0000-0000-0000C8030000}"/>
+    <cellStyle name="Input 10 17" xfId="1782" xr:uid="{00000000-0005-0000-0000-0000C9030000}"/>
+    <cellStyle name="Input 10 18" xfId="1756" xr:uid="{00000000-0005-0000-0000-0000CA030000}"/>
+    <cellStyle name="Input 10 19" xfId="1913" xr:uid="{00000000-0005-0000-0000-0000CB030000}"/>
+    <cellStyle name="Input 10 2" xfId="1013" xr:uid="{00000000-0005-0000-0000-0000CC030000}"/>
+    <cellStyle name="Input 10 20" xfId="1887" xr:uid="{00000000-0005-0000-0000-0000CD030000}"/>
+    <cellStyle name="Input 10 21" xfId="1949" xr:uid="{00000000-0005-0000-0000-0000CE030000}"/>
+    <cellStyle name="Input 10 22" xfId="2013" xr:uid="{00000000-0005-0000-0000-0000CF030000}"/>
+    <cellStyle name="Input 10 23" xfId="2074" xr:uid="{00000000-0005-0000-0000-0000D0030000}"/>
+    <cellStyle name="Input 10 24" xfId="2225" xr:uid="{00000000-0005-0000-0000-0000D1030000}"/>
+    <cellStyle name="Input 10 25" xfId="2199" xr:uid="{00000000-0005-0000-0000-0000D2030000}"/>
+    <cellStyle name="Input 10 26" xfId="2469" xr:uid="{00000000-0005-0000-0000-0000D3030000}"/>
+    <cellStyle name="Input 10 27" xfId="2320" xr:uid="{00000000-0005-0000-0000-0000D4030000}"/>
+    <cellStyle name="Input 10 28" xfId="2380" xr:uid="{00000000-0005-0000-0000-0000D5030000}"/>
+    <cellStyle name="Input 10 29" xfId="2443" xr:uid="{00000000-0005-0000-0000-0000D6030000}"/>
+    <cellStyle name="Input 10 3" xfId="768" xr:uid="{00000000-0005-0000-0000-0000D7030000}"/>
+    <cellStyle name="Input 10 30" xfId="2518" xr:uid="{00000000-0005-0000-0000-0000D8030000}"/>
+    <cellStyle name="Input 10 31" xfId="2561" xr:uid="{00000000-0005-0000-0000-0000D9030000}"/>
+    <cellStyle name="Input 10 32" xfId="2640" xr:uid="{00000000-0005-0000-0000-0000DA030000}"/>
+    <cellStyle name="Input 10 4" xfId="1045" xr:uid="{00000000-0005-0000-0000-0000DB030000}"/>
+    <cellStyle name="Input 10 5" xfId="741" xr:uid="{00000000-0005-0000-0000-0000DC030000}"/>
+    <cellStyle name="Input 10 6" xfId="1072" xr:uid="{00000000-0005-0000-0000-0000DD030000}"/>
+    <cellStyle name="Input 10 7" xfId="1180" xr:uid="{00000000-0005-0000-0000-0000DE030000}"/>
+    <cellStyle name="Input 10 8" xfId="1097" xr:uid="{00000000-0005-0000-0000-0000DF030000}"/>
+    <cellStyle name="Input 10 9" xfId="687" xr:uid="{00000000-0005-0000-0000-0000E0030000}"/>
+    <cellStyle name="Input 11" xfId="501" xr:uid="{00000000-0005-0000-0000-0000E1030000}"/>
+    <cellStyle name="Input 11 10" xfId="1169" xr:uid="{00000000-0005-0000-0000-0000E2030000}"/>
+    <cellStyle name="Input 11 11" xfId="1226" xr:uid="{00000000-0005-0000-0000-0000E3030000}"/>
+    <cellStyle name="Input 11 12" xfId="1303" xr:uid="{00000000-0005-0000-0000-0000E4030000}"/>
+    <cellStyle name="Input 11 13" xfId="1380" xr:uid="{00000000-0005-0000-0000-0000E5030000}"/>
+    <cellStyle name="Input 11 14" xfId="1471" xr:uid="{00000000-0005-0000-0000-0000E6030000}"/>
+    <cellStyle name="Input 11 15" xfId="1530" xr:uid="{00000000-0005-0000-0000-0000E7030000}"/>
+    <cellStyle name="Input 11 16" xfId="1622" xr:uid="{00000000-0005-0000-0000-0000E8030000}"/>
+    <cellStyle name="Input 11 17" xfId="1679" xr:uid="{00000000-0005-0000-0000-0000E9030000}"/>
+    <cellStyle name="Input 11 18" xfId="1772" xr:uid="{00000000-0005-0000-0000-0000EA030000}"/>
+    <cellStyle name="Input 11 19" xfId="1820" xr:uid="{00000000-0005-0000-0000-0000EB030000}"/>
+    <cellStyle name="Input 11 2" xfId="1014" xr:uid="{00000000-0005-0000-0000-0000EC030000}"/>
+    <cellStyle name="Input 11 20" xfId="1903" xr:uid="{00000000-0005-0000-0000-0000ED030000}"/>
+    <cellStyle name="Input 11 21" xfId="1950" xr:uid="{00000000-0005-0000-0000-0000EE030000}"/>
+    <cellStyle name="Input 11 22" xfId="2029" xr:uid="{00000000-0005-0000-0000-0000EF030000}"/>
+    <cellStyle name="Input 11 23" xfId="2090" xr:uid="{00000000-0005-0000-0000-0000F0030000}"/>
+    <cellStyle name="Input 11 24" xfId="2137" xr:uid="{00000000-0005-0000-0000-0000F1030000}"/>
+    <cellStyle name="Input 11 25" xfId="2215" xr:uid="{00000000-0005-0000-0000-0000F2030000}"/>
+    <cellStyle name="Input 11 26" xfId="2259" xr:uid="{00000000-0005-0000-0000-0000F3030000}"/>
+    <cellStyle name="Input 11 27" xfId="2336" xr:uid="{00000000-0005-0000-0000-0000F4030000}"/>
+    <cellStyle name="Input 11 28" xfId="2468" xr:uid="{00000000-0005-0000-0000-0000F5030000}"/>
+    <cellStyle name="Input 11 29" xfId="2459" xr:uid="{00000000-0005-0000-0000-0000F6030000}"/>
+    <cellStyle name="Input 11 3" xfId="767" xr:uid="{00000000-0005-0000-0000-0000F7030000}"/>
+    <cellStyle name="Input 11 30" xfId="2519" xr:uid="{00000000-0005-0000-0000-0000F8030000}"/>
+    <cellStyle name="Input 11 31" xfId="2562" xr:uid="{00000000-0005-0000-0000-0000F9030000}"/>
+    <cellStyle name="Input 11 32" xfId="2641" xr:uid="{00000000-0005-0000-0000-0000FA030000}"/>
+    <cellStyle name="Input 11 4" xfId="1046" xr:uid="{00000000-0005-0000-0000-0000FB030000}"/>
+    <cellStyle name="Input 11 5" xfId="740" xr:uid="{00000000-0005-0000-0000-0000FC030000}"/>
+    <cellStyle name="Input 11 6" xfId="1073" xr:uid="{00000000-0005-0000-0000-0000FD030000}"/>
+    <cellStyle name="Input 11 7" xfId="712" xr:uid="{00000000-0005-0000-0000-0000FE030000}"/>
+    <cellStyle name="Input 11 8" xfId="1098" xr:uid="{00000000-0005-0000-0000-0000FF030000}"/>
+    <cellStyle name="Input 11 9" xfId="1178" xr:uid="{00000000-0005-0000-0000-000000040000}"/>
+    <cellStyle name="Input 12" xfId="502" xr:uid="{00000000-0005-0000-0000-000001040000}"/>
+    <cellStyle name="Input 12 10" xfId="1170" xr:uid="{00000000-0005-0000-0000-000002040000}"/>
+    <cellStyle name="Input 12 11" xfId="1227" xr:uid="{00000000-0005-0000-0000-000003040000}"/>
+    <cellStyle name="Input 12 12" xfId="1304" xr:uid="{00000000-0005-0000-0000-000004040000}"/>
+    <cellStyle name="Input 12 13" xfId="1396" xr:uid="{00000000-0005-0000-0000-000005040000}"/>
+    <cellStyle name="Input 12 14" xfId="1472" xr:uid="{00000000-0005-0000-0000-000006040000}"/>
+    <cellStyle name="Input 12 15" xfId="1531" xr:uid="{00000000-0005-0000-0000-000007040000}"/>
+    <cellStyle name="Input 12 16" xfId="1623" xr:uid="{00000000-0005-0000-0000-000008040000}"/>
+    <cellStyle name="Input 12 17" xfId="1680" xr:uid="{00000000-0005-0000-0000-000009040000}"/>
+    <cellStyle name="Input 12 18" xfId="1773" xr:uid="{00000000-0005-0000-0000-00000A040000}"/>
+    <cellStyle name="Input 12 19" xfId="1821" xr:uid="{00000000-0005-0000-0000-00000B040000}"/>
+    <cellStyle name="Input 12 2" xfId="1015" xr:uid="{00000000-0005-0000-0000-00000C040000}"/>
+    <cellStyle name="Input 12 20" xfId="1904" xr:uid="{00000000-0005-0000-0000-00000D040000}"/>
+    <cellStyle name="Input 12 21" xfId="1951" xr:uid="{00000000-0005-0000-0000-00000E040000}"/>
+    <cellStyle name="Input 12 22" xfId="2030" xr:uid="{00000000-0005-0000-0000-00000F040000}"/>
+    <cellStyle name="Input 12 23" xfId="2091" xr:uid="{00000000-0005-0000-0000-000010040000}"/>
+    <cellStyle name="Input 12 24" xfId="2138" xr:uid="{00000000-0005-0000-0000-000011040000}"/>
+    <cellStyle name="Input 12 25" xfId="2216" xr:uid="{00000000-0005-0000-0000-000012040000}"/>
+    <cellStyle name="Input 12 26" xfId="2260" xr:uid="{00000000-0005-0000-0000-000013040000}"/>
+    <cellStyle name="Input 12 27" xfId="2337" xr:uid="{00000000-0005-0000-0000-000014040000}"/>
+    <cellStyle name="Input 12 28" xfId="2381" xr:uid="{00000000-0005-0000-0000-000015040000}"/>
+    <cellStyle name="Input 12 29" xfId="2460" xr:uid="{00000000-0005-0000-0000-000016040000}"/>
+    <cellStyle name="Input 12 3" xfId="766" xr:uid="{00000000-0005-0000-0000-000017040000}"/>
+    <cellStyle name="Input 12 30" xfId="2520" xr:uid="{00000000-0005-0000-0000-000018040000}"/>
+    <cellStyle name="Input 12 31" xfId="2747" xr:uid="{00000000-0005-0000-0000-000019040000}"/>
+    <cellStyle name="Input 12 32" xfId="2642" xr:uid="{00000000-0005-0000-0000-00001A040000}"/>
+    <cellStyle name="Input 12 4" xfId="1047" xr:uid="{00000000-0005-0000-0000-00001B040000}"/>
+    <cellStyle name="Input 12 5" xfId="739" xr:uid="{00000000-0005-0000-0000-00001C040000}"/>
+    <cellStyle name="Input 12 6" xfId="1074" xr:uid="{00000000-0005-0000-0000-00001D040000}"/>
+    <cellStyle name="Input 12 7" xfId="711" xr:uid="{00000000-0005-0000-0000-00001E040000}"/>
+    <cellStyle name="Input 12 8" xfId="1099" xr:uid="{00000000-0005-0000-0000-00001F040000}"/>
+    <cellStyle name="Input 12 9" xfId="686" xr:uid="{00000000-0005-0000-0000-000020040000}"/>
+    <cellStyle name="Input 13" xfId="503" xr:uid="{00000000-0005-0000-0000-000021040000}"/>
+    <cellStyle name="Input 13 10" xfId="1171" xr:uid="{00000000-0005-0000-0000-000022040000}"/>
+    <cellStyle name="Input 13 11" xfId="1228" xr:uid="{00000000-0005-0000-0000-000023040000}"/>
+    <cellStyle name="Input 13 12" xfId="1320" xr:uid="{00000000-0005-0000-0000-000024040000}"/>
+    <cellStyle name="Input 13 13" xfId="1397" xr:uid="{00000000-0005-0000-0000-000025040000}"/>
+    <cellStyle name="Input 13 14" xfId="1473" xr:uid="{00000000-0005-0000-0000-000026040000}"/>
+    <cellStyle name="Input 13 15" xfId="1547" xr:uid="{00000000-0005-0000-0000-000027040000}"/>
+    <cellStyle name="Input 13 16" xfId="1624" xr:uid="{00000000-0005-0000-0000-000028040000}"/>
+    <cellStyle name="Input 13 17" xfId="1696" xr:uid="{00000000-0005-0000-0000-000029040000}"/>
+    <cellStyle name="Input 13 18" xfId="1774" xr:uid="{00000000-0005-0000-0000-00002A040000}"/>
+    <cellStyle name="Input 13 19" xfId="1837" xr:uid="{00000000-0005-0000-0000-00002B040000}"/>
+    <cellStyle name="Input 13 2" xfId="1016" xr:uid="{00000000-0005-0000-0000-00002C040000}"/>
+    <cellStyle name="Input 13 20" xfId="1905" xr:uid="{00000000-0005-0000-0000-00002D040000}"/>
+    <cellStyle name="Input 13 21" xfId="1967" xr:uid="{00000000-0005-0000-0000-00002E040000}"/>
+    <cellStyle name="Input 13 22" xfId="2031" xr:uid="{00000000-0005-0000-0000-00002F040000}"/>
+    <cellStyle name="Input 13 23" xfId="2092" xr:uid="{00000000-0005-0000-0000-000030040000}"/>
+    <cellStyle name="Input 13 24" xfId="2154" xr:uid="{00000000-0005-0000-0000-000031040000}"/>
+    <cellStyle name="Input 13 25" xfId="2217" xr:uid="{00000000-0005-0000-0000-000032040000}"/>
+    <cellStyle name="Input 13 26" xfId="2276" xr:uid="{00000000-0005-0000-0000-000033040000}"/>
+    <cellStyle name="Input 13 27" xfId="2338" xr:uid="{00000000-0005-0000-0000-000034040000}"/>
+    <cellStyle name="Input 13 28" xfId="2397" xr:uid="{00000000-0005-0000-0000-000035040000}"/>
+    <cellStyle name="Input 13 29" xfId="2461" xr:uid="{00000000-0005-0000-0000-000036040000}"/>
+    <cellStyle name="Input 13 3" xfId="765" xr:uid="{00000000-0005-0000-0000-000037040000}"/>
+    <cellStyle name="Input 13 30" xfId="2502" xr:uid="{00000000-0005-0000-0000-000038040000}"/>
+    <cellStyle name="Input 13 31" xfId="2648" xr:uid="{00000000-0005-0000-0000-000039040000}"/>
+    <cellStyle name="Input 13 32" xfId="2624" xr:uid="{00000000-0005-0000-0000-00003A040000}"/>
+    <cellStyle name="Input 13 4" xfId="1048" xr:uid="{00000000-0005-0000-0000-00003B040000}"/>
+    <cellStyle name="Input 13 5" xfId="738" xr:uid="{00000000-0005-0000-0000-00003C040000}"/>
+    <cellStyle name="Input 13 6" xfId="1075" xr:uid="{00000000-0005-0000-0000-00003D040000}"/>
+    <cellStyle name="Input 13 7" xfId="710" xr:uid="{00000000-0005-0000-0000-00003E040000}"/>
+    <cellStyle name="Input 13 8" xfId="1100" xr:uid="{00000000-0005-0000-0000-00003F040000}"/>
+    <cellStyle name="Input 13 9" xfId="685" xr:uid="{00000000-0005-0000-0000-000040040000}"/>
+    <cellStyle name="Input 14" xfId="504" xr:uid="{00000000-0005-0000-0000-000041040000}"/>
+    <cellStyle name="Input 14 10" xfId="1172" xr:uid="{00000000-0005-0000-0000-000042040000}"/>
+    <cellStyle name="Input 14 11" xfId="1244" xr:uid="{00000000-0005-0000-0000-000043040000}"/>
+    <cellStyle name="Input 14 12" xfId="1321" xr:uid="{00000000-0005-0000-0000-000044040000}"/>
+    <cellStyle name="Input 14 13" xfId="1398" xr:uid="{00000000-0005-0000-0000-000045040000}"/>
+    <cellStyle name="Input 14 14" xfId="1474" xr:uid="{00000000-0005-0000-0000-000046040000}"/>
+    <cellStyle name="Input 14 15" xfId="1548" xr:uid="{00000000-0005-0000-0000-000047040000}"/>
+    <cellStyle name="Input 14 16" xfId="1625" xr:uid="{00000000-0005-0000-0000-000048040000}"/>
+    <cellStyle name="Input 14 17" xfId="1697" xr:uid="{00000000-0005-0000-0000-000049040000}"/>
+    <cellStyle name="Input 14 18" xfId="1775" xr:uid="{00000000-0005-0000-0000-00004A040000}"/>
+    <cellStyle name="Input 14 19" xfId="1838" xr:uid="{00000000-0005-0000-0000-00004B040000}"/>
+    <cellStyle name="Input 14 2" xfId="1017" xr:uid="{00000000-0005-0000-0000-00004C040000}"/>
+    <cellStyle name="Input 14 20" xfId="1906" xr:uid="{00000000-0005-0000-0000-00004D040000}"/>
+    <cellStyle name="Input 14 21" xfId="1968" xr:uid="{00000000-0005-0000-0000-00004E040000}"/>
+    <cellStyle name="Input 14 22" xfId="2032" xr:uid="{00000000-0005-0000-0000-00004F040000}"/>
+    <cellStyle name="Input 14 23" xfId="2093" xr:uid="{00000000-0005-0000-0000-000050040000}"/>
+    <cellStyle name="Input 14 24" xfId="2155" xr:uid="{00000000-0005-0000-0000-000051040000}"/>
+    <cellStyle name="Input 14 25" xfId="2218" xr:uid="{00000000-0005-0000-0000-000052040000}"/>
+    <cellStyle name="Input 14 26" xfId="2277" xr:uid="{00000000-0005-0000-0000-000053040000}"/>
+    <cellStyle name="Input 14 27" xfId="2339" xr:uid="{00000000-0005-0000-0000-000054040000}"/>
+    <cellStyle name="Input 14 28" xfId="2398" xr:uid="{00000000-0005-0000-0000-000055040000}"/>
+    <cellStyle name="Input 14 29" xfId="2462" xr:uid="{00000000-0005-0000-0000-000056040000}"/>
+    <cellStyle name="Input 14 3" xfId="764" xr:uid="{00000000-0005-0000-0000-000057040000}"/>
+    <cellStyle name="Input 14 30" xfId="2521" xr:uid="{00000000-0005-0000-0000-000058040000}"/>
+    <cellStyle name="Input 14 31" xfId="2564" xr:uid="{00000000-0005-0000-0000-000059040000}"/>
+    <cellStyle name="Input 14 32" xfId="2643" xr:uid="{00000000-0005-0000-0000-00005A040000}"/>
+    <cellStyle name="Input 14 4" xfId="1049" xr:uid="{00000000-0005-0000-0000-00005B040000}"/>
+    <cellStyle name="Input 14 5" xfId="737" xr:uid="{00000000-0005-0000-0000-00005C040000}"/>
+    <cellStyle name="Input 14 6" xfId="1076" xr:uid="{00000000-0005-0000-0000-00005D040000}"/>
+    <cellStyle name="Input 14 7" xfId="709" xr:uid="{00000000-0005-0000-0000-00005E040000}"/>
+    <cellStyle name="Input 14 8" xfId="1101" xr:uid="{00000000-0005-0000-0000-00005F040000}"/>
+    <cellStyle name="Input 14 9" xfId="684" xr:uid="{00000000-0005-0000-0000-000060040000}"/>
+    <cellStyle name="Input 15" xfId="505" xr:uid="{00000000-0005-0000-0000-000061040000}"/>
+    <cellStyle name="Input 15 10" xfId="1173" xr:uid="{00000000-0005-0000-0000-000062040000}"/>
+    <cellStyle name="Input 15 11" xfId="1245" xr:uid="{00000000-0005-0000-0000-000063040000}"/>
+    <cellStyle name="Input 15 12" xfId="1322" xr:uid="{00000000-0005-0000-0000-000064040000}"/>
+    <cellStyle name="Input 15 13" xfId="1399" xr:uid="{00000000-0005-0000-0000-000065040000}"/>
+    <cellStyle name="Input 15 14" xfId="1475" xr:uid="{00000000-0005-0000-0000-000066040000}"/>
+    <cellStyle name="Input 15 15" xfId="1549" xr:uid="{00000000-0005-0000-0000-000067040000}"/>
+    <cellStyle name="Input 15 16" xfId="1626" xr:uid="{00000000-0005-0000-0000-000068040000}"/>
+    <cellStyle name="Input 15 17" xfId="1698" xr:uid="{00000000-0005-0000-0000-000069040000}"/>
+    <cellStyle name="Input 15 18" xfId="1776" xr:uid="{00000000-0005-0000-0000-00006A040000}"/>
+    <cellStyle name="Input 15 19" xfId="1839" xr:uid="{00000000-0005-0000-0000-00006B040000}"/>
+    <cellStyle name="Input 15 2" xfId="1018" xr:uid="{00000000-0005-0000-0000-00006C040000}"/>
+    <cellStyle name="Input 15 20" xfId="1907" xr:uid="{00000000-0005-0000-0000-00006D040000}"/>
+    <cellStyle name="Input 15 21" xfId="1969" xr:uid="{00000000-0005-0000-0000-00006E040000}"/>
+    <cellStyle name="Input 15 22" xfId="2033" xr:uid="{00000000-0005-0000-0000-00006F040000}"/>
+    <cellStyle name="Input 15 23" xfId="2094" xr:uid="{00000000-0005-0000-0000-000070040000}"/>
+    <cellStyle name="Input 15 24" xfId="2156" xr:uid="{00000000-0005-0000-0000-000071040000}"/>
+    <cellStyle name="Input 15 25" xfId="2219" xr:uid="{00000000-0005-0000-0000-000072040000}"/>
+    <cellStyle name="Input 15 26" xfId="2278" xr:uid="{00000000-0005-0000-0000-000073040000}"/>
+    <cellStyle name="Input 15 27" xfId="2340" xr:uid="{00000000-0005-0000-0000-000074040000}"/>
+    <cellStyle name="Input 15 28" xfId="2399" xr:uid="{00000000-0005-0000-0000-000075040000}"/>
+    <cellStyle name="Input 15 29" xfId="2463" xr:uid="{00000000-0005-0000-0000-000076040000}"/>
+    <cellStyle name="Input 15 3" xfId="763" xr:uid="{00000000-0005-0000-0000-000077040000}"/>
+    <cellStyle name="Input 15 30" xfId="2522" xr:uid="{00000000-0005-0000-0000-000078040000}"/>
+    <cellStyle name="Input 15 31" xfId="2565" xr:uid="{00000000-0005-0000-0000-000079040000}"/>
+    <cellStyle name="Input 15 32" xfId="2644" xr:uid="{00000000-0005-0000-0000-00007A040000}"/>
+    <cellStyle name="Input 15 4" xfId="1050" xr:uid="{00000000-0005-0000-0000-00007B040000}"/>
+    <cellStyle name="Input 15 5" xfId="736" xr:uid="{00000000-0005-0000-0000-00007C040000}"/>
+    <cellStyle name="Input 15 6" xfId="1068" xr:uid="{00000000-0005-0000-0000-00007D040000}"/>
+    <cellStyle name="Input 15 7" xfId="708" xr:uid="{00000000-0005-0000-0000-00007E040000}"/>
+    <cellStyle name="Input 15 8" xfId="1102" xr:uid="{00000000-0005-0000-0000-00007F040000}"/>
+    <cellStyle name="Input 15 9" xfId="683" xr:uid="{00000000-0005-0000-0000-000080040000}"/>
+    <cellStyle name="Input 16" xfId="506" xr:uid="{00000000-0005-0000-0000-000081040000}"/>
+    <cellStyle name="Input 16 10" xfId="1174" xr:uid="{00000000-0005-0000-0000-000082040000}"/>
+    <cellStyle name="Input 16 11" xfId="1246" xr:uid="{00000000-0005-0000-0000-000083040000}"/>
+    <cellStyle name="Input 16 12" xfId="1323" xr:uid="{00000000-0005-0000-0000-000084040000}"/>
+    <cellStyle name="Input 16 13" xfId="1400" xr:uid="{00000000-0005-0000-0000-000085040000}"/>
+    <cellStyle name="Input 16 14" xfId="1454" xr:uid="{00000000-0005-0000-0000-000086040000}"/>
+    <cellStyle name="Input 16 15" xfId="1550" xr:uid="{00000000-0005-0000-0000-000087040000}"/>
+    <cellStyle name="Input 16 16" xfId="1604" xr:uid="{00000000-0005-0000-0000-000088040000}"/>
+    <cellStyle name="Input 16 17" xfId="1699" xr:uid="{00000000-0005-0000-0000-000089040000}"/>
+    <cellStyle name="Input 16 18" xfId="1777" xr:uid="{00000000-0005-0000-0000-00008A040000}"/>
+    <cellStyle name="Input 16 19" xfId="1840" xr:uid="{00000000-0005-0000-0000-00008B040000}"/>
+    <cellStyle name="Input 16 2" xfId="1019" xr:uid="{00000000-0005-0000-0000-00008C040000}"/>
+    <cellStyle name="Input 16 20" xfId="1908" xr:uid="{00000000-0005-0000-0000-00008D040000}"/>
+    <cellStyle name="Input 16 21" xfId="1970" xr:uid="{00000000-0005-0000-0000-00008E040000}"/>
+    <cellStyle name="Input 16 22" xfId="2012" xr:uid="{00000000-0005-0000-0000-00008F040000}"/>
+    <cellStyle name="Input 16 23" xfId="2073" xr:uid="{00000000-0005-0000-0000-000090040000}"/>
+    <cellStyle name="Input 16 24" xfId="2157" xr:uid="{00000000-0005-0000-0000-000091040000}"/>
+    <cellStyle name="Input 16 25" xfId="2198" xr:uid="{00000000-0005-0000-0000-000092040000}"/>
+    <cellStyle name="Input 16 26" xfId="2279" xr:uid="{00000000-0005-0000-0000-000093040000}"/>
+    <cellStyle name="Input 16 27" xfId="2341" xr:uid="{00000000-0005-0000-0000-000094040000}"/>
+    <cellStyle name="Input 16 28" xfId="2400" xr:uid="{00000000-0005-0000-0000-000095040000}"/>
+    <cellStyle name="Input 16 29" xfId="2464" xr:uid="{00000000-0005-0000-0000-000096040000}"/>
+    <cellStyle name="Input 16 3" xfId="762" xr:uid="{00000000-0005-0000-0000-000097040000}"/>
+    <cellStyle name="Input 16 30" xfId="2523" xr:uid="{00000000-0005-0000-0000-000098040000}"/>
+    <cellStyle name="Input 16 31" xfId="2581" xr:uid="{00000000-0005-0000-0000-000099040000}"/>
+    <cellStyle name="Input 16 32" xfId="2645" xr:uid="{00000000-0005-0000-0000-00009A040000}"/>
+    <cellStyle name="Input 16 4" xfId="1051" xr:uid="{00000000-0005-0000-0000-00009B040000}"/>
+    <cellStyle name="Input 16 5" xfId="735" xr:uid="{00000000-0005-0000-0000-00009C040000}"/>
+    <cellStyle name="Input 16 6" xfId="1077" xr:uid="{00000000-0005-0000-0000-00009D040000}"/>
+    <cellStyle name="Input 16 7" xfId="707" xr:uid="{00000000-0005-0000-0000-00009E040000}"/>
+    <cellStyle name="Input 16 8" xfId="1103" xr:uid="{00000000-0005-0000-0000-00009F040000}"/>
+    <cellStyle name="Input 16 9" xfId="682" xr:uid="{00000000-0005-0000-0000-0000A0040000}"/>
+    <cellStyle name="Input 2" xfId="507" xr:uid="{00000000-0005-0000-0000-0000A1040000}"/>
+    <cellStyle name="Input 2 10" xfId="1152" xr:uid="{00000000-0005-0000-0000-0000A2040000}"/>
+    <cellStyle name="Input 2 11" xfId="1224" xr:uid="{00000000-0005-0000-0000-0000A3040000}"/>
+    <cellStyle name="Input 2 12" xfId="1301" xr:uid="{00000000-0005-0000-0000-0000A4040000}"/>
+    <cellStyle name="Input 2 13" xfId="1378" xr:uid="{00000000-0005-0000-0000-0000A5040000}"/>
+    <cellStyle name="Input 2 14" xfId="1476" xr:uid="{00000000-0005-0000-0000-0000A6040000}"/>
+    <cellStyle name="Input 2 15" xfId="1551" xr:uid="{00000000-0005-0000-0000-0000A7040000}"/>
+    <cellStyle name="Input 2 16" xfId="1627" xr:uid="{00000000-0005-0000-0000-0000A8040000}"/>
+    <cellStyle name="Input 2 17" xfId="1700" xr:uid="{00000000-0005-0000-0000-0000A9040000}"/>
+    <cellStyle name="Input 2 18" xfId="1847" xr:uid="{00000000-0005-0000-0000-0000AA040000}"/>
+    <cellStyle name="Input 2 19" xfId="1819" xr:uid="{00000000-0005-0000-0000-0000AB040000}"/>
+    <cellStyle name="Input 2 2" xfId="1020" xr:uid="{00000000-0005-0000-0000-0000AC040000}"/>
+    <cellStyle name="Input 2 20" xfId="1886" xr:uid="{00000000-0005-0000-0000-0000AD040000}"/>
+    <cellStyle name="Input 2 21" xfId="1948" xr:uid="{00000000-0005-0000-0000-0000AE040000}"/>
+    <cellStyle name="Input 2 22" xfId="2034" xr:uid="{00000000-0005-0000-0000-0000AF040000}"/>
+    <cellStyle name="Input 2 23" xfId="2095" xr:uid="{00000000-0005-0000-0000-0000B0040000}"/>
+    <cellStyle name="Input 2 24" xfId="2158" xr:uid="{00000000-0005-0000-0000-0000B1040000}"/>
+    <cellStyle name="Input 2 25" xfId="2220" xr:uid="{00000000-0005-0000-0000-0000B2040000}"/>
+    <cellStyle name="Input 2 26" xfId="2280" xr:uid="{00000000-0005-0000-0000-0000B3040000}"/>
+    <cellStyle name="Input 2 27" xfId="2407" xr:uid="{00000000-0005-0000-0000-0000B4040000}"/>
+    <cellStyle name="Input 2 28" xfId="2379" xr:uid="{00000000-0005-0000-0000-0000B5040000}"/>
+    <cellStyle name="Input 2 29" xfId="2442" xr:uid="{00000000-0005-0000-0000-0000B6040000}"/>
+    <cellStyle name="Input 2 3" xfId="761" xr:uid="{00000000-0005-0000-0000-0000B7040000}"/>
+    <cellStyle name="Input 2 30" xfId="2524" xr:uid="{00000000-0005-0000-0000-0000B8040000}"/>
+    <cellStyle name="Input 2 31" xfId="2582" xr:uid="{00000000-0005-0000-0000-0000B9040000}"/>
+    <cellStyle name="Input 2 32" xfId="2646" xr:uid="{00000000-0005-0000-0000-0000BA040000}"/>
+    <cellStyle name="Input 2 4" xfId="1052" xr:uid="{00000000-0005-0000-0000-0000BB040000}"/>
+    <cellStyle name="Input 2 5" xfId="734" xr:uid="{00000000-0005-0000-0000-0000BC040000}"/>
+    <cellStyle name="Input 2 6" xfId="1078" xr:uid="{00000000-0005-0000-0000-0000BD040000}"/>
+    <cellStyle name="Input 2 7" xfId="706" xr:uid="{00000000-0005-0000-0000-0000BE040000}"/>
+    <cellStyle name="Input 2 8" xfId="1104" xr:uid="{00000000-0005-0000-0000-0000BF040000}"/>
+    <cellStyle name="Input 2 9" xfId="689" xr:uid="{00000000-0005-0000-0000-0000C0040000}"/>
+    <cellStyle name="Input 3" xfId="508" xr:uid="{00000000-0005-0000-0000-0000C1040000}"/>
+    <cellStyle name="Input 3 10" xfId="1175" xr:uid="{00000000-0005-0000-0000-0000C2040000}"/>
+    <cellStyle name="Input 3 11" xfId="1247" xr:uid="{00000000-0005-0000-0000-0000C3040000}"/>
+    <cellStyle name="Input 3 12" xfId="1324" xr:uid="{00000000-0005-0000-0000-0000C4040000}"/>
+    <cellStyle name="Input 3 13" xfId="1401" xr:uid="{00000000-0005-0000-0000-0000C5040000}"/>
+    <cellStyle name="Input 3 14" xfId="1477" xr:uid="{00000000-0005-0000-0000-0000C6040000}"/>
+    <cellStyle name="Input 3 15" xfId="1529" xr:uid="{00000000-0005-0000-0000-0000C7040000}"/>
+    <cellStyle name="Input 3 16" xfId="1628" xr:uid="{00000000-0005-0000-0000-0000C8040000}"/>
+    <cellStyle name="Input 3 17" xfId="1678" xr:uid="{00000000-0005-0000-0000-0000C9040000}"/>
+    <cellStyle name="Input 3 18" xfId="1778" xr:uid="{00000000-0005-0000-0000-0000CA040000}"/>
+    <cellStyle name="Input 3 19" xfId="1841" xr:uid="{00000000-0005-0000-0000-0000CB040000}"/>
+    <cellStyle name="Input 3 2" xfId="1021" xr:uid="{00000000-0005-0000-0000-0000CC040000}"/>
+    <cellStyle name="Input 3 20" xfId="1909" xr:uid="{00000000-0005-0000-0000-0000CD040000}"/>
+    <cellStyle name="Input 3 21" xfId="1971" xr:uid="{00000000-0005-0000-0000-0000CE040000}"/>
+    <cellStyle name="Input 3 22" xfId="2035" xr:uid="{00000000-0005-0000-0000-0000CF040000}"/>
+    <cellStyle name="Input 3 23" xfId="2096" xr:uid="{00000000-0005-0000-0000-0000D0040000}"/>
+    <cellStyle name="Input 3 24" xfId="2136" xr:uid="{00000000-0005-0000-0000-0000D1040000}"/>
+    <cellStyle name="Input 3 25" xfId="2221" xr:uid="{00000000-0005-0000-0000-0000D2040000}"/>
+    <cellStyle name="Input 3 26" xfId="2281" xr:uid="{00000000-0005-0000-0000-0000D3040000}"/>
+    <cellStyle name="Input 3 27" xfId="2342" xr:uid="{00000000-0005-0000-0000-0000D4040000}"/>
+    <cellStyle name="Input 3 28" xfId="2401" xr:uid="{00000000-0005-0000-0000-0000D5040000}"/>
+    <cellStyle name="Input 3 29" xfId="2465" xr:uid="{00000000-0005-0000-0000-0000D6040000}"/>
+    <cellStyle name="Input 3 3" xfId="760" xr:uid="{00000000-0005-0000-0000-0000D7040000}"/>
+    <cellStyle name="Input 3 30" xfId="2525" xr:uid="{00000000-0005-0000-0000-0000D8040000}"/>
+    <cellStyle name="Input 3 31" xfId="2583" xr:uid="{00000000-0005-0000-0000-0000D9040000}"/>
+    <cellStyle name="Input 3 32" xfId="2647" xr:uid="{00000000-0005-0000-0000-0000DA040000}"/>
+    <cellStyle name="Input 3 4" xfId="1053" xr:uid="{00000000-0005-0000-0000-0000DB040000}"/>
+    <cellStyle name="Input 3 5" xfId="733" xr:uid="{00000000-0005-0000-0000-0000DC040000}"/>
+    <cellStyle name="Input 3 6" xfId="1079" xr:uid="{00000000-0005-0000-0000-0000DD040000}"/>
+    <cellStyle name="Input 3 7" xfId="705" xr:uid="{00000000-0005-0000-0000-0000DE040000}"/>
+    <cellStyle name="Input 3 8" xfId="1096" xr:uid="{00000000-0005-0000-0000-0000DF040000}"/>
+    <cellStyle name="Input 3 9" xfId="681" xr:uid="{00000000-0005-0000-0000-0000E0040000}"/>
+    <cellStyle name="Input 4" xfId="509" xr:uid="{00000000-0005-0000-0000-0000E1040000}"/>
+    <cellStyle name="Input 4 10" xfId="1176" xr:uid="{00000000-0005-0000-0000-0000E2040000}"/>
+    <cellStyle name="Input 4 11" xfId="1248" xr:uid="{00000000-0005-0000-0000-0000E3040000}"/>
+    <cellStyle name="Input 4 12" xfId="1325" xr:uid="{00000000-0005-0000-0000-0000E4040000}"/>
+    <cellStyle name="Input 4 13" xfId="1402" xr:uid="{00000000-0005-0000-0000-0000E5040000}"/>
+    <cellStyle name="Input 4 14" xfId="1478" xr:uid="{00000000-0005-0000-0000-0000E6040000}"/>
+    <cellStyle name="Input 4 15" xfId="1552" xr:uid="{00000000-0005-0000-0000-0000E7040000}"/>
+    <cellStyle name="Input 4 16" xfId="1629" xr:uid="{00000000-0005-0000-0000-0000E8040000}"/>
+    <cellStyle name="Input 4 17" xfId="1701" xr:uid="{00000000-0005-0000-0000-0000E9040000}"/>
+    <cellStyle name="Input 4 18" xfId="1779" xr:uid="{00000000-0005-0000-0000-0000EA040000}"/>
+    <cellStyle name="Input 4 19" xfId="1842" xr:uid="{00000000-0005-0000-0000-0000EB040000}"/>
+    <cellStyle name="Input 4 2" xfId="1022" xr:uid="{00000000-0005-0000-0000-0000EC040000}"/>
+    <cellStyle name="Input 4 20" xfId="1910" xr:uid="{00000000-0005-0000-0000-0000ED040000}"/>
+    <cellStyle name="Input 4 21" xfId="1972" xr:uid="{00000000-0005-0000-0000-0000EE040000}"/>
+    <cellStyle name="Input 4 22" xfId="2036" xr:uid="{00000000-0005-0000-0000-0000EF040000}"/>
+    <cellStyle name="Input 4 23" xfId="2097" xr:uid="{00000000-0005-0000-0000-0000F0040000}"/>
+    <cellStyle name="Input 4 24" xfId="2159" xr:uid="{00000000-0005-0000-0000-0000F1040000}"/>
+    <cellStyle name="Input 4 25" xfId="2222" xr:uid="{00000000-0005-0000-0000-0000F2040000}"/>
+    <cellStyle name="Input 4 26" xfId="2346" xr:uid="{00000000-0005-0000-0000-0000F3040000}"/>
+    <cellStyle name="Input 4 27" xfId="2343" xr:uid="{00000000-0005-0000-0000-0000F4040000}"/>
+    <cellStyle name="Input 4 28" xfId="2402" xr:uid="{00000000-0005-0000-0000-0000F5040000}"/>
+    <cellStyle name="Input 4 29" xfId="2466" xr:uid="{00000000-0005-0000-0000-0000F6040000}"/>
+    <cellStyle name="Input 4 3" xfId="759" xr:uid="{00000000-0005-0000-0000-0000F7040000}"/>
+    <cellStyle name="Input 4 30" xfId="2620" xr:uid="{00000000-0005-0000-0000-0000F8040000}"/>
+    <cellStyle name="Input 4 31" xfId="2584" xr:uid="{00000000-0005-0000-0000-0000F9040000}"/>
+    <cellStyle name="Input 4 32" xfId="2727" xr:uid="{00000000-0005-0000-0000-0000FA040000}"/>
+    <cellStyle name="Input 4 4" xfId="1054" xr:uid="{00000000-0005-0000-0000-0000FB040000}"/>
+    <cellStyle name="Input 4 5" xfId="732" xr:uid="{00000000-0005-0000-0000-0000FC040000}"/>
+    <cellStyle name="Input 4 6" xfId="1080" xr:uid="{00000000-0005-0000-0000-0000FD040000}"/>
+    <cellStyle name="Input 4 7" xfId="713" xr:uid="{00000000-0005-0000-0000-0000FE040000}"/>
+    <cellStyle name="Input 4 8" xfId="1105" xr:uid="{00000000-0005-0000-0000-0000FF040000}"/>
+    <cellStyle name="Input 4 9" xfId="680" xr:uid="{00000000-0005-0000-0000-000000050000}"/>
+    <cellStyle name="Input 5" xfId="510" xr:uid="{00000000-0005-0000-0000-000001050000}"/>
+    <cellStyle name="Input 5 10" xfId="1177" xr:uid="{00000000-0005-0000-0000-000002050000}"/>
+    <cellStyle name="Input 5 11" xfId="1249" xr:uid="{00000000-0005-0000-0000-000003050000}"/>
+    <cellStyle name="Input 5 12" xfId="1326" xr:uid="{00000000-0005-0000-0000-000004050000}"/>
+    <cellStyle name="Input 5 13" xfId="1403" xr:uid="{00000000-0005-0000-0000-000005050000}"/>
+    <cellStyle name="Input 5 14" xfId="1479" xr:uid="{00000000-0005-0000-0000-000006050000}"/>
+    <cellStyle name="Input 5 15" xfId="1553" xr:uid="{00000000-0005-0000-0000-000007050000}"/>
+    <cellStyle name="Input 5 16" xfId="1630" xr:uid="{00000000-0005-0000-0000-000008050000}"/>
+    <cellStyle name="Input 5 17" xfId="1702" xr:uid="{00000000-0005-0000-0000-000009050000}"/>
+    <cellStyle name="Input 5 18" xfId="1780" xr:uid="{00000000-0005-0000-0000-00000A050000}"/>
+    <cellStyle name="Input 5 19" xfId="1843" xr:uid="{00000000-0005-0000-0000-00000B050000}"/>
+    <cellStyle name="Input 5 2" xfId="1023" xr:uid="{00000000-0005-0000-0000-00000C050000}"/>
+    <cellStyle name="Input 5 20" xfId="1911" xr:uid="{00000000-0005-0000-0000-00000D050000}"/>
+    <cellStyle name="Input 5 21" xfId="1973" xr:uid="{00000000-0005-0000-0000-00000E050000}"/>
+    <cellStyle name="Input 5 22" xfId="2037" xr:uid="{00000000-0005-0000-0000-00000F050000}"/>
+    <cellStyle name="Input 5 23" xfId="2098" xr:uid="{00000000-0005-0000-0000-000010050000}"/>
+    <cellStyle name="Input 5 24" xfId="2160" xr:uid="{00000000-0005-0000-0000-000011050000}"/>
+    <cellStyle name="Input 5 25" xfId="2223" xr:uid="{00000000-0005-0000-0000-000012050000}"/>
+    <cellStyle name="Input 5 26" xfId="2282" xr:uid="{00000000-0005-0000-0000-000013050000}"/>
+    <cellStyle name="Input 5 27" xfId="2344" xr:uid="{00000000-0005-0000-0000-000014050000}"/>
+    <cellStyle name="Input 5 28" xfId="2403" xr:uid="{00000000-0005-0000-0000-000015050000}"/>
+    <cellStyle name="Input 5 29" xfId="2467" xr:uid="{00000000-0005-0000-0000-000016050000}"/>
+    <cellStyle name="Input 5 3" xfId="758" xr:uid="{00000000-0005-0000-0000-000017050000}"/>
+    <cellStyle name="Input 5 30" xfId="2621" xr:uid="{00000000-0005-0000-0000-000018050000}"/>
+    <cellStyle name="Input 5 31" xfId="2585" xr:uid="{00000000-0005-0000-0000-000019050000}"/>
+    <cellStyle name="Input 5 32" xfId="2728" xr:uid="{00000000-0005-0000-0000-00001A050000}"/>
+    <cellStyle name="Input 5 4" xfId="1055" xr:uid="{00000000-0005-0000-0000-00001B050000}"/>
+    <cellStyle name="Input 5 5" xfId="731" xr:uid="{00000000-0005-0000-0000-00001C050000}"/>
+    <cellStyle name="Input 5 6" xfId="1081" xr:uid="{00000000-0005-0000-0000-00001D050000}"/>
+    <cellStyle name="Input 5 7" xfId="704" xr:uid="{00000000-0005-0000-0000-00001E050000}"/>
+    <cellStyle name="Input 5 8" xfId="1106" xr:uid="{00000000-0005-0000-0000-00001F050000}"/>
+    <cellStyle name="Input 5 9" xfId="679" xr:uid="{00000000-0005-0000-0000-000020050000}"/>
+    <cellStyle name="Input 6" xfId="511" xr:uid="{00000000-0005-0000-0000-000021050000}"/>
+    <cellStyle name="Input 6 10" xfId="1256" xr:uid="{00000000-0005-0000-0000-000022050000}"/>
+    <cellStyle name="Input 6 11" xfId="1250" xr:uid="{00000000-0005-0000-0000-000023050000}"/>
+    <cellStyle name="Input 6 12" xfId="1327" xr:uid="{00000000-0005-0000-0000-000024050000}"/>
+    <cellStyle name="Input 6 13" xfId="1404" xr:uid="{00000000-0005-0000-0000-000025050000}"/>
+    <cellStyle name="Input 6 14" xfId="1480" xr:uid="{00000000-0005-0000-0000-000026050000}"/>
+    <cellStyle name="Input 6 15" xfId="1554" xr:uid="{00000000-0005-0000-0000-000027050000}"/>
+    <cellStyle name="Input 6 16" xfId="1631" xr:uid="{00000000-0005-0000-0000-000028050000}"/>
+    <cellStyle name="Input 6 17" xfId="1703" xr:uid="{00000000-0005-0000-0000-000029050000}"/>
+    <cellStyle name="Input 6 18" xfId="1781" xr:uid="{00000000-0005-0000-0000-00002A050000}"/>
+    <cellStyle name="Input 6 19" xfId="1844" xr:uid="{00000000-0005-0000-0000-00002B050000}"/>
+    <cellStyle name="Input 6 2" xfId="1024" xr:uid="{00000000-0005-0000-0000-00002C050000}"/>
+    <cellStyle name="Input 6 20" xfId="1912" xr:uid="{00000000-0005-0000-0000-00002D050000}"/>
+    <cellStyle name="Input 6 21" xfId="1974" xr:uid="{00000000-0005-0000-0000-00002E050000}"/>
+    <cellStyle name="Input 6 22" xfId="2038" xr:uid="{00000000-0005-0000-0000-00002F050000}"/>
+    <cellStyle name="Input 6 23" xfId="2099" xr:uid="{00000000-0005-0000-0000-000030050000}"/>
+    <cellStyle name="Input 6 24" xfId="2161" xr:uid="{00000000-0005-0000-0000-000031050000}"/>
+    <cellStyle name="Input 6 25" xfId="2224" xr:uid="{00000000-0005-0000-0000-000032050000}"/>
+    <cellStyle name="Input 6 26" xfId="2283" xr:uid="{00000000-0005-0000-0000-000033050000}"/>
+    <cellStyle name="Input 6 27" xfId="2345" xr:uid="{00000000-0005-0000-0000-000034050000}"/>
+    <cellStyle name="Input 6 28" xfId="2404" xr:uid="{00000000-0005-0000-0000-000035050000}"/>
+    <cellStyle name="Input 6 29" xfId="2526" xr:uid="{00000000-0005-0000-0000-000036050000}"/>
+    <cellStyle name="Input 6 3" xfId="757" xr:uid="{00000000-0005-0000-0000-000037050000}"/>
+    <cellStyle name="Input 6 30" xfId="2622" xr:uid="{00000000-0005-0000-0000-000038050000}"/>
+    <cellStyle name="Input 6 31" xfId="2563" xr:uid="{00000000-0005-0000-0000-000039050000}"/>
+    <cellStyle name="Input 6 32" xfId="2729" xr:uid="{00000000-0005-0000-0000-00003A050000}"/>
+    <cellStyle name="Input 6 4" xfId="1056" xr:uid="{00000000-0005-0000-0000-00003B050000}"/>
+    <cellStyle name="Input 6 5" xfId="730" xr:uid="{00000000-0005-0000-0000-00003C050000}"/>
+    <cellStyle name="Input 6 6" xfId="1082" xr:uid="{00000000-0005-0000-0000-00003D050000}"/>
+    <cellStyle name="Input 6 7" xfId="703" xr:uid="{00000000-0005-0000-0000-00003E050000}"/>
+    <cellStyle name="Input 6 8" xfId="1138" xr:uid="{00000000-0005-0000-0000-00003F050000}"/>
+    <cellStyle name="Input 6 9" xfId="678" xr:uid="{00000000-0005-0000-0000-000040050000}"/>
+    <cellStyle name="Input 7" xfId="512" xr:uid="{00000000-0005-0000-0000-000041050000}"/>
+    <cellStyle name="Input 7 10" xfId="1257" xr:uid="{00000000-0005-0000-0000-000042050000}"/>
+    <cellStyle name="Input 7 11" xfId="1334" xr:uid="{00000000-0005-0000-0000-000043050000}"/>
+    <cellStyle name="Input 7 12" xfId="1328" xr:uid="{00000000-0005-0000-0000-000044050000}"/>
+    <cellStyle name="Input 7 13" xfId="1405" xr:uid="{00000000-0005-0000-0000-000045050000}"/>
+    <cellStyle name="Input 7 14" xfId="1593" xr:uid="{00000000-0005-0000-0000-000046050000}"/>
+    <cellStyle name="Input 7 15" xfId="1555" xr:uid="{00000000-0005-0000-0000-000047050000}"/>
+    <cellStyle name="Input 7 16" xfId="1742" xr:uid="{00000000-0005-0000-0000-000048050000}"/>
+    <cellStyle name="Input 7 17" xfId="1704" xr:uid="{00000000-0005-0000-0000-000049050000}"/>
+    <cellStyle name="Input 7 18" xfId="1882" xr:uid="{00000000-0005-0000-0000-00004A050000}"/>
+    <cellStyle name="Input 7 19" xfId="1845" xr:uid="{00000000-0005-0000-0000-00004B050000}"/>
+    <cellStyle name="Input 7 2" xfId="1025" xr:uid="{00000000-0005-0000-0000-00004C050000}"/>
+    <cellStyle name="Input 7 20" xfId="1978" xr:uid="{00000000-0005-0000-0000-00004D050000}"/>
+    <cellStyle name="Input 7 21" xfId="1975" xr:uid="{00000000-0005-0000-0000-00004E050000}"/>
+    <cellStyle name="Input 7 22" xfId="2133" xr:uid="{00000000-0005-0000-0000-00004F050000}"/>
+    <cellStyle name="Input 7 23" xfId="2195" xr:uid="{00000000-0005-0000-0000-000050050000}"/>
+    <cellStyle name="Input 7 24" xfId="2162" xr:uid="{00000000-0005-0000-0000-000051050000}"/>
+    <cellStyle name="Input 7 25" xfId="2317" xr:uid="{00000000-0005-0000-0000-000052050000}"/>
+    <cellStyle name="Input 7 26" xfId="2284" xr:uid="{00000000-0005-0000-0000-000053050000}"/>
+    <cellStyle name="Input 7 27" xfId="2439" xr:uid="{00000000-0005-0000-0000-000054050000}"/>
+    <cellStyle name="Input 7 28" xfId="2405" xr:uid="{00000000-0005-0000-0000-000055050000}"/>
+    <cellStyle name="Input 7 29" xfId="2527" xr:uid="{00000000-0005-0000-0000-000056050000}"/>
+    <cellStyle name="Input 7 3" xfId="756" xr:uid="{00000000-0005-0000-0000-000057050000}"/>
+    <cellStyle name="Input 7 30" xfId="2795" xr:uid="{00000000-0005-0000-0000-000058050000}"/>
+    <cellStyle name="Input 7 31" xfId="2586" xr:uid="{00000000-0005-0000-0000-000059050000}"/>
+    <cellStyle name="Input 7 32" xfId="2730" xr:uid="{00000000-0005-0000-0000-00005A050000}"/>
+    <cellStyle name="Input 7 4" xfId="1057" xr:uid="{00000000-0005-0000-0000-00005B050000}"/>
+    <cellStyle name="Input 7 5" xfId="729" xr:uid="{00000000-0005-0000-0000-00005C050000}"/>
+    <cellStyle name="Input 7 6" xfId="1083" xr:uid="{00000000-0005-0000-0000-00005D050000}"/>
+    <cellStyle name="Input 7 7" xfId="702" xr:uid="{00000000-0005-0000-0000-00005E050000}"/>
+    <cellStyle name="Input 7 8" xfId="1139" xr:uid="{00000000-0005-0000-0000-00005F050000}"/>
+    <cellStyle name="Input 7 9" xfId="677" xr:uid="{00000000-0005-0000-0000-000060050000}"/>
+    <cellStyle name="Input 8" xfId="513" xr:uid="{00000000-0005-0000-0000-000061050000}"/>
+    <cellStyle name="Input 8 10" xfId="1258" xr:uid="{00000000-0005-0000-0000-000062050000}"/>
+    <cellStyle name="Input 8 11" xfId="1366" xr:uid="{00000000-0005-0000-0000-000063050000}"/>
+    <cellStyle name="Input 8 12" xfId="1442" xr:uid="{00000000-0005-0000-0000-000064050000}"/>
+    <cellStyle name="Input 8 13" xfId="1517" xr:uid="{00000000-0005-0000-0000-000065050000}"/>
+    <cellStyle name="Input 8 14" xfId="1594" xr:uid="{00000000-0005-0000-0000-000066050000}"/>
+    <cellStyle name="Input 8 15" xfId="1556" xr:uid="{00000000-0005-0000-0000-000067050000}"/>
+    <cellStyle name="Input 8 16" xfId="1743" xr:uid="{00000000-0005-0000-0000-000068050000}"/>
+    <cellStyle name="Input 8 17" xfId="1705" xr:uid="{00000000-0005-0000-0000-000069050000}"/>
+    <cellStyle name="Input 8 18" xfId="1883" xr:uid="{00000000-0005-0000-0000-00006A050000}"/>
+    <cellStyle name="Input 8 19" xfId="1846" xr:uid="{00000000-0005-0000-0000-00006B050000}"/>
+    <cellStyle name="Input 8 2" xfId="1026" xr:uid="{00000000-0005-0000-0000-00006C050000}"/>
+    <cellStyle name="Input 8 20" xfId="2010" xr:uid="{00000000-0005-0000-0000-00006D050000}"/>
+    <cellStyle name="Input 8 21" xfId="2071" xr:uid="{00000000-0005-0000-0000-00006E050000}"/>
+    <cellStyle name="Input 8 22" xfId="2134" xr:uid="{00000000-0005-0000-0000-00006F050000}"/>
+    <cellStyle name="Input 8 23" xfId="2196" xr:uid="{00000000-0005-0000-0000-000070050000}"/>
+    <cellStyle name="Input 8 24" xfId="2163" xr:uid="{00000000-0005-0000-0000-000071050000}"/>
+    <cellStyle name="Input 8 25" xfId="2318" xr:uid="{00000000-0005-0000-0000-000072050000}"/>
+    <cellStyle name="Input 8 26" xfId="2285" xr:uid="{00000000-0005-0000-0000-000073050000}"/>
+    <cellStyle name="Input 8 27" xfId="2440" xr:uid="{00000000-0005-0000-0000-000074050000}"/>
+    <cellStyle name="Input 8 28" xfId="2406" xr:uid="{00000000-0005-0000-0000-000075050000}"/>
+    <cellStyle name="Input 8 29" xfId="2559" xr:uid="{00000000-0005-0000-0000-000076050000}"/>
+    <cellStyle name="Input 8 3" xfId="755" xr:uid="{00000000-0005-0000-0000-000077050000}"/>
+    <cellStyle name="Input 8 30" xfId="2623" xr:uid="{00000000-0005-0000-0000-000078050000}"/>
+    <cellStyle name="Input 8 31" xfId="2587" xr:uid="{00000000-0005-0000-0000-000079050000}"/>
+    <cellStyle name="Input 8 32" xfId="2794" xr:uid="{00000000-0005-0000-0000-00007A050000}"/>
+    <cellStyle name="Input 8 4" xfId="670" xr:uid="{00000000-0005-0000-0000-00007B050000}"/>
+    <cellStyle name="Input 8 5" xfId="728" xr:uid="{00000000-0005-0000-0000-00007C050000}"/>
+    <cellStyle name="Input 8 6" xfId="1084" xr:uid="{00000000-0005-0000-0000-00007D050000}"/>
+    <cellStyle name="Input 8 7" xfId="701" xr:uid="{00000000-0005-0000-0000-00007E050000}"/>
+    <cellStyle name="Input 8 8" xfId="1140" xr:uid="{00000000-0005-0000-0000-00007F050000}"/>
+    <cellStyle name="Input 8 9" xfId="676" xr:uid="{00000000-0005-0000-0000-000080050000}"/>
+    <cellStyle name="Input 9" xfId="514" xr:uid="{00000000-0005-0000-0000-000081050000}"/>
+    <cellStyle name="Input 9 10" xfId="1290" xr:uid="{00000000-0005-0000-0000-000082050000}"/>
+    <cellStyle name="Input 9 11" xfId="1367" xr:uid="{00000000-0005-0000-0000-000083050000}"/>
+    <cellStyle name="Input 9 12" xfId="1443" xr:uid="{00000000-0005-0000-0000-000084050000}"/>
+    <cellStyle name="Input 9 13" xfId="1518" xr:uid="{00000000-0005-0000-0000-000085050000}"/>
+    <cellStyle name="Input 9 14" xfId="1595" xr:uid="{00000000-0005-0000-0000-000086050000}"/>
+    <cellStyle name="Input 9 15" xfId="1668" xr:uid="{00000000-0005-0000-0000-000087050000}"/>
+    <cellStyle name="Input 9 16" xfId="1744" xr:uid="{00000000-0005-0000-0000-000088050000}"/>
+    <cellStyle name="Input 9 17" xfId="1818" xr:uid="{00000000-0005-0000-0000-000089050000}"/>
+    <cellStyle name="Input 9 18" xfId="1884" xr:uid="{00000000-0005-0000-0000-00008A050000}"/>
+    <cellStyle name="Input 9 19" xfId="1947" xr:uid="{00000000-0005-0000-0000-00008B050000}"/>
+    <cellStyle name="Input 9 2" xfId="1027" xr:uid="{00000000-0005-0000-0000-00008C050000}"/>
+    <cellStyle name="Input 9 20" xfId="2011" xr:uid="{00000000-0005-0000-0000-00008D050000}"/>
+    <cellStyle name="Input 9 21" xfId="2072" xr:uid="{00000000-0005-0000-0000-00008E050000}"/>
+    <cellStyle name="Input 9 22" xfId="2135" xr:uid="{00000000-0005-0000-0000-00008F050000}"/>
+    <cellStyle name="Input 9 23" xfId="2197" xr:uid="{00000000-0005-0000-0000-000090050000}"/>
+    <cellStyle name="Input 9 24" xfId="2258" xr:uid="{00000000-0005-0000-0000-000091050000}"/>
+    <cellStyle name="Input 9 25" xfId="2319" xr:uid="{00000000-0005-0000-0000-000092050000}"/>
+    <cellStyle name="Input 9 26" xfId="2378" xr:uid="{00000000-0005-0000-0000-000093050000}"/>
+    <cellStyle name="Input 9 27" xfId="2441" xr:uid="{00000000-0005-0000-0000-000094050000}"/>
+    <cellStyle name="Input 9 28" xfId="2470" xr:uid="{00000000-0005-0000-0000-000095050000}"/>
+    <cellStyle name="Input 9 29" xfId="2560" xr:uid="{00000000-0005-0000-0000-000096050000}"/>
+    <cellStyle name="Input 9 3" xfId="754" xr:uid="{00000000-0005-0000-0000-000097050000}"/>
+    <cellStyle name="Input 9 30" xfId="2695" xr:uid="{00000000-0005-0000-0000-000098050000}"/>
+    <cellStyle name="Input 9 31" xfId="2588" xr:uid="{00000000-0005-0000-0000-000099050000}"/>
+    <cellStyle name="Input 9 32" xfId="2731" xr:uid="{00000000-0005-0000-0000-00009A050000}"/>
+    <cellStyle name="Input 9 4" xfId="1058" xr:uid="{00000000-0005-0000-0000-00009B050000}"/>
+    <cellStyle name="Input 9 5" xfId="727" xr:uid="{00000000-0005-0000-0000-00009C050000}"/>
+    <cellStyle name="Input 9 6" xfId="1085" xr:uid="{00000000-0005-0000-0000-00009D050000}"/>
+    <cellStyle name="Input 9 7" xfId="700" xr:uid="{00000000-0005-0000-0000-00009E050000}"/>
+    <cellStyle name="Input 9 8" xfId="1141" xr:uid="{00000000-0005-0000-0000-00009F050000}"/>
+    <cellStyle name="Input 9 9" xfId="675" xr:uid="{00000000-0005-0000-0000-0000A0050000}"/>
+    <cellStyle name="Linked Cell 10" xfId="515" xr:uid="{00000000-0005-0000-0000-0000A1050000}"/>
+    <cellStyle name="Linked Cell 11" xfId="516" xr:uid="{00000000-0005-0000-0000-0000A2050000}"/>
+    <cellStyle name="Linked Cell 12" xfId="517" xr:uid="{00000000-0005-0000-0000-0000A3050000}"/>
+    <cellStyle name="Linked Cell 13" xfId="518" xr:uid="{00000000-0005-0000-0000-0000A4050000}"/>
+    <cellStyle name="Linked Cell 14" xfId="519" xr:uid="{00000000-0005-0000-0000-0000A5050000}"/>
+    <cellStyle name="Linked Cell 15" xfId="520" xr:uid="{00000000-0005-0000-0000-0000A6050000}"/>
+    <cellStyle name="Linked Cell 16" xfId="521" xr:uid="{00000000-0005-0000-0000-0000A7050000}"/>
+    <cellStyle name="Linked Cell 2" xfId="522" xr:uid="{00000000-0005-0000-0000-0000A8050000}"/>
+    <cellStyle name="Linked Cell 3" xfId="523" xr:uid="{00000000-0005-0000-0000-0000A9050000}"/>
+    <cellStyle name="Linked Cell 4" xfId="524" xr:uid="{00000000-0005-0000-0000-0000AA050000}"/>
+    <cellStyle name="Linked Cell 5" xfId="525" xr:uid="{00000000-0005-0000-0000-0000AB050000}"/>
+    <cellStyle name="Linked Cell 6" xfId="526" xr:uid="{00000000-0005-0000-0000-0000AC050000}"/>
+    <cellStyle name="Linked Cell 7" xfId="527" xr:uid="{00000000-0005-0000-0000-0000AD050000}"/>
+    <cellStyle name="Linked Cell 8" xfId="528" xr:uid="{00000000-0005-0000-0000-0000AE050000}"/>
+    <cellStyle name="Linked Cell 9" xfId="529" xr:uid="{00000000-0005-0000-0000-0000AF050000}"/>
+    <cellStyle name="Neutral 10" xfId="530" xr:uid="{00000000-0005-0000-0000-0000B0050000}"/>
+    <cellStyle name="Neutral 11" xfId="531" xr:uid="{00000000-0005-0000-0000-0000B1050000}"/>
+    <cellStyle name="Neutral 12" xfId="532" xr:uid="{00000000-0005-0000-0000-0000B2050000}"/>
+    <cellStyle name="Neutral 13" xfId="533" xr:uid="{00000000-0005-0000-0000-0000B3050000}"/>
+    <cellStyle name="Neutral 14" xfId="534" xr:uid="{00000000-0005-0000-0000-0000B4050000}"/>
+    <cellStyle name="Neutral 15" xfId="535" xr:uid="{00000000-0005-0000-0000-0000B5050000}"/>
+    <cellStyle name="Neutral 16" xfId="536" xr:uid="{00000000-0005-0000-0000-0000B6050000}"/>
+    <cellStyle name="Neutral 2" xfId="537" xr:uid="{00000000-0005-0000-0000-0000B7050000}"/>
+    <cellStyle name="Neutral 3" xfId="538" xr:uid="{00000000-0005-0000-0000-0000B8050000}"/>
+    <cellStyle name="Neutral 4" xfId="539" xr:uid="{00000000-0005-0000-0000-0000B9050000}"/>
+    <cellStyle name="Neutral 5" xfId="540" xr:uid="{00000000-0005-0000-0000-0000BA050000}"/>
+    <cellStyle name="Neutral 6" xfId="541" xr:uid="{00000000-0005-0000-0000-0000BB050000}"/>
+    <cellStyle name="Neutral 7" xfId="542" xr:uid="{00000000-0005-0000-0000-0000BC050000}"/>
+    <cellStyle name="Neutral 8" xfId="543" xr:uid="{00000000-0005-0000-0000-0000BD050000}"/>
+    <cellStyle name="Neutral 9" xfId="544" xr:uid="{00000000-0005-0000-0000-0000BE050000}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 10" xfId="545"/>
-    <cellStyle name="Normal 11" xfId="546"/>
-    <cellStyle name="Normal 12" xfId="547"/>
-    <cellStyle name="Normal 13" xfId="548"/>
-    <cellStyle name="Normal 14" xfId="549"/>
-    <cellStyle name="Normal 15" xfId="550"/>
-    <cellStyle name="Normal 16" xfId="551"/>
-    <cellStyle name="Normal 17" xfId="552"/>
-    <cellStyle name="Normal 18" xfId="553"/>
-    <cellStyle name="Normal 19" xfId="554"/>
-    <cellStyle name="Normal 2" xfId="2"/>
-    <cellStyle name="Normal 2 10" xfId="556"/>
-    <cellStyle name="Normal 2 11" xfId="557"/>
-    <cellStyle name="Normal 2 12" xfId="558"/>
-    <cellStyle name="Normal 2 13" xfId="559"/>
-    <cellStyle name="Normal 2 14" xfId="560"/>
-    <cellStyle name="Normal 2 15" xfId="561"/>
-    <cellStyle name="Normal 2 16" xfId="562"/>
-    <cellStyle name="Normal 2 17" xfId="563"/>
-    <cellStyle name="Normal 2 18" xfId="555"/>
-    <cellStyle name="Normal 2 19" xfId="2936"/>
-    <cellStyle name="Normal 2 2" xfId="564"/>
-    <cellStyle name="Normal 2 2 2" xfId="565"/>
-    <cellStyle name="Normal 2 2 3" xfId="2934"/>
-    <cellStyle name="Normal 2 3" xfId="566"/>
-    <cellStyle name="Normal 2 4" xfId="567"/>
-    <cellStyle name="Normal 2 5" xfId="568"/>
-    <cellStyle name="Normal 2 6" xfId="569"/>
-    <cellStyle name="Normal 2 7" xfId="570"/>
-    <cellStyle name="Normal 2 8" xfId="571"/>
-    <cellStyle name="Normal 2 9" xfId="572"/>
-    <cellStyle name="Normal 20" xfId="3"/>
-    <cellStyle name="Normal 20 2" xfId="573"/>
-    <cellStyle name="Normal 21" xfId="574"/>
-    <cellStyle name="Normal 22" xfId="575"/>
-    <cellStyle name="Normal 23" xfId="576"/>
-    <cellStyle name="Normal 24" xfId="577"/>
-    <cellStyle name="Normal 25" xfId="578"/>
-    <cellStyle name="Normal 26" xfId="579"/>
-    <cellStyle name="Normal 27" xfId="580"/>
-    <cellStyle name="Normal 28" xfId="581"/>
-    <cellStyle name="Normal 29" xfId="1"/>
-    <cellStyle name="Normal 3" xfId="4"/>
-    <cellStyle name="Normal 3 2" xfId="582"/>
-    <cellStyle name="Normal 3 3" xfId="2935"/>
-    <cellStyle name="Normal 30" xfId="3029"/>
-    <cellStyle name="Normal 31" xfId="3031"/>
-    <cellStyle name="Normal 4" xfId="583"/>
-    <cellStyle name="Normal 4 2" xfId="584"/>
-    <cellStyle name="Normal 5" xfId="585"/>
-    <cellStyle name="Normal 6" xfId="586"/>
-    <cellStyle name="Normal 6 2" xfId="587"/>
-    <cellStyle name="Normal 7" xfId="588"/>
-    <cellStyle name="Normal 7 2" xfId="589"/>
-    <cellStyle name="Normal 8" xfId="590"/>
-    <cellStyle name="Normal 8 2" xfId="591"/>
-    <cellStyle name="Normal 9" xfId="592"/>
-    <cellStyle name="Normal 9 2" xfId="593"/>
-    <cellStyle name="Note 10" xfId="594"/>
-    <cellStyle name="Note 10 10" xfId="1711"/>
-    <cellStyle name="Note 10 11" xfId="1787"/>
-    <cellStyle name="Note 10 12" xfId="1851"/>
-    <cellStyle name="Note 10 13" xfId="1916"/>
-    <cellStyle name="Note 10 14" xfId="1979"/>
-    <cellStyle name="Note 10 15" xfId="2040"/>
-    <cellStyle name="Note 10 16" xfId="2102"/>
-    <cellStyle name="Note 10 17" xfId="2164"/>
-    <cellStyle name="Note 10 18" xfId="2227"/>
-    <cellStyle name="Note 10 19" xfId="2286"/>
-    <cellStyle name="Note 10 2" xfId="1107"/>
-    <cellStyle name="Note 10 20" xfId="2347"/>
-    <cellStyle name="Note 10 21" xfId="2408"/>
-    <cellStyle name="Note 10 22" xfId="2471"/>
-    <cellStyle name="Note 10 23" xfId="2528"/>
-    <cellStyle name="Note 10 24" xfId="2589"/>
-    <cellStyle name="Note 10 25" xfId="2649"/>
-    <cellStyle name="Note 10 26" xfId="2696"/>
-    <cellStyle name="Note 10 27" xfId="2748"/>
-    <cellStyle name="Note 10 28" xfId="2796"/>
-    <cellStyle name="Note 10 29" xfId="2842"/>
-    <cellStyle name="Note 10 3" xfId="1183"/>
-    <cellStyle name="Note 10 30" xfId="2888"/>
-    <cellStyle name="Note 10 31" xfId="2937"/>
-    <cellStyle name="Note 10 32" xfId="2983"/>
-    <cellStyle name="Note 10 4" xfId="1259"/>
-    <cellStyle name="Note 10 5" xfId="1335"/>
-    <cellStyle name="Note 10 6" xfId="1411"/>
-    <cellStyle name="Note 10 7" xfId="1486"/>
-    <cellStyle name="Note 10 8" xfId="1562"/>
-    <cellStyle name="Note 10 9" xfId="1637"/>
-    <cellStyle name="Note 11" xfId="595"/>
-    <cellStyle name="Note 11 10" xfId="1712"/>
-    <cellStyle name="Note 11 11" xfId="1788"/>
-    <cellStyle name="Note 11 12" xfId="1852"/>
-    <cellStyle name="Note 11 13" xfId="1917"/>
-    <cellStyle name="Note 11 14" xfId="1980"/>
-    <cellStyle name="Note 11 15" xfId="2041"/>
-    <cellStyle name="Note 11 16" xfId="2103"/>
-    <cellStyle name="Note 11 17" xfId="2165"/>
-    <cellStyle name="Note 11 18" xfId="2228"/>
-    <cellStyle name="Note 11 19" xfId="2287"/>
-    <cellStyle name="Note 11 2" xfId="1108"/>
-    <cellStyle name="Note 11 20" xfId="2348"/>
-    <cellStyle name="Note 11 21" xfId="2409"/>
-    <cellStyle name="Note 11 22" xfId="2472"/>
-    <cellStyle name="Note 11 23" xfId="2529"/>
-    <cellStyle name="Note 11 24" xfId="2590"/>
-    <cellStyle name="Note 11 25" xfId="2650"/>
-    <cellStyle name="Note 11 26" xfId="2697"/>
-    <cellStyle name="Note 11 27" xfId="2749"/>
-    <cellStyle name="Note 11 28" xfId="2797"/>
-    <cellStyle name="Note 11 29" xfId="2843"/>
-    <cellStyle name="Note 11 3" xfId="1184"/>
-    <cellStyle name="Note 11 30" xfId="2889"/>
-    <cellStyle name="Note 11 31" xfId="2938"/>
-    <cellStyle name="Note 11 32" xfId="2984"/>
-    <cellStyle name="Note 11 4" xfId="1260"/>
-    <cellStyle name="Note 11 5" xfId="1336"/>
-    <cellStyle name="Note 11 6" xfId="1412"/>
-    <cellStyle name="Note 11 7" xfId="1487"/>
-    <cellStyle name="Note 11 8" xfId="1563"/>
-    <cellStyle name="Note 11 9" xfId="1638"/>
-    <cellStyle name="Note 12" xfId="596"/>
-    <cellStyle name="Note 12 10" xfId="1713"/>
-    <cellStyle name="Note 12 11" xfId="1789"/>
-    <cellStyle name="Note 12 12" xfId="1853"/>
-    <cellStyle name="Note 12 13" xfId="1918"/>
-    <cellStyle name="Note 12 14" xfId="1981"/>
-    <cellStyle name="Note 12 15" xfId="2042"/>
-    <cellStyle name="Note 12 16" xfId="2104"/>
-    <cellStyle name="Note 12 17" xfId="2166"/>
-    <cellStyle name="Note 12 18" xfId="2229"/>
-    <cellStyle name="Note 12 19" xfId="2288"/>
-    <cellStyle name="Note 12 2" xfId="1109"/>
-    <cellStyle name="Note 12 20" xfId="2349"/>
-    <cellStyle name="Note 12 21" xfId="2410"/>
-    <cellStyle name="Note 12 22" xfId="2473"/>
-    <cellStyle name="Note 12 23" xfId="2530"/>
-    <cellStyle name="Note 12 24" xfId="2591"/>
-    <cellStyle name="Note 12 25" xfId="2651"/>
-    <cellStyle name="Note 12 26" xfId="2698"/>
-    <cellStyle name="Note 12 27" xfId="2750"/>
-    <cellStyle name="Note 12 28" xfId="2798"/>
-    <cellStyle name="Note 12 29" xfId="2844"/>
-    <cellStyle name="Note 12 3" xfId="1185"/>
-    <cellStyle name="Note 12 30" xfId="2890"/>
-    <cellStyle name="Note 12 31" xfId="2939"/>
-    <cellStyle name="Note 12 32" xfId="2985"/>
-    <cellStyle name="Note 12 4" xfId="1261"/>
-    <cellStyle name="Note 12 5" xfId="1337"/>
-    <cellStyle name="Note 12 6" xfId="1413"/>
-    <cellStyle name="Note 12 7" xfId="1488"/>
-    <cellStyle name="Note 12 8" xfId="1564"/>
-    <cellStyle name="Note 12 9" xfId="1639"/>
-    <cellStyle name="Note 13" xfId="597"/>
-    <cellStyle name="Note 13 10" xfId="1714"/>
-    <cellStyle name="Note 13 11" xfId="1790"/>
-    <cellStyle name="Note 13 12" xfId="1854"/>
-    <cellStyle name="Note 13 13" xfId="1919"/>
-    <cellStyle name="Note 13 14" xfId="1982"/>
-    <cellStyle name="Note 13 15" xfId="2043"/>
-    <cellStyle name="Note 13 16" xfId="2105"/>
-    <cellStyle name="Note 13 17" xfId="2167"/>
-    <cellStyle name="Note 13 18" xfId="2230"/>
-    <cellStyle name="Note 13 19" xfId="2289"/>
-    <cellStyle name="Note 13 2" xfId="1110"/>
-    <cellStyle name="Note 13 20" xfId="2350"/>
-    <cellStyle name="Note 13 21" xfId="2411"/>
-    <cellStyle name="Note 13 22" xfId="2474"/>
-    <cellStyle name="Note 13 23" xfId="2531"/>
-    <cellStyle name="Note 13 24" xfId="2592"/>
-    <cellStyle name="Note 13 25" xfId="2652"/>
-    <cellStyle name="Note 13 26" xfId="2699"/>
-    <cellStyle name="Note 13 27" xfId="2751"/>
-    <cellStyle name="Note 13 28" xfId="2799"/>
-    <cellStyle name="Note 13 29" xfId="2845"/>
-    <cellStyle name="Note 13 3" xfId="1186"/>
-    <cellStyle name="Note 13 30" xfId="2891"/>
-    <cellStyle name="Note 13 31" xfId="2940"/>
-    <cellStyle name="Note 13 32" xfId="2986"/>
-    <cellStyle name="Note 13 4" xfId="1262"/>
-    <cellStyle name="Note 13 5" xfId="1338"/>
-    <cellStyle name="Note 13 6" xfId="1414"/>
-    <cellStyle name="Note 13 7" xfId="1489"/>
-    <cellStyle name="Note 13 8" xfId="1565"/>
-    <cellStyle name="Note 13 9" xfId="1640"/>
-    <cellStyle name="Note 14" xfId="598"/>
-    <cellStyle name="Note 14 10" xfId="1715"/>
-    <cellStyle name="Note 14 11" xfId="1791"/>
-    <cellStyle name="Note 14 12" xfId="1855"/>
-    <cellStyle name="Note 14 13" xfId="1920"/>
-    <cellStyle name="Note 14 14" xfId="1983"/>
-    <cellStyle name="Note 14 15" xfId="2044"/>
-    <cellStyle name="Note 14 16" xfId="2106"/>
-    <cellStyle name="Note 14 17" xfId="2168"/>
-    <cellStyle name="Note 14 18" xfId="2231"/>
-    <cellStyle name="Note 14 19" xfId="2290"/>
-    <cellStyle name="Note 14 2" xfId="1111"/>
-    <cellStyle name="Note 14 20" xfId="2351"/>
-    <cellStyle name="Note 14 21" xfId="2412"/>
-    <cellStyle name="Note 14 22" xfId="2475"/>
-    <cellStyle name="Note 14 23" xfId="2532"/>
-    <cellStyle name="Note 14 24" xfId="2593"/>
-    <cellStyle name="Note 14 25" xfId="2653"/>
-    <cellStyle name="Note 14 26" xfId="2700"/>
-    <cellStyle name="Note 14 27" xfId="2752"/>
-    <cellStyle name="Note 14 28" xfId="2800"/>
-    <cellStyle name="Note 14 29" xfId="2846"/>
-    <cellStyle name="Note 14 3" xfId="1187"/>
-    <cellStyle name="Note 14 30" xfId="2892"/>
-    <cellStyle name="Note 14 31" xfId="2941"/>
-    <cellStyle name="Note 14 32" xfId="2987"/>
-    <cellStyle name="Note 14 4" xfId="1263"/>
-    <cellStyle name="Note 14 5" xfId="1339"/>
-    <cellStyle name="Note 14 6" xfId="1415"/>
-    <cellStyle name="Note 14 7" xfId="1490"/>
-    <cellStyle name="Note 14 8" xfId="1566"/>
-    <cellStyle name="Note 14 9" xfId="1641"/>
-    <cellStyle name="Note 15" xfId="599"/>
-    <cellStyle name="Note 15 10" xfId="1716"/>
-    <cellStyle name="Note 15 11" xfId="1792"/>
-    <cellStyle name="Note 15 12" xfId="1856"/>
-    <cellStyle name="Note 15 13" xfId="1921"/>
-    <cellStyle name="Note 15 14" xfId="1984"/>
-    <cellStyle name="Note 15 15" xfId="2045"/>
-    <cellStyle name="Note 15 16" xfId="2107"/>
-    <cellStyle name="Note 15 17" xfId="2169"/>
-    <cellStyle name="Note 15 18" xfId="2232"/>
-    <cellStyle name="Note 15 19" xfId="2291"/>
-    <cellStyle name="Note 15 2" xfId="1112"/>
-    <cellStyle name="Note 15 20" xfId="2352"/>
-    <cellStyle name="Note 15 21" xfId="2413"/>
-    <cellStyle name="Note 15 22" xfId="2476"/>
-    <cellStyle name="Note 15 23" xfId="2533"/>
-    <cellStyle name="Note 15 24" xfId="2594"/>
-    <cellStyle name="Note 15 25" xfId="2654"/>
-    <cellStyle name="Note 15 26" xfId="2701"/>
-    <cellStyle name="Note 15 27" xfId="2753"/>
-    <cellStyle name="Note 15 28" xfId="2801"/>
-    <cellStyle name="Note 15 29" xfId="2847"/>
-    <cellStyle name="Note 15 3" xfId="1188"/>
-    <cellStyle name="Note 15 30" xfId="2893"/>
-    <cellStyle name="Note 15 31" xfId="2942"/>
-    <cellStyle name="Note 15 32" xfId="2988"/>
-    <cellStyle name="Note 15 4" xfId="1264"/>
-    <cellStyle name="Note 15 5" xfId="1340"/>
-    <cellStyle name="Note 15 6" xfId="1416"/>
-    <cellStyle name="Note 15 7" xfId="1491"/>
-    <cellStyle name="Note 15 8" xfId="1567"/>
-    <cellStyle name="Note 15 9" xfId="1642"/>
-    <cellStyle name="Note 16" xfId="600"/>
-    <cellStyle name="Note 16 10" xfId="1717"/>
-    <cellStyle name="Note 16 11" xfId="1793"/>
-    <cellStyle name="Note 16 12" xfId="1857"/>
-    <cellStyle name="Note 16 13" xfId="1922"/>
-    <cellStyle name="Note 16 14" xfId="1985"/>
-    <cellStyle name="Note 16 15" xfId="2046"/>
-    <cellStyle name="Note 16 16" xfId="2108"/>
-    <cellStyle name="Note 16 17" xfId="2170"/>
-    <cellStyle name="Note 16 18" xfId="2233"/>
-    <cellStyle name="Note 16 19" xfId="2292"/>
-    <cellStyle name="Note 16 2" xfId="1113"/>
-    <cellStyle name="Note 16 20" xfId="2353"/>
-    <cellStyle name="Note 16 21" xfId="2414"/>
-    <cellStyle name="Note 16 22" xfId="2477"/>
-    <cellStyle name="Note 16 23" xfId="2534"/>
-    <cellStyle name="Note 16 24" xfId="2595"/>
-    <cellStyle name="Note 16 25" xfId="2655"/>
-    <cellStyle name="Note 16 26" xfId="2702"/>
-    <cellStyle name="Note 16 27" xfId="2754"/>
-    <cellStyle name="Note 16 28" xfId="2802"/>
-    <cellStyle name="Note 16 29" xfId="2848"/>
-    <cellStyle name="Note 16 3" xfId="1189"/>
-    <cellStyle name="Note 16 30" xfId="2894"/>
-    <cellStyle name="Note 16 31" xfId="2943"/>
-    <cellStyle name="Note 16 32" xfId="2989"/>
-    <cellStyle name="Note 16 4" xfId="1265"/>
-    <cellStyle name="Note 16 5" xfId="1341"/>
-    <cellStyle name="Note 16 6" xfId="1417"/>
-    <cellStyle name="Note 16 7" xfId="1492"/>
-    <cellStyle name="Note 16 8" xfId="1568"/>
-    <cellStyle name="Note 16 9" xfId="1643"/>
-    <cellStyle name="Note 17" xfId="601"/>
-    <cellStyle name="Note 17 10" xfId="1718"/>
-    <cellStyle name="Note 17 11" xfId="1794"/>
-    <cellStyle name="Note 17 12" xfId="1858"/>
-    <cellStyle name="Note 17 13" xfId="1923"/>
-    <cellStyle name="Note 17 14" xfId="1986"/>
-    <cellStyle name="Note 17 15" xfId="2047"/>
-    <cellStyle name="Note 17 16" xfId="2109"/>
-    <cellStyle name="Note 17 17" xfId="2171"/>
-    <cellStyle name="Note 17 18" xfId="2234"/>
-    <cellStyle name="Note 17 19" xfId="2293"/>
-    <cellStyle name="Note 17 2" xfId="1114"/>
-    <cellStyle name="Note 17 20" xfId="2354"/>
-    <cellStyle name="Note 17 21" xfId="2415"/>
-    <cellStyle name="Note 17 22" xfId="2478"/>
-    <cellStyle name="Note 17 23" xfId="2535"/>
-    <cellStyle name="Note 17 24" xfId="2596"/>
-    <cellStyle name="Note 17 25" xfId="2656"/>
-    <cellStyle name="Note 17 26" xfId="2703"/>
-    <cellStyle name="Note 17 27" xfId="2755"/>
-    <cellStyle name="Note 17 28" xfId="2803"/>
-    <cellStyle name="Note 17 29" xfId="2849"/>
-    <cellStyle name="Note 17 3" xfId="1190"/>
-    <cellStyle name="Note 17 30" xfId="2895"/>
-    <cellStyle name="Note 17 31" xfId="2944"/>
-    <cellStyle name="Note 17 32" xfId="2990"/>
-    <cellStyle name="Note 17 4" xfId="1266"/>
-    <cellStyle name="Note 17 5" xfId="1342"/>
-    <cellStyle name="Note 17 6" xfId="1418"/>
-    <cellStyle name="Note 17 7" xfId="1493"/>
-    <cellStyle name="Note 17 8" xfId="1569"/>
-    <cellStyle name="Note 17 9" xfId="1644"/>
-    <cellStyle name="Note 2" xfId="602"/>
-    <cellStyle name="Note 2 10" xfId="1719"/>
-    <cellStyle name="Note 2 11" xfId="1795"/>
-    <cellStyle name="Note 2 12" xfId="1859"/>
-    <cellStyle name="Note 2 13" xfId="1924"/>
-    <cellStyle name="Note 2 14" xfId="1987"/>
-    <cellStyle name="Note 2 15" xfId="2048"/>
-    <cellStyle name="Note 2 16" xfId="2110"/>
-    <cellStyle name="Note 2 17" xfId="2172"/>
-    <cellStyle name="Note 2 18" xfId="2235"/>
-    <cellStyle name="Note 2 19" xfId="2294"/>
-    <cellStyle name="Note 2 2" xfId="1115"/>
-    <cellStyle name="Note 2 20" xfId="2355"/>
-    <cellStyle name="Note 2 21" xfId="2416"/>
-    <cellStyle name="Note 2 22" xfId="2479"/>
-    <cellStyle name="Note 2 23" xfId="2536"/>
-    <cellStyle name="Note 2 24" xfId="2597"/>
-    <cellStyle name="Note 2 25" xfId="2657"/>
-    <cellStyle name="Note 2 26" xfId="2704"/>
-    <cellStyle name="Note 2 27" xfId="2756"/>
-    <cellStyle name="Note 2 28" xfId="2804"/>
-    <cellStyle name="Note 2 29" xfId="2850"/>
-    <cellStyle name="Note 2 3" xfId="1191"/>
-    <cellStyle name="Note 2 30" xfId="2896"/>
-    <cellStyle name="Note 2 31" xfId="2945"/>
-    <cellStyle name="Note 2 32" xfId="2991"/>
-    <cellStyle name="Note 2 4" xfId="1267"/>
-    <cellStyle name="Note 2 5" xfId="1343"/>
-    <cellStyle name="Note 2 6" xfId="1419"/>
-    <cellStyle name="Note 2 7" xfId="1494"/>
-    <cellStyle name="Note 2 8" xfId="1570"/>
-    <cellStyle name="Note 2 9" xfId="1645"/>
-    <cellStyle name="Note 3" xfId="603"/>
-    <cellStyle name="Note 3 10" xfId="1720"/>
-    <cellStyle name="Note 3 11" xfId="1796"/>
-    <cellStyle name="Note 3 12" xfId="1860"/>
-    <cellStyle name="Note 3 13" xfId="1925"/>
-    <cellStyle name="Note 3 14" xfId="1988"/>
-    <cellStyle name="Note 3 15" xfId="2049"/>
-    <cellStyle name="Note 3 16" xfId="2111"/>
-    <cellStyle name="Note 3 17" xfId="2173"/>
-    <cellStyle name="Note 3 18" xfId="2236"/>
-    <cellStyle name="Note 3 19" xfId="2295"/>
-    <cellStyle name="Note 3 2" xfId="1116"/>
-    <cellStyle name="Note 3 20" xfId="2356"/>
-    <cellStyle name="Note 3 21" xfId="2417"/>
-    <cellStyle name="Note 3 22" xfId="2480"/>
-    <cellStyle name="Note 3 23" xfId="2537"/>
-    <cellStyle name="Note 3 24" xfId="2598"/>
-    <cellStyle name="Note 3 25" xfId="2658"/>
-    <cellStyle name="Note 3 26" xfId="2705"/>
-    <cellStyle name="Note 3 27" xfId="2757"/>
-    <cellStyle name="Note 3 28" xfId="2805"/>
-    <cellStyle name="Note 3 29" xfId="2851"/>
-    <cellStyle name="Note 3 3" xfId="1192"/>
-    <cellStyle name="Note 3 30" xfId="2897"/>
-    <cellStyle name="Note 3 31" xfId="2946"/>
-    <cellStyle name="Note 3 32" xfId="2992"/>
-    <cellStyle name="Note 3 4" xfId="1268"/>
-    <cellStyle name="Note 3 5" xfId="1344"/>
-    <cellStyle name="Note 3 6" xfId="1420"/>
-    <cellStyle name="Note 3 7" xfId="1495"/>
-    <cellStyle name="Note 3 8" xfId="1571"/>
-    <cellStyle name="Note 3 9" xfId="1646"/>
-    <cellStyle name="Note 4" xfId="604"/>
-    <cellStyle name="Note 4 10" xfId="1721"/>
-    <cellStyle name="Note 4 11" xfId="1797"/>
-    <cellStyle name="Note 4 12" xfId="1861"/>
-    <cellStyle name="Note 4 13" xfId="1926"/>
-    <cellStyle name="Note 4 14" xfId="1989"/>
-    <cellStyle name="Note 4 15" xfId="2050"/>
-    <cellStyle name="Note 4 16" xfId="2112"/>
-    <cellStyle name="Note 4 17" xfId="2174"/>
-    <cellStyle name="Note 4 18" xfId="2237"/>
-    <cellStyle name="Note 4 19" xfId="2296"/>
-    <cellStyle name="Note 4 2" xfId="1117"/>
-    <cellStyle name="Note 4 20" xfId="2357"/>
-    <cellStyle name="Note 4 21" xfId="2418"/>
-    <cellStyle name="Note 4 22" xfId="2481"/>
-    <cellStyle name="Note 4 23" xfId="2538"/>
-    <cellStyle name="Note 4 24" xfId="2599"/>
-    <cellStyle name="Note 4 25" xfId="2659"/>
-    <cellStyle name="Note 4 26" xfId="2706"/>
-    <cellStyle name="Note 4 27" xfId="2758"/>
-    <cellStyle name="Note 4 28" xfId="2806"/>
-    <cellStyle name="Note 4 29" xfId="2852"/>
-    <cellStyle name="Note 4 3" xfId="1193"/>
-    <cellStyle name="Note 4 30" xfId="2898"/>
-    <cellStyle name="Note 4 31" xfId="2947"/>
-    <cellStyle name="Note 4 32" xfId="2993"/>
-    <cellStyle name="Note 4 4" xfId="1269"/>
-    <cellStyle name="Note 4 5" xfId="1345"/>
-    <cellStyle name="Note 4 6" xfId="1421"/>
-    <cellStyle name="Note 4 7" xfId="1496"/>
-    <cellStyle name="Note 4 8" xfId="1572"/>
-    <cellStyle name="Note 4 9" xfId="1647"/>
-    <cellStyle name="Note 5" xfId="605"/>
-    <cellStyle name="Note 5 10" xfId="1722"/>
-    <cellStyle name="Note 5 11" xfId="1798"/>
-    <cellStyle name="Note 5 12" xfId="1862"/>
-    <cellStyle name="Note 5 13" xfId="1927"/>
-    <cellStyle name="Note 5 14" xfId="1990"/>
-    <cellStyle name="Note 5 15" xfId="2051"/>
-    <cellStyle name="Note 5 16" xfId="2113"/>
-    <cellStyle name="Note 5 17" xfId="2175"/>
-    <cellStyle name="Note 5 18" xfId="2238"/>
-    <cellStyle name="Note 5 19" xfId="2297"/>
-    <cellStyle name="Note 5 2" xfId="1118"/>
-    <cellStyle name="Note 5 20" xfId="2358"/>
-    <cellStyle name="Note 5 21" xfId="2419"/>
-    <cellStyle name="Note 5 22" xfId="2482"/>
-    <cellStyle name="Note 5 23" xfId="2539"/>
-    <cellStyle name="Note 5 24" xfId="2600"/>
-    <cellStyle name="Note 5 25" xfId="2660"/>
-    <cellStyle name="Note 5 26" xfId="2707"/>
-    <cellStyle name="Note 5 27" xfId="2759"/>
-    <cellStyle name="Note 5 28" xfId="2807"/>
-    <cellStyle name="Note 5 29" xfId="2853"/>
-    <cellStyle name="Note 5 3" xfId="1194"/>
-    <cellStyle name="Note 5 30" xfId="2899"/>
-    <cellStyle name="Note 5 31" xfId="2948"/>
-    <cellStyle name="Note 5 32" xfId="2994"/>
-    <cellStyle name="Note 5 4" xfId="1270"/>
-    <cellStyle name="Note 5 5" xfId="1346"/>
-    <cellStyle name="Note 5 6" xfId="1422"/>
-    <cellStyle name="Note 5 7" xfId="1497"/>
-    <cellStyle name="Note 5 8" xfId="1573"/>
-    <cellStyle name="Note 5 9" xfId="1648"/>
-    <cellStyle name="Note 6" xfId="606"/>
-    <cellStyle name="Note 6 10" xfId="1723"/>
-    <cellStyle name="Note 6 11" xfId="1799"/>
-    <cellStyle name="Note 6 12" xfId="1863"/>
-    <cellStyle name="Note 6 13" xfId="1928"/>
-    <cellStyle name="Note 6 14" xfId="1991"/>
-    <cellStyle name="Note 6 15" xfId="2052"/>
-    <cellStyle name="Note 6 16" xfId="2114"/>
-    <cellStyle name="Note 6 17" xfId="2176"/>
-    <cellStyle name="Note 6 18" xfId="2239"/>
-    <cellStyle name="Note 6 19" xfId="2298"/>
-    <cellStyle name="Note 6 2" xfId="1119"/>
-    <cellStyle name="Note 6 20" xfId="2359"/>
-    <cellStyle name="Note 6 21" xfId="2420"/>
-    <cellStyle name="Note 6 22" xfId="2483"/>
-    <cellStyle name="Note 6 23" xfId="2540"/>
-    <cellStyle name="Note 6 24" xfId="2601"/>
-    <cellStyle name="Note 6 25" xfId="2661"/>
-    <cellStyle name="Note 6 26" xfId="2708"/>
-    <cellStyle name="Note 6 27" xfId="2760"/>
-    <cellStyle name="Note 6 28" xfId="2808"/>
-    <cellStyle name="Note 6 29" xfId="2854"/>
-    <cellStyle name="Note 6 3" xfId="1195"/>
-    <cellStyle name="Note 6 30" xfId="2900"/>
-    <cellStyle name="Note 6 31" xfId="2949"/>
-    <cellStyle name="Note 6 32" xfId="2995"/>
-    <cellStyle name="Note 6 4" xfId="1271"/>
-    <cellStyle name="Note 6 5" xfId="1347"/>
-    <cellStyle name="Note 6 6" xfId="1423"/>
-    <cellStyle name="Note 6 7" xfId="1498"/>
-    <cellStyle name="Note 6 8" xfId="1574"/>
-    <cellStyle name="Note 6 9" xfId="1649"/>
-    <cellStyle name="Note 7" xfId="607"/>
-    <cellStyle name="Note 7 10" xfId="1724"/>
-    <cellStyle name="Note 7 11" xfId="1800"/>
-    <cellStyle name="Note 7 12" xfId="1864"/>
-    <cellStyle name="Note 7 13" xfId="1929"/>
-    <cellStyle name="Note 7 14" xfId="1992"/>
-    <cellStyle name="Note 7 15" xfId="2053"/>
-    <cellStyle name="Note 7 16" xfId="2115"/>
-    <cellStyle name="Note 7 17" xfId="2177"/>
-    <cellStyle name="Note 7 18" xfId="2240"/>
-    <cellStyle name="Note 7 19" xfId="2299"/>
-    <cellStyle name="Note 7 2" xfId="1120"/>
-    <cellStyle name="Note 7 20" xfId="2360"/>
-    <cellStyle name="Note 7 21" xfId="2421"/>
-    <cellStyle name="Note 7 22" xfId="2484"/>
-    <cellStyle name="Note 7 23" xfId="2541"/>
-    <cellStyle name="Note 7 24" xfId="2602"/>
-    <cellStyle name="Note 7 25" xfId="2662"/>
-    <cellStyle name="Note 7 26" xfId="2709"/>
-    <cellStyle name="Note 7 27" xfId="2761"/>
-    <cellStyle name="Note 7 28" xfId="2809"/>
-    <cellStyle name="Note 7 29" xfId="2855"/>
-    <cellStyle name="Note 7 3" xfId="1196"/>
-    <cellStyle name="Note 7 30" xfId="2901"/>
-    <cellStyle name="Note 7 31" xfId="2950"/>
-    <cellStyle name="Note 7 32" xfId="2996"/>
-    <cellStyle name="Note 7 4" xfId="1272"/>
-    <cellStyle name="Note 7 5" xfId="1348"/>
-    <cellStyle name="Note 7 6" xfId="1424"/>
-    <cellStyle name="Note 7 7" xfId="1499"/>
-    <cellStyle name="Note 7 8" xfId="1575"/>
-    <cellStyle name="Note 7 9" xfId="1650"/>
-    <cellStyle name="Note 8" xfId="608"/>
-    <cellStyle name="Note 8 10" xfId="1725"/>
-    <cellStyle name="Note 8 11" xfId="1801"/>
-    <cellStyle name="Note 8 12" xfId="1865"/>
-    <cellStyle name="Note 8 13" xfId="1930"/>
-    <cellStyle name="Note 8 14" xfId="1993"/>
-    <cellStyle name="Note 8 15" xfId="2054"/>
-    <cellStyle name="Note 8 16" xfId="2116"/>
-    <cellStyle name="Note 8 17" xfId="2178"/>
-    <cellStyle name="Note 8 18" xfId="2241"/>
-    <cellStyle name="Note 8 19" xfId="2300"/>
-    <cellStyle name="Note 8 2" xfId="1121"/>
-    <cellStyle name="Note 8 20" xfId="2361"/>
-    <cellStyle name="Note 8 21" xfId="2422"/>
-    <cellStyle name="Note 8 22" xfId="2485"/>
-    <cellStyle name="Note 8 23" xfId="2542"/>
-    <cellStyle name="Note 8 24" xfId="2603"/>
-    <cellStyle name="Note 8 25" xfId="2663"/>
-    <cellStyle name="Note 8 26" xfId="2710"/>
-    <cellStyle name="Note 8 27" xfId="2762"/>
-    <cellStyle name="Note 8 28" xfId="2810"/>
-    <cellStyle name="Note 8 29" xfId="2856"/>
-    <cellStyle name="Note 8 3" xfId="1197"/>
-    <cellStyle name="Note 8 30" xfId="2902"/>
-    <cellStyle name="Note 8 31" xfId="2951"/>
-    <cellStyle name="Note 8 32" xfId="2997"/>
-    <cellStyle name="Note 8 4" xfId="1273"/>
-    <cellStyle name="Note 8 5" xfId="1349"/>
-    <cellStyle name="Note 8 6" xfId="1425"/>
-    <cellStyle name="Note 8 7" xfId="1500"/>
-    <cellStyle name="Note 8 8" xfId="1576"/>
-    <cellStyle name="Note 8 9" xfId="1651"/>
-    <cellStyle name="Note 9" xfId="609"/>
-    <cellStyle name="Note 9 10" xfId="1726"/>
-    <cellStyle name="Note 9 11" xfId="1802"/>
-    <cellStyle name="Note 9 12" xfId="1866"/>
-    <cellStyle name="Note 9 13" xfId="1931"/>
-    <cellStyle name="Note 9 14" xfId="1994"/>
-    <cellStyle name="Note 9 15" xfId="2055"/>
-    <cellStyle name="Note 9 16" xfId="2117"/>
-    <cellStyle name="Note 9 17" xfId="2179"/>
-    <cellStyle name="Note 9 18" xfId="2242"/>
-    <cellStyle name="Note 9 19" xfId="2301"/>
-    <cellStyle name="Note 9 2" xfId="1122"/>
-    <cellStyle name="Note 9 20" xfId="2362"/>
-    <cellStyle name="Note 9 21" xfId="2423"/>
-    <cellStyle name="Note 9 22" xfId="2486"/>
-    <cellStyle name="Note 9 23" xfId="2543"/>
-    <cellStyle name="Note 9 24" xfId="2604"/>
-    <cellStyle name="Note 9 25" xfId="2664"/>
-    <cellStyle name="Note 9 26" xfId="2711"/>
-    <cellStyle name="Note 9 27" xfId="2763"/>
-    <cellStyle name="Note 9 28" xfId="2811"/>
-    <cellStyle name="Note 9 29" xfId="2857"/>
-    <cellStyle name="Note 9 3" xfId="1198"/>
-    <cellStyle name="Note 9 30" xfId="2903"/>
-    <cellStyle name="Note 9 31" xfId="2952"/>
-    <cellStyle name="Note 9 32" xfId="2998"/>
-    <cellStyle name="Note 9 4" xfId="1274"/>
-    <cellStyle name="Note 9 5" xfId="1350"/>
-    <cellStyle name="Note 9 6" xfId="1426"/>
-    <cellStyle name="Note 9 7" xfId="1501"/>
-    <cellStyle name="Note 9 8" xfId="1577"/>
-    <cellStyle name="Note 9 9" xfId="1652"/>
-    <cellStyle name="Output 10" xfId="610"/>
-    <cellStyle name="Output 10 10" xfId="1727"/>
-    <cellStyle name="Output 10 11" xfId="1803"/>
-    <cellStyle name="Output 10 12" xfId="1867"/>
-    <cellStyle name="Output 10 13" xfId="1932"/>
-    <cellStyle name="Output 10 14" xfId="1995"/>
-    <cellStyle name="Output 10 15" xfId="2056"/>
-    <cellStyle name="Output 10 16" xfId="2118"/>
-    <cellStyle name="Output 10 17" xfId="2180"/>
-    <cellStyle name="Output 10 18" xfId="2243"/>
-    <cellStyle name="Output 10 19" xfId="2302"/>
-    <cellStyle name="Output 10 2" xfId="1123"/>
-    <cellStyle name="Output 10 20" xfId="2363"/>
-    <cellStyle name="Output 10 21" xfId="2424"/>
-    <cellStyle name="Output 10 22" xfId="2487"/>
-    <cellStyle name="Output 10 23" xfId="2544"/>
-    <cellStyle name="Output 10 24" xfId="2605"/>
-    <cellStyle name="Output 10 25" xfId="2665"/>
-    <cellStyle name="Output 10 26" xfId="2712"/>
-    <cellStyle name="Output 10 27" xfId="2764"/>
-    <cellStyle name="Output 10 28" xfId="2812"/>
-    <cellStyle name="Output 10 29" xfId="2858"/>
-    <cellStyle name="Output 10 3" xfId="1199"/>
-    <cellStyle name="Output 10 30" xfId="2904"/>
-    <cellStyle name="Output 10 31" xfId="2953"/>
-    <cellStyle name="Output 10 32" xfId="2999"/>
-    <cellStyle name="Output 10 4" xfId="1275"/>
-    <cellStyle name="Output 10 5" xfId="1351"/>
-    <cellStyle name="Output 10 6" xfId="1427"/>
-    <cellStyle name="Output 10 7" xfId="1502"/>
-    <cellStyle name="Output 10 8" xfId="1578"/>
-    <cellStyle name="Output 10 9" xfId="1653"/>
-    <cellStyle name="Output 11" xfId="611"/>
-    <cellStyle name="Output 11 10" xfId="1728"/>
-    <cellStyle name="Output 11 11" xfId="1804"/>
-    <cellStyle name="Output 11 12" xfId="1868"/>
-    <cellStyle name="Output 11 13" xfId="1933"/>
-    <cellStyle name="Output 11 14" xfId="1996"/>
-    <cellStyle name="Output 11 15" xfId="2057"/>
-    <cellStyle name="Output 11 16" xfId="2119"/>
-    <cellStyle name="Output 11 17" xfId="2181"/>
-    <cellStyle name="Output 11 18" xfId="2244"/>
-    <cellStyle name="Output 11 19" xfId="2303"/>
-    <cellStyle name="Output 11 2" xfId="1124"/>
-    <cellStyle name="Output 11 20" xfId="2364"/>
-    <cellStyle name="Output 11 21" xfId="2425"/>
-    <cellStyle name="Output 11 22" xfId="2488"/>
-    <cellStyle name="Output 11 23" xfId="2545"/>
-    <cellStyle name="Output 11 24" xfId="2606"/>
-    <cellStyle name="Output 11 25" xfId="2666"/>
-    <cellStyle name="Output 11 26" xfId="2713"/>
-    <cellStyle name="Output 11 27" xfId="2765"/>
-    <cellStyle name="Output 11 28" xfId="2813"/>
-    <cellStyle name="Output 11 29" xfId="2859"/>
-    <cellStyle name="Output 11 3" xfId="1200"/>
-    <cellStyle name="Output 11 30" xfId="2905"/>
-    <cellStyle name="Output 11 31" xfId="2954"/>
-    <cellStyle name="Output 11 32" xfId="3000"/>
-    <cellStyle name="Output 11 4" xfId="1276"/>
-    <cellStyle name="Output 11 5" xfId="1352"/>
-    <cellStyle name="Output 11 6" xfId="1428"/>
-    <cellStyle name="Output 11 7" xfId="1503"/>
-    <cellStyle name="Output 11 8" xfId="1579"/>
-    <cellStyle name="Output 11 9" xfId="1654"/>
-    <cellStyle name="Output 12" xfId="612"/>
-    <cellStyle name="Output 12 10" xfId="1729"/>
-    <cellStyle name="Output 12 11" xfId="1805"/>
-    <cellStyle name="Output 12 12" xfId="1869"/>
-    <cellStyle name="Output 12 13" xfId="1934"/>
-    <cellStyle name="Output 12 14" xfId="1997"/>
-    <cellStyle name="Output 12 15" xfId="2058"/>
-    <cellStyle name="Output 12 16" xfId="2120"/>
-    <cellStyle name="Output 12 17" xfId="2182"/>
-    <cellStyle name="Output 12 18" xfId="2245"/>
-    <cellStyle name="Output 12 19" xfId="2304"/>
-    <cellStyle name="Output 12 2" xfId="1125"/>
-    <cellStyle name="Output 12 20" xfId="2365"/>
-    <cellStyle name="Output 12 21" xfId="2426"/>
-    <cellStyle name="Output 12 22" xfId="2489"/>
-    <cellStyle name="Output 12 23" xfId="2546"/>
-    <cellStyle name="Output 12 24" xfId="2607"/>
-    <cellStyle name="Output 12 25" xfId="2667"/>
-    <cellStyle name="Output 12 26" xfId="2714"/>
-    <cellStyle name="Output 12 27" xfId="2766"/>
-    <cellStyle name="Output 12 28" xfId="2814"/>
-    <cellStyle name="Output 12 29" xfId="2860"/>
-    <cellStyle name="Output 12 3" xfId="1201"/>
-    <cellStyle name="Output 12 30" xfId="2906"/>
-    <cellStyle name="Output 12 31" xfId="2955"/>
-    <cellStyle name="Output 12 32" xfId="3001"/>
-    <cellStyle name="Output 12 4" xfId="1277"/>
-    <cellStyle name="Output 12 5" xfId="1353"/>
-    <cellStyle name="Output 12 6" xfId="1429"/>
-    <cellStyle name="Output 12 7" xfId="1504"/>
-    <cellStyle name="Output 12 8" xfId="1580"/>
-    <cellStyle name="Output 12 9" xfId="1655"/>
-    <cellStyle name="Output 13" xfId="613"/>
-    <cellStyle name="Output 13 10" xfId="1730"/>
-    <cellStyle name="Output 13 11" xfId="1806"/>
-    <cellStyle name="Output 13 12" xfId="1870"/>
-    <cellStyle name="Output 13 13" xfId="1935"/>
-    <cellStyle name="Output 13 14" xfId="1998"/>
-    <cellStyle name="Output 13 15" xfId="2059"/>
-    <cellStyle name="Output 13 16" xfId="2121"/>
-    <cellStyle name="Output 13 17" xfId="2183"/>
-    <cellStyle name="Output 13 18" xfId="2246"/>
-    <cellStyle name="Output 13 19" xfId="2305"/>
-    <cellStyle name="Output 13 2" xfId="1126"/>
-    <cellStyle name="Output 13 20" xfId="2366"/>
-    <cellStyle name="Output 13 21" xfId="2427"/>
-    <cellStyle name="Output 13 22" xfId="2490"/>
-    <cellStyle name="Output 13 23" xfId="2547"/>
-    <cellStyle name="Output 13 24" xfId="2608"/>
-    <cellStyle name="Output 13 25" xfId="2668"/>
-    <cellStyle name="Output 13 26" xfId="2715"/>
-    <cellStyle name="Output 13 27" xfId="2767"/>
-    <cellStyle name="Output 13 28" xfId="2815"/>
-    <cellStyle name="Output 13 29" xfId="2861"/>
-    <cellStyle name="Output 13 3" xfId="1202"/>
-    <cellStyle name="Output 13 30" xfId="2907"/>
-    <cellStyle name="Output 13 31" xfId="2956"/>
-    <cellStyle name="Output 13 32" xfId="3002"/>
-    <cellStyle name="Output 13 4" xfId="1278"/>
-    <cellStyle name="Output 13 5" xfId="1354"/>
-    <cellStyle name="Output 13 6" xfId="1430"/>
-    <cellStyle name="Output 13 7" xfId="1505"/>
-    <cellStyle name="Output 13 8" xfId="1581"/>
-    <cellStyle name="Output 13 9" xfId="1656"/>
-    <cellStyle name="Output 14" xfId="614"/>
-    <cellStyle name="Output 14 10" xfId="1731"/>
-    <cellStyle name="Output 14 11" xfId="1807"/>
-    <cellStyle name="Output 14 12" xfId="1871"/>
-    <cellStyle name="Output 14 13" xfId="1936"/>
-    <cellStyle name="Output 14 14" xfId="1999"/>
-    <cellStyle name="Output 14 15" xfId="2060"/>
-    <cellStyle name="Output 14 16" xfId="2122"/>
-    <cellStyle name="Output 14 17" xfId="2184"/>
-    <cellStyle name="Output 14 18" xfId="2247"/>
-    <cellStyle name="Output 14 19" xfId="2306"/>
-    <cellStyle name="Output 14 2" xfId="1127"/>
-    <cellStyle name="Output 14 20" xfId="2367"/>
-    <cellStyle name="Output 14 21" xfId="2428"/>
-    <cellStyle name="Output 14 22" xfId="2491"/>
-    <cellStyle name="Output 14 23" xfId="2548"/>
-    <cellStyle name="Output 14 24" xfId="2609"/>
-    <cellStyle name="Output 14 25" xfId="2669"/>
-    <cellStyle name="Output 14 26" xfId="2716"/>
-    <cellStyle name="Output 14 27" xfId="2768"/>
-    <cellStyle name="Output 14 28" xfId="2816"/>
-    <cellStyle name="Output 14 29" xfId="2862"/>
-    <cellStyle name="Output 14 3" xfId="1203"/>
-    <cellStyle name="Output 14 30" xfId="2908"/>
-    <cellStyle name="Output 14 31" xfId="2957"/>
-    <cellStyle name="Output 14 32" xfId="3003"/>
-    <cellStyle name="Output 14 4" xfId="1279"/>
-    <cellStyle name="Output 14 5" xfId="1355"/>
-    <cellStyle name="Output 14 6" xfId="1431"/>
-    <cellStyle name="Output 14 7" xfId="1506"/>
-    <cellStyle name="Output 14 8" xfId="1582"/>
-    <cellStyle name="Output 14 9" xfId="1657"/>
-    <cellStyle name="Output 15" xfId="615"/>
-    <cellStyle name="Output 15 10" xfId="1732"/>
-    <cellStyle name="Output 15 11" xfId="1808"/>
-    <cellStyle name="Output 15 12" xfId="1872"/>
-    <cellStyle name="Output 15 13" xfId="1937"/>
-    <cellStyle name="Output 15 14" xfId="2000"/>
-    <cellStyle name="Output 15 15" xfId="2061"/>
-    <cellStyle name="Output 15 16" xfId="2123"/>
-    <cellStyle name="Output 15 17" xfId="2185"/>
-    <cellStyle name="Output 15 18" xfId="2248"/>
-    <cellStyle name="Output 15 19" xfId="2307"/>
-    <cellStyle name="Output 15 2" xfId="1128"/>
-    <cellStyle name="Output 15 20" xfId="2368"/>
-    <cellStyle name="Output 15 21" xfId="2429"/>
-    <cellStyle name="Output 15 22" xfId="2492"/>
-    <cellStyle name="Output 15 23" xfId="2549"/>
-    <cellStyle name="Output 15 24" xfId="2610"/>
-    <cellStyle name="Output 15 25" xfId="2670"/>
-    <cellStyle name="Output 15 26" xfId="2717"/>
-    <cellStyle name="Output 15 27" xfId="2769"/>
-    <cellStyle name="Output 15 28" xfId="2817"/>
-    <cellStyle name="Output 15 29" xfId="2863"/>
-    <cellStyle name="Output 15 3" xfId="1204"/>
-    <cellStyle name="Output 15 30" xfId="2909"/>
-    <cellStyle name="Output 15 31" xfId="2958"/>
-    <cellStyle name="Output 15 32" xfId="3004"/>
-    <cellStyle name="Output 15 4" xfId="1280"/>
-    <cellStyle name="Output 15 5" xfId="1356"/>
-    <cellStyle name="Output 15 6" xfId="1432"/>
-    <cellStyle name="Output 15 7" xfId="1507"/>
-    <cellStyle name="Output 15 8" xfId="1583"/>
-    <cellStyle name="Output 15 9" xfId="1658"/>
-    <cellStyle name="Output 16" xfId="616"/>
-    <cellStyle name="Output 16 10" xfId="1733"/>
-    <cellStyle name="Output 16 11" xfId="1809"/>
-    <cellStyle name="Output 16 12" xfId="1873"/>
-    <cellStyle name="Output 16 13" xfId="1938"/>
-    <cellStyle name="Output 16 14" xfId="2001"/>
-    <cellStyle name="Output 16 15" xfId="2062"/>
-    <cellStyle name="Output 16 16" xfId="2124"/>
-    <cellStyle name="Output 16 17" xfId="2186"/>
-    <cellStyle name="Output 16 18" xfId="2249"/>
-    <cellStyle name="Output 16 19" xfId="2308"/>
-    <cellStyle name="Output 16 2" xfId="1129"/>
-    <cellStyle name="Output 16 20" xfId="2369"/>
-    <cellStyle name="Output 16 21" xfId="2430"/>
-    <cellStyle name="Output 16 22" xfId="2493"/>
-    <cellStyle name="Output 16 23" xfId="2550"/>
-    <cellStyle name="Output 16 24" xfId="2611"/>
-    <cellStyle name="Output 16 25" xfId="2671"/>
-    <cellStyle name="Output 16 26" xfId="2718"/>
-    <cellStyle name="Output 16 27" xfId="2770"/>
-    <cellStyle name="Output 16 28" xfId="2818"/>
-    <cellStyle name="Output 16 29" xfId="2864"/>
-    <cellStyle name="Output 16 3" xfId="1205"/>
-    <cellStyle name="Output 16 30" xfId="2910"/>
-    <cellStyle name="Output 16 31" xfId="2959"/>
-    <cellStyle name="Output 16 32" xfId="3005"/>
-    <cellStyle name="Output 16 4" xfId="1281"/>
-    <cellStyle name="Output 16 5" xfId="1357"/>
-    <cellStyle name="Output 16 6" xfId="1433"/>
-    <cellStyle name="Output 16 7" xfId="1508"/>
-    <cellStyle name="Output 16 8" xfId="1584"/>
-    <cellStyle name="Output 16 9" xfId="1659"/>
-    <cellStyle name="Output 2" xfId="617"/>
-    <cellStyle name="Output 2 10" xfId="1734"/>
-    <cellStyle name="Output 2 11" xfId="1810"/>
-    <cellStyle name="Output 2 12" xfId="1874"/>
-    <cellStyle name="Output 2 13" xfId="1939"/>
-    <cellStyle name="Output 2 14" xfId="2002"/>
-    <cellStyle name="Output 2 15" xfId="2063"/>
-    <cellStyle name="Output 2 16" xfId="2125"/>
-    <cellStyle name="Output 2 17" xfId="2187"/>
-    <cellStyle name="Output 2 18" xfId="2250"/>
-    <cellStyle name="Output 2 19" xfId="2309"/>
-    <cellStyle name="Output 2 2" xfId="1130"/>
-    <cellStyle name="Output 2 20" xfId="2370"/>
-    <cellStyle name="Output 2 21" xfId="2431"/>
-    <cellStyle name="Output 2 22" xfId="2494"/>
-    <cellStyle name="Output 2 23" xfId="2551"/>
-    <cellStyle name="Output 2 24" xfId="2612"/>
-    <cellStyle name="Output 2 25" xfId="2672"/>
-    <cellStyle name="Output 2 26" xfId="2719"/>
-    <cellStyle name="Output 2 27" xfId="2771"/>
-    <cellStyle name="Output 2 28" xfId="2819"/>
-    <cellStyle name="Output 2 29" xfId="2865"/>
-    <cellStyle name="Output 2 3" xfId="1206"/>
-    <cellStyle name="Output 2 30" xfId="2911"/>
-    <cellStyle name="Output 2 31" xfId="2960"/>
-    <cellStyle name="Output 2 32" xfId="3006"/>
-    <cellStyle name="Output 2 4" xfId="1282"/>
-    <cellStyle name="Output 2 5" xfId="1358"/>
-    <cellStyle name="Output 2 6" xfId="1434"/>
-    <cellStyle name="Output 2 7" xfId="1509"/>
-    <cellStyle name="Output 2 8" xfId="1585"/>
-    <cellStyle name="Output 2 9" xfId="1660"/>
-    <cellStyle name="Output 3" xfId="618"/>
-    <cellStyle name="Output 3 10" xfId="1735"/>
-    <cellStyle name="Output 3 11" xfId="1811"/>
-    <cellStyle name="Output 3 12" xfId="1875"/>
-    <cellStyle name="Output 3 13" xfId="1940"/>
-    <cellStyle name="Output 3 14" xfId="2003"/>
-    <cellStyle name="Output 3 15" xfId="2064"/>
-    <cellStyle name="Output 3 16" xfId="2126"/>
-    <cellStyle name="Output 3 17" xfId="2188"/>
-    <cellStyle name="Output 3 18" xfId="2251"/>
-    <cellStyle name="Output 3 19" xfId="2310"/>
-    <cellStyle name="Output 3 2" xfId="1131"/>
-    <cellStyle name="Output 3 20" xfId="2371"/>
-    <cellStyle name="Output 3 21" xfId="2432"/>
-    <cellStyle name="Output 3 22" xfId="2495"/>
-    <cellStyle name="Output 3 23" xfId="2552"/>
-    <cellStyle name="Output 3 24" xfId="2613"/>
-    <cellStyle name="Output 3 25" xfId="2673"/>
-    <cellStyle name="Output 3 26" xfId="2720"/>
-    <cellStyle name="Output 3 27" xfId="2772"/>
-    <cellStyle name="Output 3 28" xfId="2820"/>
-    <cellStyle name="Output 3 29" xfId="2866"/>
-    <cellStyle name="Output 3 3" xfId="1207"/>
-    <cellStyle name="Output 3 30" xfId="2912"/>
-    <cellStyle name="Output 3 31" xfId="2961"/>
-    <cellStyle name="Output 3 32" xfId="3007"/>
-    <cellStyle name="Output 3 4" xfId="1283"/>
-    <cellStyle name="Output 3 5" xfId="1359"/>
-    <cellStyle name="Output 3 6" xfId="1435"/>
-    <cellStyle name="Output 3 7" xfId="1510"/>
-    <cellStyle name="Output 3 8" xfId="1586"/>
-    <cellStyle name="Output 3 9" xfId="1661"/>
-    <cellStyle name="Output 4" xfId="619"/>
-    <cellStyle name="Output 4 10" xfId="1736"/>
-    <cellStyle name="Output 4 11" xfId="1812"/>
-    <cellStyle name="Output 4 12" xfId="1876"/>
-    <cellStyle name="Output 4 13" xfId="1941"/>
-    <cellStyle name="Output 4 14" xfId="2004"/>
-    <cellStyle name="Output 4 15" xfId="2065"/>
-    <cellStyle name="Output 4 16" xfId="2127"/>
-    <cellStyle name="Output 4 17" xfId="2189"/>
-    <cellStyle name="Output 4 18" xfId="2252"/>
-    <cellStyle name="Output 4 19" xfId="2311"/>
-    <cellStyle name="Output 4 2" xfId="1132"/>
-    <cellStyle name="Output 4 20" xfId="2372"/>
-    <cellStyle name="Output 4 21" xfId="2433"/>
-    <cellStyle name="Output 4 22" xfId="2496"/>
-    <cellStyle name="Output 4 23" xfId="2553"/>
-    <cellStyle name="Output 4 24" xfId="2614"/>
-    <cellStyle name="Output 4 25" xfId="2674"/>
-    <cellStyle name="Output 4 26" xfId="2721"/>
-    <cellStyle name="Output 4 27" xfId="2773"/>
-    <cellStyle name="Output 4 28" xfId="2821"/>
-    <cellStyle name="Output 4 29" xfId="2867"/>
-    <cellStyle name="Output 4 3" xfId="1208"/>
-    <cellStyle name="Output 4 30" xfId="2913"/>
-    <cellStyle name="Output 4 31" xfId="2962"/>
-    <cellStyle name="Output 4 32" xfId="3008"/>
-    <cellStyle name="Output 4 4" xfId="1284"/>
-    <cellStyle name="Output 4 5" xfId="1360"/>
-    <cellStyle name="Output 4 6" xfId="1436"/>
-    <cellStyle name="Output 4 7" xfId="1511"/>
-    <cellStyle name="Output 4 8" xfId="1587"/>
-    <cellStyle name="Output 4 9" xfId="1662"/>
-    <cellStyle name="Output 5" xfId="620"/>
-    <cellStyle name="Output 5 10" xfId="1737"/>
-    <cellStyle name="Output 5 11" xfId="1813"/>
-    <cellStyle name="Output 5 12" xfId="1877"/>
-    <cellStyle name="Output 5 13" xfId="1942"/>
-    <cellStyle name="Output 5 14" xfId="2005"/>
-    <cellStyle name="Output 5 15" xfId="2066"/>
-    <cellStyle name="Output 5 16" xfId="2128"/>
-    <cellStyle name="Output 5 17" xfId="2190"/>
-    <cellStyle name="Output 5 18" xfId="2253"/>
-    <cellStyle name="Output 5 19" xfId="2312"/>
-    <cellStyle name="Output 5 2" xfId="1133"/>
-    <cellStyle name="Output 5 20" xfId="2373"/>
-    <cellStyle name="Output 5 21" xfId="2434"/>
-    <cellStyle name="Output 5 22" xfId="2497"/>
-    <cellStyle name="Output 5 23" xfId="2554"/>
-    <cellStyle name="Output 5 24" xfId="2615"/>
-    <cellStyle name="Output 5 25" xfId="2675"/>
-    <cellStyle name="Output 5 26" xfId="2722"/>
-    <cellStyle name="Output 5 27" xfId="2774"/>
-    <cellStyle name="Output 5 28" xfId="2822"/>
-    <cellStyle name="Output 5 29" xfId="2868"/>
-    <cellStyle name="Output 5 3" xfId="1209"/>
-    <cellStyle name="Output 5 30" xfId="2914"/>
-    <cellStyle name="Output 5 31" xfId="2963"/>
-    <cellStyle name="Output 5 32" xfId="3009"/>
-    <cellStyle name="Output 5 4" xfId="1285"/>
-    <cellStyle name="Output 5 5" xfId="1361"/>
-    <cellStyle name="Output 5 6" xfId="1437"/>
-    <cellStyle name="Output 5 7" xfId="1512"/>
-    <cellStyle name="Output 5 8" xfId="1588"/>
-    <cellStyle name="Output 5 9" xfId="1663"/>
-    <cellStyle name="Output 6" xfId="621"/>
-    <cellStyle name="Output 6 10" xfId="1738"/>
-    <cellStyle name="Output 6 11" xfId="1814"/>
-    <cellStyle name="Output 6 12" xfId="1878"/>
-    <cellStyle name="Output 6 13" xfId="1943"/>
-    <cellStyle name="Output 6 14" xfId="2006"/>
-    <cellStyle name="Output 6 15" xfId="2067"/>
-    <cellStyle name="Output 6 16" xfId="2129"/>
-    <cellStyle name="Output 6 17" xfId="2191"/>
-    <cellStyle name="Output 6 18" xfId="2254"/>
-    <cellStyle name="Output 6 19" xfId="2313"/>
-    <cellStyle name="Output 6 2" xfId="1134"/>
-    <cellStyle name="Output 6 20" xfId="2374"/>
-    <cellStyle name="Output 6 21" xfId="2435"/>
-    <cellStyle name="Output 6 22" xfId="2498"/>
-    <cellStyle name="Output 6 23" xfId="2555"/>
-    <cellStyle name="Output 6 24" xfId="2616"/>
-    <cellStyle name="Output 6 25" xfId="2676"/>
-    <cellStyle name="Output 6 26" xfId="2723"/>
-    <cellStyle name="Output 6 27" xfId="2775"/>
-    <cellStyle name="Output 6 28" xfId="2823"/>
-    <cellStyle name="Output 6 29" xfId="2869"/>
-    <cellStyle name="Output 6 3" xfId="1210"/>
-    <cellStyle name="Output 6 30" xfId="2915"/>
-    <cellStyle name="Output 6 31" xfId="2964"/>
-    <cellStyle name="Output 6 32" xfId="3010"/>
-    <cellStyle name="Output 6 4" xfId="1286"/>
-    <cellStyle name="Output 6 5" xfId="1362"/>
-    <cellStyle name="Output 6 6" xfId="1438"/>
-    <cellStyle name="Output 6 7" xfId="1513"/>
-    <cellStyle name="Output 6 8" xfId="1589"/>
-    <cellStyle name="Output 6 9" xfId="1664"/>
-    <cellStyle name="Output 7" xfId="622"/>
-    <cellStyle name="Output 7 10" xfId="1739"/>
-    <cellStyle name="Output 7 11" xfId="1815"/>
-    <cellStyle name="Output 7 12" xfId="1879"/>
-    <cellStyle name="Output 7 13" xfId="1944"/>
-    <cellStyle name="Output 7 14" xfId="2007"/>
-    <cellStyle name="Output 7 15" xfId="2068"/>
-    <cellStyle name="Output 7 16" xfId="2130"/>
-    <cellStyle name="Output 7 17" xfId="2192"/>
-    <cellStyle name="Output 7 18" xfId="2255"/>
-    <cellStyle name="Output 7 19" xfId="2314"/>
-    <cellStyle name="Output 7 2" xfId="1135"/>
-    <cellStyle name="Output 7 20" xfId="2375"/>
-    <cellStyle name="Output 7 21" xfId="2436"/>
-    <cellStyle name="Output 7 22" xfId="2499"/>
-    <cellStyle name="Output 7 23" xfId="2556"/>
-    <cellStyle name="Output 7 24" xfId="2617"/>
-    <cellStyle name="Output 7 25" xfId="2677"/>
-    <cellStyle name="Output 7 26" xfId="2724"/>
-    <cellStyle name="Output 7 27" xfId="2776"/>
-    <cellStyle name="Output 7 28" xfId="2824"/>
-    <cellStyle name="Output 7 29" xfId="2870"/>
-    <cellStyle name="Output 7 3" xfId="1211"/>
-    <cellStyle name="Output 7 30" xfId="2916"/>
-    <cellStyle name="Output 7 31" xfId="2965"/>
-    <cellStyle name="Output 7 32" xfId="3011"/>
-    <cellStyle name="Output 7 4" xfId="1287"/>
-    <cellStyle name="Output 7 5" xfId="1363"/>
-    <cellStyle name="Output 7 6" xfId="1439"/>
-    <cellStyle name="Output 7 7" xfId="1514"/>
-    <cellStyle name="Output 7 8" xfId="1590"/>
-    <cellStyle name="Output 7 9" xfId="1665"/>
-    <cellStyle name="Output 8" xfId="623"/>
-    <cellStyle name="Output 8 10" xfId="1740"/>
-    <cellStyle name="Output 8 11" xfId="1816"/>
-    <cellStyle name="Output 8 12" xfId="1880"/>
-    <cellStyle name="Output 8 13" xfId="1945"/>
-    <cellStyle name="Output 8 14" xfId="2008"/>
-    <cellStyle name="Output 8 15" xfId="2069"/>
-    <cellStyle name="Output 8 16" xfId="2131"/>
-    <cellStyle name="Output 8 17" xfId="2193"/>
-    <cellStyle name="Output 8 18" xfId="2256"/>
-    <cellStyle name="Output 8 19" xfId="2315"/>
-    <cellStyle name="Output 8 2" xfId="1136"/>
-    <cellStyle name="Output 8 20" xfId="2376"/>
-    <cellStyle name="Output 8 21" xfId="2437"/>
-    <cellStyle name="Output 8 22" xfId="2500"/>
-    <cellStyle name="Output 8 23" xfId="2557"/>
-    <cellStyle name="Output 8 24" xfId="2618"/>
-    <cellStyle name="Output 8 25" xfId="2678"/>
-    <cellStyle name="Output 8 26" xfId="2725"/>
-    <cellStyle name="Output 8 27" xfId="2777"/>
-    <cellStyle name="Output 8 28" xfId="2825"/>
-    <cellStyle name="Output 8 29" xfId="2871"/>
-    <cellStyle name="Output 8 3" xfId="1212"/>
-    <cellStyle name="Output 8 30" xfId="2917"/>
-    <cellStyle name="Output 8 31" xfId="2966"/>
-    <cellStyle name="Output 8 32" xfId="3012"/>
-    <cellStyle name="Output 8 4" xfId="1288"/>
-    <cellStyle name="Output 8 5" xfId="1364"/>
-    <cellStyle name="Output 8 6" xfId="1440"/>
-    <cellStyle name="Output 8 7" xfId="1515"/>
-    <cellStyle name="Output 8 8" xfId="1591"/>
-    <cellStyle name="Output 8 9" xfId="1666"/>
-    <cellStyle name="Output 9" xfId="624"/>
-    <cellStyle name="Output 9 10" xfId="1741"/>
-    <cellStyle name="Output 9 11" xfId="1817"/>
-    <cellStyle name="Output 9 12" xfId="1881"/>
-    <cellStyle name="Output 9 13" xfId="1946"/>
-    <cellStyle name="Output 9 14" xfId="2009"/>
-    <cellStyle name="Output 9 15" xfId="2070"/>
-    <cellStyle name="Output 9 16" xfId="2132"/>
-    <cellStyle name="Output 9 17" xfId="2194"/>
-    <cellStyle name="Output 9 18" xfId="2257"/>
-    <cellStyle name="Output 9 19" xfId="2316"/>
-    <cellStyle name="Output 9 2" xfId="1137"/>
-    <cellStyle name="Output 9 20" xfId="2377"/>
-    <cellStyle name="Output 9 21" xfId="2438"/>
-    <cellStyle name="Output 9 22" xfId="2501"/>
-    <cellStyle name="Output 9 23" xfId="2558"/>
-    <cellStyle name="Output 9 24" xfId="2619"/>
-    <cellStyle name="Output 9 25" xfId="2679"/>
-    <cellStyle name="Output 9 26" xfId="2726"/>
-    <cellStyle name="Output 9 27" xfId="2778"/>
-    <cellStyle name="Output 9 28" xfId="2826"/>
-    <cellStyle name="Output 9 29" xfId="2872"/>
-    <cellStyle name="Output 9 3" xfId="1213"/>
-    <cellStyle name="Output 9 30" xfId="2918"/>
-    <cellStyle name="Output 9 31" xfId="2967"/>
-    <cellStyle name="Output 9 32" xfId="3013"/>
-    <cellStyle name="Output 9 4" xfId="1289"/>
-    <cellStyle name="Output 9 5" xfId="1365"/>
-    <cellStyle name="Output 9 6" xfId="1441"/>
-    <cellStyle name="Output 9 7" xfId="1516"/>
-    <cellStyle name="Output 9 8" xfId="1592"/>
-    <cellStyle name="Output 9 9" xfId="1667"/>
-    <cellStyle name="Percent 2" xfId="3032"/>
-    <cellStyle name="Title 10" xfId="625"/>
-    <cellStyle name="Title 11" xfId="626"/>
-    <cellStyle name="Title 12" xfId="627"/>
-    <cellStyle name="Title 13" xfId="628"/>
-    <cellStyle name="Title 14" xfId="629"/>
-    <cellStyle name="Title 15" xfId="630"/>
-    <cellStyle name="Title 16" xfId="631"/>
-    <cellStyle name="Title 2" xfId="632"/>
-    <cellStyle name="Title 3" xfId="633"/>
-    <cellStyle name="Title 4" xfId="634"/>
-    <cellStyle name="Title 5" xfId="635"/>
-    <cellStyle name="Title 6" xfId="636"/>
-    <cellStyle name="Title 7" xfId="637"/>
-    <cellStyle name="Title 8" xfId="638"/>
-    <cellStyle name="Title 9" xfId="639"/>
-    <cellStyle name="Total 10" xfId="640"/>
-    <cellStyle name="Total 10 10" xfId="1757"/>
-    <cellStyle name="Total 10 11" xfId="1822"/>
-    <cellStyle name="Total 10 12" xfId="1888"/>
-    <cellStyle name="Total 10 13" xfId="1952"/>
-    <cellStyle name="Total 10 14" xfId="2014"/>
-    <cellStyle name="Total 10 15" xfId="2075"/>
-    <cellStyle name="Total 10 16" xfId="2139"/>
-    <cellStyle name="Total 10 17" xfId="2200"/>
-    <cellStyle name="Total 10 18" xfId="2261"/>
-    <cellStyle name="Total 10 19" xfId="2321"/>
-    <cellStyle name="Total 10 2" xfId="1153"/>
-    <cellStyle name="Total 10 20" xfId="2382"/>
-    <cellStyle name="Total 10 21" xfId="2444"/>
-    <cellStyle name="Total 10 22" xfId="2503"/>
-    <cellStyle name="Total 10 23" xfId="2566"/>
-    <cellStyle name="Total 10 24" xfId="2625"/>
-    <cellStyle name="Total 10 25" xfId="2680"/>
-    <cellStyle name="Total 10 26" xfId="2732"/>
-    <cellStyle name="Total 10 27" xfId="2779"/>
-    <cellStyle name="Total 10 28" xfId="2827"/>
-    <cellStyle name="Total 10 29" xfId="2873"/>
-    <cellStyle name="Total 10 3" xfId="1229"/>
-    <cellStyle name="Total 10 30" xfId="2919"/>
-    <cellStyle name="Total 10 31" xfId="2968"/>
-    <cellStyle name="Total 10 32" xfId="3014"/>
-    <cellStyle name="Total 10 4" xfId="1305"/>
-    <cellStyle name="Total 10 5" xfId="1381"/>
-    <cellStyle name="Total 10 6" xfId="1456"/>
-    <cellStyle name="Total 10 7" xfId="1532"/>
-    <cellStyle name="Total 10 8" xfId="1607"/>
-    <cellStyle name="Total 10 9" xfId="1681"/>
-    <cellStyle name="Total 11" xfId="641"/>
-    <cellStyle name="Total 11 10" xfId="1758"/>
-    <cellStyle name="Total 11 11" xfId="1823"/>
-    <cellStyle name="Total 11 12" xfId="1889"/>
-    <cellStyle name="Total 11 13" xfId="1953"/>
-    <cellStyle name="Total 11 14" xfId="2015"/>
-    <cellStyle name="Total 11 15" xfId="2076"/>
-    <cellStyle name="Total 11 16" xfId="2140"/>
-    <cellStyle name="Total 11 17" xfId="2201"/>
-    <cellStyle name="Total 11 18" xfId="2262"/>
-    <cellStyle name="Total 11 19" xfId="2322"/>
-    <cellStyle name="Total 11 2" xfId="1154"/>
-    <cellStyle name="Total 11 20" xfId="2383"/>
-    <cellStyle name="Total 11 21" xfId="2445"/>
-    <cellStyle name="Total 11 22" xfId="2504"/>
-    <cellStyle name="Total 11 23" xfId="2567"/>
-    <cellStyle name="Total 11 24" xfId="2626"/>
-    <cellStyle name="Total 11 25" xfId="2681"/>
-    <cellStyle name="Total 11 26" xfId="2733"/>
-    <cellStyle name="Total 11 27" xfId="2780"/>
-    <cellStyle name="Total 11 28" xfId="2828"/>
-    <cellStyle name="Total 11 29" xfId="2874"/>
-    <cellStyle name="Total 11 3" xfId="1230"/>
-    <cellStyle name="Total 11 30" xfId="2920"/>
-    <cellStyle name="Total 11 31" xfId="2969"/>
-    <cellStyle name="Total 11 32" xfId="3015"/>
-    <cellStyle name="Total 11 4" xfId="1306"/>
-    <cellStyle name="Total 11 5" xfId="1382"/>
-    <cellStyle name="Total 11 6" xfId="1457"/>
-    <cellStyle name="Total 11 7" xfId="1533"/>
-    <cellStyle name="Total 11 8" xfId="1608"/>
-    <cellStyle name="Total 11 9" xfId="1682"/>
-    <cellStyle name="Total 12" xfId="642"/>
-    <cellStyle name="Total 12 10" xfId="1759"/>
-    <cellStyle name="Total 12 11" xfId="1824"/>
-    <cellStyle name="Total 12 12" xfId="1890"/>
-    <cellStyle name="Total 12 13" xfId="1954"/>
-    <cellStyle name="Total 12 14" xfId="2016"/>
-    <cellStyle name="Total 12 15" xfId="2077"/>
-    <cellStyle name="Total 12 16" xfId="2141"/>
-    <cellStyle name="Total 12 17" xfId="2202"/>
-    <cellStyle name="Total 12 18" xfId="2263"/>
-    <cellStyle name="Total 12 19" xfId="2323"/>
-    <cellStyle name="Total 12 2" xfId="1155"/>
-    <cellStyle name="Total 12 20" xfId="2384"/>
-    <cellStyle name="Total 12 21" xfId="2446"/>
-    <cellStyle name="Total 12 22" xfId="2505"/>
-    <cellStyle name="Total 12 23" xfId="2568"/>
-    <cellStyle name="Total 12 24" xfId="2627"/>
-    <cellStyle name="Total 12 25" xfId="2682"/>
-    <cellStyle name="Total 12 26" xfId="2734"/>
-    <cellStyle name="Total 12 27" xfId="2781"/>
-    <cellStyle name="Total 12 28" xfId="2829"/>
-    <cellStyle name="Total 12 29" xfId="2875"/>
-    <cellStyle name="Total 12 3" xfId="1231"/>
-    <cellStyle name="Total 12 30" xfId="2921"/>
-    <cellStyle name="Total 12 31" xfId="2970"/>
-    <cellStyle name="Total 12 32" xfId="3016"/>
-    <cellStyle name="Total 12 4" xfId="1307"/>
-    <cellStyle name="Total 12 5" xfId="1383"/>
-    <cellStyle name="Total 12 6" xfId="1458"/>
-    <cellStyle name="Total 12 7" xfId="1534"/>
-    <cellStyle name="Total 12 8" xfId="1609"/>
-    <cellStyle name="Total 12 9" xfId="1683"/>
-    <cellStyle name="Total 13" xfId="643"/>
-    <cellStyle name="Total 13 10" xfId="1760"/>
-    <cellStyle name="Total 13 11" xfId="1825"/>
-    <cellStyle name="Total 13 12" xfId="1891"/>
-    <cellStyle name="Total 13 13" xfId="1955"/>
-    <cellStyle name="Total 13 14" xfId="2017"/>
-    <cellStyle name="Total 13 15" xfId="2078"/>
-    <cellStyle name="Total 13 16" xfId="2142"/>
-    <cellStyle name="Total 13 17" xfId="2203"/>
-    <cellStyle name="Total 13 18" xfId="2264"/>
-    <cellStyle name="Total 13 19" xfId="2324"/>
-    <cellStyle name="Total 13 2" xfId="1156"/>
-    <cellStyle name="Total 13 20" xfId="2385"/>
-    <cellStyle name="Total 13 21" xfId="2447"/>
-    <cellStyle name="Total 13 22" xfId="2506"/>
-    <cellStyle name="Total 13 23" xfId="2569"/>
-    <cellStyle name="Total 13 24" xfId="2628"/>
-    <cellStyle name="Total 13 25" xfId="2683"/>
-    <cellStyle name="Total 13 26" xfId="2735"/>
-    <cellStyle name="Total 13 27" xfId="2782"/>
-    <cellStyle name="Total 13 28" xfId="2830"/>
-    <cellStyle name="Total 13 29" xfId="2876"/>
-    <cellStyle name="Total 13 3" xfId="1232"/>
-    <cellStyle name="Total 13 30" xfId="2922"/>
-    <cellStyle name="Total 13 31" xfId="2971"/>
-    <cellStyle name="Total 13 32" xfId="3017"/>
-    <cellStyle name="Total 13 4" xfId="1308"/>
-    <cellStyle name="Total 13 5" xfId="1384"/>
-    <cellStyle name="Total 13 6" xfId="1459"/>
-    <cellStyle name="Total 13 7" xfId="1535"/>
-    <cellStyle name="Total 13 8" xfId="1610"/>
-    <cellStyle name="Total 13 9" xfId="1684"/>
-    <cellStyle name="Total 14" xfId="644"/>
-    <cellStyle name="Total 14 10" xfId="1761"/>
-    <cellStyle name="Total 14 11" xfId="1826"/>
-    <cellStyle name="Total 14 12" xfId="1892"/>
-    <cellStyle name="Total 14 13" xfId="1956"/>
-    <cellStyle name="Total 14 14" xfId="2018"/>
-    <cellStyle name="Total 14 15" xfId="2079"/>
-    <cellStyle name="Total 14 16" xfId="2143"/>
-    <cellStyle name="Total 14 17" xfId="2204"/>
-    <cellStyle name="Total 14 18" xfId="2265"/>
-    <cellStyle name="Total 14 19" xfId="2325"/>
-    <cellStyle name="Total 14 2" xfId="1157"/>
-    <cellStyle name="Total 14 20" xfId="2386"/>
-    <cellStyle name="Total 14 21" xfId="2448"/>
-    <cellStyle name="Total 14 22" xfId="2507"/>
-    <cellStyle name="Total 14 23" xfId="2570"/>
-    <cellStyle name="Total 14 24" xfId="2629"/>
-    <cellStyle name="Total 14 25" xfId="2684"/>
-    <cellStyle name="Total 14 26" xfId="2736"/>
-    <cellStyle name="Total 14 27" xfId="2783"/>
-    <cellStyle name="Total 14 28" xfId="2831"/>
-    <cellStyle name="Total 14 29" xfId="2877"/>
-    <cellStyle name="Total 14 3" xfId="1233"/>
-    <cellStyle name="Total 14 30" xfId="2923"/>
-    <cellStyle name="Total 14 31" xfId="2972"/>
-    <cellStyle name="Total 14 32" xfId="3018"/>
-    <cellStyle name="Total 14 4" xfId="1309"/>
-    <cellStyle name="Total 14 5" xfId="1385"/>
-    <cellStyle name="Total 14 6" xfId="1460"/>
-    <cellStyle name="Total 14 7" xfId="1536"/>
-    <cellStyle name="Total 14 8" xfId="1611"/>
-    <cellStyle name="Total 14 9" xfId="1685"/>
-    <cellStyle name="Total 15" xfId="645"/>
-    <cellStyle name="Total 15 10" xfId="1762"/>
-    <cellStyle name="Total 15 11" xfId="1827"/>
-    <cellStyle name="Total 15 12" xfId="1893"/>
-    <cellStyle name="Total 15 13" xfId="1957"/>
-    <cellStyle name="Total 15 14" xfId="2019"/>
-    <cellStyle name="Total 15 15" xfId="2080"/>
-    <cellStyle name="Total 15 16" xfId="2144"/>
-    <cellStyle name="Total 15 17" xfId="2205"/>
-    <cellStyle name="Total 15 18" xfId="2266"/>
-    <cellStyle name="Total 15 19" xfId="2326"/>
-    <cellStyle name="Total 15 2" xfId="1158"/>
-    <cellStyle name="Total 15 20" xfId="2387"/>
-    <cellStyle name="Total 15 21" xfId="2449"/>
-    <cellStyle name="Total 15 22" xfId="2508"/>
-    <cellStyle name="Total 15 23" xfId="2571"/>
-    <cellStyle name="Total 15 24" xfId="2630"/>
-    <cellStyle name="Total 15 25" xfId="2685"/>
-    <cellStyle name="Total 15 26" xfId="2737"/>
-    <cellStyle name="Total 15 27" xfId="2784"/>
-    <cellStyle name="Total 15 28" xfId="2832"/>
-    <cellStyle name="Total 15 29" xfId="2878"/>
-    <cellStyle name="Total 15 3" xfId="1234"/>
-    <cellStyle name="Total 15 30" xfId="2924"/>
-    <cellStyle name="Total 15 31" xfId="2973"/>
-    <cellStyle name="Total 15 32" xfId="3019"/>
-    <cellStyle name="Total 15 4" xfId="1310"/>
-    <cellStyle name="Total 15 5" xfId="1386"/>
-    <cellStyle name="Total 15 6" xfId="1461"/>
-    <cellStyle name="Total 15 7" xfId="1537"/>
-    <cellStyle name="Total 15 8" xfId="1612"/>
-    <cellStyle name="Total 15 9" xfId="1686"/>
-    <cellStyle name="Total 16" xfId="646"/>
-    <cellStyle name="Total 16 10" xfId="1763"/>
-    <cellStyle name="Total 16 11" xfId="1828"/>
-    <cellStyle name="Total 16 12" xfId="1894"/>
-    <cellStyle name="Total 16 13" xfId="1958"/>
-    <cellStyle name="Total 16 14" xfId="2020"/>
-    <cellStyle name="Total 16 15" xfId="2081"/>
-    <cellStyle name="Total 16 16" xfId="2145"/>
-    <cellStyle name="Total 16 17" xfId="2206"/>
-    <cellStyle name="Total 16 18" xfId="2267"/>
-    <cellStyle name="Total 16 19" xfId="2327"/>
-    <cellStyle name="Total 16 2" xfId="1159"/>
-    <cellStyle name="Total 16 20" xfId="2388"/>
-    <cellStyle name="Total 16 21" xfId="2450"/>
-    <cellStyle name="Total 16 22" xfId="2509"/>
-    <cellStyle name="Total 16 23" xfId="2572"/>
-    <cellStyle name="Total 16 24" xfId="2631"/>
-    <cellStyle name="Total 16 25" xfId="2686"/>
-    <cellStyle name="Total 16 26" xfId="2738"/>
-    <cellStyle name="Total 16 27" xfId="2785"/>
-    <cellStyle name="Total 16 28" xfId="2833"/>
-    <cellStyle name="Total 16 29" xfId="2879"/>
-    <cellStyle name="Total 16 3" xfId="1235"/>
-    <cellStyle name="Total 16 30" xfId="2925"/>
-    <cellStyle name="Total 16 31" xfId="2974"/>
-    <cellStyle name="Total 16 32" xfId="3020"/>
-    <cellStyle name="Total 16 4" xfId="1311"/>
-    <cellStyle name="Total 16 5" xfId="1387"/>
-    <cellStyle name="Total 16 6" xfId="1462"/>
-    <cellStyle name="Total 16 7" xfId="1538"/>
-    <cellStyle name="Total 16 8" xfId="1613"/>
-    <cellStyle name="Total 16 9" xfId="1687"/>
-    <cellStyle name="Total 2" xfId="647"/>
-    <cellStyle name="Total 2 10" xfId="1764"/>
-    <cellStyle name="Total 2 11" xfId="1829"/>
-    <cellStyle name="Total 2 12" xfId="1895"/>
-    <cellStyle name="Total 2 13" xfId="1959"/>
-    <cellStyle name="Total 2 14" xfId="2021"/>
-    <cellStyle name="Total 2 15" xfId="2082"/>
-    <cellStyle name="Total 2 16" xfId="2146"/>
-    <cellStyle name="Total 2 17" xfId="2207"/>
-    <cellStyle name="Total 2 18" xfId="2268"/>
-    <cellStyle name="Total 2 19" xfId="2328"/>
-    <cellStyle name="Total 2 2" xfId="1160"/>
-    <cellStyle name="Total 2 20" xfId="2389"/>
-    <cellStyle name="Total 2 21" xfId="2451"/>
-    <cellStyle name="Total 2 22" xfId="2510"/>
-    <cellStyle name="Total 2 23" xfId="2573"/>
-    <cellStyle name="Total 2 24" xfId="2632"/>
-    <cellStyle name="Total 2 25" xfId="2687"/>
-    <cellStyle name="Total 2 26" xfId="2739"/>
-    <cellStyle name="Total 2 27" xfId="2786"/>
-    <cellStyle name="Total 2 28" xfId="2834"/>
-    <cellStyle name="Total 2 29" xfId="2880"/>
-    <cellStyle name="Total 2 3" xfId="1236"/>
-    <cellStyle name="Total 2 30" xfId="2926"/>
-    <cellStyle name="Total 2 31" xfId="2975"/>
-    <cellStyle name="Total 2 32" xfId="3021"/>
-    <cellStyle name="Total 2 4" xfId="1312"/>
-    <cellStyle name="Total 2 5" xfId="1388"/>
-    <cellStyle name="Total 2 6" xfId="1463"/>
-    <cellStyle name="Total 2 7" xfId="1539"/>
-    <cellStyle name="Total 2 8" xfId="1614"/>
-    <cellStyle name="Total 2 9" xfId="1688"/>
-    <cellStyle name="Total 3" xfId="648"/>
-    <cellStyle name="Total 3 10" xfId="1765"/>
-    <cellStyle name="Total 3 11" xfId="1830"/>
-    <cellStyle name="Total 3 12" xfId="1896"/>
-    <cellStyle name="Total 3 13" xfId="1960"/>
-    <cellStyle name="Total 3 14" xfId="2022"/>
-    <cellStyle name="Total 3 15" xfId="2083"/>
-    <cellStyle name="Total 3 16" xfId="2147"/>
-    <cellStyle name="Total 3 17" xfId="2208"/>
-    <cellStyle name="Total 3 18" xfId="2269"/>
-    <cellStyle name="Total 3 19" xfId="2329"/>
-    <cellStyle name="Total 3 2" xfId="1161"/>
-    <cellStyle name="Total 3 20" xfId="2390"/>
-    <cellStyle name="Total 3 21" xfId="2452"/>
-    <cellStyle name="Total 3 22" xfId="2511"/>
-    <cellStyle name="Total 3 23" xfId="2574"/>
-    <cellStyle name="Total 3 24" xfId="2633"/>
-    <cellStyle name="Total 3 25" xfId="2688"/>
-    <cellStyle name="Total 3 26" xfId="2740"/>
-    <cellStyle name="Total 3 27" xfId="2787"/>
-    <cellStyle name="Total 3 28" xfId="2835"/>
-    <cellStyle name="Total 3 29" xfId="2881"/>
-    <cellStyle name="Total 3 3" xfId="1237"/>
-    <cellStyle name="Total 3 30" xfId="2927"/>
-    <cellStyle name="Total 3 31" xfId="2976"/>
-    <cellStyle name="Total 3 32" xfId="3022"/>
-    <cellStyle name="Total 3 4" xfId="1313"/>
-    <cellStyle name="Total 3 5" xfId="1389"/>
-    <cellStyle name="Total 3 6" xfId="1464"/>
-    <cellStyle name="Total 3 7" xfId="1540"/>
-    <cellStyle name="Total 3 8" xfId="1615"/>
-    <cellStyle name="Total 3 9" xfId="1689"/>
-    <cellStyle name="Total 4" xfId="649"/>
-    <cellStyle name="Total 4 10" xfId="1766"/>
-    <cellStyle name="Total 4 11" xfId="1831"/>
-    <cellStyle name="Total 4 12" xfId="1897"/>
-    <cellStyle name="Total 4 13" xfId="1961"/>
-    <cellStyle name="Total 4 14" xfId="2023"/>
-    <cellStyle name="Total 4 15" xfId="2084"/>
-    <cellStyle name="Total 4 16" xfId="2148"/>
-    <cellStyle name="Total 4 17" xfId="2209"/>
-    <cellStyle name="Total 4 18" xfId="2270"/>
-    <cellStyle name="Total 4 19" xfId="2330"/>
-    <cellStyle name="Total 4 2" xfId="1162"/>
-    <cellStyle name="Total 4 20" xfId="2391"/>
-    <cellStyle name="Total 4 21" xfId="2453"/>
-    <cellStyle name="Total 4 22" xfId="2512"/>
-    <cellStyle name="Total 4 23" xfId="2575"/>
-    <cellStyle name="Total 4 24" xfId="2634"/>
-    <cellStyle name="Total 4 25" xfId="2689"/>
-    <cellStyle name="Total 4 26" xfId="2741"/>
-    <cellStyle name="Total 4 27" xfId="2788"/>
-    <cellStyle name="Total 4 28" xfId="2836"/>
-    <cellStyle name="Total 4 29" xfId="2882"/>
-    <cellStyle name="Total 4 3" xfId="1238"/>
-    <cellStyle name="Total 4 30" xfId="2928"/>
-    <cellStyle name="Total 4 31" xfId="2977"/>
-    <cellStyle name="Total 4 32" xfId="3023"/>
-    <cellStyle name="Total 4 4" xfId="1314"/>
-    <cellStyle name="Total 4 5" xfId="1390"/>
-    <cellStyle name="Total 4 6" xfId="1465"/>
-    <cellStyle name="Total 4 7" xfId="1541"/>
-    <cellStyle name="Total 4 8" xfId="1616"/>
-    <cellStyle name="Total 4 9" xfId="1690"/>
-    <cellStyle name="Total 5" xfId="650"/>
-    <cellStyle name="Total 5 10" xfId="1767"/>
-    <cellStyle name="Total 5 11" xfId="1832"/>
-    <cellStyle name="Total 5 12" xfId="1898"/>
-    <cellStyle name="Total 5 13" xfId="1962"/>
-    <cellStyle name="Total 5 14" xfId="2024"/>
-    <cellStyle name="Total 5 15" xfId="2085"/>
-    <cellStyle name="Total 5 16" xfId="2149"/>
-    <cellStyle name="Total 5 17" xfId="2210"/>
-    <cellStyle name="Total 5 18" xfId="2271"/>
-    <cellStyle name="Total 5 19" xfId="2331"/>
-    <cellStyle name="Total 5 2" xfId="1163"/>
-    <cellStyle name="Total 5 20" xfId="2392"/>
-    <cellStyle name="Total 5 21" xfId="2454"/>
-    <cellStyle name="Total 5 22" xfId="2513"/>
-    <cellStyle name="Total 5 23" xfId="2576"/>
-    <cellStyle name="Total 5 24" xfId="2635"/>
-    <cellStyle name="Total 5 25" xfId="2690"/>
-    <cellStyle name="Total 5 26" xfId="2742"/>
-    <cellStyle name="Total 5 27" xfId="2789"/>
-    <cellStyle name="Total 5 28" xfId="2837"/>
-    <cellStyle name="Total 5 29" xfId="2883"/>
-    <cellStyle name="Total 5 3" xfId="1239"/>
-    <cellStyle name="Total 5 30" xfId="2929"/>
-    <cellStyle name="Total 5 31" xfId="2978"/>
-    <cellStyle name="Total 5 32" xfId="3024"/>
-    <cellStyle name="Total 5 4" xfId="1315"/>
-    <cellStyle name="Total 5 5" xfId="1391"/>
-    <cellStyle name="Total 5 6" xfId="1466"/>
-    <cellStyle name="Total 5 7" xfId="1542"/>
-    <cellStyle name="Total 5 8" xfId="1617"/>
-    <cellStyle name="Total 5 9" xfId="1691"/>
-    <cellStyle name="Total 6" xfId="651"/>
-    <cellStyle name="Total 6 10" xfId="1768"/>
-    <cellStyle name="Total 6 11" xfId="1833"/>
-    <cellStyle name="Total 6 12" xfId="1899"/>
-    <cellStyle name="Total 6 13" xfId="1963"/>
-    <cellStyle name="Total 6 14" xfId="2025"/>
-    <cellStyle name="Total 6 15" xfId="2086"/>
-    <cellStyle name="Total 6 16" xfId="2150"/>
-    <cellStyle name="Total 6 17" xfId="2211"/>
-    <cellStyle name="Total 6 18" xfId="2272"/>
-    <cellStyle name="Total 6 19" xfId="2332"/>
-    <cellStyle name="Total 6 2" xfId="1164"/>
-    <cellStyle name="Total 6 20" xfId="2393"/>
-    <cellStyle name="Total 6 21" xfId="2455"/>
-    <cellStyle name="Total 6 22" xfId="2514"/>
-    <cellStyle name="Total 6 23" xfId="2577"/>
-    <cellStyle name="Total 6 24" xfId="2636"/>
-    <cellStyle name="Total 6 25" xfId="2691"/>
-    <cellStyle name="Total 6 26" xfId="2743"/>
-    <cellStyle name="Total 6 27" xfId="2790"/>
-    <cellStyle name="Total 6 28" xfId="2838"/>
-    <cellStyle name="Total 6 29" xfId="2884"/>
-    <cellStyle name="Total 6 3" xfId="1240"/>
-    <cellStyle name="Total 6 30" xfId="2930"/>
-    <cellStyle name="Total 6 31" xfId="2979"/>
-    <cellStyle name="Total 6 32" xfId="3025"/>
-    <cellStyle name="Total 6 4" xfId="1316"/>
-    <cellStyle name="Total 6 5" xfId="1392"/>
-    <cellStyle name="Total 6 6" xfId="1467"/>
-    <cellStyle name="Total 6 7" xfId="1543"/>
-    <cellStyle name="Total 6 8" xfId="1618"/>
-    <cellStyle name="Total 6 9" xfId="1692"/>
-    <cellStyle name="Total 7" xfId="652"/>
-    <cellStyle name="Total 7 10" xfId="1769"/>
-    <cellStyle name="Total 7 11" xfId="1834"/>
-    <cellStyle name="Total 7 12" xfId="1900"/>
-    <cellStyle name="Total 7 13" xfId="1964"/>
-    <cellStyle name="Total 7 14" xfId="2026"/>
-    <cellStyle name="Total 7 15" xfId="2087"/>
-    <cellStyle name="Total 7 16" xfId="2151"/>
-    <cellStyle name="Total 7 17" xfId="2212"/>
-    <cellStyle name="Total 7 18" xfId="2273"/>
-    <cellStyle name="Total 7 19" xfId="2333"/>
-    <cellStyle name="Total 7 2" xfId="1165"/>
-    <cellStyle name="Total 7 20" xfId="2394"/>
-    <cellStyle name="Total 7 21" xfId="2456"/>
-    <cellStyle name="Total 7 22" xfId="2515"/>
-    <cellStyle name="Total 7 23" xfId="2578"/>
-    <cellStyle name="Total 7 24" xfId="2637"/>
-    <cellStyle name="Total 7 25" xfId="2692"/>
-    <cellStyle name="Total 7 26" xfId="2744"/>
-    <cellStyle name="Total 7 27" xfId="2791"/>
-    <cellStyle name="Total 7 28" xfId="2839"/>
-    <cellStyle name="Total 7 29" xfId="2885"/>
-    <cellStyle name="Total 7 3" xfId="1241"/>
-    <cellStyle name="Total 7 30" xfId="2931"/>
-    <cellStyle name="Total 7 31" xfId="2980"/>
-    <cellStyle name="Total 7 32" xfId="3026"/>
-    <cellStyle name="Total 7 4" xfId="1317"/>
-    <cellStyle name="Total 7 5" xfId="1393"/>
-    <cellStyle name="Total 7 6" xfId="1468"/>
-    <cellStyle name="Total 7 7" xfId="1544"/>
-    <cellStyle name="Total 7 8" xfId="1619"/>
-    <cellStyle name="Total 7 9" xfId="1693"/>
-    <cellStyle name="Total 8" xfId="653"/>
-    <cellStyle name="Total 8 10" xfId="1770"/>
-    <cellStyle name="Total 8 11" xfId="1835"/>
-    <cellStyle name="Total 8 12" xfId="1901"/>
-    <cellStyle name="Total 8 13" xfId="1965"/>
-    <cellStyle name="Total 8 14" xfId="2027"/>
-    <cellStyle name="Total 8 15" xfId="2088"/>
-    <cellStyle name="Total 8 16" xfId="2152"/>
-    <cellStyle name="Total 8 17" xfId="2213"/>
-    <cellStyle name="Total 8 18" xfId="2274"/>
-    <cellStyle name="Total 8 19" xfId="2334"/>
-    <cellStyle name="Total 8 2" xfId="1166"/>
-    <cellStyle name="Total 8 20" xfId="2395"/>
-    <cellStyle name="Total 8 21" xfId="2457"/>
-    <cellStyle name="Total 8 22" xfId="2516"/>
-    <cellStyle name="Total 8 23" xfId="2579"/>
-    <cellStyle name="Total 8 24" xfId="2638"/>
-    <cellStyle name="Total 8 25" xfId="2693"/>
-    <cellStyle name="Total 8 26" xfId="2745"/>
-    <cellStyle name="Total 8 27" xfId="2792"/>
-    <cellStyle name="Total 8 28" xfId="2840"/>
-    <cellStyle name="Total 8 29" xfId="2886"/>
-    <cellStyle name="Total 8 3" xfId="1242"/>
-    <cellStyle name="Total 8 30" xfId="2932"/>
-    <cellStyle name="Total 8 31" xfId="2981"/>
-    <cellStyle name="Total 8 32" xfId="3027"/>
-    <cellStyle name="Total 8 4" xfId="1318"/>
-    <cellStyle name="Total 8 5" xfId="1394"/>
-    <cellStyle name="Total 8 6" xfId="1469"/>
-    <cellStyle name="Total 8 7" xfId="1545"/>
-    <cellStyle name="Total 8 8" xfId="1620"/>
-    <cellStyle name="Total 8 9" xfId="1694"/>
-    <cellStyle name="Total 9" xfId="654"/>
-    <cellStyle name="Total 9 10" xfId="1771"/>
-    <cellStyle name="Total 9 11" xfId="1836"/>
-    <cellStyle name="Total 9 12" xfId="1902"/>
-    <cellStyle name="Total 9 13" xfId="1966"/>
-    <cellStyle name="Total 9 14" xfId="2028"/>
-    <cellStyle name="Total 9 15" xfId="2089"/>
-    <cellStyle name="Total 9 16" xfId="2153"/>
-    <cellStyle name="Total 9 17" xfId="2214"/>
-    <cellStyle name="Total 9 18" xfId="2275"/>
-    <cellStyle name="Total 9 19" xfId="2335"/>
-    <cellStyle name="Total 9 2" xfId="1167"/>
-    <cellStyle name="Total 9 20" xfId="2396"/>
-    <cellStyle name="Total 9 21" xfId="2458"/>
-    <cellStyle name="Total 9 22" xfId="2517"/>
-    <cellStyle name="Total 9 23" xfId="2580"/>
-    <cellStyle name="Total 9 24" xfId="2639"/>
-    <cellStyle name="Total 9 25" xfId="2694"/>
-    <cellStyle name="Total 9 26" xfId="2746"/>
-    <cellStyle name="Total 9 27" xfId="2793"/>
-    <cellStyle name="Total 9 28" xfId="2841"/>
-    <cellStyle name="Total 9 29" xfId="2887"/>
-    <cellStyle name="Total 9 3" xfId="1243"/>
-    <cellStyle name="Total 9 30" xfId="2933"/>
-    <cellStyle name="Total 9 31" xfId="2982"/>
-    <cellStyle name="Total 9 32" xfId="3028"/>
-    <cellStyle name="Total 9 4" xfId="1319"/>
-    <cellStyle name="Total 9 5" xfId="1395"/>
-    <cellStyle name="Total 9 6" xfId="1470"/>
-    <cellStyle name="Total 9 7" xfId="1546"/>
-    <cellStyle name="Total 9 8" xfId="1621"/>
-    <cellStyle name="Total 9 9" xfId="1695"/>
-    <cellStyle name="Warning Text 10" xfId="655"/>
-    <cellStyle name="Warning Text 11" xfId="656"/>
-    <cellStyle name="Warning Text 12" xfId="657"/>
-    <cellStyle name="Warning Text 13" xfId="658"/>
-    <cellStyle name="Warning Text 14" xfId="659"/>
-    <cellStyle name="Warning Text 15" xfId="660"/>
-    <cellStyle name="Warning Text 16" xfId="661"/>
-    <cellStyle name="Warning Text 2" xfId="662"/>
-    <cellStyle name="Warning Text 3" xfId="663"/>
-    <cellStyle name="Warning Text 4" xfId="664"/>
-    <cellStyle name="Warning Text 5" xfId="665"/>
-    <cellStyle name="Warning Text 6" xfId="666"/>
-    <cellStyle name="Warning Text 7" xfId="667"/>
-    <cellStyle name="Warning Text 8" xfId="668"/>
-    <cellStyle name="Warning Text 9" xfId="669"/>
+    <cellStyle name="Normal 10" xfId="545" xr:uid="{00000000-0005-0000-0000-0000C0050000}"/>
+    <cellStyle name="Normal 11" xfId="546" xr:uid="{00000000-0005-0000-0000-0000C1050000}"/>
+    <cellStyle name="Normal 12" xfId="547" xr:uid="{00000000-0005-0000-0000-0000C2050000}"/>
+    <cellStyle name="Normal 13" xfId="548" xr:uid="{00000000-0005-0000-0000-0000C3050000}"/>
+    <cellStyle name="Normal 14" xfId="549" xr:uid="{00000000-0005-0000-0000-0000C4050000}"/>
+    <cellStyle name="Normal 15" xfId="550" xr:uid="{00000000-0005-0000-0000-0000C5050000}"/>
+    <cellStyle name="Normal 16" xfId="551" xr:uid="{00000000-0005-0000-0000-0000C6050000}"/>
+    <cellStyle name="Normal 17" xfId="552" xr:uid="{00000000-0005-0000-0000-0000C7050000}"/>
+    <cellStyle name="Normal 18" xfId="553" xr:uid="{00000000-0005-0000-0000-0000C8050000}"/>
+    <cellStyle name="Normal 19" xfId="554" xr:uid="{00000000-0005-0000-0000-0000C9050000}"/>
+    <cellStyle name="Normal 2" xfId="2" xr:uid="{00000000-0005-0000-0000-0000CA050000}"/>
+    <cellStyle name="Normal 2 10" xfId="556" xr:uid="{00000000-0005-0000-0000-0000CB050000}"/>
+    <cellStyle name="Normal 2 11" xfId="557" xr:uid="{00000000-0005-0000-0000-0000CC050000}"/>
+    <cellStyle name="Normal 2 12" xfId="558" xr:uid="{00000000-0005-0000-0000-0000CD050000}"/>
+    <cellStyle name="Normal 2 13" xfId="559" xr:uid="{00000000-0005-0000-0000-0000CE050000}"/>
+    <cellStyle name="Normal 2 14" xfId="560" xr:uid="{00000000-0005-0000-0000-0000CF050000}"/>
+    <cellStyle name="Normal 2 15" xfId="561" xr:uid="{00000000-0005-0000-0000-0000D0050000}"/>
+    <cellStyle name="Normal 2 16" xfId="562" xr:uid="{00000000-0005-0000-0000-0000D1050000}"/>
+    <cellStyle name="Normal 2 17" xfId="563" xr:uid="{00000000-0005-0000-0000-0000D2050000}"/>
+    <cellStyle name="Normal 2 18" xfId="555" xr:uid="{00000000-0005-0000-0000-0000D3050000}"/>
+    <cellStyle name="Normal 2 19" xfId="2936" xr:uid="{00000000-0005-0000-0000-0000D4050000}"/>
+    <cellStyle name="Normal 2 2" xfId="564" xr:uid="{00000000-0005-0000-0000-0000D5050000}"/>
+    <cellStyle name="Normal 2 2 2" xfId="565" xr:uid="{00000000-0005-0000-0000-0000D6050000}"/>
+    <cellStyle name="Normal 2 2 3" xfId="2934" xr:uid="{00000000-0005-0000-0000-0000D7050000}"/>
+    <cellStyle name="Normal 2 3" xfId="566" xr:uid="{00000000-0005-0000-0000-0000D8050000}"/>
+    <cellStyle name="Normal 2 4" xfId="567" xr:uid="{00000000-0005-0000-0000-0000D9050000}"/>
+    <cellStyle name="Normal 2 5" xfId="568" xr:uid="{00000000-0005-0000-0000-0000DA050000}"/>
+    <cellStyle name="Normal 2 6" xfId="569" xr:uid="{00000000-0005-0000-0000-0000DB050000}"/>
+    <cellStyle name="Normal 2 7" xfId="570" xr:uid="{00000000-0005-0000-0000-0000DC050000}"/>
+    <cellStyle name="Normal 2 8" xfId="571" xr:uid="{00000000-0005-0000-0000-0000DD050000}"/>
+    <cellStyle name="Normal 2 9" xfId="572" xr:uid="{00000000-0005-0000-0000-0000DE050000}"/>
+    <cellStyle name="Normal 20" xfId="3" xr:uid="{00000000-0005-0000-0000-0000DF050000}"/>
+    <cellStyle name="Normal 20 2" xfId="573" xr:uid="{00000000-0005-0000-0000-0000E0050000}"/>
+    <cellStyle name="Normal 21" xfId="574" xr:uid="{00000000-0005-0000-0000-0000E1050000}"/>
+    <cellStyle name="Normal 22" xfId="575" xr:uid="{00000000-0005-0000-0000-0000E2050000}"/>
+    <cellStyle name="Normal 23" xfId="576" xr:uid="{00000000-0005-0000-0000-0000E3050000}"/>
+    <cellStyle name="Normal 24" xfId="577" xr:uid="{00000000-0005-0000-0000-0000E4050000}"/>
+    <cellStyle name="Normal 25" xfId="578" xr:uid="{00000000-0005-0000-0000-0000E5050000}"/>
+    <cellStyle name="Normal 26" xfId="579" xr:uid="{00000000-0005-0000-0000-0000E6050000}"/>
+    <cellStyle name="Normal 27" xfId="580" xr:uid="{00000000-0005-0000-0000-0000E7050000}"/>
+    <cellStyle name="Normal 28" xfId="581" xr:uid="{00000000-0005-0000-0000-0000E8050000}"/>
+    <cellStyle name="Normal 29" xfId="1" xr:uid="{00000000-0005-0000-0000-0000E9050000}"/>
+    <cellStyle name="Normal 3" xfId="4" xr:uid="{00000000-0005-0000-0000-0000EA050000}"/>
+    <cellStyle name="Normal 3 2" xfId="582" xr:uid="{00000000-0005-0000-0000-0000EB050000}"/>
+    <cellStyle name="Normal 3 3" xfId="2935" xr:uid="{00000000-0005-0000-0000-0000EC050000}"/>
+    <cellStyle name="Normal 30" xfId="3029" xr:uid="{00000000-0005-0000-0000-0000ED050000}"/>
+    <cellStyle name="Normal 31" xfId="3031" xr:uid="{00000000-0005-0000-0000-0000EE050000}"/>
+    <cellStyle name="Normal 4" xfId="583" xr:uid="{00000000-0005-0000-0000-0000EF050000}"/>
+    <cellStyle name="Normal 4 2" xfId="584" xr:uid="{00000000-0005-0000-0000-0000F0050000}"/>
+    <cellStyle name="Normal 5" xfId="585" xr:uid="{00000000-0005-0000-0000-0000F1050000}"/>
+    <cellStyle name="Normal 6" xfId="586" xr:uid="{00000000-0005-0000-0000-0000F2050000}"/>
+    <cellStyle name="Normal 6 2" xfId="587" xr:uid="{00000000-0005-0000-0000-0000F3050000}"/>
+    <cellStyle name="Normal 7" xfId="588" xr:uid="{00000000-0005-0000-0000-0000F4050000}"/>
+    <cellStyle name="Normal 7 2" xfId="589" xr:uid="{00000000-0005-0000-0000-0000F5050000}"/>
+    <cellStyle name="Normal 8" xfId="590" xr:uid="{00000000-0005-0000-0000-0000F6050000}"/>
+    <cellStyle name="Normal 8 2" xfId="591" xr:uid="{00000000-0005-0000-0000-0000F7050000}"/>
+    <cellStyle name="Normal 9" xfId="592" xr:uid="{00000000-0005-0000-0000-0000F8050000}"/>
+    <cellStyle name="Normal 9 2" xfId="593" xr:uid="{00000000-0005-0000-0000-0000F9050000}"/>
+    <cellStyle name="Note 10" xfId="594" xr:uid="{00000000-0005-0000-0000-0000FA050000}"/>
+    <cellStyle name="Note 10 10" xfId="1711" xr:uid="{00000000-0005-0000-0000-0000FB050000}"/>
+    <cellStyle name="Note 10 11" xfId="1787" xr:uid="{00000000-0005-0000-0000-0000FC050000}"/>
+    <cellStyle name="Note 10 12" xfId="1851" xr:uid="{00000000-0005-0000-0000-0000FD050000}"/>
+    <cellStyle name="Note 10 13" xfId="1916" xr:uid="{00000000-0005-0000-0000-0000FE050000}"/>
+    <cellStyle name="Note 10 14" xfId="1979" xr:uid="{00000000-0005-0000-0000-0000FF050000}"/>
+    <cellStyle name="Note 10 15" xfId="2040" xr:uid="{00000000-0005-0000-0000-000000060000}"/>
+    <cellStyle name="Note 10 16" xfId="2102" xr:uid="{00000000-0005-0000-0000-000001060000}"/>
+    <cellStyle name="Note 10 17" xfId="2164" xr:uid="{00000000-0005-0000-0000-000002060000}"/>
+    <cellStyle name="Note 10 18" xfId="2227" xr:uid="{00000000-0005-0000-0000-000003060000}"/>
+    <cellStyle name="Note 10 19" xfId="2286" xr:uid="{00000000-0005-0000-0000-000004060000}"/>
+    <cellStyle name="Note 10 2" xfId="1107" xr:uid="{00000000-0005-0000-0000-000005060000}"/>
+    <cellStyle name="Note 10 20" xfId="2347" xr:uid="{00000000-0005-0000-0000-000006060000}"/>
+    <cellStyle name="Note 10 21" xfId="2408" xr:uid="{00000000-0005-0000-0000-000007060000}"/>
+    <cellStyle name="Note 10 22" xfId="2471" xr:uid="{00000000-0005-0000-0000-000008060000}"/>
+    <cellStyle name="Note 10 23" xfId="2528" xr:uid="{00000000-0005-0000-0000-000009060000}"/>
+    <cellStyle name="Note 10 24" xfId="2589" xr:uid="{00000000-0005-0000-0000-00000A060000}"/>
+    <cellStyle name="Note 10 25" xfId="2649" xr:uid="{00000000-0005-0000-0000-00000B060000}"/>
+    <cellStyle name="Note 10 26" xfId="2696" xr:uid="{00000000-0005-0000-0000-00000C060000}"/>
+    <cellStyle name="Note 10 27" xfId="2748" xr:uid="{00000000-0005-0000-0000-00000D060000}"/>
+    <cellStyle name="Note 10 28" xfId="2796" xr:uid="{00000000-0005-0000-0000-00000E060000}"/>
+    <cellStyle name="Note 10 29" xfId="2842" xr:uid="{00000000-0005-0000-0000-00000F060000}"/>
+    <cellStyle name="Note 10 3" xfId="1183" xr:uid="{00000000-0005-0000-0000-000010060000}"/>
+    <cellStyle name="Note 10 30" xfId="2888" xr:uid="{00000000-0005-0000-0000-000011060000}"/>
+    <cellStyle name="Note 10 31" xfId="2937" xr:uid="{00000000-0005-0000-0000-000012060000}"/>
+    <cellStyle name="Note 10 32" xfId="2983" xr:uid="{00000000-0005-0000-0000-000013060000}"/>
+    <cellStyle name="Note 10 4" xfId="1259" xr:uid="{00000000-0005-0000-0000-000014060000}"/>
+    <cellStyle name="Note 10 5" xfId="1335" xr:uid="{00000000-0005-0000-0000-000015060000}"/>
+    <cellStyle name="Note 10 6" xfId="1411" xr:uid="{00000000-0005-0000-0000-000016060000}"/>
+    <cellStyle name="Note 10 7" xfId="1486" xr:uid="{00000000-0005-0000-0000-000017060000}"/>
+    <cellStyle name="Note 10 8" xfId="1562" xr:uid="{00000000-0005-0000-0000-000018060000}"/>
+    <cellStyle name="Note 10 9" xfId="1637" xr:uid="{00000000-0005-0000-0000-000019060000}"/>
+    <cellStyle name="Note 11" xfId="595" xr:uid="{00000000-0005-0000-0000-00001A060000}"/>
+    <cellStyle name="Note 11 10" xfId="1712" xr:uid="{00000000-0005-0000-0000-00001B060000}"/>
+    <cellStyle name="Note 11 11" xfId="1788" xr:uid="{00000000-0005-0000-0000-00001C060000}"/>
+    <cellStyle name="Note 11 12" xfId="1852" xr:uid="{00000000-0005-0000-0000-00001D060000}"/>
+    <cellStyle name="Note 11 13" xfId="1917" xr:uid="{00000000-0005-0000-0000-00001E060000}"/>
+    <cellStyle name="Note 11 14" xfId="1980" xr:uid="{00000000-0005-0000-0000-00001F060000}"/>
+    <cellStyle name="Note 11 15" xfId="2041" xr:uid="{00000000-0005-0000-0000-000020060000}"/>
+    <cellStyle name="Note 11 16" xfId="2103" xr:uid="{00000000-0005-0000-0000-000021060000}"/>
+    <cellStyle name="Note 11 17" xfId="2165" xr:uid="{00000000-0005-0000-0000-000022060000}"/>
+    <cellStyle name="Note 11 18" xfId="2228" xr:uid="{00000000-0005-0000-0000-000023060000}"/>
+    <cellStyle name="Note 11 19" xfId="2287" xr:uid="{00000000-0005-0000-0000-000024060000}"/>
+    <cellStyle name="Note 11 2" xfId="1108" xr:uid="{00000000-0005-0000-0000-000025060000}"/>
+    <cellStyle name="Note 11 20" xfId="2348" xr:uid="{00000000-0005-0000-0000-000026060000}"/>
+    <cellStyle name="Note 11 21" xfId="2409" xr:uid="{00000000-0005-0000-0000-000027060000}"/>
+    <cellStyle name="Note 11 22" xfId="2472" xr:uid="{00000000-0005-0000-0000-000028060000}"/>
+    <cellStyle name="Note 11 23" xfId="2529" xr:uid="{00000000-0005-0000-0000-000029060000}"/>
+    <cellStyle name="Note 11 24" xfId="2590" xr:uid="{00000000-0005-0000-0000-00002A060000}"/>
+    <cellStyle name="Note 11 25" xfId="2650" xr:uid="{00000000-0005-0000-0000-00002B060000}"/>
+    <cellStyle name="Note 11 26" xfId="2697" xr:uid="{00000000-0005-0000-0000-00002C060000}"/>
+    <cellStyle name="Note 11 27" xfId="2749" xr:uid="{00000000-0005-0000-0000-00002D060000}"/>
+    <cellStyle name="Note 11 28" xfId="2797" xr:uid="{00000000-0005-0000-0000-00002E060000}"/>
+    <cellStyle name="Note 11 29" xfId="2843" xr:uid="{00000000-0005-0000-0000-00002F060000}"/>
+    <cellStyle name="Note 11 3" xfId="1184" xr:uid="{00000000-0005-0000-0000-000030060000}"/>
+    <cellStyle name="Note 11 30" xfId="2889" xr:uid="{00000000-0005-0000-0000-000031060000}"/>
+    <cellStyle name="Note 11 31" xfId="2938" xr:uid="{00000000-0005-0000-0000-000032060000}"/>
+    <cellStyle name="Note 11 32" xfId="2984" xr:uid="{00000000-0005-0000-0000-000033060000}"/>
+    <cellStyle name="Note 11 4" xfId="1260" xr:uid="{00000000-0005-0000-0000-000034060000}"/>
+    <cellStyle name="Note 11 5" xfId="1336" xr:uid="{00000000-0005-0000-0000-000035060000}"/>
+    <cellStyle name="Note 11 6" xfId="1412" xr:uid="{00000000-0005-0000-0000-000036060000}"/>
+    <cellStyle name="Note 11 7" xfId="1487" xr:uid="{00000000-0005-0000-0000-000037060000}"/>
+    <cellStyle name="Note 11 8" xfId="1563" xr:uid="{00000000-0005-0000-0000-000038060000}"/>
+    <cellStyle name="Note 11 9" xfId="1638" xr:uid="{00000000-0005-0000-0000-000039060000}"/>
+    <cellStyle name="Note 12" xfId="596" xr:uid="{00000000-0005-0000-0000-00003A060000}"/>
+    <cellStyle name="Note 12 10" xfId="1713" xr:uid="{00000000-0005-0000-0000-00003B060000}"/>
+    <cellStyle name="Note 12 11" xfId="1789" xr:uid="{00000000-0005-0000-0000-00003C060000}"/>
+    <cellStyle name="Note 12 12" xfId="1853" xr:uid="{00000000-0005-0000-0000-00003D060000}"/>
+    <cellStyle name="Note 12 13" xfId="1918" xr:uid="{00000000-0005-0000-0000-00003E060000}"/>
+    <cellStyle name="Note 12 14" xfId="1981" xr:uid="{00000000-0005-0000-0000-00003F060000}"/>
+    <cellStyle name="Note 12 15" xfId="2042" xr:uid="{00000000-0005-0000-0000-000040060000}"/>
+    <cellStyle name="Note 12 16" xfId="2104" xr:uid="{00000000-0005-0000-0000-000041060000}"/>
+    <cellStyle name="Note 12 17" xfId="2166" xr:uid="{00000000-0005-0000-0000-000042060000}"/>
+    <cellStyle name="Note 12 18" xfId="2229" xr:uid="{00000000-0005-0000-0000-000043060000}"/>
+    <cellStyle name="Note 12 19" xfId="2288" xr:uid="{00000000-0005-0000-0000-000044060000}"/>
+    <cellStyle name="Note 12 2" xfId="1109" xr:uid="{00000000-0005-0000-0000-000045060000}"/>
+    <cellStyle name="Note 12 20" xfId="2349" xr:uid="{00000000-0005-0000-0000-000046060000}"/>
+    <cellStyle name="Note 12 21" xfId="2410" xr:uid="{00000000-0005-0000-0000-000047060000}"/>
+    <cellStyle name="Note 12 22" xfId="2473" xr:uid="{00000000-0005-0000-0000-000048060000}"/>
+    <cellStyle name="Note 12 23" xfId="2530" xr:uid="{00000000-0005-0000-0000-000049060000}"/>
+    <cellStyle name="Note 12 24" xfId="2591" xr:uid="{00000000-0005-0000-0000-00004A060000}"/>
+    <cellStyle name="Note 12 25" xfId="2651" xr:uid="{00000000-0005-0000-0000-00004B060000}"/>
+    <cellStyle name="Note 12 26" xfId="2698" xr:uid="{00000000-0005-0000-0000-00004C060000}"/>
+    <cellStyle name="Note 12 27" xfId="2750" xr:uid="{00000000-0005-0000-0000-00004D060000}"/>
+    <cellStyle name="Note 12 28" xfId="2798" xr:uid="{00000000-0005-0000-0000-00004E060000}"/>
+    <cellStyle name="Note 12 29" xfId="2844" xr:uid="{00000000-0005-0000-0000-00004F060000}"/>
+    <cellStyle name="Note 12 3" xfId="1185" xr:uid="{00000000-0005-0000-0000-000050060000}"/>
+    <cellStyle name="Note 12 30" xfId="2890" xr:uid="{00000000-0005-0000-0000-000051060000}"/>
+    <cellStyle name="Note 12 31" xfId="2939" xr:uid="{00000000-0005-0000-0000-000052060000}"/>
+    <cellStyle name="Note 12 32" xfId="2985" xr:uid="{00000000-0005-0000-0000-000053060000}"/>
+    <cellStyle name="Note 12 4" xfId="1261" xr:uid="{00000000-0005-0000-0000-000054060000}"/>
+    <cellStyle name="Note 12 5" xfId="1337" xr:uid="{00000000-0005-0000-0000-000055060000}"/>
+    <cellStyle name="Note 12 6" xfId="1413" xr:uid="{00000000-0005-0000-0000-000056060000}"/>
+    <cellStyle name="Note 12 7" xfId="1488" xr:uid="{00000000-0005-0000-0000-000057060000}"/>
+    <cellStyle name="Note 12 8" xfId="1564" xr:uid="{00000000-0005-0000-0000-000058060000}"/>
+    <cellStyle name="Note 12 9" xfId="1639" xr:uid="{00000000-0005-0000-0000-000059060000}"/>
+    <cellStyle name="Note 13" xfId="597" xr:uid="{00000000-0005-0000-0000-00005A060000}"/>
+    <cellStyle name="Note 13 10" xfId="1714" xr:uid="{00000000-0005-0000-0000-00005B060000}"/>
+    <cellStyle name="Note 13 11" xfId="1790" xr:uid="{00000000-0005-0000-0000-00005C060000}"/>
+    <cellStyle name="Note 13 12" xfId="1854" xr:uid="{00000000-0005-0000-0000-00005D060000}"/>
+    <cellStyle name="Note 13 13" xfId="1919" xr:uid="{00000000-0005-0000-0000-00005E060000}"/>
+    <cellStyle name="Note 13 14" xfId="1982" xr:uid="{00000000-0005-0000-0000-00005F060000}"/>
+    <cellStyle name="Note 13 15" xfId="2043" xr:uid="{00000000-0005-0000-0000-000060060000}"/>
+    <cellStyle name="Note 13 16" xfId="2105" xr:uid="{00000000-0005-0000-0000-000061060000}"/>
+    <cellStyle name="Note 13 17" xfId="2167" xr:uid="{00000000-0005-0000-0000-000062060000}"/>
+    <cellStyle name="Note 13 18" xfId="2230" xr:uid="{00000000-0005-0000-0000-000063060000}"/>
+    <cellStyle name="Note 13 19" xfId="2289" xr:uid="{00000000-0005-0000-0000-000064060000}"/>
+    <cellStyle name="Note 13 2" xfId="1110" xr:uid="{00000000-0005-0000-0000-000065060000}"/>
+    <cellStyle name="Note 13 20" xfId="2350" xr:uid="{00000000-0005-0000-0000-000066060000}"/>
+    <cellStyle name="Note 13 21" xfId="2411" xr:uid="{00000000-0005-0000-0000-000067060000}"/>
+    <cellStyle name="Note 13 22" xfId="2474" xr:uid="{00000000-0005-0000-0000-000068060000}"/>
+    <cellStyle name="Note 13 23" xfId="2531" xr:uid="{00000000-0005-0000-0000-000069060000}"/>
+    <cellStyle name="Note 13 24" xfId="2592" xr:uid="{00000000-0005-0000-0000-00006A060000}"/>
+    <cellStyle name="Note 13 25" xfId="2652" xr:uid="{00000000-0005-0000-0000-00006B060000}"/>
+    <cellStyle name="Note 13 26" xfId="2699" xr:uid="{00000000-0005-0000-0000-00006C060000}"/>
+    <cellStyle name="Note 13 27" xfId="2751" xr:uid="{00000000-0005-0000-0000-00006D060000}"/>
+    <cellStyle name="Note 13 28" xfId="2799" xr:uid="{00000000-0005-0000-0000-00006E060000}"/>
+    <cellStyle name="Note 13 29" xfId="2845" xr:uid="{00000000-0005-0000-0000-00006F060000}"/>
+    <cellStyle name="Note 13 3" xfId="1186" xr:uid="{00000000-0005-0000-0000-000070060000}"/>
+    <cellStyle name="Note 13 30" xfId="2891" xr:uid="{00000000-0005-0000-0000-000071060000}"/>
+    <cellStyle name="Note 13 31" xfId="2940" xr:uid="{00000000-0005-0000-0000-000072060000}"/>
+    <cellStyle name="Note 13 32" xfId="2986" xr:uid="{00000000-0005-0000-0000-000073060000}"/>
+    <cellStyle name="Note 13 4" xfId="1262" xr:uid="{00000000-0005-0000-0000-000074060000}"/>
+    <cellStyle name="Note 13 5" xfId="1338" xr:uid="{00000000-0005-0000-0000-000075060000}"/>
+    <cellStyle name="Note 13 6" xfId="1414" xr:uid="{00000000-0005-0000-0000-000076060000}"/>
+    <cellStyle name="Note 13 7" xfId="1489" xr:uid="{00000000-0005-0000-0000-000077060000}"/>
+    <cellStyle name="Note 13 8" xfId="1565" xr:uid="{00000000-0005-0000-0000-000078060000}"/>
+    <cellStyle name="Note 13 9" xfId="1640" xr:uid="{00000000-0005-0000-0000-000079060000}"/>
+    <cellStyle name="Note 14" xfId="598" xr:uid="{00000000-0005-0000-0000-00007A060000}"/>
+    <cellStyle name="Note 14 10" xfId="1715" xr:uid="{00000000-0005-0000-0000-00007B060000}"/>
+    <cellStyle name="Note 14 11" xfId="1791" xr:uid="{00000000-0005-0000-0000-00007C060000}"/>
+    <cellStyle name="Note 14 12" xfId="1855" xr:uid="{00000000-0005-0000-0000-00007D060000}"/>
+    <cellStyle name="Note 14 13" xfId="1920" xr:uid="{00000000-0005-0000-0000-00007E060000}"/>
+    <cellStyle name="Note 14 14" xfId="1983" xr:uid="{00000000-0005-0000-0000-00007F060000}"/>
+    <cellStyle name="Note 14 15" xfId="2044" xr:uid="{00000000-0005-0000-0000-000080060000}"/>
+    <cellStyle name="Note 14 16" xfId="2106" xr:uid="{00000000-0005-0000-0000-000081060000}"/>
+    <cellStyle name="Note 14 17" xfId="2168" xr:uid="{00000000-0005-0000-0000-000082060000}"/>
+    <cellStyle name="Note 14 18" xfId="2231" xr:uid="{00000000-0005-0000-0000-000083060000}"/>
+    <cellStyle name="Note 14 19" xfId="2290" xr:uid="{00000000-0005-0000-0000-000084060000}"/>
+    <cellStyle name="Note 14 2" xfId="1111" xr:uid="{00000000-0005-0000-0000-000085060000}"/>
+    <cellStyle name="Note 14 20" xfId="2351" xr:uid="{00000000-0005-0000-0000-000086060000}"/>
+    <cellStyle name="Note 14 21" xfId="2412" xr:uid="{00000000-0005-0000-0000-000087060000}"/>
+    <cellStyle name="Note 14 22" xfId="2475" xr:uid="{00000000-0005-0000-0000-000088060000}"/>
+    <cellStyle name="Note 14 23" xfId="2532" xr:uid="{00000000-0005-0000-0000-000089060000}"/>
+    <cellStyle name="Note 14 24" xfId="2593" xr:uid="{00000000-0005-0000-0000-00008A060000}"/>
+    <cellStyle name="Note 14 25" xfId="2653" xr:uid="{00000000-0005-0000-0000-00008B060000}"/>
+    <cellStyle name="Note 14 26" xfId="2700" xr:uid="{00000000-0005-0000-0000-00008C060000}"/>
+    <cellStyle name="Note 14 27" xfId="2752" xr:uid="{00000000-0005-0000-0000-00008D060000}"/>
+    <cellStyle name="Note 14 28" xfId="2800" xr:uid="{00000000-0005-0000-0000-00008E060000}"/>
+    <cellStyle name="Note 14 29" xfId="2846" xr:uid="{00000000-0005-0000-0000-00008F060000}"/>
+    <cellStyle name="Note 14 3" xfId="1187" xr:uid="{00000000-0005-0000-0000-000090060000}"/>
+    <cellStyle name="Note 14 30" xfId="2892" xr:uid="{00000000-0005-0000-0000-000091060000}"/>
+    <cellStyle name="Note 14 31" xfId="2941" xr:uid="{00000000-0005-0000-0000-000092060000}"/>
+    <cellStyle name="Note 14 32" xfId="2987" xr:uid="{00000000-0005-0000-0000-000093060000}"/>
+    <cellStyle name="Note 14 4" xfId="1263" xr:uid="{00000000-0005-0000-0000-000094060000}"/>
+    <cellStyle name="Note 14 5" xfId="1339" xr:uid="{00000000-0005-0000-0000-000095060000}"/>
+    <cellStyle name="Note 14 6" xfId="1415" xr:uid="{00000000-0005-0000-0000-000096060000}"/>
+    <cellStyle name="Note 14 7" xfId="1490" xr:uid="{00000000-0005-0000-0000-000097060000}"/>
+    <cellStyle name="Note 14 8" xfId="1566" xr:uid="{00000000-0005-0000-0000-000098060000}"/>
+    <cellStyle name="Note 14 9" xfId="1641" xr:uid="{00000000-0005-0000-0000-000099060000}"/>
+    <cellStyle name="Note 15" xfId="599" xr:uid="{00000000-0005-0000-0000-00009A060000}"/>
+    <cellStyle name="Note 15 10" xfId="1716" xr:uid="{00000000-0005-0000-0000-00009B060000}"/>
+    <cellStyle name="Note 15 11" xfId="1792" xr:uid="{00000000-0005-0000-0000-00009C060000}"/>
+    <cellStyle name="Note 15 12" xfId="1856" xr:uid="{00000000-0005-0000-0000-00009D060000}"/>
+    <cellStyle name="Note 15 13" xfId="1921" xr:uid="{00000000-0005-0000-0000-00009E060000}"/>
+    <cellStyle name="Note 15 14" xfId="1984" xr:uid="{00000000-0005-0000-0000-00009F060000}"/>
+    <cellStyle name="Note 15 15" xfId="2045" xr:uid="{00000000-0005-0000-0000-0000A0060000}"/>
+    <cellStyle name="Note 15 16" xfId="2107" xr:uid="{00000000-0005-0000-0000-0000A1060000}"/>
+    <cellStyle name="Note 15 17" xfId="2169" xr:uid="{00000000-0005-0000-0000-0000A2060000}"/>
+    <cellStyle name="Note 15 18" xfId="2232" xr:uid="{00000000-0005-0000-0000-0000A3060000}"/>
+    <cellStyle name="Note 15 19" xfId="2291" xr:uid="{00000000-0005-0000-0000-0000A4060000}"/>
+    <cellStyle name="Note 15 2" xfId="1112" xr:uid="{00000000-0005-0000-0000-0000A5060000}"/>
+    <cellStyle name="Note 15 20" xfId="2352" xr:uid="{00000000-0005-0000-0000-0000A6060000}"/>
+    <cellStyle name="Note 15 21" xfId="2413" xr:uid="{00000000-0005-0000-0000-0000A7060000}"/>
+    <cellStyle name="Note 15 22" xfId="2476" xr:uid="{00000000-0005-0000-0000-0000A8060000}"/>
+    <cellStyle name="Note 15 23" xfId="2533" xr:uid="{00000000-0005-0000-0000-0000A9060000}"/>
+    <cellStyle name="Note 15 24" xfId="2594" xr:uid="{00000000-0005-0000-0000-0000AA060000}"/>
+    <cellStyle name="Note 15 25" xfId="2654" xr:uid="{00000000-0005-0000-0000-0000AB060000}"/>
+    <cellStyle name="Note 15 26" xfId="2701" xr:uid="{00000000-0005-0000-0000-0000AC060000}"/>
+    <cellStyle name="Note 15 27" xfId="2753" xr:uid="{00000000-0005-0000-0000-0000AD060000}"/>
+    <cellStyle name="Note 15 28" xfId="2801" xr:uid="{00000000-0005-0000-0000-0000AE060000}"/>
+    <cellStyle name="Note 15 29" xfId="2847" xr:uid="{00000000-0005-0000-0000-0000AF060000}"/>
+    <cellStyle name="Note 15 3" xfId="1188" xr:uid="{00000000-0005-0000-0000-0000B0060000}"/>
+    <cellStyle name="Note 15 30" xfId="2893" xr:uid="{00000000-0005-0000-0000-0000B1060000}"/>
+    <cellStyle name="Note 15 31" xfId="2942" xr:uid="{00000000-0005-0000-0000-0000B2060000}"/>
+    <cellStyle name="Note 15 32" xfId="2988" xr:uid="{00000000-0005-0000-0000-0000B3060000}"/>
+    <cellStyle name="Note 15 4" xfId="1264" xr:uid="{00000000-0005-0000-0000-0000B4060000}"/>
+    <cellStyle name="Note 15 5" xfId="1340" xr:uid="{00000000-0005-0000-0000-0000B5060000}"/>
+    <cellStyle name="Note 15 6" xfId="1416" xr:uid="{00000000-0005-0000-0000-0000B6060000}"/>
+    <cellStyle name="Note 15 7" xfId="1491" xr:uid="{00000000-0005-0000-0000-0000B7060000}"/>
+    <cellStyle name="Note 15 8" xfId="1567" xr:uid="{00000000-0005-0000-0000-0000B8060000}"/>
+    <cellStyle name="Note 15 9" xfId="1642" xr:uid="{00000000-0005-0000-0000-0000B9060000}"/>
+    <cellStyle name="Note 16" xfId="600" xr:uid="{00000000-0005-0000-0000-0000BA060000}"/>
+    <cellStyle name="Note 16 10" xfId="1717" xr:uid="{00000000-0005-0000-0000-0000BB060000}"/>
+    <cellStyle name="Note 16 11" xfId="1793" xr:uid="{00000000-0005-0000-0000-0000BC060000}"/>
+    <cellStyle name="Note 16 12" xfId="1857" xr:uid="{00000000-0005-0000-0000-0000BD060000}"/>
+    <cellStyle name="Note 16 13" xfId="1922" xr:uid="{00000000-0005-0000-0000-0000BE060000}"/>
+    <cellStyle name="Note 16 14" xfId="1985" xr:uid="{00000000-0005-0000-0000-0000BF060000}"/>
+    <cellStyle name="Note 16 15" xfId="2046" xr:uid="{00000000-0005-0000-0000-0000C0060000}"/>
+    <cellStyle name="Note 16 16" xfId="2108" xr:uid="{00000000-0005-0000-0000-0000C1060000}"/>
+    <cellStyle name="Note 16 17" xfId="2170" xr:uid="{00000000-0005-0000-0000-0000C2060000}"/>
+    <cellStyle name="Note 16 18" xfId="2233" xr:uid="{00000000-0005-0000-0000-0000C3060000}"/>
+    <cellStyle name="Note 16 19" xfId="2292" xr:uid="{00000000-0005-0000-0000-0000C4060000}"/>
+    <cellStyle name="Note 16 2" xfId="1113" xr:uid="{00000000-0005-0000-0000-0000C5060000}"/>
+    <cellStyle name="Note 16 20" xfId="2353" xr:uid="{00000000-0005-0000-0000-0000C6060000}"/>
+    <cellStyle name="Note 16 21" xfId="2414" xr:uid="{00000000-0005-0000-0000-0000C7060000}"/>
+    <cellStyle name="Note 16 22" xfId="2477" xr:uid="{00000000-0005-0000-0000-0000C8060000}"/>
+    <cellStyle name="Note 16 23" xfId="2534" xr:uid="{00000000-0005-0000-0000-0000C9060000}"/>
+    <cellStyle name="Note 16 24" xfId="2595" xr:uid="{00000000-0005-0000-0000-0000CA060000}"/>
+    <cellStyle name="Note 16 25" xfId="2655" xr:uid="{00000000-0005-0000-0000-0000CB060000}"/>
+    <cellStyle name="Note 16 26" xfId="2702" xr:uid="{00000000-0005-0000-0000-0000CC060000}"/>
+    <cellStyle name="Note 16 27" xfId="2754" xr:uid="{00000000-0005-0000-0000-0000CD060000}"/>
+    <cellStyle name="Note 16 28" xfId="2802" xr:uid="{00000000-0005-0000-0000-0000CE060000}"/>
+    <cellStyle name="Note 16 29" xfId="2848" xr:uid="{00000000-0005-0000-0000-0000CF060000}"/>
+    <cellStyle name="Note 16 3" xfId="1189" xr:uid="{00000000-0005-0000-0000-0000D0060000}"/>
+    <cellStyle name="Note 16 30" xfId="2894" xr:uid="{00000000-0005-0000-0000-0000D1060000}"/>
+    <cellStyle name="Note 16 31" xfId="2943" xr:uid="{00000000-0005-0000-0000-0000D2060000}"/>
+    <cellStyle name="Note 16 32" xfId="2989" xr:uid="{00000000-0005-0000-0000-0000D3060000}"/>
+    <cellStyle name="Note 16 4" xfId="1265" xr:uid="{00000000-0005-0000-0000-0000D4060000}"/>
+    <cellStyle name="Note 16 5" xfId="1341" xr:uid="{00000000-0005-0000-0000-0000D5060000}"/>
+    <cellStyle name="Note 16 6" xfId="1417" xr:uid="{00000000-0005-0000-0000-0000D6060000}"/>
+    <cellStyle name="Note 16 7" xfId="1492" xr:uid="{00000000-0005-0000-0000-0000D7060000}"/>
+    <cellStyle name="Note 16 8" xfId="1568" xr:uid="{00000000-0005-0000-0000-0000D8060000}"/>
+    <cellStyle name="Note 16 9" xfId="1643" xr:uid="{00000000-0005-0000-0000-0000D9060000}"/>
+    <cellStyle name="Note 17" xfId="601" xr:uid="{00000000-0005-0000-0000-0000DA060000}"/>
+    <cellStyle name="Note 17 10" xfId="1718" xr:uid="{00000000-0005-0000-0000-0000DB060000}"/>
+    <cellStyle name="Note 17 11" xfId="1794" xr:uid="{00000000-0005-0000-0000-0000DC060000}"/>
+    <cellStyle name="Note 17 12" xfId="1858" xr:uid="{00000000-0005-0000-0000-0000DD060000}"/>
+    <cellStyle name="Note 17 13" xfId="1923" xr:uid="{00000000-0005-0000-0000-0000DE060000}"/>
+    <cellStyle name="Note 17 14" xfId="1986" xr:uid="{00000000-0005-0000-0000-0000DF060000}"/>
+    <cellStyle name="Note 17 15" xfId="2047" xr:uid="{00000000-0005-0000-0000-0000E0060000}"/>
+    <cellStyle name="Note 17 16" xfId="2109" xr:uid="{00000000-0005-0000-0000-0000E1060000}"/>
+    <cellStyle name="Note 17 17" xfId="2171" xr:uid="{00000000-0005-0000-0000-0000E2060000}"/>
+    <cellStyle name="Note 17 18" xfId="2234" xr:uid="{00000000-0005-0000-0000-0000E3060000}"/>
+    <cellStyle name="Note 17 19" xfId="2293" xr:uid="{00000000-0005-0000-0000-0000E4060000}"/>
+    <cellStyle name="Note 17 2" xfId="1114" xr:uid="{00000000-0005-0000-0000-0000E5060000}"/>
+    <cellStyle name="Note 17 20" xfId="2354" xr:uid="{00000000-0005-0000-0000-0000E6060000}"/>
+    <cellStyle name="Note 17 21" xfId="2415" xr:uid="{00000000-0005-0000-0000-0000E7060000}"/>
+    <cellStyle name="Note 17 22" xfId="2478" xr:uid="{00000000-0005-0000-0000-0000E8060000}"/>
+    <cellStyle name="Note 17 23" xfId="2535" xr:uid="{00000000-0005-0000-0000-0000E9060000}"/>
+    <cellStyle name="Note 17 24" xfId="2596" xr:uid="{00000000-0005-0000-0000-0000EA060000}"/>
+    <cellStyle name="Note 17 25" xfId="2656" xr:uid="{00000000-0005-0000-0000-0000EB060000}"/>
+    <cellStyle name="Note 17 26" xfId="2703" xr:uid="{00000000-0005-0000-0000-0000EC060000}"/>
+    <cellStyle name="Note 17 27" xfId="2755" xr:uid="{00000000-0005-0000-0000-0000ED060000}"/>
+    <cellStyle name="Note 17 28" xfId="2803" xr:uid="{00000000-0005-0000-0000-0000EE060000}"/>
+    <cellStyle name="Note 17 29" xfId="2849" xr:uid="{00000000-0005-0000-0000-0000EF060000}"/>
+    <cellStyle name="Note 17 3" xfId="1190" xr:uid="{00000000-0005-0000-0000-0000F0060000}"/>
+    <cellStyle name="Note 17 30" xfId="2895" xr:uid="{00000000-0005-0000-0000-0000F1060000}"/>
+    <cellStyle name="Note 17 31" xfId="2944" xr:uid="{00000000-0005-0000-0000-0000F2060000}"/>
+    <cellStyle name="Note 17 32" xfId="2990" xr:uid="{00000000-0005-0000-0000-0000F3060000}"/>
+    <cellStyle name="Note 17 4" xfId="1266" xr:uid="{00000000-0005-0000-0000-0000F4060000}"/>
+    <cellStyle name="Note 17 5" xfId="1342" xr:uid="{00000000-0005-0000-0000-0000F5060000}"/>
+    <cellStyle name="Note 17 6" xfId="1418" xr:uid="{00000000-0005-0000-0000-0000F6060000}"/>
+    <cellStyle name="Note 17 7" xfId="1493" xr:uid="{00000000-0005-0000-0000-0000F7060000}"/>
+    <cellStyle name="Note 17 8" xfId="1569" xr:uid="{00000000-0005-0000-0000-0000F8060000}"/>
+    <cellStyle name="Note 17 9" xfId="1644" xr:uid="{00000000-0005-0000-0000-0000F9060000}"/>
+    <cellStyle name="Note 2" xfId="602" xr:uid="{00000000-0005-0000-0000-0000FA060000}"/>
+    <cellStyle name="Note 2 10" xfId="1719" xr:uid="{00000000-0005-0000-0000-0000FB060000}"/>
+    <cellStyle name="Note 2 11" xfId="1795" xr:uid="{00000000-0005-0000-0000-0000FC060000}"/>
+    <cellStyle name="Note 2 12" xfId="1859" xr:uid="{00000000-0005-0000-0000-0000FD060000}"/>
+    <cellStyle name="Note 2 13" xfId="1924" xr:uid="{00000000-0005-0000-0000-0000FE060000}"/>
+    <cellStyle name="Note 2 14" xfId="1987" xr:uid="{00000000-0005-0000-0000-0000FF060000}"/>
+    <cellStyle name="Note 2 15" xfId="2048" xr:uid="{00000000-0005-0000-0000-000000070000}"/>
+    <cellStyle name="Note 2 16" xfId="2110" xr:uid="{00000000-0005-0000-0000-000001070000}"/>
+    <cellStyle name="Note 2 17" xfId="2172" xr:uid="{00000000-0005-0000-0000-000002070000}"/>
+    <cellStyle name="Note 2 18" xfId="2235" xr:uid="{00000000-0005-0000-0000-000003070000}"/>
+    <cellStyle name="Note 2 19" xfId="2294" xr:uid="{00000000-0005-0000-0000-000004070000}"/>
+    <cellStyle name="Note 2 2" xfId="1115" xr:uid="{00000000-0005-0000-0000-000005070000}"/>
+    <cellStyle name="Note 2 20" xfId="2355" xr:uid="{00000000-0005-0000-0000-000006070000}"/>
+    <cellStyle name="Note 2 21" xfId="2416" xr:uid="{00000000-0005-0000-0000-000007070000}"/>
+    <cellStyle name="Note 2 22" xfId="2479" xr:uid="{00000000-0005-0000-0000-000008070000}"/>
+    <cellStyle name="Note 2 23" xfId="2536" xr:uid="{00000000-0005-0000-0000-000009070000}"/>
+    <cellStyle name="Note 2 24" xfId="2597" xr:uid="{00000000-0005-0000-0000-00000A070000}"/>
+    <cellStyle name="Note 2 25" xfId="2657" xr:uid="{00000000-0005-0000-0000-00000B070000}"/>
+    <cellStyle name="Note 2 26" xfId="2704" xr:uid="{00000000-0005-0000-0000-00000C070000}"/>
+    <cellStyle name="Note 2 27" xfId="2756" xr:uid="{00000000-0005-0000-0000-00000D070000}"/>
+    <cellStyle name="Note 2 28" xfId="2804" xr:uid="{00000000-0005-0000-0000-00000E070000}"/>
+    <cellStyle name="Note 2 29" xfId="2850" xr:uid="{00000000-0005-0000-0000-00000F070000}"/>
+    <cellStyle name="Note 2 3" xfId="1191" xr:uid="{00000000-0005-0000-0000-000010070000}"/>
+    <cellStyle name="Note 2 30" xfId="2896" xr:uid="{00000000-0005-0000-0000-000011070000}"/>
+    <cellStyle name="Note 2 31" xfId="2945" xr:uid="{00000000-0005-0000-0000-000012070000}"/>
+    <cellStyle name="Note 2 32" xfId="2991" xr:uid="{00000000-0005-0000-0000-000013070000}"/>
+    <cellStyle name="Note 2 4" xfId="1267" xr:uid="{00000000-0005-0000-0000-000014070000}"/>
+    <cellStyle name="Note 2 5" xfId="1343" xr:uid="{00000000-0005-0000-0000-000015070000}"/>
+    <cellStyle name="Note 2 6" xfId="1419" xr:uid="{00000000-0005-0000-0000-000016070000}"/>
+    <cellStyle name="Note 2 7" xfId="1494" xr:uid="{00000000-0005-0000-0000-000017070000}"/>
+    <cellStyle name="Note 2 8" xfId="1570" xr:uid="{00000000-0005-0000-0000-000018070000}"/>
+    <cellStyle name="Note 2 9" xfId="1645" xr:uid="{00000000-0005-0000-0000-000019070000}"/>
+    <cellStyle name="Note 3" xfId="603" xr:uid="{00000000-0005-0000-0000-00001A070000}"/>
+    <cellStyle name="Note 3 10" xfId="1720" xr:uid="{00000000-0005-0000-0000-00001B070000}"/>
+    <cellStyle name="Note 3 11" xfId="1796" xr:uid="{00000000-0005-0000-0000-00001C070000}"/>
+    <cellStyle name="Note 3 12" xfId="1860" xr:uid="{00000000-0005-0000-0000-00001D070000}"/>
+    <cellStyle name="Note 3 13" xfId="1925" xr:uid="{00000000-0005-0000-0000-00001E070000}"/>
+    <cellStyle name="Note 3 14" xfId="1988" xr:uid="{00000000-0005-0000-0000-00001F070000}"/>
+    <cellStyle name="Note 3 15" xfId="2049" xr:uid="{00000000-0005-0000-0000-000020070000}"/>
+    <cellStyle name="Note 3 16" xfId="2111" xr:uid="{00000000-0005-0000-0000-000021070000}"/>
+    <cellStyle name="Note 3 17" xfId="2173" xr:uid="{00000000-0005-0000-0000-000022070000}"/>
+    <cellStyle name="Note 3 18" xfId="2236" xr:uid="{00000000-0005-0000-0000-000023070000}"/>
+    <cellStyle name="Note 3 19" xfId="2295" xr:uid="{00000000-0005-0000-0000-000024070000}"/>
+    <cellStyle name="Note 3 2" xfId="1116" xr:uid="{00000000-0005-0000-0000-000025070000}"/>
+    <cellStyle name="Note 3 20" xfId="2356" xr:uid="{00000000-0005-0000-0000-000026070000}"/>
+    <cellStyle name="Note 3 21" xfId="2417" xr:uid="{00000000-0005-0000-0000-000027070000}"/>
+    <cellStyle name="Note 3 22" xfId="2480" xr:uid="{00000000-0005-0000-0000-000028070000}"/>
+    <cellStyle name="Note 3 23" xfId="2537" xr:uid="{00000000-0005-0000-0000-000029070000}"/>
+    <cellStyle name="Note 3 24" xfId="2598" xr:uid="{00000000-0005-0000-0000-00002A070000}"/>
+    <cellStyle name="Note 3 25" xfId="2658" xr:uid="{00000000-0005-0000-0000-00002B070000}"/>
+    <cellStyle name="Note 3 26" xfId="2705" xr:uid="{00000000-0005-0000-0000-00002C070000}"/>
+    <cellStyle name="Note 3 27" xfId="2757" xr:uid="{00000000-0005-0000-0000-00002D070000}"/>
+    <cellStyle name="Note 3 28" xfId="2805" xr:uid="{00000000-0005-0000-0000-00002E070000}"/>
+    <cellStyle name="Note 3 29" xfId="2851" xr:uid="{00000000-0005-0000-0000-00002F070000}"/>
+    <cellStyle name="Note 3 3" xfId="1192" xr:uid="{00000000-0005-0000-0000-000030070000}"/>
+    <cellStyle name="Note 3 30" xfId="2897" xr:uid="{00000000-0005-0000-0000-000031070000}"/>
+    <cellStyle name="Note 3 31" xfId="2946" xr:uid="{00000000-0005-0000-0000-000032070000}"/>
+    <cellStyle name="Note 3 32" xfId="2992" xr:uid="{00000000-0005-0000-0000-000033070000}"/>
+    <cellStyle name="Note 3 4" xfId="1268" xr:uid="{00000000-0005-0000-0000-000034070000}"/>
+    <cellStyle name="Note 3 5" xfId="1344" xr:uid="{00000000-0005-0000-0000-000035070000}"/>
+    <cellStyle name="Note 3 6" xfId="1420" xr:uid="{00000000-0005-0000-0000-000036070000}"/>
+    <cellStyle name="Note 3 7" xfId="1495" xr:uid="{00000000-0005-0000-0000-000037070000}"/>
+    <cellStyle name="Note 3 8" xfId="1571" xr:uid="{00000000-0005-0000-0000-000038070000}"/>
+    <cellStyle name="Note 3 9" xfId="1646" xr:uid="{00000000-0005-0000-0000-000039070000}"/>
+    <cellStyle name="Note 4" xfId="604" xr:uid="{00000000-0005-0000-0000-00003A070000}"/>
+    <cellStyle name="Note 4 10" xfId="1721" xr:uid="{00000000-0005-0000-0000-00003B070000}"/>
+    <cellStyle name="Note 4 11" xfId="1797" xr:uid="{00000000-0005-0000-0000-00003C070000}"/>
+    <cellStyle name="Note 4 12" xfId="1861" xr:uid="{00000000-0005-0000-0000-00003D070000}"/>
+    <cellStyle name="Note 4 13" xfId="1926" xr:uid="{00000000-0005-0000-0000-00003E070000}"/>
+    <cellStyle name="Note 4 14" xfId="1989" xr:uid="{00000000-0005-0000-0000-00003F070000}"/>
+    <cellStyle name="Note 4 15" xfId="2050" xr:uid="{00000000-0005-0000-0000-000040070000}"/>
+    <cellStyle name="Note 4 16" xfId="2112" xr:uid="{00000000-0005-0000-0000-000041070000}"/>
+    <cellStyle name="Note 4 17" xfId="2174" xr:uid="{00000000-0005-0000-0000-000042070000}"/>
+    <cellStyle name="Note 4 18" xfId="2237" xr:uid="{00000000-0005-0000-0000-000043070000}"/>
+    <cellStyle name="Note 4 19" xfId="2296" xr:uid="{00000000-0005-0000-0000-000044070000}"/>
+    <cellStyle name="Note 4 2" xfId="1117" xr:uid="{00000000-0005-0000-0000-000045070000}"/>
+    <cellStyle name="Note 4 20" xfId="2357" xr:uid="{00000000-0005-0000-0000-000046070000}"/>
+    <cellStyle name="Note 4 21" xfId="2418" xr:uid="{00000000-0005-0000-0000-000047070000}"/>
+    <cellStyle name="Note 4 22" xfId="2481" xr:uid="{00000000-0005-0000-0000-000048070000}"/>
+    <cellStyle name="Note 4 23" xfId="2538" xr:uid="{00000000-0005-0000-0000-000049070000}"/>
+    <cellStyle name="Note 4 24" xfId="2599" xr:uid="{00000000-0005-0000-0000-00004A070000}"/>
+    <cellStyle name="Note 4 25" xfId="2659" xr:uid="{00000000-0005-0000-0000-00004B070000}"/>
+    <cellStyle name="Note 4 26" xfId="2706" xr:uid="{00000000-0005-0000-0000-00004C070000}"/>
+    <cellStyle name="Note 4 27" xfId="2758" xr:uid="{00000000-0005-0000-0000-00004D070000}"/>
+    <cellStyle name="Note 4 28" xfId="2806" xr:uid="{00000000-0005-0000-0000-00004E070000}"/>
+    <cellStyle name="Note 4 29" xfId="2852" xr:uid="{00000000-0005-0000-0000-00004F070000}"/>
+    <cellStyle name="Note 4 3" xfId="1193" xr:uid="{00000000-0005-0000-0000-000050070000}"/>
+    <cellStyle name="Note 4 30" xfId="2898" xr:uid="{00000000-0005-0000-0000-000051070000}"/>
+    <cellStyle name="Note 4 31" xfId="2947" xr:uid="{00000000-0005-0000-0000-000052070000}"/>
+    <cellStyle name="Note 4 32" xfId="2993" xr:uid="{00000000-0005-0000-0000-000053070000}"/>
+    <cellStyle name="Note 4 4" xfId="1269" xr:uid="{00000000-0005-0000-0000-000054070000}"/>
+    <cellStyle name="Note 4 5" xfId="1345" xr:uid="{00000000-0005-0000-0000-000055070000}"/>
+    <cellStyle name="Note 4 6" xfId="1421" xr:uid="{00000000-0005-0000-0000-000056070000}"/>
+    <cellStyle name="Note 4 7" xfId="1496" xr:uid="{00000000-0005-0000-0000-000057070000}"/>
+    <cellStyle name="Note 4 8" xfId="1572" xr:uid="{00000000-0005-0000-0000-000058070000}"/>
+    <cellStyle name="Note 4 9" xfId="1647" xr:uid="{00000000-0005-0000-0000-000059070000}"/>
+    <cellStyle name="Note 5" xfId="605" xr:uid="{00000000-0005-0000-0000-00005A070000}"/>
+    <cellStyle name="Note 5 10" xfId="1722" xr:uid="{00000000-0005-0000-0000-00005B070000}"/>
+    <cellStyle name="Note 5 11" xfId="1798" xr:uid="{00000000-0005-0000-0000-00005C070000}"/>
+    <cellStyle name="Note 5 12" xfId="1862" xr:uid="{00000000-0005-0000-0000-00005D070000}"/>
+    <cellStyle name="Note 5 13" xfId="1927" xr:uid="{00000000-0005-0000-0000-00005E070000}"/>
+    <cellStyle name="Note 5 14" xfId="1990" xr:uid="{00000000-0005-0000-0000-00005F070000}"/>
+    <cellStyle name="Note 5 15" xfId="2051" xr:uid="{00000000-0005-0000-0000-000060070000}"/>
+    <cellStyle name="Note 5 16" xfId="2113" xr:uid="{00000000-0005-0000-0000-000061070000}"/>
+    <cellStyle name="Note 5 17" xfId="2175" xr:uid="{00000000-0005-0000-0000-000062070000}"/>
+    <cellStyle name="Note 5 18" xfId="2238" xr:uid="{00000000-0005-0000-0000-000063070000}"/>
+    <cellStyle name="Note 5 19" xfId="2297" xr:uid="{00000000-0005-0000-0000-000064070000}"/>
+    <cellStyle name="Note 5 2" xfId="1118" xr:uid="{00000000-0005-0000-0000-000065070000}"/>
+    <cellStyle name="Note 5 20" xfId="2358" xr:uid="{00000000-0005-0000-0000-000066070000}"/>
+    <cellStyle name="Note 5 21" xfId="2419" xr:uid="{00000000-0005-0000-0000-000067070000}"/>
+    <cellStyle name="Note 5 22" xfId="2482" xr:uid="{00000000-0005-0000-0000-000068070000}"/>
+    <cellStyle name="Note 5 23" xfId="2539" xr:uid="{00000000-0005-0000-0000-000069070000}"/>
+    <cellStyle name="Note 5 24" xfId="2600" xr:uid="{00000000-0005-0000-0000-00006A070000}"/>
+    <cellStyle name="Note 5 25" xfId="2660" xr:uid="{00000000-0005-0000-0000-00006B070000}"/>
+    <cellStyle name="Note 5 26" xfId="2707" xr:uid="{00000000-0005-0000-0000-00006C070000}"/>
+    <cellStyle name="Note 5 27" xfId="2759" xr:uid="{00000000-0005-0000-0000-00006D070000}"/>
+    <cellStyle name="Note 5 28" xfId="2807" xr:uid="{00000000-0005-0000-0000-00006E070000}"/>
+    <cellStyle name="Note 5 29" xfId="2853" xr:uid="{00000000-0005-0000-0000-00006F070000}"/>
+    <cellStyle name="Note 5 3" xfId="1194" xr:uid="{00000000-0005-0000-0000-000070070000}"/>
+    <cellStyle name="Note 5 30" xfId="2899" xr:uid="{00000000-0005-0000-0000-000071070000}"/>
+    <cellStyle name="Note 5 31" xfId="2948" xr:uid="{00000000-0005-0000-0000-000072070000}"/>
+    <cellStyle name="Note 5 32" xfId="2994" xr:uid="{00000000-0005-0000-0000-000073070000}"/>
+    <cellStyle name="Note 5 4" xfId="1270" xr:uid="{00000000-0005-0000-0000-000074070000}"/>
+    <cellStyle name="Note 5 5" xfId="1346" xr:uid="{00000000-0005-0000-0000-000075070000}"/>
+    <cellStyle name="Note 5 6" xfId="1422" xr:uid="{00000000-0005-0000-0000-000076070000}"/>
+    <cellStyle name="Note 5 7" xfId="1497" xr:uid="{00000000-0005-0000-0000-000077070000}"/>
+    <cellStyle name="Note 5 8" xfId="1573" xr:uid="{00000000-0005-0000-0000-000078070000}"/>
+    <cellStyle name="Note 5 9" xfId="1648" xr:uid="{00000000-0005-0000-0000-000079070000}"/>
+    <cellStyle name="Note 6" xfId="606" xr:uid="{00000000-0005-0000-0000-00007A070000}"/>
+    <cellStyle name="Note 6 10" xfId="1723" xr:uid="{00000000-0005-0000-0000-00007B070000}"/>
+    <cellStyle name="Note 6 11" xfId="1799" xr:uid="{00000000-0005-0000-0000-00007C070000}"/>
+    <cellStyle name="Note 6 12" xfId="1863" xr:uid="{00000000-0005-0000-0000-00007D070000}"/>
+    <cellStyle name="Note 6 13" xfId="1928" xr:uid="{00000000-0005-0000-0000-00007E070000}"/>
+    <cellStyle name="Note 6 14" xfId="1991" xr:uid="{00000000-0005-0000-0000-00007F070000}"/>
+    <cellStyle name="Note 6 15" xfId="2052" xr:uid="{00000000-0005-0000-0000-000080070000}"/>
+    <cellStyle name="Note 6 16" xfId="2114" xr:uid="{00000000-0005-0000-0000-000081070000}"/>
+    <cellStyle name="Note 6 17" xfId="2176" xr:uid="{00000000-0005-0000-0000-000082070000}"/>
+    <cellStyle name="Note 6 18" xfId="2239" xr:uid="{00000000-0005-0000-0000-000083070000}"/>
+    <cellStyle name="Note 6 19" xfId="2298" xr:uid="{00000000-0005-0000-0000-000084070000}"/>
+    <cellStyle name="Note 6 2" xfId="1119" xr:uid="{00000000-0005-0000-0000-000085070000}"/>
+    <cellStyle name="Note 6 20" xfId="2359" xr:uid="{00000000-0005-0000-0000-000086070000}"/>
+    <cellStyle name="Note 6 21" xfId="2420" xr:uid="{00000000-0005-0000-0000-000087070000}"/>
+    <cellStyle name="Note 6 22" xfId="2483" xr:uid="{00000000-0005-0000-0000-000088070000}"/>
+    <cellStyle name="Note 6 23" xfId="2540" xr:uid="{00000000-0005-0000-0000-000089070000}"/>
+    <cellStyle name="Note 6 24" xfId="2601" xr:uid="{00000000-0005-0000-0000-00008A070000}"/>
+    <cellStyle name="Note 6 25" xfId="2661" xr:uid="{00000000-0005-0000-0000-00008B070000}"/>
+    <cellStyle name="Note 6 26" xfId="2708" xr:uid="{00000000-0005-0000-0000-00008C070000}"/>
+    <cellStyle name="Note 6 27" xfId="2760" xr:uid="{00000000-0005-0000-0000-00008D070000}"/>
+    <cellStyle name="Note 6 28" xfId="2808" xr:uid="{00000000-0005-0000-0000-00008E070000}"/>
+    <cellStyle name="Note 6 29" xfId="2854" xr:uid="{00000000-0005-0000-0000-00008F070000}"/>
+    <cellStyle name="Note 6 3" xfId="1195" xr:uid="{00000000-0005-0000-0000-000090070000}"/>
+    <cellStyle name="Note 6 30" xfId="2900" xr:uid="{00000000-0005-0000-0000-000091070000}"/>
+    <cellStyle name="Note 6 31" xfId="2949" xr:uid="{00000000-0005-0000-0000-000092070000}"/>
+    <cellStyle name="Note 6 32" xfId="2995" xr:uid="{00000000-0005-0000-0000-000093070000}"/>
+    <cellStyle name="Note 6 4" xfId="1271" xr:uid="{00000000-0005-0000-0000-000094070000}"/>
+    <cellStyle name="Note 6 5" xfId="1347" xr:uid="{00000000-0005-0000-0000-000095070000}"/>
+    <cellStyle name="Note 6 6" xfId="1423" xr:uid="{00000000-0005-0000-0000-000096070000}"/>
+    <cellStyle name="Note 6 7" xfId="1498" xr:uid="{00000000-0005-0000-0000-000097070000}"/>
+    <cellStyle name="Note 6 8" xfId="1574" xr:uid="{00000000-0005-0000-0000-000098070000}"/>
+    <cellStyle name="Note 6 9" xfId="1649" xr:uid="{00000000-0005-0000-0000-000099070000}"/>
+    <cellStyle name="Note 7" xfId="607" xr:uid="{00000000-0005-0000-0000-00009A070000}"/>
+    <cellStyle name="Note 7 10" xfId="1724" xr:uid="{00000000-0005-0000-0000-00009B070000}"/>
+    <cellStyle name="Note 7 11" xfId="1800" xr:uid="{00000000-0005-0000-0000-00009C070000}"/>
+    <cellStyle name="Note 7 12" xfId="1864" xr:uid="{00000000-0005-0000-0000-00009D070000}"/>
+    <cellStyle name="Note 7 13" xfId="1929" xr:uid="{00000000-0005-0000-0000-00009E070000}"/>
+    <cellStyle name="Note 7 14" xfId="1992" xr:uid="{00000000-0005-0000-0000-00009F070000}"/>
+    <cellStyle name="Note 7 15" xfId="2053" xr:uid="{00000000-0005-0000-0000-0000A0070000}"/>
+    <cellStyle name="Note 7 16" xfId="2115" xr:uid="{00000000-0005-0000-0000-0000A1070000}"/>
+    <cellStyle name="Note 7 17" xfId="2177" xr:uid="{00000000-0005-0000-0000-0000A2070000}"/>
+    <cellStyle name="Note 7 18" xfId="2240" xr:uid="{00000000-0005-0000-0000-0000A3070000}"/>
+    <cellStyle name="Note 7 19" xfId="2299" xr:uid="{00000000-0005-0000-0000-0000A4070000}"/>
+    <cellStyle name="Note 7 2" xfId="1120" xr:uid="{00000000-0005-0000-0000-0000A5070000}"/>
+    <cellStyle name="Note 7 20" xfId="2360" xr:uid="{00000000-0005-0000-0000-0000A6070000}"/>
+    <cellStyle name="Note 7 21" xfId="2421" xr:uid="{00000000-0005-0000-0000-0000A7070000}"/>
+    <cellStyle name="Note 7 22" xfId="2484" xr:uid="{00000000-0005-0000-0000-0000A8070000}"/>
+    <cellStyle name="Note 7 23" xfId="2541" xr:uid="{00000000-0005-0000-0000-0000A9070000}"/>
+    <cellStyle name="Note 7 24" xfId="2602" xr:uid="{00000000-0005-0000-0000-0000AA070000}"/>
+    <cellStyle name="Note 7 25" xfId="2662" xr:uid="{00000000-0005-0000-0000-0000AB070000}"/>
+    <cellStyle name="Note 7 26" xfId="2709" xr:uid="{00000000-0005-0000-0000-0000AC070000}"/>
+    <cellStyle name="Note 7 27" xfId="2761" xr:uid="{00000000-0005-0000-0000-0000AD070000}"/>
+    <cellStyle name="Note 7 28" xfId="2809" xr:uid="{00000000-0005-0000-0000-0000AE070000}"/>
+    <cellStyle name="Note 7 29" xfId="2855" xr:uid="{00000000-0005-0000-0000-0000AF070000}"/>
+    <cellStyle name="Note 7 3" xfId="1196" xr:uid="{00000000-0005-0000-0000-0000B0070000}"/>
+    <cellStyle name="Note 7 30" xfId="2901" xr:uid="{00000000-0005-0000-0000-0000B1070000}"/>
+    <cellStyle name="Note 7 31" xfId="2950" xr:uid="{00000000-0005-0000-0000-0000B2070000}"/>
+    <cellStyle name="Note 7 32" xfId="2996" xr:uid="{00000000-0005-0000-0000-0000B3070000}"/>
+    <cellStyle name="Note 7 4" xfId="1272" xr:uid="{00000000-0005-0000-0000-0000B4070000}"/>
+    <cellStyle name="Note 7 5" xfId="1348" xr:uid="{00000000-0005-0000-0000-0000B5070000}"/>
+    <cellStyle name="Note 7 6" xfId="1424" xr:uid="{00000000-0005-0000-0000-0000B6070000}"/>
+    <cellStyle name="Note 7 7" xfId="1499" xr:uid="{00000000-0005-0000-0000-0000B7070000}"/>
+    <cellStyle name="Note 7 8" xfId="1575" xr:uid="{00000000-0005-0000-0000-0000B8070000}"/>
+    <cellStyle name="Note 7 9" xfId="1650" xr:uid="{00000000-0005-0000-0000-0000B9070000}"/>
+    <cellStyle name="Note 8" xfId="608" xr:uid="{00000000-0005-0000-0000-0000BA070000}"/>
+    <cellStyle name="Note 8 10" xfId="1725" xr:uid="{00000000-0005-0000-0000-0000BB070000}"/>
+    <cellStyle name="Note 8 11" xfId="1801" xr:uid="{00000000-0005-0000-0000-0000BC070000}"/>
+    <cellStyle name="Note 8 12" xfId="1865" xr:uid="{00000000-0005-0000-0000-0000BD070000}"/>
+    <cellStyle name="Note 8 13" xfId="1930" xr:uid="{00000000-0005-0000-0000-0000BE070000}"/>
+    <cellStyle name="Note 8 14" xfId="1993" xr:uid="{00000000-0005-0000-0000-0000BF070000}"/>
+    <cellStyle name="Note 8 15" xfId="2054" xr:uid="{00000000-0005-0000-0000-0000C0070000}"/>
+    <cellStyle name="Note 8 16" xfId="2116" xr:uid="{00000000-0005-0000-0000-0000C1070000}"/>
+    <cellStyle name="Note 8 17" xfId="2178" xr:uid="{00000000-0005-0000-0000-0000C2070000}"/>
+    <cellStyle name="Note 8 18" xfId="2241" xr:uid="{00000000-0005-0000-0000-0000C3070000}"/>
+    <cellStyle name="Note 8 19" xfId="2300" xr:uid="{00000000-0005-0000-0000-0000C4070000}"/>
+    <cellStyle name="Note 8 2" xfId="1121" xr:uid="{00000000-0005-0000-0000-0000C5070000}"/>
+    <cellStyle name="Note 8 20" xfId="2361" xr:uid="{00000000-0005-0000-0000-0000C6070000}"/>
+    <cellStyle name="Note 8 21" xfId="2422" xr:uid="{00000000-0005-0000-0000-0000C7070000}"/>
+    <cellStyle name="Note 8 22" xfId="2485" xr:uid="{00000000-0005-0000-0000-0000C8070000}"/>
+    <cellStyle name="Note 8 23" xfId="2542" xr:uid="{00000000-0005-0000-0000-0000C9070000}"/>
+    <cellStyle name="Note 8 24" xfId="2603" xr:uid="{00000000-0005-0000-0000-0000CA070000}"/>
+    <cellStyle name="Note 8 25" xfId="2663" xr:uid="{00000000-0005-0000-0000-0000CB070000}"/>
+    <cellStyle name="Note 8 26" xfId="2710" xr:uid="{00000000-0005-0000-0000-0000CC070000}"/>
+    <cellStyle name="Note 8 27" xfId="2762" xr:uid="{00000000-0005-0000-0000-0000CD070000}"/>
+    <cellStyle name="Note 8 28" xfId="2810" xr:uid="{00000000-0005-0000-0000-0000CE070000}"/>
+    <cellStyle name="Note 8 29" xfId="2856" xr:uid="{00000000-0005-0000-0000-0000CF070000}"/>
+    <cellStyle name="Note 8 3" xfId="1197" xr:uid="{00000000-0005-0000-0000-0000D0070000}"/>
+    <cellStyle name="Note 8 30" xfId="2902" xr:uid="{00000000-0005-0000-0000-0000D1070000}"/>
+    <cellStyle name="Note 8 31" xfId="2951" xr:uid="{00000000-0005-0000-0000-0000D2070000}"/>
+    <cellStyle name="Note 8 32" xfId="2997" xr:uid="{00000000-0005-0000-0000-0000D3070000}"/>
+    <cellStyle name="Note 8 4" xfId="1273" xr:uid="{00000000-0005-0000-0000-0000D4070000}"/>
+    <cellStyle name="Note 8 5" xfId="1349" xr:uid="{00000000-0005-0000-0000-0000D5070000}"/>
+    <cellStyle name="Note 8 6" xfId="1425" xr:uid="{00000000-0005-0000-0000-0000D6070000}"/>
+    <cellStyle name="Note 8 7" xfId="1500" xr:uid="{00000000-0005-0000-0000-0000D7070000}"/>
+    <cellStyle name="Note 8 8" xfId="1576" xr:uid="{00000000-0005-0000-0000-0000D8070000}"/>
+    <cellStyle name="Note 8 9" xfId="1651" xr:uid="{00000000-0005-0000-0000-0000D9070000}"/>
+    <cellStyle name="Note 9" xfId="609" xr:uid="{00000000-0005-0000-0000-0000DA070000}"/>
+    <cellStyle name="Note 9 10" xfId="1726" xr:uid="{00000000-0005-0000-0000-0000DB070000}"/>
+    <cellStyle name="Note 9 11" xfId="1802" xr:uid="{00000000-0005-0000-0000-0000DC070000}"/>
+    <cellStyle name="Note 9 12" xfId="1866" xr:uid="{00000000-0005-0000-0000-0000DD070000}"/>
+    <cellStyle name="Note 9 13" xfId="1931" xr:uid="{00000000-0005-0000-0000-0000DE070000}"/>
+    <cellStyle name="Note 9 14" xfId="1994" xr:uid="{00000000-0005-0000-0000-0000DF070000}"/>
+    <cellStyle name="Note 9 15" xfId="2055" xr:uid="{00000000-0005-0000-0000-0000E0070000}"/>
+    <cellStyle name="Note 9 16" xfId="2117" xr:uid="{00000000-0005-0000-0000-0000E1070000}"/>
+    <cellStyle name="Note 9 17" xfId="2179" xr:uid="{00000000-0005-0000-0000-0000E2070000}"/>
+    <cellStyle name="Note 9 18" xfId="2242" xr:uid="{00000000-0005-0000-0000-0000E3070000}"/>
+    <cellStyle name="Note 9 19" xfId="2301" xr:uid="{00000000-0005-0000-0000-0000E4070000}"/>
+    <cellStyle name="Note 9 2" xfId="1122" xr:uid="{00000000-0005-0000-0000-0000E5070000}"/>
+    <cellStyle name="Note 9 20" xfId="2362" xr:uid="{00000000-0005-0000-0000-0000E6070000}"/>
+    <cellStyle name="Note 9 21" xfId="2423" xr:uid="{00000000-0005-0000-0000-0000E7070000}"/>
+    <cellStyle name="Note 9 22" xfId="2486" xr:uid="{00000000-0005-0000-0000-0000E8070000}"/>
+    <cellStyle name="Note 9 23" xfId="2543" xr:uid="{00000000-0005-0000-0000-0000E9070000}"/>
+    <cellStyle name="Note 9 24" xfId="2604" xr:uid="{00000000-0005-0000-0000-0000EA070000}"/>
+    <cellStyle name="Note 9 25" xfId="2664" xr:uid="{00000000-0005-0000-0000-0000EB070000}"/>
+    <cellStyle name="Note 9 26" xfId="2711" xr:uid="{00000000-0005-0000-0000-0000EC070000}"/>
+    <cellStyle name="Note 9 27" xfId="2763" xr:uid="{00000000-0005-0000-0000-0000ED070000}"/>
+    <cellStyle name="Note 9 28" xfId="2811" xr:uid="{00000000-0005-0000-0000-0000EE070000}"/>
+    <cellStyle name="Note 9 29" xfId="2857" xr:uid="{00000000-0005-0000-0000-0000EF070000}"/>
+    <cellStyle name="Note 9 3" xfId="1198" xr:uid="{00000000-0005-0000-0000-0000F0070000}"/>
+    <cellStyle name="Note 9 30" xfId="2903" xr:uid="{00000000-0005-0000-0000-0000F1070000}"/>
+    <cellStyle name="Note 9 31" xfId="2952" xr:uid="{00000000-0005-0000-0000-0000F2070000}"/>
+    <cellStyle name="Note 9 32" xfId="2998" xr:uid="{00000000-0005-0000-0000-0000F3070000}"/>
+    <cellStyle name="Note 9 4" xfId="1274" xr:uid="{00000000-0005-0000-0000-0000F4070000}"/>
+    <cellStyle name="Note 9 5" xfId="1350" xr:uid="{00000000-0005-0000-0000-0000F5070000}"/>
+    <cellStyle name="Note 9 6" xfId="1426" xr:uid="{00000000-0005-0000-0000-0000F6070000}"/>
+    <cellStyle name="Note 9 7" xfId="1501" xr:uid="{00000000-0005-0000-0000-0000F7070000}"/>
+    <cellStyle name="Note 9 8" xfId="1577" xr:uid="{00000000-0005-0000-0000-0000F8070000}"/>
+    <cellStyle name="Note 9 9" xfId="1652" xr:uid="{00000000-0005-0000-0000-0000F9070000}"/>
+    <cellStyle name="Output 10" xfId="610" xr:uid="{00000000-0005-0000-0000-0000FA070000}"/>
+    <cellStyle name="Output 10 10" xfId="1727" xr:uid="{00000000-0005-0000-0000-0000FB070000}"/>
+    <cellStyle name="Output 10 11" xfId="1803" xr:uid="{00000000-0005-0000-0000-0000FC070000}"/>
+    <cellStyle name="Output 10 12" xfId="1867" xr:uid="{00000000-0005-0000-0000-0000FD070000}"/>
+    <cellStyle name="Output 10 13" xfId="1932" xr:uid="{00000000-0005-0000-0000-0000FE070000}"/>
+    <cellStyle name="Output 10 14" xfId="1995" xr:uid="{00000000-0005-0000-0000-0000FF070000}"/>
+    <cellStyle name="Output 10 15" xfId="2056" xr:uid="{00000000-0005-0000-0000-000000080000}"/>
+    <cellStyle name="Output 10 16" xfId="2118" xr:uid="{00000000-0005-0000-0000-000001080000}"/>
+    <cellStyle name="Output 10 17" xfId="2180" xr:uid="{00000000-0005-0000-0000-000002080000}"/>
+    <cellStyle name="Output 10 18" xfId="2243" xr:uid="{00000000-0005-0000-0000-000003080000}"/>
+    <cellStyle name="Output 10 19" xfId="2302" xr:uid="{00000000-0005-0000-0000-000004080000}"/>
+    <cellStyle name="Output 10 2" xfId="1123" xr:uid="{00000000-0005-0000-0000-000005080000}"/>
+    <cellStyle name="Output 10 20" xfId="2363" xr:uid="{00000000-0005-0000-0000-000006080000}"/>
+    <cellStyle name="Output 10 21" xfId="2424" xr:uid="{00000000-0005-0000-0000-000007080000}"/>
+    <cellStyle name="Output 10 22" xfId="2487" xr:uid="{00000000-0005-0000-0000-000008080000}"/>
+    <cellStyle name="Output 10 23" xfId="2544" xr:uid="{00000000-0005-0000-0000-000009080000}"/>
+    <cellStyle name="Output 10 24" xfId="2605" xr:uid="{00000000-0005-0000-0000-00000A080000}"/>
+    <cellStyle name="Output 10 25" xfId="2665" xr:uid="{00000000-0005-0000-0000-00000B080000}"/>
+    <cellStyle name="Output 10 26" xfId="2712" xr:uid="{00000000-0005-0000-0000-00000C080000}"/>
+    <cellStyle name="Output 10 27" xfId="2764" xr:uid="{00000000-0005-0000-0000-00000D080000}"/>
+    <cellStyle name="Output 10 28" xfId="2812" xr:uid="{00000000-0005-0000-0000-00000E080000}"/>
+    <cellStyle name="Output 10 29" xfId="2858" xr:uid="{00000000-0005-0000-0000-00000F080000}"/>
+    <cellStyle name="Output 10 3" xfId="1199" xr:uid="{00000000-0005-0000-0000-000010080000}"/>
+    <cellStyle name="Output 10 30" xfId="2904" xr:uid="{00000000-0005-0000-0000-000011080000}"/>
+    <cellStyle name="Output 10 31" xfId="2953" xr:uid="{00000000-0005-0000-0000-000012080000}"/>
+    <cellStyle name="Output 10 32" xfId="2999" xr:uid="{00000000-0005-0000-0000-000013080000}"/>
+    <cellStyle name="Output 10 4" xfId="1275" xr:uid="{00000000-0005-0000-0000-000014080000}"/>
+    <cellStyle name="Output 10 5" xfId="1351" xr:uid="{00000000-0005-0000-0000-000015080000}"/>
+    <cellStyle name="Output 10 6" xfId="1427" xr:uid="{00000000-0005-0000-0000-000016080000}"/>
+    <cellStyle name="Output 10 7" xfId="1502" xr:uid="{00000000-0005-0000-0000-000017080000}"/>
+    <cellStyle name="Output 10 8" xfId="1578" xr:uid="{00000000-0005-0000-0000-000018080000}"/>
+    <cellStyle name="Output 10 9" xfId="1653" xr:uid="{00000000-0005-0000-0000-000019080000}"/>
+    <cellStyle name="Output 11" xfId="611" xr:uid="{00000000-0005-0000-0000-00001A080000}"/>
+    <cellStyle name="Output 11 10" xfId="1728" xr:uid="{00000000-0005-0000-0000-00001B080000}"/>
+    <cellStyle name="Output 11 11" xfId="1804" xr:uid="{00000000-0005-0000-0000-00001C080000}"/>
+    <cellStyle name="Output 11 12" xfId="1868" xr:uid="{00000000-0005-0000-0000-00001D080000}"/>
+    <cellStyle name="Output 11 13" xfId="1933" xr:uid="{00000000-0005-0000-0000-00001E080000}"/>
+    <cellStyle name="Output 11 14" xfId="1996" xr:uid="{00000000-0005-0000-0000-00001F080000}"/>
+    <cellStyle name="Output 11 15" xfId="2057" xr:uid="{00000000-0005-0000-0000-000020080000}"/>
+    <cellStyle name="Output 11 16" xfId="2119" xr:uid="{00000000-0005-0000-0000-000021080000}"/>
+    <cellStyle name="Output 11 17" xfId="2181" xr:uid="{00000000-0005-0000-0000-000022080000}"/>
+    <cellStyle name="Output 11 18" xfId="2244" xr:uid="{00000000-0005-0000-0000-000023080000}"/>
+    <cellStyle name="Output 11 19" xfId="2303" xr:uid="{00000000-0005-0000-0000-000024080000}"/>
+    <cellStyle name="Output 11 2" xfId="1124" xr:uid="{00000000-0005-0000-0000-000025080000}"/>
+    <cellStyle name="Output 11 20" xfId="2364" xr:uid="{00000000-0005-0000-0000-000026080000}"/>
+    <cellStyle name="Output 11 21" xfId="2425" xr:uid="{00000000-0005-0000-0000-000027080000}"/>
+    <cellStyle name="Output 11 22" xfId="2488" xr:uid="{00000000-0005-0000-0000-000028080000}"/>
+    <cellStyle name="Output 11 23" xfId="2545" xr:uid="{00000000-0005-0000-0000-000029080000}"/>
+    <cellStyle name="Output 11 24" xfId="2606" xr:uid="{00000000-0005-0000-0000-00002A080000}"/>
+    <cellStyle name="Output 11 25" xfId="2666" xr:uid="{00000000-0005-0000-0000-00002B080000}"/>
+    <cellStyle name="Output 11 26" xfId="2713" xr:uid="{00000000-0005-0000-0000-00002C080000}"/>
+    <cellStyle name="Output 11 27" xfId="2765" xr:uid="{00000000-0005-0000-0000-00002D080000}"/>
+    <cellStyle name="Output 11 28" xfId="2813" xr:uid="{00000000-0005-0000-0000-00002E080000}"/>
+    <cellStyle name="Output 11 29" xfId="2859" xr:uid="{00000000-0005-0000-0000-00002F080000}"/>
+    <cellStyle name="Output 11 3" xfId="1200" xr:uid="{00000000-0005-0000-0000-000030080000}"/>
+    <cellStyle name="Output 11 30" xfId="2905" xr:uid="{00000000-0005-0000-0000-000031080000}"/>
+    <cellStyle name="Output 11 31" xfId="2954" xr:uid="{00000000-0005-0000-0000-000032080000}"/>
+    <cellStyle name="Output 11 32" xfId="3000" xr:uid="{00000000-0005-0000-0000-000033080000}"/>
+    <cellStyle name="Output 11 4" xfId="1276" xr:uid="{00000000-0005-0000-0000-000034080000}"/>
+    <cellStyle name="Output 11 5" xfId="1352" xr:uid="{00000000-0005-0000-0000-000035080000}"/>
+    <cellStyle name="Output 11 6" xfId="1428" xr:uid="{00000000-0005-0000-0000-000036080000}"/>
+    <cellStyle name="Output 11 7" xfId="1503" xr:uid="{00000000-0005-0000-0000-000037080000}"/>
+    <cellStyle name="Output 11 8" xfId="1579" xr:uid="{00000000-0005-0000-0000-000038080000}"/>
+    <cellStyle name="Output 11 9" xfId="1654" xr:uid="{00000000-0005-0000-0000-000039080000}"/>
+    <cellStyle name="Output 12" xfId="612" xr:uid="{00000000-0005-0000-0000-00003A080000}"/>
+    <cellStyle name="Output 12 10" xfId="1729" xr:uid="{00000000-0005-0000-0000-00003B080000}"/>
+    <cellStyle name="Output 12 11" xfId="1805" xr:uid="{00000000-0005-0000-0000-00003C080000}"/>
+    <cellStyle name="Output 12 12" xfId="1869" xr:uid="{00000000-0005-0000-0000-00003D080000}"/>
+    <cellStyle name="Output 12 13" xfId="1934" xr:uid="{00000000-0005-0000-0000-00003E080000}"/>
+    <cellStyle name="Output 12 14" xfId="1997" xr:uid="{00000000-0005-0000-0000-00003F080000}"/>
+    <cellStyle name="Output 12 15" xfId="2058" xr:uid="{00000000-0005-0000-0000-000040080000}"/>
+    <cellStyle name="Output 12 16" xfId="2120" xr:uid="{00000000-0005-0000-0000-000041080000}"/>
+    <cellStyle name="Output 12 17" xfId="2182" xr:uid="{00000000-0005-0000-0000-000042080000}"/>
+    <cellStyle name="Output 12 18" xfId="2245" xr:uid="{00000000-0005-0000-0000-000043080000}"/>
+    <cellStyle name="Output 12 19" xfId="2304" xr:uid="{00000000-0005-0000-0000-000044080000}"/>
+    <cellStyle name="Output 12 2" xfId="1125" xr:uid="{00000000-0005-0000-0000-000045080000}"/>
+    <cellStyle name="Output 12 20" xfId="2365" xr:uid="{00000000-0005-0000-0000-000046080000}"/>
+    <cellStyle name="Output 12 21" xfId="2426" xr:uid="{00000000-0005-0000-0000-000047080000}"/>
+    <cellStyle name="Output 12 22" xfId="2489" xr:uid="{00000000-0005-0000-0000-000048080000}"/>
+    <cellStyle name="Output 12 23" xfId="2546" xr:uid="{00000000-0005-0000-0000-000049080000}"/>
+    <cellStyle name="Output 12 24" xfId="2607" xr:uid="{00000000-0005-0000-0000-00004A080000}"/>
+    <cellStyle name="Output 12 25" xfId="2667" xr:uid="{00000000-0005-0000-0000-00004B080000}"/>
+    <cellStyle name="Output 12 26" xfId="2714" xr:uid="{00000000-0005-0000-0000-00004C080000}"/>
+    <cellStyle name="Output 12 27" xfId="2766" xr:uid="{00000000-0005-0000-0000-00004D080000}"/>
+    <cellStyle name="Output 12 28" xfId="2814" xr:uid="{00000000-0005-0000-0000-00004E080000}"/>
+    <cellStyle name="Output 12 29" xfId="2860" xr:uid="{00000000-0005-0000-0000-00004F080000}"/>
+    <cellStyle name="Output 12 3" xfId="1201" xr:uid="{00000000-0005-0000-0000-000050080000}"/>
+    <cellStyle name="Output 12 30" xfId="2906" xr:uid="{00000000-0005-0000-0000-000051080000}"/>
+    <cellStyle name="Output 12 31" xfId="2955" xr:uid="{00000000-0005-0000-0000-000052080000}"/>
+    <cellStyle name="Output 12 32" xfId="3001" xr:uid="{00000000-0005-0000-0000-000053080000}"/>
+    <cellStyle name="Output 12 4" xfId="1277" xr:uid="{00000000-0005-0000-0000-000054080000}"/>
+    <cellStyle name="Output 12 5" xfId="1353" xr:uid="{00000000-0005-0000-0000-000055080000}"/>
+    <cellStyle name="Output 12 6" xfId="1429" xr:uid="{00000000-0005-0000-0000-000056080000}"/>
+    <cellStyle name="Output 12 7" xfId="1504" xr:uid="{00000000-0005-0000-0000-000057080000}"/>
+    <cellStyle name="Output 12 8" xfId="1580" xr:uid="{00000000-0005-0000-0000-000058080000}"/>
+    <cellStyle name="Output 12 9" xfId="1655" xr:uid="{00000000-0005-0000-0000-000059080000}"/>
+    <cellStyle name="Output 13" xfId="613" xr:uid="{00000000-0005-0000-0000-00005A080000}"/>
+    <cellStyle name="Output 13 10" xfId="1730" xr:uid="{00000000-0005-0000-0000-00005B080000}"/>
+    <cellStyle name="Output 13 11" xfId="1806" xr:uid="{00000000-0005-0000-0000-00005C080000}"/>
+    <cellStyle name="Output 13 12" xfId="1870" xr:uid="{00000000-0005-0000-0000-00005D080000}"/>
+    <cellStyle name="Output 13 13" xfId="1935" xr:uid="{00000000-0005-0000-0000-00005E080000}"/>
+    <cellStyle name="Output 13 14" xfId="1998" xr:uid="{00000000-0005-0000-0000-00005F080000}"/>
+    <cellStyle name="Output 13 15" xfId="2059" xr:uid="{00000000-0005-0000-0000-000060080000}"/>
+    <cellStyle name="Output 13 16" xfId="2121" xr:uid="{00000000-0005-0000-0000-000061080000}"/>
+    <cellStyle name="Output 13 17" xfId="2183" xr:uid="{00000000-0005-0000-0000-000062080000}"/>
+    <cellStyle name="Output 13 18" xfId="2246" xr:uid="{00000000-0005-0000-0000-000063080000}"/>
+    <cellStyle name="Output 13 19" xfId="2305" xr:uid="{00000000-0005-0000-0000-000064080000}"/>
+    <cellStyle name="Output 13 2" xfId="1126" xr:uid="{00000000-0005-0000-0000-000065080000}"/>
+    <cellStyle name="Output 13 20" xfId="2366" xr:uid="{00000000-0005-0000-0000-000066080000}"/>
+    <cellStyle name="Output 13 21" xfId="2427" xr:uid="{00000000-0005-0000-0000-000067080000}"/>
+    <cellStyle name="Output 13 22" xfId="2490" xr:uid="{00000000-0005-0000-0000-000068080000}"/>
+    <cellStyle name="Output 13 23" xfId="2547" xr:uid="{00000000-0005-0000-0000-000069080000}"/>
+    <cellStyle name="Output 13 24" xfId="2608" xr:uid="{00000000-0005-0000-0000-00006A080000}"/>
+    <cellStyle name="Output 13 25" xfId="2668" xr:uid="{00000000-0005-0000-0000-00006B080000}"/>
+    <cellStyle name="Output 13 26" xfId="2715" xr:uid="{00000000-0005-0000-0000-00006C080000}"/>
+    <cellStyle name="Output 13 27" xfId="2767" xr:uid="{00000000-0005-0000-0000-00006D080000}"/>
+    <cellStyle name="Output 13 28" xfId="2815" xr:uid="{00000000-0005-0000-0000-00006E080000}"/>
+    <cellStyle name="Output 13 29" xfId="2861" xr:uid="{00000000-0005-0000-0000-00006F080000}"/>
+    <cellStyle name="Output 13 3" xfId="1202" xr:uid="{00000000-0005-0000-0000-000070080000}"/>
+    <cellStyle name="Output 13 30" xfId="2907" xr:uid="{00000000-0005-0000-0000-000071080000}"/>
+    <cellStyle name="Output 13 31" xfId="2956" xr:uid="{00000000-0005-0000-0000-000072080000}"/>
+    <cellStyle name="Output 13 32" xfId="3002" xr:uid="{00000000-0005-0000-0000-000073080000}"/>
+    <cellStyle name="Output 13 4" xfId="1278" xr:uid="{00000000-0005-0000-0000-000074080000}"/>
+    <cellStyle name="Output 13 5" xfId="1354" xr:uid="{00000000-0005-0000-0000-000075080000}"/>
+    <cellStyle name="Output 13 6" xfId="1430" xr:uid="{00000000-0005-0000-0000-000076080000}"/>
+    <cellStyle name="Output 13 7" xfId="1505" xr:uid="{00000000-0005-0000-0000-000077080000}"/>
+    <cellStyle name="Output 13 8" xfId="1581" xr:uid="{00000000-0005-0000-0000-000078080000}"/>
+    <cellStyle name="Output 13 9" xfId="1656" xr:uid="{00000000-0005-0000-0000-000079080000}"/>
+    <cellStyle name="Output 14" xfId="614" xr:uid="{00000000-0005-0000-0000-00007A080000}"/>
+    <cellStyle name="Output 14 10" xfId="1731" xr:uid="{00000000-0005-0000-0000-00007B080000}"/>
+    <cellStyle name="Output 14 11" xfId="1807" xr:uid="{00000000-0005-0000-0000-00007C080000}"/>
+    <cellStyle name="Output 14 12" xfId="1871" xr:uid="{00000000-0005-0000-0000-00007D080000}"/>
+    <cellStyle name="Output 14 13" xfId="1936" xr:uid="{00000000-0005-0000-0000-00007E080000}"/>
+    <cellStyle name="Output 14 14" xfId="1999" xr:uid="{00000000-0005-0000-0000-00007F080000}"/>
+    <cellStyle name="Output 14 15" xfId="2060" xr:uid="{00000000-0005-0000-0000-000080080000}"/>
+    <cellStyle name="Output 14 16" xfId="2122" xr:uid="{00000000-0005-0000-0000-000081080000}"/>
+    <cellStyle name="Output 14 17" xfId="2184" xr:uid="{00000000-0005-0000-0000-000082080000}"/>
+    <cellStyle name="Output 14 18" xfId="2247" xr:uid="{00000000-0005-0000-0000-000083080000}"/>
+    <cellStyle name="Output 14 19" xfId="2306" xr:uid="{00000000-0005-0000-0000-000084080000}"/>
+    <cellStyle name="Output 14 2" xfId="1127" xr:uid="{00000000-0005-0000-0000-000085080000}"/>
+    <cellStyle name="Output 14 20" xfId="2367" xr:uid="{00000000-0005-0000-0000-000086080000}"/>
+    <cellStyle name="Output 14 21" xfId="2428" xr:uid="{00000000-0005-0000-0000-000087080000}"/>
+    <cellStyle name="Output 14 22" xfId="2491" xr:uid="{00000000-0005-0000-0000-000088080000}"/>
+    <cellStyle name="Output 14 23" xfId="2548" xr:uid="{00000000-0005-0000-0000-000089080000}"/>
+    <cellStyle name="Output 14 24" xfId="2609" xr:uid="{00000000-0005-0000-0000-00008A080000}"/>
+    <cellStyle name="Output 14 25" xfId="2669" xr:uid="{00000000-0005-0000-0000-00008B080000}"/>
+    <cellStyle name="Output 14 26" xfId="2716" xr:uid="{00000000-0005-0000-0000-00008C080000}"/>
+    <cellStyle name="Output 14 27" xfId="2768" xr:uid="{00000000-0005-0000-0000-00008D080000}"/>
+    <cellStyle name="Output 14 28" xfId="2816" xr:uid="{00000000-0005-0000-0000-00008E080000}"/>
+    <cellStyle name="Output 14 29" xfId="2862" xr:uid="{00000000-0005-0000-0000-00008F080000}"/>
+    <cellStyle name="Output 14 3" xfId="1203" xr:uid="{00000000-0005-0000-0000-000090080000}"/>
+    <cellStyle name="Output 14 30" xfId="2908" xr:uid="{00000000-0005-0000-0000-000091080000}"/>
+    <cellStyle name="Output 14 31" xfId="2957" xr:uid="{00000000-0005-0000-0000-000092080000}"/>
+    <cellStyle name="Output 14 32" xfId="3003" xr:uid="{00000000-0005-0000-0000-000093080000}"/>
+    <cellStyle name="Output 14 4" xfId="1279" xr:uid="{00000000-0005-0000-0000-000094080000}"/>
+    <cellStyle name="Output 14 5" xfId="1355" xr:uid="{00000000-0005-0000-0000-000095080000}"/>
+    <cellStyle name="Output 14 6" xfId="1431" xr:uid="{00000000-0005-0000-0000-000096080000}"/>
+    <cellStyle name="Output 14 7" xfId="1506" xr:uid="{00000000-0005-0000-0000-000097080000}"/>
+    <cellStyle name="Output 14 8" xfId="1582" xr:uid="{00000000-0005-0000-0000-000098080000}"/>
+    <cellStyle name="Output 14 9" xfId="1657" xr:uid="{00000000-0005-0000-0000-000099080000}"/>
+    <cellStyle name="Output 15" xfId="615" xr:uid="{00000000-0005-0000-0000-00009A080000}"/>
+    <cellStyle name="Output 15 10" xfId="1732" xr:uid="{00000000-0005-0000-0000-00009B080000}"/>
+    <cellStyle name="Output 15 11" xfId="1808" xr:uid="{00000000-0005-0000-0000-00009C080000}"/>
+    <cellStyle name="Output 15 12" xfId="1872" xr:uid="{00000000-0005-0000-0000-00009D080000}"/>
+    <cellStyle name="Output 15 13" xfId="1937" xr:uid="{00000000-0005-0000-0000-00009E080000}"/>
+    <cellStyle name="Output 15 14" xfId="2000" xr:uid="{00000000-0005-0000-0000-00009F080000}"/>
+    <cellStyle name="Output 15 15" xfId="2061" xr:uid="{00000000-0005-0000-0000-0000A0080000}"/>
+    <cellStyle name="Output 15 16" xfId="2123" xr:uid="{00000000-0005-0000-0000-0000A1080000}"/>
+    <cellStyle name="Output 15 17" xfId="2185" xr:uid="{00000000-0005-0000-0000-0000A2080000}"/>
+    <cellStyle name="Output 15 18" xfId="2248" xr:uid="{00000000-0005-0000-0000-0000A3080000}"/>
+    <cellStyle name="Output 15 19" xfId="2307" xr:uid="{00000000-0005-0000-0000-0000A4080000}"/>
+    <cellStyle name="Output 15 2" xfId="1128" xr:uid="{00000000-0005-0000-0000-0000A5080000}"/>
+    <cellStyle name="Output 15 20" xfId="2368" xr:uid="{00000000-0005-0000-0000-0000A6080000}"/>
+    <cellStyle name="Output 15 21" xfId="2429" xr:uid="{00000000-0005-0000-0000-0000A7080000}"/>
+    <cellStyle name="Output 15 22" xfId="2492" xr:uid="{00000000-0005-0000-0000-0000A8080000}"/>
+    <cellStyle name="Output 15 23" xfId="2549" xr:uid="{00000000-0005-0000-0000-0000A9080000}"/>
+    <cellStyle name="Output 15 24" xfId="2610" xr:uid="{00000000-0005-0000-0000-0000AA080000}"/>
+    <cellStyle name="Output 15 25" xfId="2670" xr:uid="{00000000-0005-0000-0000-0000AB080000}"/>
+    <cellStyle name="Output 15 26" xfId="2717" xr:uid="{00000000-0005-0000-0000-0000AC080000}"/>
+    <cellStyle name="Output 15 27" xfId="2769" xr:uid="{00000000-0005-0000-0000-0000AD080000}"/>
+    <cellStyle name="Output 15 28" xfId="2817" xr:uid="{00000000-0005-0000-0000-0000AE080000}"/>
+    <cellStyle name="Output 15 29" xfId="2863" xr:uid="{00000000-0005-0000-0000-0000AF080000}"/>
+    <cellStyle name="Output 15 3" xfId="1204" xr:uid="{00000000-0005-0000-0000-0000B0080000}"/>
+    <cellStyle name="Output 15 30" xfId="2909" xr:uid="{00000000-0005-0000-0000-0000B1080000}"/>
+    <cellStyle name="Output 15 31" xfId="2958" xr:uid="{00000000-0005-0000-0000-0000B2080000}"/>
+    <cellStyle name="Output 15 32" xfId="3004" xr:uid="{00000000-0005-0000-0000-0000B3080000}"/>
+    <cellStyle name="Output 15 4" xfId="1280" xr:uid="{00000000-0005-0000-0000-0000B4080000}"/>
+    <cellStyle name="Output 15 5" xfId="1356" xr:uid="{00000000-0005-0000-0000-0000B5080000}"/>
+    <cellStyle name="Output 15 6" xfId="1432" xr:uid="{00000000-0005-0000-0000-0000B6080000}"/>
+    <cellStyle name="Output 15 7" xfId="1507" xr:uid="{00000000-0005-0000-0000-0000B7080000}"/>
+    <cellStyle name="Output 15 8" xfId="1583" xr:uid="{00000000-0005-0000-0000-0000B8080000}"/>
+    <cellStyle name="Output 15 9" xfId="1658" xr:uid="{00000000-0005-0000-0000-0000B9080000}"/>
+    <cellStyle name="Output 16" xfId="616" xr:uid="{00000000-0005-0000-0000-0000BA080000}"/>
+    <cellStyle name="Output 16 10" xfId="1733" xr:uid="{00000000-0005-0000-0000-0000BB080000}"/>
+    <cellStyle name="Output 16 11" xfId="1809" xr:uid="{00000000-0005-0000-0000-0000BC080000}"/>
+    <cellStyle name="Output 16 12" xfId="1873" xr:uid="{00000000-0005-0000-0000-0000BD080000}"/>
+    <cellStyle name="Output 16 13" xfId="1938" xr:uid="{00000000-0005-0000-0000-0000BE080000}"/>
+    <cellStyle name="Output 16 14" xfId="2001" xr:uid="{00000000-0005-0000-0000-0000BF080000}"/>
+    <cellStyle name="Output 16 15" xfId="2062" xr:uid="{00000000-0005-0000-0000-0000C0080000}"/>
+    <cellStyle name="Output 16 16" xfId="2124" xr:uid="{00000000-0005-0000-0000-0000C1080000}"/>
+    <cellStyle name="Output 16 17" xfId="2186" xr:uid="{00000000-0005-0000-0000-0000C2080000}"/>
+    <cellStyle name="Output 16 18" xfId="2249" xr:uid="{00000000-0005-0000-0000-0000C3080000}"/>
+    <cellStyle name="Output 16 19" xfId="2308" xr:uid="{00000000-0005-0000-0000-0000C4080000}"/>
+    <cellStyle name="Output 16 2" xfId="1129" xr:uid="{00000000-0005-0000-0000-0000C5080000}"/>
+    <cellStyle name="Output 16 20" xfId="2369" xr:uid="{00000000-0005-0000-0000-0000C6080000}"/>
+    <cellStyle name="Output 16 21" xfId="2430" xr:uid="{00000000-0005-0000-0000-0000C7080000}"/>
+    <cellStyle name="Output 16 22" xfId="2493" xr:uid="{00000000-0005-0000-0000-0000C8080000}"/>
+    <cellStyle name="Output 16 23" xfId="2550" xr:uid="{00000000-0005-0000-0000-0000C9080000}"/>
+    <cellStyle name="Output 16 24" xfId="2611" xr:uid="{00000000-0005-0000-0000-0000CA080000}"/>
+    <cellStyle name="Output 16 25" xfId="2671" xr:uid="{00000000-0005-0000-0000-0000CB080000}"/>
+    <cellStyle name="Output 16 26" xfId="2718" xr:uid="{00000000-0005-0000-0000-0000CC080000}"/>
+    <cellStyle name="Output 16 27" xfId="2770" xr:uid="{00000000-0005-0000-0000-0000CD080000}"/>
+    <cellStyle name="Output 16 28" xfId="2818" xr:uid="{00000000-0005-0000-0000-0000CE080000}"/>
+    <cellStyle name="Output 16 29" xfId="2864" xr:uid="{00000000-0005-0000-0000-0000CF080000}"/>
+    <cellStyle name="Output 16 3" xfId="1205" xr:uid="{00000000-0005-0000-0000-0000D0080000}"/>
+    <cellStyle name="Output 16 30" xfId="2910" xr:uid="{00000000-0005-0000-0000-0000D1080000}"/>
+    <cellStyle name="Output 16 31" xfId="2959" xr:uid="{00000000-0005-0000-0000-0000D2080000}"/>
+    <cellStyle name="Output 16 32" xfId="3005" xr:uid="{00000000-0005-0000-0000-0000D3080000}"/>
+    <cellStyle name="Output 16 4" xfId="1281" xr:uid="{00000000-0005-0000-0000-0000D4080000}"/>
+    <cellStyle name="Output 16 5" xfId="1357" xr:uid="{00000000-0005-0000-0000-0000D5080000}"/>
+    <cellStyle name="Output 16 6" xfId="1433" xr:uid="{00000000-0005-0000-0000-0000D6080000}"/>
+    <cellStyle name="Output 16 7" xfId="1508" xr:uid="{00000000-0005-0000-0000-0000D7080000}"/>
+    <cellStyle name="Output 16 8" xfId="1584" xr:uid="{00000000-0005-0000-0000-0000D8080000}"/>
+    <cellStyle name="Output 16 9" xfId="1659" xr:uid="{00000000-0005-0000-0000-0000D9080000}"/>
+    <cellStyle name="Output 2" xfId="617" xr:uid="{00000000-0005-0000-0000-0000DA080000}"/>
+    <cellStyle name="Output 2 10" xfId="1734" xr:uid="{00000000-0005-0000-0000-0000DB080000}"/>
+    <cellStyle name="Output 2 11" xfId="1810" xr:uid="{00000000-0005-0000-0000-0000DC080000}"/>
+    <cellStyle name="Output 2 12" xfId="1874" xr:uid="{00000000-0005-0000-0000-0000DD080000}"/>
+    <cellStyle name="Output 2 13" xfId="1939" xr:uid="{00000000-0005-0000-0000-0000DE080000}"/>
+    <cellStyle name="Output 2 14" xfId="2002" xr:uid="{00000000-0005-0000-0000-0000DF080000}"/>
+    <cellStyle name="Output 2 15" xfId="2063" xr:uid="{00000000-0005-0000-0000-0000E0080000}"/>
+    <cellStyle name="Output 2 16" xfId="2125" xr:uid="{00000000-0005-0000-0000-0000E1080000}"/>
+    <cellStyle name="Output 2 17" xfId="2187" xr:uid="{00000000-0005-0000-0000-0000E2080000}"/>
+    <cellStyle name="Output 2 18" xfId="2250" xr:uid="{00000000-0005-0000-0000-0000E3080000}"/>
+    <cellStyle name="Output 2 19" xfId="2309" xr:uid="{00000000-0005-0000-0000-0000E4080000}"/>
+    <cellStyle name="Output 2 2" xfId="1130" xr:uid="{00000000-0005-0000-0000-0000E5080000}"/>
+    <cellStyle name="Output 2 20" xfId="2370" xr:uid="{00000000-0005-0000-0000-0000E6080000}"/>
+    <cellStyle name="Output 2 21" xfId="2431" xr:uid="{00000000-0005-0000-0000-0000E7080000}"/>
+    <cellStyle name="Output 2 22" xfId="2494" xr:uid="{00000000-0005-0000-0000-0000E8080000}"/>
+    <cellStyle name="Output 2 23" xfId="2551" xr:uid="{00000000-0005-0000-0000-0000E9080000}"/>
+    <cellStyle name="Output 2 24" xfId="2612" xr:uid="{00000000-0005-0000-0000-0000EA080000}"/>
+    <cellStyle name="Output 2 25" xfId="2672" xr:uid="{00000000-0005-0000-0000-0000EB080000}"/>
+    <cellStyle name="Output 2 26" xfId="2719" xr:uid="{00000000-0005-0000-0000-0000EC080000}"/>
+    <cellStyle name="Output 2 27" xfId="2771" xr:uid="{00000000-0005-0000-0000-0000ED080000}"/>
+    <cellStyle name="Output 2 28" xfId="2819" xr:uid="{00000000-0005-0000-0000-0000EE080000}"/>
+    <cellStyle name="Output 2 29" xfId="2865" xr:uid="{00000000-0005-0000-0000-0000EF080000}"/>
+    <cellStyle name="Output 2 3" xfId="1206" xr:uid="{00000000-0005-0000-0000-0000F0080000}"/>
+    <cellStyle name="Output 2 30" xfId="2911" xr:uid="{00000000-0005-0000-0000-0000F1080000}"/>
+    <cellStyle name="Output 2 31" xfId="2960" xr:uid="{00000000-0005-0000-0000-0000F2080000}"/>
+    <cellStyle name="Output 2 32" xfId="3006" xr:uid="{00000000-0005-0000-0000-0000F3080000}"/>
+    <cellStyle name="Output 2 4" xfId="1282" xr:uid="{00000000-0005-0000-0000-0000F4080000}"/>
+    <cellStyle name="Output 2 5" xfId="1358" xr:uid="{00000000-0005-0000-0000-0000F5080000}"/>
+    <cellStyle name="Output 2 6" xfId="1434" xr:uid="{00000000-0005-0000-0000-0000F6080000}"/>
+    <cellStyle name="Output 2 7" xfId="1509" xr:uid="{00000000-0005-0000-0000-0000F7080000}"/>
+    <cellStyle name="Output 2 8" xfId="1585" xr:uid="{00000000-0005-0000-0000-0000F8080000}"/>
+    <cellStyle name="Output 2 9" xfId="1660" xr:uid="{00000000-0005-0000-0000-0000F9080000}"/>
+    <cellStyle name="Output 3" xfId="618" xr:uid="{00000000-0005-0000-0000-0000FA080000}"/>
+    <cellStyle name="Output 3 10" xfId="1735" xr:uid="{00000000-0005-0000-0000-0000FB080000}"/>
+    <cellStyle name="Output 3 11" xfId="1811" xr:uid="{00000000-0005-0000-0000-0000FC080000}"/>
+    <cellStyle name="Output 3 12" xfId="1875" xr:uid="{00000000-0005-0000-0000-0000FD080000}"/>
+    <cellStyle name="Output 3 13" xfId="1940" xr:uid="{00000000-0005-0000-0000-0000FE080000}"/>
+    <cellStyle name="Output 3 14" xfId="2003" xr:uid="{00000000-0005-0000-0000-0000FF080000}"/>
+    <cellStyle name="Output 3 15" xfId="2064" xr:uid="{00000000-0005-0000-0000-000000090000}"/>
+    <cellStyle name="Output 3 16" xfId="2126" xr:uid="{00000000-0005-0000-0000-000001090000}"/>
+    <cellStyle name="Output 3 17" xfId="2188" xr:uid="{00000000-0005-0000-0000-000002090000}"/>
+    <cellStyle name="Output 3 18" xfId="2251" xr:uid="{00000000-0005-0000-0000-000003090000}"/>
+    <cellStyle name="Output 3 19" xfId="2310" xr:uid="{00000000-0005-0000-0000-000004090000}"/>
+    <cellStyle name="Output 3 2" xfId="1131" xr:uid="{00000000-0005-0000-0000-000005090000}"/>
+    <cellStyle name="Output 3 20" xfId="2371" xr:uid="{00000000-0005-0000-0000-000006090000}"/>
+    <cellStyle name="Output 3 21" xfId="2432" xr:uid="{00000000-0005-0000-0000-000007090000}"/>
+    <cellStyle name="Output 3 22" xfId="2495" xr:uid="{00000000-0005-0000-0000-000008090000}"/>
+    <cellStyle name="Output 3 23" xfId="2552" xr:uid="{00000000-0005-0000-0000-000009090000}"/>
+    <cellStyle name="Output 3 24" xfId="2613" xr:uid="{00000000-0005-0000-0000-00000A090000}"/>
+    <cellStyle name="Output 3 25" xfId="2673" xr:uid="{00000000-0005-0000-0000-00000B090000}"/>
+    <cellStyle name="Output 3 26" xfId="2720" xr:uid="{00000000-0005-0000-0000-00000C090000}"/>
+    <cellStyle name="Output 3 27" xfId="2772" xr:uid="{00000000-0005-0000-0000-00000D090000}"/>
+    <cellStyle name="Output 3 28" xfId="2820" xr:uid="{00000000-0005-0000-0000-00000E090000}"/>
+    <cellStyle name="Output 3 29" xfId="2866" xr:uid="{00000000-0005-0000-0000-00000F090000}"/>
+    <cellStyle name="Output 3 3" xfId="1207" xr:uid="{00000000-0005-0000-0000-000010090000}"/>
+    <cellStyle name="Output 3 30" xfId="2912" xr:uid="{00000000-0005-0000-0000-000011090000}"/>
+    <cellStyle name="Output 3 31" xfId="2961" xr:uid="{00000000-0005-0000-0000-000012090000}"/>
+    <cellStyle name="Output 3 32" xfId="3007" xr:uid="{00000000-0005-0000-0000-000013090000}"/>
+    <cellStyle name="Output 3 4" xfId="1283" xr:uid="{00000000-0005-0000-0000-000014090000}"/>
+    <cellStyle name="Output 3 5" xfId="1359" xr:uid="{00000000-0005-0000-0000-000015090000}"/>
+    <cellStyle name="Output 3 6" xfId="1435" xr:uid="{00000000-0005-0000-0000-000016090000}"/>
+    <cellStyle name="Output 3 7" xfId="1510" xr:uid="{00000000-0005-0000-0000-000017090000}"/>
+    <cellStyle name="Output 3 8" xfId="1586" xr:uid="{00000000-0005-0000-0000-000018090000}"/>
+    <cellStyle name="Output 3 9" xfId="1661" xr:uid="{00000000-0005-0000-0000-000019090000}"/>
+    <cellStyle name="Output 4" xfId="619" xr:uid="{00000000-0005-0000-0000-00001A090000}"/>
+    <cellStyle name="Output 4 10" xfId="1736" xr:uid="{00000000-0005-0000-0000-00001B090000}"/>
+    <cellStyle name="Output 4 11" xfId="1812" xr:uid="{00000000-0005-0000-0000-00001C090000}"/>
+    <cellStyle name="Output 4 12" xfId="1876" xr:uid="{00000000-0005-0000-0000-00001D090000}"/>
+    <cellStyle name="Output 4 13" xfId="1941" xr:uid="{00000000-0005-0000-0000-00001E090000}"/>
+    <cellStyle name="Output 4 14" xfId="2004" xr:uid="{00000000-0005-0000-0000-00001F090000}"/>
+    <cellStyle name="Output 4 15" xfId="2065" xr:uid="{00000000-0005-0000-0000-000020090000}"/>
+    <cellStyle name="Output 4 16" xfId="2127" xr:uid="{00000000-0005-0000-0000-000021090000}"/>
+    <cellStyle name="Output 4 17" xfId="2189" xr:uid="{00000000-0005-0000-0000-000022090000}"/>
+    <cellStyle name="Output 4 18" xfId="2252" xr:uid="{00000000-0005-0000-0000-000023090000}"/>
+    <cellStyle name="Output 4 19" xfId="2311" xr:uid="{00000000-0005-0000-0000-000024090000}"/>
+    <cellStyle name="Output 4 2" xfId="1132" xr:uid="{00000000-0005-0000-0000-000025090000}"/>
+    <cellStyle name="Output 4 20" xfId="2372" xr:uid="{00000000-0005-0000-0000-000026090000}"/>
+    <cellStyle name="Output 4 21" xfId="2433" xr:uid="{00000000-0005-0000-0000-000027090000}"/>
+    <cellStyle name="Output 4 22" xfId="2496" xr:uid="{00000000-0005-0000-0000-000028090000}"/>
+    <cellStyle name="Output 4 23" xfId="2553" xr:uid="{00000000-0005-0000-0000-000029090000}"/>
+    <cellStyle name="Output 4 24" xfId="2614" xr:uid="{00000000-0005-0000-0000-00002A090000}"/>
+    <cellStyle name="Output 4 25" xfId="2674" xr:uid="{00000000-0005-0000-0000-00002B090000}"/>
+    <cellStyle name="Output 4 26" xfId="2721" xr:uid="{00000000-0005-0000-0000-00002C090000}"/>
+    <cellStyle name="Output 4 27" xfId="2773" xr:uid="{00000000-0005-0000-0000-00002D090000}"/>
+    <cellStyle name="Output 4 28" xfId="2821" xr:uid="{00000000-0005-0000-0000-00002E090000}"/>
+    <cellStyle name="Output 4 29" xfId="2867" xr:uid="{00000000-0005-0000-0000-00002F090000}"/>
+    <cellStyle name="Output 4 3" xfId="1208" xr:uid="{00000000-0005-0000-0000-000030090000}"/>
+    <cellStyle name="Output 4 30" xfId="2913" xr:uid="{00000000-0005-0000-0000-000031090000}"/>
+    <cellStyle name="Output 4 31" xfId="2962" xr:uid="{00000000-0005-0000-0000-000032090000}"/>
+    <cellStyle name="Output 4 32" xfId="3008" xr:uid="{00000000-0005-0000-0000-000033090000}"/>
+    <cellStyle name="Output 4 4" xfId="1284" xr:uid="{00000000-0005-0000-0000-000034090000}"/>
+    <cellStyle name="Output 4 5" xfId="1360" xr:uid="{00000000-0005-0000-0000-000035090000}"/>
+    <cellStyle name="Output 4 6" xfId="1436" xr:uid="{00000000-0005-0000-0000-000036090000}"/>
+    <cellStyle name="Output 4 7" xfId="1511" xr:uid="{00000000-0005-0000-0000-000037090000}"/>
+    <cellStyle name="Output 4 8" xfId="1587" xr:uid="{00000000-0005-0000-0000-000038090000}"/>
+    <cellStyle name="Output 4 9" xfId="1662" xr:uid="{00000000-0005-0000-0000-000039090000}"/>
+    <cellStyle name="Output 5" xfId="620" xr:uid="{00000000-0005-0000-0000-00003A090000}"/>
+    <cellStyle name="Output 5 10" xfId="1737" xr:uid="{00000000-0005-0000-0000-00003B090000}"/>
+    <cellStyle name="Output 5 11" xfId="1813" xr:uid="{00000000-0005-0000-0000-00003C090000}"/>
+    <cellStyle name="Output 5 12" xfId="1877" xr:uid="{00000000-0005-0000-0000-00003D090000}"/>
+    <cellStyle name="Output 5 13" xfId="1942" xr:uid="{00000000-0005-0000-0000-00003E090000}"/>
+    <cellStyle name="Output 5 14" xfId="2005" xr:uid="{00000000-0005-0000-0000-00003F090000}"/>
+    <cellStyle name="Output 5 15" xfId="2066" xr:uid="{00000000-0005-0000-0000-000040090000}"/>
+    <cellStyle name="Output 5 16" xfId="2128" xr:uid="{00000000-0005-0000-0000-000041090000}"/>
+    <cellStyle name="Output 5 17" xfId="2190" xr:uid="{00000000-0005-0000-0000-000042090000}"/>
+    <cellStyle name="Output 5 18" xfId="2253" xr:uid="{00000000-0005-0000-0000-000043090000}"/>
+    <cellStyle name="Output 5 19" xfId="2312" xr:uid="{00000000-0005-0000-0000-000044090000}"/>
+    <cellStyle name="Output 5 2" xfId="1133" xr:uid="{00000000-0005-0000-0000-000045090000}"/>
+    <cellStyle name="Output 5 20" xfId="2373" xr:uid="{00000000-0005-0000-0000-000046090000}"/>
+    <cellStyle name="Output 5 21" xfId="2434" xr:uid="{00000000-0005-0000-0000-000047090000}"/>
+    <cellStyle name="Output 5 22" xfId="2497" xr:uid="{00000000-0005-0000-0000-000048090000}"/>
+    <cellStyle name="Output 5 23" xfId="2554" xr:uid="{00000000-0005-0000-0000-000049090000}"/>
+    <cellStyle name="Output 5 24" xfId="2615" xr:uid="{00000000-0005-0000-0000-00004A090000}"/>
+    <cellStyle name="Output 5 25" xfId="2675" xr:uid="{00000000-0005-0000-0000-00004B090000}"/>
+    <cellStyle name="Output 5 26" xfId="2722" xr:uid="{00000000-0005-0000-0000-00004C090000}"/>
+    <cellStyle name="Output 5 27" xfId="2774" xr:uid="{00000000-0005-0000-0000-00004D090000}"/>
+    <cellStyle name="Output 5 28" xfId="2822" xr:uid="{00000000-0005-0000-0000-00004E090000}"/>
+    <cellStyle name="Output 5 29" xfId="2868" xr:uid="{00000000-0005-0000-0000-00004F090000}"/>
+    <cellStyle name="Output 5 3" xfId="1209" xr:uid="{00000000-0005-0000-0000-000050090000}"/>
+    <cellStyle name="Output 5 30" xfId="2914" xr:uid="{00000000-0005-0000-0000-000051090000}"/>
+    <cellStyle name="Output 5 31" xfId="2963" xr:uid="{00000000-0005-0000-0000-000052090000}"/>
+    <cellStyle name="Output 5 32" xfId="3009" xr:uid="{00000000-0005-0000-0000-000053090000}"/>
+    <cellStyle name="Output 5 4" xfId="1285" xr:uid="{00000000-0005-0000-0000-000054090000}"/>
+    <cellStyle name="Output 5 5" xfId="1361" xr:uid="{00000000-0005-0000-0000-000055090000}"/>
+    <cellStyle name="Output 5 6" xfId="1437" xr:uid="{00000000-0005-0000-0000-000056090000}"/>
+    <cellStyle name="Output 5 7" xfId="1512" xr:uid="{00000000-0005-0000-0000-000057090000}"/>
+    <cellStyle name="Output 5 8" xfId="1588" xr:uid="{00000000-0005-0000-0000-000058090000}"/>
+    <cellStyle name="Output 5 9" xfId="1663" xr:uid="{00000000-0005-0000-0000-000059090000}"/>
+    <cellStyle name="Output 6" xfId="621" xr:uid="{00000000-0005-0000-0000-00005A090000}"/>
+    <cellStyle name="Output 6 10" xfId="1738" xr:uid="{00000000-0005-0000-0000-00005B090000}"/>
+    <cellStyle name="Output 6 11" xfId="1814" xr:uid="{00000000-0005-0000-0000-00005C090000}"/>
+    <cellStyle name="Output 6 12" xfId="1878" xr:uid="{00000000-0005-0000-0000-00005D090000}"/>
+    <cellStyle name="Output 6 13" xfId="1943" xr:uid="{00000000-0005-0000-0000-00005E090000}"/>
+    <cellStyle name="Output 6 14" xfId="2006" xr:uid="{00000000-0005-0000-0000-00005F090000}"/>
+    <cellStyle name="Output 6 15" xfId="2067" xr:uid="{00000000-0005-0000-0000-000060090000}"/>
+    <cellStyle name="Output 6 16" xfId="2129" xr:uid="{00000000-0005-0000-0000-000061090000}"/>
+    <cellStyle name="Output 6 17" xfId="2191" xr:uid="{00000000-0005-0000-0000-000062090000}"/>
+    <cellStyle name="Output 6 18" xfId="2254" xr:uid="{00000000-0005-0000-0000-000063090000}"/>
+    <cellStyle name="Output 6 19" xfId="2313" xr:uid="{00000000-0005-0000-0000-000064090000}"/>
+    <cellStyle name="Output 6 2" xfId="1134" xr:uid="{00000000-0005-0000-0000-000065090000}"/>
+    <cellStyle name="Output 6 20" xfId="2374" xr:uid="{00000000-0005-0000-0000-000066090000}"/>
+    <cellStyle name="Output 6 21" xfId="2435" xr:uid="{00000000-0005-0000-0000-000067090000}"/>
+    <cellStyle name="Output 6 22" xfId="2498" xr:uid="{00000000-0005-0000-0000-000068090000}"/>
+    <cellStyle name="Output 6 23" xfId="2555" xr:uid="{00000000-0005-0000-0000-000069090000}"/>
+    <cellStyle name="Output 6 24" xfId="2616" xr:uid="{00000000-0005-0000-0000-00006A090000}"/>
+    <cellStyle name="Output 6 25" xfId="2676" xr:uid="{00000000-0005-0000-0000-00006B090000}"/>
+    <cellStyle name="Output 6 26" xfId="2723" xr:uid="{00000000-0005-0000-0000-00006C090000}"/>
+    <cellStyle name="Output 6 27" xfId="2775" xr:uid="{00000000-0005-0000-0000-00006D090000}"/>
+    <cellStyle name="Output 6 28" xfId="2823" xr:uid="{00000000-0005-0000-0000-00006E090000}"/>
+    <cellStyle name="Output 6 29" xfId="2869" xr:uid="{00000000-0005-0000-0000-00006F090000}"/>
+    <cellStyle name="Output 6 3" xfId="1210" xr:uid="{00000000-0005-0000-0000-000070090000}"/>
+    <cellStyle name="Output 6 30" xfId="2915" xr:uid="{00000000-0005-0000-0000-000071090000}"/>
+    <cellStyle name="Output 6 31" xfId="2964" xr:uid="{00000000-0005-0000-0000-000072090000}"/>
+    <cellStyle name="Output 6 32" xfId="3010" xr:uid="{00000000-0005-0000-0000-000073090000}"/>
+    <cellStyle name="Output 6 4" xfId="1286" xr:uid="{00000000-0005-0000-0000-000074090000}"/>
+    <cellStyle name="Output 6 5" xfId="1362" xr:uid="{00000000-0005-0000-0000-000075090000}"/>
+    <cellStyle name="Output 6 6" xfId="1438" xr:uid="{00000000-0005-0000-0000-000076090000}"/>
+    <cellStyle name="Output 6 7" xfId="1513" xr:uid="{00000000-0005-0000-0000-000077090000}"/>
+    <cellStyle name="Output 6 8" xfId="1589" xr:uid="{00000000-0005-0000-0000-000078090000}"/>
+    <cellStyle name="Output 6 9" xfId="1664" xr:uid="{00000000-0005-0000-0000-000079090000}"/>
+    <cellStyle name="Output 7" xfId="622" xr:uid="{00000000-0005-0000-0000-00007A090000}"/>
+    <cellStyle name="Output 7 10" xfId="1739" xr:uid="{00000000-0005-0000-0000-00007B090000}"/>
+    <cellStyle name="Output 7 11" xfId="1815" xr:uid="{00000000-0005-0000-0000-00007C090000}"/>
+    <cellStyle name="Output 7 12" xfId="1879" xr:uid="{00000000-0005-0000-0000-00007D090000}"/>
+    <cellStyle name="Output 7 13" xfId="1944" xr:uid="{00000000-0005-0000-0000-00007E090000}"/>
+    <cellStyle name="Output 7 14" xfId="2007" xr:uid="{00000000-0005-0000-0000-00007F090000}"/>
+    <cellStyle name="Output 7 15" xfId="2068" xr:uid="{00000000-0005-0000-0000-000080090000}"/>
+    <cellStyle name="Output 7 16" xfId="2130" xr:uid="{00000000-0005-0000-0000-000081090000}"/>
+    <cellStyle name="Output 7 17" xfId="2192" xr:uid="{00000000-0005-0000-0000-000082090000}"/>
+    <cellStyle name="Output 7 18" xfId="2255" xr:uid="{00000000-0005-0000-0000-000083090000}"/>
+    <cellStyle name="Output 7 19" xfId="2314" xr:uid="{00000000-0005-0000-0000-000084090000}"/>
+    <cellStyle name="Output 7 2" xfId="1135" xr:uid="{00000000-0005-0000-0000-000085090000}"/>
+    <cellStyle name="Output 7 20" xfId="2375" xr:uid="{00000000-0005-0000-0000-000086090000}"/>
+    <cellStyle name="Output 7 21" xfId="2436" xr:uid="{00000000-0005-0000-0000-000087090000}"/>
+    <cellStyle name="Output 7 22" xfId="2499" xr:uid="{00000000-0005-0000-0000-000088090000}"/>
+    <cellStyle name="Output 7 23" xfId="2556" xr:uid="{00000000-0005-0000-0000-000089090000}"/>
+    <cellStyle name="Output 7 24" xfId="2617" xr:uid="{00000000-0005-0000-0000-00008A090000}"/>
+    <cellStyle name="Output 7 25" xfId="2677" xr:uid="{00000000-0005-0000-0000-00008B090000}"/>
+    <cellStyle name="Output 7 26" xfId="2724" xr:uid="{00000000-0005-0000-0000-00008C090000}"/>
+    <cellStyle name="Output 7 27" xfId="2776" xr:uid="{00000000-0005-0000-0000-00008D090000}"/>
+    <cellStyle name="Output 7 28" xfId="2824" xr:uid="{00000000-0005-0000-0000-00008E090000}"/>
+    <cellStyle name="Output 7 29" xfId="2870" xr:uid="{00000000-0005-0000-0000-00008F090000}"/>
+    <cellStyle name="Output 7 3" xfId="1211" xr:uid="{00000000-0005-0000-0000-000090090000}"/>
+    <cellStyle name="Output 7 30" xfId="2916" xr:uid="{00000000-0005-0000-0000-000091090000}"/>
+    <cellStyle name="Output 7 31" xfId="2965" xr:uid="{00000000-0005-0000-0000-000092090000}"/>
+    <cellStyle name="Output 7 32" xfId="3011" xr:uid="{00000000-0005-0000-0000-000093090000}"/>
+    <cellStyle name="Output 7 4" xfId="1287" xr:uid="{00000000-0005-0000-0000-000094090000}"/>
+    <cellStyle name="Output 7 5" xfId="1363" xr:uid="{00000000-0005-0000-0000-000095090000}"/>
+    <cellStyle name="Output 7 6" xfId="1439" xr:uid="{00000000-0005-0000-0000-000096090000}"/>
+    <cellStyle name="Output 7 7" xfId="1514" xr:uid="{00000000-0005-0000-0000-000097090000}"/>
+    <cellStyle name="Output 7 8" xfId="1590" xr:uid="{00000000-0005-0000-0000-000098090000}"/>
+    <cellStyle name="Output 7 9" xfId="1665" xr:uid="{00000000-0005-0000-0000-000099090000}"/>
+    <cellStyle name="Output 8" xfId="623" xr:uid="{00000000-0005-0000-0000-00009A090000}"/>
+    <cellStyle name="Output 8 10" xfId="1740" xr:uid="{00000000-0005-0000-0000-00009B090000}"/>
+    <cellStyle name="Output 8 11" xfId="1816" xr:uid="{00000000-0005-0000-0000-00009C090000}"/>
+    <cellStyle name="Output 8 12" xfId="1880" xr:uid="{00000000-0005-0000-0000-00009D090000}"/>
+    <cellStyle name="Output 8 13" xfId="1945" xr:uid="{00000000-0005-0000-0000-00009E090000}"/>
+    <cellStyle name="Output 8 14" xfId="2008" xr:uid="{00000000-0005-0000-0000-00009F090000}"/>
+    <cellStyle name="Output 8 15" xfId="2069" xr:uid="{00000000-0005-0000-0000-0000A0090000}"/>
+    <cellStyle name="Output 8 16" xfId="2131" xr:uid="{00000000-0005-0000-0000-0000A1090000}"/>
+    <cellStyle name="Output 8 17" xfId="2193" xr:uid="{00000000-0005-0000-0000-0000A2090000}"/>
+    <cellStyle name="Output 8 18" xfId="2256" xr:uid="{00000000-0005-0000-0000-0000A3090000}"/>
+    <cellStyle name="Output 8 19" xfId="2315" xr:uid="{00000000-0005-0000-0000-0000A4090000}"/>
+    <cellStyle name="Output 8 2" xfId="1136" xr:uid="{00000000-0005-0000-0000-0000A5090000}"/>
+    <cellStyle name="Output 8 20" xfId="2376" xr:uid="{00000000-0005-0000-0000-0000A6090000}"/>
+    <cellStyle name="Output 8 21" xfId="2437" xr:uid="{00000000-0005-0000-0000-0000A7090000}"/>
+    <cellStyle name="Output 8 22" xfId="2500" xr:uid="{00000000-0005-0000-0000-0000A8090000}"/>
+    <cellStyle name="Output 8 23" xfId="2557" xr:uid="{00000000-0005-0000-0000-0000A9090000}"/>
+    <cellStyle name="Output 8 24" xfId="2618" xr:uid="{00000000-0005-0000-0000-0000AA090000}"/>
+    <cellStyle name="Output 8 25" xfId="2678" xr:uid="{00000000-0005-0000-0000-0000AB090000}"/>
+    <cellStyle name="Output 8 26" xfId="2725" xr:uid="{00000000-0005-0000-0000-0000AC090000}"/>
+    <cellStyle name="Output 8 27" xfId="2777" xr:uid="{00000000-0005-0000-0000-0000AD090000}"/>
+    <cellStyle name="Output 8 28" xfId="2825" xr:uid="{00000000-0005-0000-0000-0000AE090000}"/>
+    <cellStyle name="Output 8 29" xfId="2871" xr:uid="{00000000-0005-0000-0000-0000AF090000}"/>
+    <cellStyle name="Output 8 3" xfId="1212" xr:uid="{00000000-0005-0000-0000-0000B0090000}"/>
+    <cellStyle name="Output 8 30" xfId="2917" xr:uid="{00000000-0005-0000-0000-0000B1090000}"/>
+    <cellStyle name="Output 8 31" xfId="2966" xr:uid="{00000000-0005-0000-0000-0000B2090000}"/>
+    <cellStyle name="Output 8 32" xfId="3012" xr:uid="{00000000-0005-0000-0000-0000B3090000}"/>
+    <cellStyle name="Output 8 4" xfId="1288" xr:uid="{00000000-0005-0000-0000-0000B4090000}"/>
+    <cellStyle name="Output 8 5" xfId="1364" xr:uid="{00000000-0005-0000-0000-0000B5090000}"/>
+    <cellStyle name="Output 8 6" xfId="1440" xr:uid="{00000000-0005-0000-0000-0000B6090000}"/>
+    <cellStyle name="Output 8 7" xfId="1515" xr:uid="{00000000-0005-0000-0000-0000B7090000}"/>
+    <cellStyle name="Output 8 8" xfId="1591" xr:uid="{00000000-0005-0000-0000-0000B8090000}"/>
+    <cellStyle name="Output 8 9" xfId="1666" xr:uid="{00000000-0005-0000-0000-0000B9090000}"/>
+    <cellStyle name="Output 9" xfId="624" xr:uid="{00000000-0005-0000-0000-0000BA090000}"/>
+    <cellStyle name="Output 9 10" xfId="1741" xr:uid="{00000000-0005-0000-0000-0000BB090000}"/>
+    <cellStyle name="Output 9 11" xfId="1817" xr:uid="{00000000-0005-0000-0000-0000BC090000}"/>
+    <cellStyle name="Output 9 12" xfId="1881" xr:uid="{00000000-0005-0000-0000-0000BD090000}"/>
+    <cellStyle name="Output 9 13" xfId="1946" xr:uid="{00000000-0005-0000-0000-0000BE090000}"/>
+    <cellStyle name="Output 9 14" xfId="2009" xr:uid="{00000000-0005-0000-0000-0000BF090000}"/>
+    <cellStyle name="Output 9 15" xfId="2070" xr:uid="{00000000-0005-0000-0000-0000C0090000}"/>
+    <cellStyle name="Output 9 16" xfId="2132" xr:uid="{00000000-0005-0000-0000-0000C1090000}"/>
+    <cellStyle name="Output 9 17" xfId="2194" xr:uid="{00000000-0005-0000-0000-0000C2090000}"/>
+    <cellStyle name="Output 9 18" xfId="2257" xr:uid="{00000000-0005-0000-0000-0000C3090000}"/>
+    <cellStyle name="Output 9 19" xfId="2316" xr:uid="{00000000-0005-0000-0000-0000C4090000}"/>
+    <cellStyle name="Output 9 2" xfId="1137" xr:uid="{00000000-0005-0000-0000-0000C5090000}"/>
+    <cellStyle name="Output 9 20" xfId="2377" xr:uid="{00000000-0005-0000-0000-0000C6090000}"/>
+    <cellStyle name="Output 9 21" xfId="2438" xr:uid="{00000000-0005-0000-0000-0000C7090000}"/>
+    <cellStyle name="Output 9 22" xfId="2501" xr:uid="{00000000-0005-0000-0000-0000C8090000}"/>
+    <cellStyle name="Output 9 23" xfId="2558" xr:uid="{00000000-0005-0000-0000-0000C9090000}"/>
+    <cellStyle name="Output 9 24" xfId="2619" xr:uid="{00000000-0005-0000-0000-0000CA090000}"/>
+    <cellStyle name="Output 9 25" xfId="2679" xr:uid="{00000000-0005-0000-0000-0000CB090000}"/>
+    <cellStyle name="Output 9 26" xfId="2726" xr:uid="{00000000-0005-0000-0000-0000CC090000}"/>
+    <cellStyle name="Output 9 27" xfId="2778" xr:uid="{00000000-0005-0000-0000-0000CD090000}"/>
+    <cellStyle name="Output 9 28" xfId="2826" xr:uid="{00000000-0005-0000-0000-0000CE090000}"/>
+    <cellStyle name="Output 9 29" xfId="2872" xr:uid="{00000000-0005-0000-0000-0000CF090000}"/>
+    <cellStyle name="Output 9 3" xfId="1213" xr:uid="{00000000-0005-0000-0000-0000D0090000}"/>
+    <cellStyle name="Output 9 30" xfId="2918" xr:uid="{00000000-0005-0000-0000-0000D1090000}"/>
+    <cellStyle name="Output 9 31" xfId="2967" xr:uid="{00000000-0005-0000-0000-0000D2090000}"/>
+    <cellStyle name="Output 9 32" xfId="3013" xr:uid="{00000000-0005-0000-0000-0000D3090000}"/>
+    <cellStyle name="Output 9 4" xfId="1289" xr:uid="{00000000-0005-0000-0000-0000D4090000}"/>
+    <cellStyle name="Output 9 5" xfId="1365" xr:uid="{00000000-0005-0000-0000-0000D5090000}"/>
+    <cellStyle name="Output 9 6" xfId="1441" xr:uid="{00000000-0005-0000-0000-0000D6090000}"/>
+    <cellStyle name="Output 9 7" xfId="1516" xr:uid="{00000000-0005-0000-0000-0000D7090000}"/>
+    <cellStyle name="Output 9 8" xfId="1592" xr:uid="{00000000-0005-0000-0000-0000D8090000}"/>
+    <cellStyle name="Output 9 9" xfId="1667" xr:uid="{00000000-0005-0000-0000-0000D9090000}"/>
+    <cellStyle name="Percent 2" xfId="3032" xr:uid="{00000000-0005-0000-0000-0000DA090000}"/>
+    <cellStyle name="Title 10" xfId="625" xr:uid="{00000000-0005-0000-0000-0000DB090000}"/>
+    <cellStyle name="Title 11" xfId="626" xr:uid="{00000000-0005-0000-0000-0000DC090000}"/>
+    <cellStyle name="Title 12" xfId="627" xr:uid="{00000000-0005-0000-0000-0000DD090000}"/>
+    <cellStyle name="Title 13" xfId="628" xr:uid="{00000000-0005-0000-0000-0000DE090000}"/>
+    <cellStyle name="Title 14" xfId="629" xr:uid="{00000000-0005-0000-0000-0000DF090000}"/>
+    <cellStyle name="Title 15" xfId="630" xr:uid="{00000000-0005-0000-0000-0000E0090000}"/>
+    <cellStyle name="Title 16" xfId="631" xr:uid="{00000000-0005-0000-0000-0000E1090000}"/>
+    <cellStyle name="Title 2" xfId="632" xr:uid="{00000000-0005-0000-0000-0000E2090000}"/>
+    <cellStyle name="Title 3" xfId="633" xr:uid="{00000000-0005-0000-0000-0000E3090000}"/>
+    <cellStyle name="Title 4" xfId="634" xr:uid="{00000000-0005-0000-0000-0000E4090000}"/>
+    <cellStyle name="Title 5" xfId="635" xr:uid="{00000000-0005-0000-0000-0000E5090000}"/>
+    <cellStyle name="Title 6" xfId="636" xr:uid="{00000000-0005-0000-0000-0000E6090000}"/>
+    <cellStyle name="Title 7" xfId="637" xr:uid="{00000000-0005-0000-0000-0000E7090000}"/>
+    <cellStyle name="Title 8" xfId="638" xr:uid="{00000000-0005-0000-0000-0000E8090000}"/>
+    <cellStyle name="Title 9" xfId="639" xr:uid="{00000000-0005-0000-0000-0000E9090000}"/>
+    <cellStyle name="Total 10" xfId="640" xr:uid="{00000000-0005-0000-0000-0000EA090000}"/>
+    <cellStyle name="Total 10 10" xfId="1757" xr:uid="{00000000-0005-0000-0000-0000EB090000}"/>
+    <cellStyle name="Total 10 11" xfId="1822" xr:uid="{00000000-0005-0000-0000-0000EC090000}"/>
+    <cellStyle name="Total 10 12" xfId="1888" xr:uid="{00000000-0005-0000-0000-0000ED090000}"/>
+    <cellStyle name="Total 10 13" xfId="1952" xr:uid="{00000000-0005-0000-0000-0000EE090000}"/>
+    <cellStyle name="Total 10 14" xfId="2014" xr:uid="{00000000-0005-0000-0000-0000EF090000}"/>
+    <cellStyle name="Total 10 15" xfId="2075" xr:uid="{00000000-0005-0000-0000-0000F0090000}"/>
+    <cellStyle name="Total 10 16" xfId="2139" xr:uid="{00000000-0005-0000-0000-0000F1090000}"/>
+    <cellStyle name="Total 10 17" xfId="2200" xr:uid="{00000000-0005-0000-0000-0000F2090000}"/>
+    <cellStyle name="Total 10 18" xfId="2261" xr:uid="{00000000-0005-0000-0000-0000F3090000}"/>
+    <cellStyle name="Total 10 19" xfId="2321" xr:uid="{00000000-0005-0000-0000-0000F4090000}"/>
+    <cellStyle name="Total 10 2" xfId="1153" xr:uid="{00000000-0005-0000-0000-0000F5090000}"/>
+    <cellStyle name="Total 10 20" xfId="2382" xr:uid="{00000000-0005-0000-0000-0000F6090000}"/>
+    <cellStyle name="Total 10 21" xfId="2444" xr:uid="{00000000-0005-0000-0000-0000F7090000}"/>
+    <cellStyle name="Total 10 22" xfId="2503" xr:uid="{00000000-0005-0000-0000-0000F8090000}"/>
+    <cellStyle name="Total 10 23" xfId="2566" xr:uid="{00000000-0005-0000-0000-0000F9090000}"/>
+    <cellStyle name="Total 10 24" xfId="2625" xr:uid="{00000000-0005-0000-0000-0000FA090000}"/>
+    <cellStyle name="Total 10 25" xfId="2680" xr:uid="{00000000-0005-0000-0000-0000FB090000}"/>
+    <cellStyle name="Total 10 26" xfId="2732" xr:uid="{00000000-0005-0000-0000-0000FC090000}"/>
+    <cellStyle name="Total 10 27" xfId="2779" xr:uid="{00000000-0005-0000-0000-0000FD090000}"/>
+    <cellStyle name="Total 10 28" xfId="2827" xr:uid="{00000000-0005-0000-0000-0000FE090000}"/>
+    <cellStyle name="Total 10 29" xfId="2873" xr:uid="{00000000-0005-0000-0000-0000FF090000}"/>
+    <cellStyle name="Total 10 3" xfId="1229" xr:uid="{00000000-0005-0000-0000-0000000A0000}"/>
+    <cellStyle name="Total 10 30" xfId="2919" xr:uid="{00000000-0005-0000-0000-0000010A0000}"/>
+    <cellStyle name="Total 10 31" xfId="2968" xr:uid="{00000000-0005-0000-0000-0000020A0000}"/>
+    <cellStyle name="Total 10 32" xfId="3014" xr:uid="{00000000-0005-0000-0000-0000030A0000}"/>
+    <cellStyle name="Total 10 4" xfId="1305" xr:uid="{00000000-0005-0000-0000-0000040A0000}"/>
+    <cellStyle name="Total 10 5" xfId="1381" xr:uid="{00000000-0005-0000-0000-0000050A0000}"/>
+    <cellStyle name="Total 10 6" xfId="1456" xr:uid="{00000000-0005-0000-0000-0000060A0000}"/>
+    <cellStyle name="Total 10 7" xfId="1532" xr:uid="{00000000-0005-0000-0000-0000070A0000}"/>
+    <cellStyle name="Total 10 8" xfId="1607" xr:uid="{00000000-0005-0000-0000-0000080A0000}"/>
+    <cellStyle name="Total 10 9" xfId="1681" xr:uid="{00000000-0005-0000-0000-0000090A0000}"/>
+    <cellStyle name="Total 11" xfId="641" xr:uid="{00000000-0005-0000-0000-00000A0A0000}"/>
+    <cellStyle name="Total 11 10" xfId="1758" xr:uid="{00000000-0005-0000-0000-00000B0A0000}"/>
+    <cellStyle name="Total 11 11" xfId="1823" xr:uid="{00000000-0005-0000-0000-00000C0A0000}"/>
+    <cellStyle name="Total 11 12" xfId="1889" xr:uid="{00000000-0005-0000-0000-00000D0A0000}"/>
+    <cellStyle name="Total 11 13" xfId="1953" xr:uid="{00000000-0005-0000-0000-00000E0A0000}"/>
+    <cellStyle name="Total 11 14" xfId="2015" xr:uid="{00000000-0005-0000-0000-00000F0A0000}"/>
+    <cellStyle name="Total 11 15" xfId="2076" xr:uid="{00000000-0005-0000-0000-0000100A0000}"/>
+    <cellStyle name="Total 11 16" xfId="2140" xr:uid="{00000000-0005-0000-0000-0000110A0000}"/>
+    <cellStyle name="Total 11 17" xfId="2201" xr:uid="{00000000-0005-0000-0000-0000120A0000}"/>
+    <cellStyle name="Total 11 18" xfId="2262" xr:uid="{00000000-0005-0000-0000-0000130A0000}"/>
+    <cellStyle name="Total 11 19" xfId="2322" xr:uid="{00000000-0005-0000-0000-0000140A0000}"/>
+    <cellStyle name="Total 11 2" xfId="1154" xr:uid="{00000000-0005-0000-0000-0000150A0000}"/>
+    <cellStyle name="Total 11 20" xfId="2383" xr:uid="{00000000-0005-0000-0000-0000160A0000}"/>
+    <cellStyle name="Total 11 21" xfId="2445" xr:uid="{00000000-0005-0000-0000-0000170A0000}"/>
+    <cellStyle name="Total 11 22" xfId="2504" xr:uid="{00000000-0005-0000-0000-0000180A0000}"/>
+    <cellStyle name="Total 11 23" xfId="2567" xr:uid="{00000000-0005-0000-0000-0000190A0000}"/>
+    <cellStyle name="Total 11 24" xfId="2626" xr:uid="{00000000-0005-0000-0000-00001A0A0000}"/>
+    <cellStyle name="Total 11 25" xfId="2681" xr:uid="{00000000-0005-0000-0000-00001B0A0000}"/>
+    <cellStyle name="Total 11 26" xfId="2733" xr:uid="{00000000-0005-0000-0000-00001C0A0000}"/>
+    <cellStyle name="Total 11 27" xfId="2780" xr:uid="{00000000-0005-0000-0000-00001D0A0000}"/>
+    <cellStyle name="Total 11 28" xfId="2828" xr:uid="{00000000-0005-0000-0000-00001E0A0000}"/>
+    <cellStyle name="Total 11 29" xfId="2874" xr:uid="{00000000-0005-0000-0000-00001F0A0000}"/>
+    <cellStyle name="Total 11 3" xfId="1230" xr:uid="{00000000-0005-0000-0000-0000200A0000}"/>
+    <cellStyle name="Total 11 30" xfId="2920" xr:uid="{00000000-0005-0000-0000-0000210A0000}"/>
+    <cellStyle name="Total 11 31" xfId="2969" xr:uid="{00000000-0005-0000-0000-0000220A0000}"/>
+    <cellStyle name="Total 11 32" xfId="3015" xr:uid="{00000000-0005-0000-0000-0000230A0000}"/>
+    <cellStyle name="Total 11 4" xfId="1306" xr:uid="{00000000-0005-0000-0000-0000240A0000}"/>
+    <cellStyle name="Total 11 5" xfId="1382" xr:uid="{00000000-0005-0000-0000-0000250A0000}"/>
+    <cellStyle name="Total 11 6" xfId="1457" xr:uid="{00000000-0005-0000-0000-0000260A0000}"/>
+    <cellStyle name="Total 11 7" xfId="1533" xr:uid="{00000000-0005-0000-0000-0000270A0000}"/>
+    <cellStyle name="Total 11 8" xfId="1608" xr:uid="{00000000-0005-0000-0000-0000280A0000}"/>
+    <cellStyle name="Total 11 9" xfId="1682" xr:uid="{00000000-0005-0000-0000-0000290A0000}"/>
+    <cellStyle name="Total 12" xfId="642" xr:uid="{00000000-0005-0000-0000-00002A0A0000}"/>
+    <cellStyle name="Total 12 10" xfId="1759" xr:uid="{00000000-0005-0000-0000-00002B0A0000}"/>
+    <cellStyle name="Total 12 11" xfId="1824" xr:uid="{00000000-0005-0000-0000-00002C0A0000}"/>
+    <cellStyle name="Total 12 12" xfId="1890" xr:uid="{00000000-0005-0000-0000-00002D0A0000}"/>
+    <cellStyle name="Total 12 13" xfId="1954" xr:uid="{00000000-0005-0000-0000-00002E0A0000}"/>
+    <cellStyle name="Total 12 14" xfId="2016" xr:uid="{00000000-0005-0000-0000-00002F0A0000}"/>
+    <cellStyle name="Total 12 15" xfId="2077" xr:uid="{00000000-0005-0000-0000-0000300A0000}"/>
+    <cellStyle name="Total 12 16" xfId="2141" xr:uid="{00000000-0005-0000-0000-0000310A0000}"/>
+    <cellStyle name="Total 12 17" xfId="2202" xr:uid="{00000000-0005-0000-0000-0000320A0000}"/>
+    <cellStyle name="Total 12 18" xfId="2263" xr:uid="{00000000-0005-0000-0000-0000330A0000}"/>
+    <cellStyle name="Total 12 19" xfId="2323" xr:uid="{00000000-0005-0000-0000-0000340A0000}"/>
+    <cellStyle name="Total 12 2" xfId="1155" xr:uid="{00000000-0005-0000-0000-0000350A0000}"/>
+    <cellStyle name="Total 12 20" xfId="2384" xr:uid="{00000000-0005-0000-0000-0000360A0000}"/>
+    <cellStyle name="Total 12 21" xfId="2446" xr:uid="{00000000-0005-0000-0000-0000370A0000}"/>
+    <cellStyle name="Total 12 22" xfId="2505" xr:uid="{00000000-0005-0000-0000-0000380A0000}"/>
+    <cellStyle name="Total 12 23" xfId="2568" xr:uid="{00000000-0005-0000-0000-0000390A0000}"/>
+    <cellStyle name="Total 12 24" xfId="2627" xr:uid="{00000000-0005-0000-0000-00003A0A0000}"/>
+    <cellStyle name="Total 12 25" xfId="2682" xr:uid="{00000000-0005-0000-0000-00003B0A0000}"/>
+    <cellStyle name="Total 12 26" xfId="2734" xr:uid="{00000000-0005-0000-0000-00003C0A0000}"/>
+    <cellStyle name="Total 12 27" xfId="2781" xr:uid="{00000000-0005-0000-0000-00003D0A0000}"/>
+    <cellStyle name="Total 12 28" xfId="2829" xr:uid="{00000000-0005-0000-0000-00003E0A0000}"/>
+    <cellStyle name="Total 12 29" xfId="2875" xr:uid="{00000000-0005-0000-0000-00003F0A0000}"/>
+    <cellStyle name="Total 12 3" xfId="1231" xr:uid="{00000000-0005-0000-0000-0000400A0000}"/>
+    <cellStyle name="Total 12 30" xfId="2921" xr:uid="{00000000-0005-0000-0000-0000410A0000}"/>
+    <cellStyle name="Total 12 31" xfId="2970" xr:uid="{00000000-0005-0000-0000-0000420A0000}"/>
+    <cellStyle name="Total 12 32" xfId="3016" xr:uid="{00000000-0005-0000-0000-0000430A0000}"/>
+    <cellStyle name="Total 12 4" xfId="1307" xr:uid="{00000000-0005-0000-0000-0000440A0000}"/>
+    <cellStyle name="Total 12 5" xfId="1383" xr:uid="{00000000-0005-0000-0000-0000450A0000}"/>
+    <cellStyle name="Total 12 6" xfId="1458" xr:uid="{00000000-0005-0000-0000-0000460A0000}"/>
+    <cellStyle name="Total 12 7" xfId="1534" xr:uid="{00000000-0005-0000-0000-0000470A0000}"/>
+    <cellStyle name="Total 12 8" xfId="1609" xr:uid="{00000000-0005-0000-0000-0000480A0000}"/>
+    <cellStyle name="Total 12 9" xfId="1683" xr:uid="{00000000-0005-0000-0000-0000490A0000}"/>
+    <cellStyle name="Total 13" xfId="643" xr:uid="{00000000-0005-0000-0000-00004A0A0000}"/>
+    <cellStyle name="Total 13 10" xfId="1760" xr:uid="{00000000-0005-0000-0000-00004B0A0000}"/>
+    <cellStyle name="Total 13 11" xfId="1825" xr:uid="{00000000-0005-0000-0000-00004C0A0000}"/>
+    <cellStyle name="Total 13 12" xfId="1891" xr:uid="{00000000-0005-0000-0000-00004D0A0000}"/>
+    <cellStyle name="Total 13 13" xfId="1955" xr:uid="{00000000-0005-0000-0000-00004E0A0000}"/>
+    <cellStyle name="Total 13 14" xfId="2017" xr:uid="{00000000-0005-0000-0000-00004F0A0000}"/>
+    <cellStyle name="Total 13 15" xfId="2078" xr:uid="{00000000-0005-0000-0000-0000500A0000}"/>
+    <cellStyle name="Total 13 16" xfId="2142" xr:uid="{00000000-0005-0000-0000-0000510A0000}"/>
+    <cellStyle name="Total 13 17" xfId="2203" xr:uid="{00000000-0005-0000-0000-0000520A0000}"/>
+    <cellStyle name="Total 13 18" xfId="2264" xr:uid="{00000000-0005-0000-0000-0000530A0000}"/>
+    <cellStyle name="Total 13 19" xfId="2324" xr:uid="{00000000-0005-0000-0000-0000540A0000}"/>
+    <cellStyle name="Total 13 2" xfId="1156" xr:uid="{00000000-0005-0000-0000-0000550A0000}"/>
+    <cellStyle name="Total 13 20" xfId="2385" xr:uid="{00000000-0005-0000-0000-0000560A0000}"/>
+    <cellStyle name="Total 13 21" xfId="2447" xr:uid="{00000000-0005-0000-0000-0000570A0000}"/>
+    <cellStyle name="Total 13 22" xfId="2506" xr:uid="{00000000-0005-0000-0000-0000580A0000}"/>
+    <cellStyle name="Total 13 23" xfId="2569" xr:uid="{00000000-0005-0000-0000-0000590A0000}"/>
+    <cellStyle name="Total 13 24" xfId="2628" xr:uid="{00000000-0005-0000-0000-00005A0A0000}"/>
+    <cellStyle name="Total 13 25" xfId="2683" xr:uid="{00000000-0005-0000-0000-00005B0A0000}"/>
+    <cellStyle name="Total 13 26" xfId="2735" xr:uid="{00000000-0005-0000-0000-00005C0A0000}"/>
+    <cellStyle name="Total 13 27" xfId="2782" xr:uid="{00000000-0005-0000-0000-00005D0A0000}"/>
+    <cellStyle name="Total 13 28" xfId="2830" xr:uid="{00000000-0005-0000-0000-00005E0A0000}"/>
+    <cellStyle name="Total 13 29" xfId="2876" xr:uid="{00000000-0005-0000-0000-00005F0A0000}"/>
+    <cellStyle name="Total 13 3" xfId="1232" xr:uid="{00000000-0005-0000-0000-0000600A0000}"/>
+    <cellStyle name="Total 13 30" xfId="2922" xr:uid="{00000000-0005-0000-0000-0000610A0000}"/>
+    <cellStyle name="Total 13 31" xfId="2971" xr:uid="{00000000-0005-0000-0000-0000620A0000}"/>
+    <cellStyle name="Total 13 32" xfId="3017" xr:uid="{00000000-0005-0000-0000-0000630A0000}"/>
+    <cellStyle name="Total 13 4" xfId="1308" xr:uid="{00000000-0005-0000-0000-0000640A0000}"/>
+    <cellStyle name="Total 13 5" xfId="1384" xr:uid="{00000000-0005-0000-0000-0000650A0000}"/>
+    <cellStyle name="Total 13 6" xfId="1459" xr:uid="{00000000-0005-0000-0000-0000660A0000}"/>
+    <cellStyle name="Total 13 7" xfId="1535" xr:uid="{00000000-0005-0000-0000-0000670A0000}"/>
+    <cellStyle name="Total 13 8" xfId="1610" xr:uid="{00000000-0005-0000-0000-0000680A0000}"/>
+    <cellStyle name="Total 13 9" xfId="1684" xr:uid="{00000000-0005-0000-0000-0000690A0000}"/>
+    <cellStyle name="Total 14" xfId="644" xr:uid="{00000000-0005-0000-0000-00006A0A0000}"/>
+    <cellStyle name="Total 14 10" xfId="1761" xr:uid="{00000000-0005-0000-0000-00006B0A0000}"/>
+    <cellStyle name="Total 14 11" xfId="1826" xr:uid="{00000000-0005-0000-0000-00006C0A0000}"/>
+    <cellStyle name="Total 14 12" xfId="1892" xr:uid="{00000000-0005-0000-0000-00006D0A0000}"/>
+    <cellStyle name="Total 14 13" xfId="1956" xr:uid="{00000000-0005-0000-0000-00006E0A0000}"/>
+    <cellStyle name="Total 14 14" xfId="2018" xr:uid="{00000000-0005-0000-0000-00006F0A0000}"/>
+    <cellStyle name="Total 14 15" xfId="2079" xr:uid="{00000000-0005-0000-0000-0000700A0000}"/>
+    <cellStyle name="Total 14 16" xfId="2143" xr:uid="{00000000-0005-0000-0000-0000710A0000}"/>
+    <cellStyle name="Total 14 17" xfId="2204" xr:uid="{00000000-0005-0000-0000-0000720A0000}"/>
+    <cellStyle name="Total 14 18" xfId="2265" xr:uid="{00000000-0005-0000-0000-0000730A0000}"/>
+    <cellStyle name="Total 14 19" xfId="2325" xr:uid="{00000000-0005-0000-0000-0000740A0000}"/>
+    <cellStyle name="Total 14 2" xfId="1157" xr:uid="{00000000-0005-0000-0000-0000750A0000}"/>
+    <cellStyle name="Total 14 20" xfId="2386" xr:uid="{00000000-0005-0000-0000-0000760A0000}"/>
+    <cellStyle name="Total 14 21" xfId="2448" xr:uid="{00000000-0005-0000-0000-0000770A0000}"/>
+    <cellStyle name="Total 14 22" xfId="2507" xr:uid="{00000000-0005-0000-0000-0000780A0000}"/>
+    <cellStyle name="Total 14 23" xfId="2570" xr:uid="{00000000-0005-0000-0000-0000790A0000}"/>
+    <cellStyle name="Total 14 24" xfId="2629" xr:uid="{00000000-0005-0000-0000-00007A0A0000}"/>
+    <cellStyle name="Total 14 25" xfId="2684" xr:uid="{00000000-0005-0000-0000-00007B0A0000}"/>
+    <cellStyle name="Total 14 26" xfId="2736" xr:uid="{00000000-0005-0000-0000-00007C0A0000}"/>
+    <cellStyle name="Total 14 27" xfId="2783" xr:uid="{00000000-0005-0000-0000-00007D0A0000}"/>
+    <cellStyle name="Total 14 28" xfId="2831" xr:uid="{00000000-0005-0000-0000-00007E0A0000}"/>
+    <cellStyle name="Total 14 29" xfId="2877" xr:uid="{00000000-0005-0000-0000-00007F0A0000}"/>
+    <cellStyle name="Total 14 3" xfId="1233" xr:uid="{00000000-0005-0000-0000-0000800A0000}"/>
+    <cellStyle name="Total 14 30" xfId="2923" xr:uid="{00000000-0005-0000-0000-0000810A0000}"/>
+    <cellStyle name="Total 14 31" xfId="2972" xr:uid="{00000000-0005-0000-0000-0000820A0000}"/>
+    <cellStyle name="Total 14 32" xfId="3018" xr:uid="{00000000-0005-0000-0000-0000830A0000}"/>
+    <cellStyle name="Total 14 4" xfId="1309" xr:uid="{00000000-0005-0000-0000-0000840A0000}"/>
+    <cellStyle name="Total 14 5" xfId="1385" xr:uid="{00000000-0005-0000-0000-0000850A0000}"/>
+    <cellStyle name="Total 14 6" xfId="1460" xr:uid="{00000000-0005-0000-0000-0000860A0000}"/>
+    <cellStyle name="Total 14 7" xfId="1536" xr:uid="{00000000-0005-0000-0000-0000870A0000}"/>
+    <cellStyle name="Total 14 8" xfId="1611" xr:uid="{00000000-0005-0000-0000-0000880A0000}"/>
+    <cellStyle name="Total 14 9" xfId="1685" xr:uid="{00000000-0005-0000-0000-0000890A0000}"/>
+    <cellStyle name="Total 15" xfId="645" xr:uid="{00000000-0005-0000-0000-00008A0A0000}"/>
+    <cellStyle name="Total 15 10" xfId="1762" xr:uid="{00000000-0005-0000-0000-00008B0A0000}"/>
+    <cellStyle name="Total 15 11" xfId="1827" xr:uid="{00000000-0005-0000-0000-00008C0A0000}"/>
+    <cellStyle name="Total 15 12" xfId="1893" xr:uid="{00000000-0005-0000-0000-00008D0A0000}"/>
+    <cellStyle name="Total 15 13" xfId="1957" xr:uid="{00000000-0005-0000-0000-00008E0A0000}"/>
+    <cellStyle name="Total 15 14" xfId="2019" xr:uid="{00000000-0005-0000-0000-00008F0A0000}"/>
+    <cellStyle name="Total 15 15" xfId="2080" xr:uid="{00000000-0005-0000-0000-0000900A0000}"/>
+    <cellStyle name="Total 15 16" xfId="2144" xr:uid="{00000000-0005-0000-0000-0000910A0000}"/>
+    <cellStyle name="Total 15 17" xfId="2205" xr:uid="{00000000-0005-0000-0000-0000920A0000}"/>
+    <cellStyle name="Total 15 18" xfId="2266" xr:uid="{00000000-0005-0000-0000-0000930A0000}"/>
+    <cellStyle name="Total 15 19" xfId="2326" xr:uid="{00000000-0005-0000-0000-0000940A0000}"/>
+    <cellStyle name="Total 15 2" xfId="1158" xr:uid="{00000000-0005-0000-0000-0000950A0000}"/>
+    <cellStyle name="Total 15 20" xfId="2387" xr:uid="{00000000-0005-0000-0000-0000960A0000}"/>
+    <cellStyle name="Total 15 21" xfId="2449" xr:uid="{00000000-0005-0000-0000-0000970A0000}"/>
+    <cellStyle name="Total 15 22" xfId="2508" xr:uid="{00000000-0005-0000-0000-0000980A0000}"/>
+    <cellStyle name="Total 15 23" xfId="2571" xr:uid="{00000000-0005-0000-0000-0000990A0000}"/>
+    <cellStyle name="Total 15 24" xfId="2630" xr:uid="{00000000-0005-0000-0000-00009A0A0000}"/>
+    <cellStyle name="Total 15 25" xfId="2685" xr:uid="{00000000-0005-0000-0000-00009B0A0000}"/>
+    <cellStyle name="Total 15 26" xfId="2737" xr:uid="{00000000-0005-0000-0000-00009C0A0000}"/>
+    <cellStyle name="Total 15 27" xfId="2784" xr:uid="{00000000-0005-0000-0000-00009D0A0000}"/>
+    <cellStyle name="Total 15 28" xfId="2832" xr:uid="{00000000-0005-0000-0000-00009E0A0000}"/>
+    <cellStyle name="Total 15 29" xfId="2878" xr:uid="{00000000-0005-0000-0000-00009F0A0000}"/>
+    <cellStyle name="Total 15 3" xfId="1234" xr:uid="{00000000-0005-0000-0000-0000A00A0000}"/>
+    <cellStyle name="Total 15 30" xfId="2924" xr:uid="{00000000-0005-0000-0000-0000A10A0000}"/>
+    <cellStyle name="Total 15 31" xfId="2973" xr:uid="{00000000-0005-0000-0000-0000A20A0000}"/>
+    <cellStyle name="Total 15 32" xfId="3019" xr:uid="{00000000-0005-0000-0000-0000A30A0000}"/>
+    <cellStyle name="Total 15 4" xfId="1310" xr:uid="{00000000-0005-0000-0000-0000A40A0000}"/>
+    <cellStyle name="Total 15 5" xfId="1386" xr:uid="{00000000-0005-0000-0000-0000A50A0000}"/>
+    <cellStyle name="Total 15 6" xfId="1461" xr:uid="{00000000-0005-0000-0000-0000A60A0000}"/>
+    <cellStyle name="Total 15 7" xfId="1537" xr:uid="{00000000-0005-0000-0000-0000A70A0000}"/>
+    <cellStyle name="Total 15 8" xfId="1612" xr:uid="{00000000-0005-0000-0000-0000A80A0000}"/>
+    <cellStyle name="Total 15 9" xfId="1686" xr:uid="{00000000-0005-0000-0000-0000A90A0000}"/>
+    <cellStyle name="Total 16" xfId="646" xr:uid="{00000000-0005-0000-0000-0000AA0A0000}"/>
+    <cellStyle name="Total 16 10" xfId="1763" xr:uid="{00000000-0005-0000-0000-0000AB0A0000}"/>
+    <cellStyle name="Total 16 11" xfId="1828" xr:uid="{00000000-0005-0000-0000-0000AC0A0000}"/>
+    <cellStyle name="Total 16 12" xfId="1894" xr:uid="{00000000-0005-0000-0000-0000AD0A0000}"/>
+    <cellStyle name="Total 16 13" xfId="1958" xr:uid="{00000000-0005-0000-0000-0000AE0A0000}"/>
+    <cellStyle name="Total 16 14" xfId="2020" xr:uid="{00000000-0005-0000-0000-0000AF0A0000}"/>
+    <cellStyle name="Total 16 15" xfId="2081" xr:uid="{00000000-0005-0000-0000-0000B00A0000}"/>
+    <cellStyle name="Total 16 16" xfId="2145" xr:uid="{00000000-0005-0000-0000-0000B10A0000}"/>
+    <cellStyle name="Total 16 17" xfId="2206" xr:uid="{00000000-0005-0000-0000-0000B20A0000}"/>
+    <cellStyle name="Total 16 18" xfId="2267" xr:uid="{00000000-0005-0000-0000-0000B30A0000}"/>
+    <cellStyle name="Total 16 19" xfId="2327" xr:uid="{00000000-0005-0000-0000-0000B40A0000}"/>
+    <cellStyle name="Total 16 2" xfId="1159" xr:uid="{00000000-0005-0000-0000-0000B50A0000}"/>
+    <cellStyle name="Total 16 20" xfId="2388" xr:uid="{00000000-0005-0000-0000-0000B60A0000}"/>
+    <cellStyle name="Total 16 21" xfId="2450" xr:uid="{00000000-0005-0000-0000-0000B70A0000}"/>
+    <cellStyle name="Total 16 22" xfId="2509" xr:uid="{00000000-0005-0000-0000-0000B80A0000}"/>
+    <cellStyle name="Total 16 23" xfId="2572" xr:uid="{00000000-0005-0000-0000-0000B90A0000}"/>
+    <cellStyle name="Total 16 24" xfId="2631" xr:uid="{00000000-0005-0000-0000-0000BA0A0000}"/>
+    <cellStyle name="Total 16 25" xfId="2686" xr:uid="{00000000-0005-0000-0000-0000BB0A0000}"/>
+    <cellStyle name="Total 16 26" xfId="2738" xr:uid="{00000000-0005-0000-0000-0000BC0A0000}"/>
+    <cellStyle name="Total 16 27" xfId="2785" xr:uid="{00000000-0005-0000-0000-0000BD0A0000}"/>
+    <cellStyle name="Total 16 28" xfId="2833" xr:uid="{00000000-0005-0000-0000-0000BE0A0000}"/>
+    <cellStyle name="Total 16 29" xfId="2879" xr:uid="{00000000-0005-0000-0000-0000BF0A0000}"/>
+    <cellStyle name="Total 16 3" xfId="1235" xr:uid="{00000000-0005-0000-0000-0000C00A0000}"/>
+    <cellStyle name="Total 16 30" xfId="2925" xr:uid="{00000000-0005-0000-0000-0000C10A0000}"/>
+    <cellStyle name="Total 16 31" xfId="2974" xr:uid="{00000000-0005-0000-0000-0000C20A0000}"/>
+    <cellStyle name="Total 16 32" xfId="3020" xr:uid="{00000000-0005-0000-0000-0000C30A0000}"/>
+    <cellStyle name="Total 16 4" xfId="1311" xr:uid="{00000000-0005-0000-0000-0000C40A0000}"/>
+    <cellStyle name="Total 16 5" xfId="1387" xr:uid="{00000000-0005-0000-0000-0000C50A0000}"/>
+    <cellStyle name="Total 16 6" xfId="1462" xr:uid="{00000000-0005-0000-0000-0000C60A0000}"/>
+    <cellStyle name="Total 16 7" xfId="1538" xr:uid="{00000000-0005-0000-0000-0000C70A0000}"/>
+    <cellStyle name="Total 16 8" xfId="1613" xr:uid="{00000000-0005-0000-0000-0000C80A0000}"/>
+    <cellStyle name="Total 16 9" xfId="1687" xr:uid="{00000000-0005-0000-0000-0000C90A0000}"/>
+    <cellStyle name="Total 2" xfId="647" xr:uid="{00000000-0005-0000-0000-0000CA0A0000}"/>
+    <cellStyle name="Total 2 10" xfId="1764" xr:uid="{00000000-0005-0000-0000-0000CB0A0000}"/>
+    <cellStyle name="Total 2 11" xfId="1829" xr:uid="{00000000-0005-0000-0000-0000CC0A0000}"/>
+    <cellStyle name="Total 2 12" xfId="1895" xr:uid="{00000000-0005-0000-0000-0000CD0A0000}"/>
+    <cellStyle name="Total 2 13" xfId="1959" xr:uid="{00000000-0005-0000-0000-0000CE0A0000}"/>
+    <cellStyle name="Total 2 14" xfId="2021" xr:uid="{00000000-0005-0000-0000-0000CF0A0000}"/>
+    <cellStyle name="Total 2 15" xfId="2082" xr:uid="{00000000-0005-0000-0000-0000D00A0000}"/>
+    <cellStyle name="Total 2 16" xfId="2146" xr:uid="{00000000-0005-0000-0000-0000D10A0000}"/>
+    <cellStyle name="Total 2 17" xfId="2207" xr:uid="{00000000-0005-0000-0000-0000D20A0000}"/>
+    <cellStyle name="Total 2 18" xfId="2268" xr:uid="{00000000-0005-0000-0000-0000D30A0000}"/>
+    <cellStyle name="Total 2 19" xfId="2328" xr:uid="{00000000-0005-0000-0000-0000D40A0000}"/>
+    <cellStyle name="Total 2 2" xfId="1160" xr:uid="{00000000-0005-0000-0000-0000D50A0000}"/>
+    <cellStyle name="Total 2 20" xfId="2389" xr:uid="{00000000-0005-0000-0000-0000D60A0000}"/>
+    <cellStyle name="Total 2 21" xfId="2451" xr:uid="{00000000-0005-0000-0000-0000D70A0000}"/>
+    <cellStyle name="Total 2 22" xfId="2510" xr:uid="{00000000-0005-0000-0000-0000D80A0000}"/>
+    <cellStyle name="Total 2 23" xfId="2573" xr:uid="{00000000-0005-0000-0000-0000D90A0000}"/>
+    <cellStyle name="Total 2 24" xfId="2632" xr:uid="{00000000-0005-0000-0000-0000DA0A0000}"/>
+    <cellStyle name="Total 2 25" xfId="2687" xr:uid="{00000000-0005-0000-0000-0000DB0A0000}"/>
+    <cellStyle name="Total 2 26" xfId="2739" xr:uid="{00000000-0005-0000-0000-0000DC0A0000}"/>
+    <cellStyle name="Total 2 27" xfId="2786" xr:uid="{00000000-0005-0000-0000-0000DD0A0000}"/>
+    <cellStyle name="Total 2 28" xfId="2834" xr:uid="{00000000-0005-0000-0000-0000DE0A0000}"/>
+    <cellStyle name="Total 2 29" xfId="2880" xr:uid="{00000000-0005-0000-0000-0000DF0A0000}"/>
+    <cellStyle name="Total 2 3" xfId="1236" xr:uid="{00000000-0005-0000-0000-0000E00A0000}"/>
+    <cellStyle name="Total 2 30" xfId="2926" xr:uid="{00000000-0005-0000-0000-0000E10A0000}"/>
+    <cellStyle name="Total 2 31" xfId="2975" xr:uid="{00000000-0005-0000-0000-0000E20A0000}"/>
+    <cellStyle name="Total 2 32" xfId="3021" xr:uid="{00000000-0005-0000-0000-0000E30A0000}"/>
+    <cellStyle name="Total 2 4" xfId="1312" xr:uid="{00000000-0005-0000-0000-0000E40A0000}"/>
+    <cellStyle name="Total 2 5" xfId="1388" xr:uid="{00000000-0005-0000-0000-0000E50A0000}"/>
+    <cellStyle name="Total 2 6" xfId="1463" xr:uid="{00000000-0005-0000-0000-0000E60A0000}"/>
+    <cellStyle name="Total 2 7" xfId="1539" xr:uid="{00000000-0005-0000-0000-0000E70A0000}"/>
+    <cellStyle name="Total 2 8" xfId="1614" xr:uid="{00000000-0005-0000-0000-0000E80A0000}"/>
+    <cellStyle name="Total 2 9" xfId="1688" xr:uid="{00000000-0005-0000-0000-0000E90A0000}"/>
+    <cellStyle name="Total 3" xfId="648" xr:uid="{00000000-0005-0000-0000-0000EA0A0000}"/>
+    <cellStyle name="Total 3 10" xfId="1765" xr:uid="{00000000-0005-0000-0000-0000EB0A0000}"/>
+    <cellStyle name="Total 3 11" xfId="1830" xr:uid="{00000000-0005-0000-0000-0000EC0A0000}"/>
+    <cellStyle name="Total 3 12" xfId="1896" xr:uid="{00000000-0005-0000-0000-0000ED0A0000}"/>
+    <cellStyle name="Total 3 13" xfId="1960" xr:uid="{00000000-0005-0000-0000-0000EE0A0000}"/>
+    <cellStyle name="Total 3 14" xfId="2022" xr:uid="{00000000-0005-0000-0000-0000EF0A0000}"/>
+    <cellStyle name="Total 3 15" xfId="2083" xr:uid="{00000000-0005-0000-0000-0000F00A0000}"/>
+    <cellStyle name="Total 3 16" xfId="2147" xr:uid="{00000000-0005-0000-0000-0000F10A0000}"/>
+    <cellStyle name="Total 3 17" xfId="2208" xr:uid="{00000000-0005-0000-0000-0000F20A0000}"/>
+    <cellStyle name="Total 3 18" xfId="2269" xr:uid="{00000000-0005-0000-0000-0000F30A0000}"/>
+    <cellStyle name="Total 3 19" xfId="2329" xr:uid="{00000000-0005-0000-0000-0000F40A0000}"/>
+    <cellStyle name="Total 3 2" xfId="1161" xr:uid="{00000000-0005-0000-0000-0000F50A0000}"/>
+    <cellStyle name="Total 3 20" xfId="2390" xr:uid="{00000000-0005-0000-0000-0000F60A0000}"/>
+    <cellStyle name="Total 3 21" xfId="2452" xr:uid="{00000000-0005-0000-0000-0000F70A0000}"/>
+    <cellStyle name="Total 3 22" xfId="2511" xr:uid="{00000000-0005-0000-0000-0000F80A0000}"/>
+    <cellStyle name="Total 3 23" xfId="2574" xr:uid="{00000000-0005-0000-0000-0000F90A0000}"/>
+    <cellStyle name="Total 3 24" xfId="2633" xr:uid="{00000000-0005-0000-0000-0000FA0A0000}"/>
+    <cellStyle name="Total 3 25" xfId="2688" xr:uid="{00000000-0005-0000-0000-0000FB0A0000}"/>
+    <cellStyle name="Total 3 26" xfId="2740" xr:uid="{00000000-0005-0000-0000-0000FC0A0000}"/>
+    <cellStyle name="Total 3 27" xfId="2787" xr:uid="{00000000-0005-0000-0000-0000FD0A0000}"/>
+    <cellStyle name="Total 3 28" xfId="2835" xr:uid="{00000000-0005-0000-0000-0000FE0A0000}"/>
+    <cellStyle name="Total 3 29" xfId="2881" xr:uid="{00000000-0005-0000-0000-0000FF0A0000}"/>
+    <cellStyle name="Total 3 3" xfId="1237" xr:uid="{00000000-0005-0000-0000-0000000B0000}"/>
+    <cellStyle name="Total 3 30" xfId="2927" xr:uid="{00000000-0005-0000-0000-0000010B0000}"/>
+    <cellStyle name="Total 3 31" xfId="2976" xr:uid="{00000000-0005-0000-0000-0000020B0000}"/>
+    <cellStyle name="Total 3 32" xfId="3022" xr:uid="{00000000-0005-0000-0000-0000030B0000}"/>
+    <cellStyle name="Total 3 4" xfId="1313" xr:uid="{00000000-0005-0000-0000-0000040B0000}"/>
+    <cellStyle name="Total 3 5" xfId="1389" xr:uid="{00000000-0005-0000-0000-0000050B0000}"/>
+    <cellStyle name="Total 3 6" xfId="1464" xr:uid="{00000000-0005-0000-0000-0000060B0000}"/>
+    <cellStyle name="Total 3 7" xfId="1540" xr:uid="{00000000-0005-0000-0000-0000070B0000}"/>
+    <cellStyle name="Total 3 8" xfId="1615" xr:uid="{00000000-0005-0000-0000-0000080B0000}"/>
+    <cellStyle name="Total 3 9" xfId="1689" xr:uid="{00000000-0005-0000-0000-0000090B0000}"/>
+    <cellStyle name="Total 4" xfId="649" xr:uid="{00000000-0005-0000-0000-00000A0B0000}"/>
+    <cellStyle name="Total 4 10" xfId="1766" xr:uid="{00000000-0005-0000-0000-00000B0B0000}"/>
+    <cellStyle name="Total 4 11" xfId="1831" xr:uid="{00000000-0005-0000-0000-00000C0B0000}"/>
+    <cellStyle name="Total 4 12" xfId="1897" xr:uid="{00000000-0005-0000-0000-00000D0B0000}"/>
+    <cellStyle name="Total 4 13" xfId="1961" xr:uid="{00000000-0005-0000-0000-00000E0B0000}"/>
+    <cellStyle name="Total 4 14" xfId="2023" xr:uid="{00000000-0005-0000-0000-00000F0B0000}"/>
+    <cellStyle name="Total 4 15" xfId="2084" xr:uid="{00000000-0005-0000-0000-0000100B0000}"/>
+    <cellStyle name="Total 4 16" xfId="2148" xr:uid="{00000000-0005-0000-0000-0000110B0000}"/>
+    <cellStyle name="Total 4 17" xfId="2209" xr:uid="{00000000-0005-0000-0000-0000120B0000}"/>
+    <cellStyle name="Total 4 18" xfId="2270" xr:uid="{00000000-0005-0000-0000-0000130B0000}"/>
+    <cellStyle name="Total 4 19" xfId="2330" xr:uid="{00000000-0005-0000-0000-0000140B0000}"/>
+    <cellStyle name="Total 4 2" xfId="1162" xr:uid="{00000000-0005-0000-0000-0000150B0000}"/>
+    <cellStyle name="Total 4 20" xfId="2391" xr:uid="{00000000-0005-0000-0000-0000160B0000}"/>
+    <cellStyle name="Total 4 21" xfId="2453" xr:uid="{00000000-0005-0000-0000-0000170B0000}"/>
+    <cellStyle name="Total 4 22" xfId="2512" xr:uid="{00000000-0005-0000-0000-0000180B0000}"/>
+    <cellStyle name="Total 4 23" xfId="2575" xr:uid="{00000000-0005-0000-0000-0000190B0000}"/>
+    <cellStyle name="Total 4 24" xfId="2634" xr:uid="{00000000-0005-0000-0000-00001A0B0000}"/>
+    <cellStyle name="Total 4 25" xfId="2689" xr:uid="{00000000-0005-0000-0000-00001B0B0000}"/>
+    <cellStyle name="Total 4 26" xfId="2741" xr:uid="{00000000-0005-0000-0000-00001C0B0000}"/>
+    <cellStyle name="Total 4 27" xfId="2788" xr:uid="{00000000-0005-0000-0000-00001D0B0000}"/>
+    <cellStyle name="Total 4 28" xfId="2836" xr:uid="{00000000-0005-0000-0000-00001E0B0000}"/>
+    <cellStyle name="Total 4 29" xfId="2882" xr:uid="{00000000-0005-0000-0000-00001F0B0000}"/>
+    <cellStyle name="Total 4 3" xfId="1238" xr:uid="{00000000-0005-0000-0000-0000200B0000}"/>
+    <cellStyle name="Total 4 30" xfId="2928" xr:uid="{00000000-0005-0000-0000-0000210B0000}"/>
+    <cellStyle name="Total 4 31" xfId="2977" xr:uid="{00000000-0005-0000-0000-0000220B0000}"/>
+    <cellStyle name="Total 4 32" xfId="3023" xr:uid="{00000000-0005-0000-0000-0000230B0000}"/>
+    <cellStyle name="Total 4 4" xfId="1314" xr:uid="{00000000-0005-0000-0000-0000240B0000}"/>
+    <cellStyle name="Total 4 5" xfId="1390" xr:uid="{00000000-0005-0000-0000-0000250B0000}"/>
+    <cellStyle name="Total 4 6" xfId="1465" xr:uid="{00000000-0005-0000-0000-0000260B0000}"/>
+    <cellStyle name="Total 4 7" xfId="1541" xr:uid="{00000000-0005-0000-0000-0000270B0000}"/>
+    <cellStyle name="Total 4 8" xfId="1616" xr:uid="{00000000-0005-0000-0000-0000280B0000}"/>
+    <cellStyle name="Total 4 9" xfId="1690" xr:uid="{00000000-0005-0000-0000-0000290B0000}"/>
+    <cellStyle name="Total 5" xfId="650" xr:uid="{00000000-0005-0000-0000-00002A0B0000}"/>
+    <cellStyle name="Total 5 10" xfId="1767" xr:uid="{00000000-0005-0000-0000-00002B0B0000}"/>
+    <cellStyle name="Total 5 11" xfId="1832" xr:uid="{00000000-0005-0000-0000-00002C0B0000}"/>
+    <cellStyle name="Total 5 12" xfId="1898" xr:uid="{00000000-0005-0000-0000-00002D0B0000}"/>
+    <cellStyle name="Total 5 13" xfId="1962" xr:uid="{00000000-0005-0000-0000-00002E0B0000}"/>
+    <cellStyle name="Total 5 14" xfId="2024" xr:uid="{00000000-0005-0000-0000-00002F0B0000}"/>
+    <cellStyle name="Total 5 15" xfId="2085" xr:uid="{00000000-0005-0000-0000-0000300B0000}"/>
+    <cellStyle name="Total 5 16" xfId="2149" xr:uid="{00000000-0005-0000-0000-0000310B0000}"/>
+    <cellStyle name="Total 5 17" xfId="2210" xr:uid="{00000000-0005-0000-0000-0000320B0000}"/>
+    <cellStyle name="Total 5 18" xfId="2271" xr:uid="{00000000-0005-0000-0000-0000330B0000}"/>
+    <cellStyle name="Total 5 19" xfId="2331" xr:uid="{00000000-0005-0000-0000-0000340B0000}"/>
+    <cellStyle name="Total 5 2" xfId="1163" xr:uid="{00000000-0005-0000-0000-0000350B0000}"/>
+    <cellStyle name="Total 5 20" xfId="2392" xr:uid="{00000000-0005-0000-0000-0000360B0000}"/>
+    <cellStyle name="Total 5 21" xfId="2454" xr:uid="{00000000-0005-0000-0000-0000370B0000}"/>
+    <cellStyle name="Total 5 22" xfId="2513" xr:uid="{00000000-0005-0000-0000-0000380B0000}"/>
+    <cellStyle name="Total 5 23" xfId="2576" xr:uid="{00000000-0005-0000-0000-0000390B0000}"/>
+    <cellStyle name="Total 5 24" xfId="2635" xr:uid="{00000000-0005-0000-0000-00003A0B0000}"/>
+    <cellStyle name="Total 5 25" xfId="2690" xr:uid="{00000000-0005-0000-0000-00003B0B0000}"/>
+    <cellStyle name="Total 5 26" xfId="2742" xr:uid="{00000000-0005-0000-0000-00003C0B0000}"/>
+    <cellStyle name="Total 5 27" xfId="2789" xr:uid="{00000000-0005-0000-0000-00003D0B0000}"/>
+    <cellStyle name="Total 5 28" xfId="2837" xr:uid="{00000000-0005-0000-0000-00003E0B0000}"/>
+    <cellStyle name="Total 5 29" xfId="2883" xr:uid="{00000000-0005-0000-0000-00003F0B0000}"/>
+    <cellStyle name="Total 5 3" xfId="1239" xr:uid="{00000000-0005-0000-0000-0000400B0000}"/>
+    <cellStyle name="Total 5 30" xfId="2929" xr:uid="{00000000-0005-0000-0000-0000410B0000}"/>
+    <cellStyle name="Total 5 31" xfId="2978" xr:uid="{00000000-0005-0000-0000-0000420B0000}"/>
+    <cellStyle name="Total 5 32" xfId="3024" xr:uid="{00000000-0005-0000-0000-0000430B0000}"/>
+    <cellStyle name="Total 5 4" xfId="1315" xr:uid="{00000000-0005-0000-0000-0000440B0000}"/>
+    <cellStyle name="Total 5 5" xfId="1391" xr:uid="{00000000-0005-0000-0000-0000450B0000}"/>
+    <cellStyle name="Total 5 6" xfId="1466" xr:uid="{00000000-0005-0000-0000-0000460B0000}"/>
+    <cellStyle name="Total 5 7" xfId="1542" xr:uid="{00000000-0005-0000-0000-0000470B0000}"/>
+    <cellStyle name="Total 5 8" xfId="1617" xr:uid="{00000000-0005-0000-0000-0000480B0000}"/>
+    <cellStyle name="Total 5 9" xfId="1691" xr:uid="{00000000-0005-0000-0000-0000490B0000}"/>
+    <cellStyle name="Total 6" xfId="651" xr:uid="{00000000-0005-0000-0000-00004A0B0000}"/>
+    <cellStyle name="Total 6 10" xfId="1768" xr:uid="{00000000-0005-0000-0000-00004B0B0000}"/>
+    <cellStyle name="Total 6 11" xfId="1833" xr:uid="{00000000-0005-0000-0000-00004C0B0000}"/>
+    <cellStyle name="Total 6 12" xfId="1899" xr:uid="{00000000-0005-0000-0000-00004D0B0000}"/>
+    <cellStyle name="Total 6 13" xfId="1963" xr:uid="{00000000-0005-0000-0000-00004E0B0000}"/>
+    <cellStyle name="Total 6 14" xfId="2025" xr:uid="{00000000-0005-0000-0000-00004F0B0000}"/>
+    <cellStyle name="Total 6 15" xfId="2086" xr:uid="{00000000-0005-0000-0000-0000500B0000}"/>
+    <cellStyle name="Total 6 16" xfId="2150" xr:uid="{00000000-0005-0000-0000-0000510B0000}"/>
+    <cellStyle name="Total 6 17" xfId="2211" xr:uid="{00000000-0005-0000-0000-0000520B0000}"/>
+    <cellStyle name="Total 6 18" xfId="2272" xr:uid="{00000000-0005-0000-0000-0000530B0000}"/>
+    <cellStyle name="Total 6 19" xfId="2332" xr:uid="{00000000-0005-0000-0000-0000540B0000}"/>
+    <cellStyle name="Total 6 2" xfId="1164" xr:uid="{00000000-0005-0000-0000-0000550B0000}"/>
+    <cellStyle name="Total 6 20" xfId="2393" xr:uid="{00000000-0005-0000-0000-0000560B0000}"/>
+    <cellStyle name="Total 6 21" xfId="2455" xr:uid="{00000000-0005-0000-0000-0000570B0000}"/>
+    <cellStyle name="Total 6 22" xfId="2514" xr:uid="{00000000-0005-0000-0000-0000580B0000}"/>
+    <cellStyle name="Total 6 23" xfId="2577" xr:uid="{00000000-0005-0000-0000-0000590B0000}"/>
+    <cellStyle name="Total 6 24" xfId="2636" xr:uid="{00000000-0005-0000-0000-00005A0B0000}"/>
+    <cellStyle name="Total 6 25" xfId="2691" xr:uid="{00000000-0005-0000-0000-00005B0B0000}"/>
+    <cellStyle name="Total 6 26" xfId="2743" xr:uid="{00000000-0005-0000-0000-00005C0B0000}"/>
+    <cellStyle name="Total 6 27" xfId="2790" xr:uid="{00000000-0005-0000-0000-00005D0B0000}"/>
+    <cellStyle name="Total 6 28" xfId="2838" xr:uid="{00000000-0005-0000-0000-00005E0B0000}"/>
+    <cellStyle name="Total 6 29" xfId="2884" xr:uid="{00000000-0005-0000-0000-00005F0B0000}"/>
+    <cellStyle name="Total 6 3" xfId="1240" xr:uid="{00000000-0005-0000-0000-0000600B0000}"/>
+    <cellStyle name="Total 6 30" xfId="2930" xr:uid="{00000000-0005-0000-0000-0000610B0000}"/>
+    <cellStyle name="Total 6 31" xfId="2979" xr:uid="{00000000-0005-0000-0000-0000620B0000}"/>
+    <cellStyle name="Total 6 32" xfId="3025" xr:uid="{00000000-0005-0000-0000-0000630B0000}"/>
+    <cellStyle name="Total 6 4" xfId="1316" xr:uid="{00000000-0005-0000-0000-0000640B0000}"/>
+    <cellStyle name="Total 6 5" xfId="1392" xr:uid="{00000000-0005-0000-0000-0000650B0000}"/>
+    <cellStyle name="Total 6 6" xfId="1467" xr:uid="{00000000-0005-0000-0000-0000660B0000}"/>
+    <cellStyle name="Total 6 7" xfId="1543" xr:uid="{00000000-0005-0000-0000-0000670B0000}"/>
+    <cellStyle name="Total 6 8" xfId="1618" xr:uid="{00000000-0005-0000-0000-0000680B0000}"/>
+    <cellStyle name="Total 6 9" xfId="1692" xr:uid="{00000000-0005-0000-0000-0000690B0000}"/>
+    <cellStyle name="Total 7" xfId="652" xr:uid="{00000000-0005-0000-0000-00006A0B0000}"/>
+    <cellStyle name="Total 7 10" xfId="1769" xr:uid="{00000000-0005-0000-0000-00006B0B0000}"/>
+    <cellStyle name="Total 7 11" xfId="1834" xr:uid="{00000000-0005-0000-0000-00006C0B0000}"/>
+    <cellStyle name="Total 7 12" xfId="1900" xr:uid="{00000000-0005-0000-0000-00006D0B0000}"/>
+    <cellStyle name="Total 7 13" xfId="1964" xr:uid="{00000000-0005-0000-0000-00006E0B0000}"/>
+    <cellStyle name="Total 7 14" xfId="2026" xr:uid="{00000000-0005-0000-0000-00006F0B0000}"/>
+    <cellStyle name="Total 7 15" xfId="2087" xr:uid="{00000000-0005-0000-0000-0000700B0000}"/>
+    <cellStyle name="Total 7 16" xfId="2151" xr:uid="{00000000-0005-0000-0000-0000710B0000}"/>
+    <cellStyle name="Total 7 17" xfId="2212" xr:uid="{00000000-0005-0000-0000-0000720B0000}"/>
+    <cellStyle name="Total 7 18" xfId="2273" xr:uid="{00000000-0005-0000-0000-0000730B0000}"/>
+    <cellStyle name="Total 7 19" xfId="2333" xr:uid="{00000000-0005-0000-0000-0000740B0000}"/>
+    <cellStyle name="Total 7 2" xfId="1165" xr:uid="{00000000-0005-0000-0000-0000750B0000}"/>
+    <cellStyle name="Total 7 20" xfId="2394" xr:uid="{00000000-0005-0000-0000-0000760B0000}"/>
+    <cellStyle name="Total 7 21" xfId="2456" xr:uid="{00000000-0005-0000-0000-0000770B0000}"/>
+    <cellStyle name="Total 7 22" xfId="2515" xr:uid="{00000000-0005-0000-0000-0000780B0000}"/>
+    <cellStyle name="Total 7 23" xfId="2578" xr:uid="{00000000-0005-0000-0000-0000790B0000}"/>
+    <cellStyle name="Total 7 24" xfId="2637" xr:uid="{00000000-0005-0000-0000-00007A0B0000}"/>
+    <cellStyle name="Total 7 25" xfId="2692" xr:uid="{00000000-0005-0000-0000-00007B0B0000}"/>
+    <cellStyle name="Total 7 26" xfId="2744" xr:uid="{00000000-0005-0000-0000-00007C0B0000}"/>
+    <cellStyle name="Total 7 27" xfId="2791" xr:uid="{00000000-0005-0000-0000-00007D0B0000}"/>
+    <cellStyle name="Total 7 28" xfId="2839" xr:uid="{00000000-0005-0000-0000-00007E0B0000}"/>
+    <cellStyle name="Total 7 29" xfId="2885" xr:uid="{00000000-0005-0000-0000-00007F0B0000}"/>
+    <cellStyle name="Total 7 3" xfId="1241" xr:uid="{00000000-0005-0000-0000-0000800B0000}"/>
+    <cellStyle name="Total 7 30" xfId="2931" xr:uid="{00000000-0005-0000-0000-0000810B0000}"/>
+    <cellStyle name="Total 7 31" xfId="2980" xr:uid="{00000000-0005-0000-0000-0000820B0000}"/>
+    <cellStyle name="Total 7 32" xfId="3026" xr:uid="{00000000-0005-0000-0000-0000830B0000}"/>
+    <cellStyle name="Total 7 4" xfId="1317" xr:uid="{00000000-0005-0000-0000-0000840B0000}"/>
+    <cellStyle name="Total 7 5" xfId="1393" xr:uid="{00000000-0005-0000-0000-0000850B0000}"/>
+    <cellStyle name="Total 7 6" xfId="1468" xr:uid="{00000000-0005-0000-0000-0000860B0000}"/>
+    <cellStyle name="Total 7 7" xfId="1544" xr:uid="{00000000-0005-0000-0000-0000870B0000}"/>
+    <cellStyle name="Total 7 8" xfId="1619" xr:uid="{00000000-0005-0000-0000-0000880B0000}"/>
+    <cellStyle name="Total 7 9" xfId="1693" xr:uid="{00000000-0005-0000-0000-0000890B0000}"/>
+    <cellStyle name="Total 8" xfId="653" xr:uid="{00000000-0005-0000-0000-00008A0B0000}"/>
+    <cellStyle name="Total 8 10" xfId="1770" xr:uid="{00000000-0005-0000-0000-00008B0B0000}"/>
+    <cellStyle name="Total 8 11" xfId="1835" xr:uid="{00000000-0005-0000-0000-00008C0B0000}"/>
+    <cellStyle name="Total 8 12" xfId="1901" xr:uid="{00000000-0005-0000-0000-00008D0B0000}"/>
+    <cellStyle name="Total 8 13" xfId="1965" xr:uid="{00000000-0005-0000-0000-00008E0B0000}"/>
+    <cellStyle name="Total 8 14" xfId="2027" xr:uid="{00000000-0005-0000-0000-00008F0B0000}"/>
+    <cellStyle name="Total 8 15" xfId="2088" xr:uid="{00000000-0005-0000-0000-0000900B0000}"/>
+    <cellStyle name="Total 8 16" xfId="2152" xr:uid="{00000000-0005-0000-0000-0000910B0000}"/>
+    <cellStyle name="Total 8 17" xfId="2213" xr:uid="{00000000-0005-0000-0000-0000920B0000}"/>
+    <cellStyle name="Total 8 18" xfId="2274" xr:uid="{00000000-0005-0000-0000-0000930B0000}"/>
+    <cellStyle name="Total 8 19" xfId="2334" xr:uid="{00000000-0005-0000-0000-0000940B0000}"/>
+    <cellStyle name="Total 8 2" xfId="1166" xr:uid="{00000000-0005-0000-0000-0000950B0000}"/>
+    <cellStyle name="Total 8 20" xfId="2395" xr:uid="{00000000-0005-0000-0000-0000960B0000}"/>
+    <cellStyle name="Total 8 21" xfId="2457" xr:uid="{00000000-0005-0000-0000-0000970B0000}"/>
+    <cellStyle name="Total 8 22" xfId="2516" xr:uid="{00000000-0005-0000-0000-0000980B0000}"/>
+    <cellStyle name="Total 8 23" xfId="2579" xr:uid="{00000000-0005-0000-0000-0000990B0000}"/>
+    <cellStyle name="Total 8 24" xfId="2638" xr:uid="{00000000-0005-0000-0000-00009A0B0000}"/>
+    <cellStyle name="Total 8 25" xfId="2693" xr:uid="{00000000-0005-0000-0000-00009B0B0000}"/>
+    <cellStyle name="Total 8 26" xfId="2745" xr:uid="{00000000-0005-0000-0000-00009C0B0000}"/>
+    <cellStyle name="Total 8 27" xfId="2792" xr:uid="{00000000-0005-0000-0000-00009D0B0000}"/>
+    <cellStyle name="Total 8 28" xfId="2840" xr:uid="{00000000-0005-0000-0000-00009E0B0000}"/>
+    <cellStyle name="Total 8 29" xfId="2886" xr:uid="{00000000-0005-0000-0000-00009F0B0000}"/>
+    <cellStyle name="Total 8 3" xfId="1242" xr:uid="{00000000-0005-0000-0000-0000A00B0000}"/>
+    <cellStyle name="Total 8 30" xfId="2932" xr:uid="{00000000-0005-0000-0000-0000A10B0000}"/>
+    <cellStyle name="Total 8 31" xfId="2981" xr:uid="{00000000-0005-0000-0000-0000A20B0000}"/>
+    <cellStyle name="Total 8 32" xfId="3027" xr:uid="{00000000-0005-0000-0000-0000A30B0000}"/>
+    <cellStyle name="Total 8 4" xfId="1318" xr:uid="{00000000-0005-0000-0000-0000A40B0000}"/>
+    <cellStyle name="Total 8 5" xfId="1394" xr:uid="{00000000-0005-0000-0000-0000A50B0000}"/>
+    <cellStyle name="Total 8 6" xfId="1469" xr:uid="{00000000-0005-0000-0000-0000A60B0000}"/>
+    <cellStyle name="Total 8 7" xfId="1545" xr:uid="{00000000-0005-0000-0000-0000A70B0000}"/>
+    <cellStyle name="Total 8 8" xfId="1620" xr:uid="{00000000-0005-0000-0000-0000A80B0000}"/>
+    <cellStyle name="Total 8 9" xfId="1694" xr:uid="{00000000-0005-0000-0000-0000A90B0000}"/>
+    <cellStyle name="Total 9" xfId="654" xr:uid="{00000000-0005-0000-0000-0000AA0B0000}"/>
+    <cellStyle name="Total 9 10" xfId="1771" xr:uid="{00000000-0005-0000-0000-0000AB0B0000}"/>
+    <cellStyle name="Total 9 11" xfId="1836" xr:uid="{00000000-0005-0000-0000-0000AC0B0000}"/>
+    <cellStyle name="Total 9 12" xfId="1902" xr:uid="{00000000-0005-0000-0000-0000AD0B0000}"/>
+    <cellStyle name="Total 9 13" xfId="1966" xr:uid="{00000000-0005-0000-0000-0000AE0B0000}"/>
+    <cellStyle name="Total 9 14" xfId="2028" xr:uid="{00000000-0005-0000-0000-0000AF0B0000}"/>
+    <cellStyle name="Total 9 15" xfId="2089" xr:uid="{00000000-0005-0000-0000-0000B00B0000}"/>
+    <cellStyle name="Total 9 16" xfId="2153" xr:uid="{00000000-0005-0000-0000-0000B10B0000}"/>
+    <cellStyle name="Total 9 17" xfId="2214" xr:uid="{00000000-0005-0000-0000-0000B20B0000}"/>
+    <cellStyle name="Total 9 18" xfId="2275" xr:uid="{00000000-0005-0000-0000-0000B30B0000}"/>
+    <cellStyle name="Total 9 19" xfId="2335" xr:uid="{00000000-0005-0000-0000-0000B40B0000}"/>
+    <cellStyle name="Total 9 2" xfId="1167" xr:uid="{00000000-0005-0000-0000-0000B50B0000}"/>
+    <cellStyle name="Total 9 20" xfId="2396" xr:uid="{00000000-0005-0000-0000-0000B60B0000}"/>
+    <cellStyle name="Total 9 21" xfId="2458" xr:uid="{00000000-0005-0000-0000-0000B70B0000}"/>
+    <cellStyle name="Total 9 22" xfId="2517" xr:uid="{00000000-0005-0000-0000-0000B80B0000}"/>
+    <cellStyle name="Total 9 23" xfId="2580" xr:uid="{00000000-0005-0000-0000-0000B90B0000}"/>
+    <cellStyle name="Total 9 24" xfId="2639" xr:uid="{00000000-0005-0000-0000-0000BA0B0000}"/>
+    <cellStyle name="Total 9 25" xfId="2694" xr:uid="{00000000-0005-0000-0000-0000BB0B0000}"/>
+    <cellStyle name="Total 9 26" xfId="2746" xr:uid="{00000000-0005-0000-0000-0000BC0B0000}"/>
+    <cellStyle name="Total 9 27" xfId="2793" xr:uid="{00000000-0005-0000-0000-0000BD0B0000}"/>
+    <cellStyle name="Total 9 28" xfId="2841" xr:uid="{00000000-0005-0000-0000-0000BE0B0000}"/>
+    <cellStyle name="Total 9 29" xfId="2887" xr:uid="{00000000-0005-0000-0000-0000BF0B0000}"/>
+    <cellStyle name="Total 9 3" xfId="1243" xr:uid="{00000000-0005-0000-0000-0000C00B0000}"/>
+    <cellStyle name="Total 9 30" xfId="2933" xr:uid="{00000000-0005-0000-0000-0000C10B0000}"/>
+    <cellStyle name="Total 9 31" xfId="2982" xr:uid="{00000000-0005-0000-0000-0000C20B0000}"/>
+    <cellStyle name="Total 9 32" xfId="3028" xr:uid="{00000000-0005-0000-0000-0000C30B0000}"/>
+    <cellStyle name="Total 9 4" xfId="1319" xr:uid="{00000000-0005-0000-0000-0000C40B0000}"/>
+    <cellStyle name="Total 9 5" xfId="1395" xr:uid="{00000000-0005-0000-0000-0000C50B0000}"/>
+    <cellStyle name="Total 9 6" xfId="1470" xr:uid="{00000000-0005-0000-0000-0000C60B0000}"/>
+    <cellStyle name="Total 9 7" xfId="1546" xr:uid="{00000000-0005-0000-0000-0000C70B0000}"/>
+    <cellStyle name="Total 9 8" xfId="1621" xr:uid="{00000000-0005-0000-0000-0000C80B0000}"/>
+    <cellStyle name="Total 9 9" xfId="1695" xr:uid="{00000000-0005-0000-0000-0000C90B0000}"/>
+    <cellStyle name="Warning Text 10" xfId="655" xr:uid="{00000000-0005-0000-0000-0000CA0B0000}"/>
+    <cellStyle name="Warning Text 11" xfId="656" xr:uid="{00000000-0005-0000-0000-0000CB0B0000}"/>
+    <cellStyle name="Warning Text 12" xfId="657" xr:uid="{00000000-0005-0000-0000-0000CC0B0000}"/>
+    <cellStyle name="Warning Text 13" xfId="658" xr:uid="{00000000-0005-0000-0000-0000CD0B0000}"/>
+    <cellStyle name="Warning Text 14" xfId="659" xr:uid="{00000000-0005-0000-0000-0000CE0B0000}"/>
+    <cellStyle name="Warning Text 15" xfId="660" xr:uid="{00000000-0005-0000-0000-0000CF0B0000}"/>
+    <cellStyle name="Warning Text 16" xfId="661" xr:uid="{00000000-0005-0000-0000-0000D00B0000}"/>
+    <cellStyle name="Warning Text 2" xfId="662" xr:uid="{00000000-0005-0000-0000-0000D10B0000}"/>
+    <cellStyle name="Warning Text 3" xfId="663" xr:uid="{00000000-0005-0000-0000-0000D20B0000}"/>
+    <cellStyle name="Warning Text 4" xfId="664" xr:uid="{00000000-0005-0000-0000-0000D30B0000}"/>
+    <cellStyle name="Warning Text 5" xfId="665" xr:uid="{00000000-0005-0000-0000-0000D40B0000}"/>
+    <cellStyle name="Warning Text 6" xfId="666" xr:uid="{00000000-0005-0000-0000-0000D50B0000}"/>
+    <cellStyle name="Warning Text 7" xfId="667" xr:uid="{00000000-0005-0000-0000-0000D60B0000}"/>
+    <cellStyle name="Warning Text 8" xfId="668" xr:uid="{00000000-0005-0000-0000-0000D70B0000}"/>
+    <cellStyle name="Warning Text 9" xfId="669" xr:uid="{00000000-0005-0000-0000-0000D80B0000}"/>
   </cellStyles>
   <dxfs count="17">
     <dxf>
@@ -9524,7 +9527,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7">
+    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
       <tableStyleElement type="wholeTable" dxfId="16"/>
       <tableStyleElement type="headerRow" dxfId="15"/>
       <tableStyleElement type="totalRow" dxfId="14"/>
@@ -9533,7 +9536,7 @@
       <tableStyleElement type="firstRowStripe" dxfId="11"/>
       <tableStyleElement type="firstColumnStripe" dxfId="10"/>
     </tableStyle>
-    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10">
+    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{00000000-0011-0000-FFFF-FFFF01000000}">
       <tableStyleElement type="headerRow" dxfId="9"/>
       <tableStyleElement type="totalRow" dxfId="8"/>
       <tableStyleElement type="firstRowStripe" dxfId="7"/>
@@ -9549,6 +9552,9 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -9863,30 +9869,31 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M86"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="41.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.69921875" customWidth="1"/>
-    <col min="3" max="3" width="45" style="57" customWidth="1"/>
-    <col min="4" max="4" width="13.5" style="2" customWidth="1"/>
-    <col min="5" max="5" width="14.59765625" customWidth="1"/>
-    <col min="6" max="6" width="11.796875" customWidth="1"/>
-    <col min="7" max="7" width="14.796875" customWidth="1"/>
-    <col min="8" max="8" width="15.5" customWidth="1"/>
-    <col min="9" max="9" width="11.296875" customWidth="1"/>
-    <col min="10" max="10" width="10.59765625" style="6" customWidth="1"/>
+    <col min="1" max="1" width="69.1796875" customWidth="1"/>
+    <col min="2" max="2" width="14.08984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="183.90625" style="57" customWidth="1"/>
+    <col min="4" max="4" width="21.36328125" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.08984375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.26953125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.7265625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.6328125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.54296875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="5.7265625" style="6" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="19.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="24.6">
+    <row r="1" spans="1:11" ht="26">
       <c r="A1" s="18" t="s">
         <v>74</v>
       </c>
@@ -9932,7 +9939,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="23.4" customHeight="1">
+    <row r="3" spans="1:11">
       <c r="A3" s="25" t="s">
         <v>45</v>
       </c>
@@ -9962,7 +9969,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="22.2" customHeight="1">
+    <row r="4" spans="1:11">
       <c r="A4" s="25" t="s">
         <v>45</v>
       </c>
@@ -9992,7 +9999,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="22.2" customHeight="1">
+    <row r="5" spans="1:11">
       <c r="A5" s="25" t="s">
         <v>45</v>
       </c>
@@ -10022,7 +10029,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="22.2" customHeight="1">
+    <row r="6" spans="1:11">
       <c r="A6" s="25" t="s">
         <v>45</v>
       </c>
@@ -10054,7 +10061,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="22.2" customHeight="1">
+    <row r="7" spans="1:11">
       <c r="A7" s="25" t="s">
         <v>46</v>
       </c>
@@ -10084,7 +10091,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="22.2" customHeight="1">
+    <row r="8" spans="1:11">
       <c r="A8" s="25" t="s">
         <v>46</v>
       </c>
@@ -10114,7 +10121,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="22.2" customHeight="1">
+    <row r="9" spans="1:11">
       <c r="A9" s="25" t="s">
         <v>46</v>
       </c>
@@ -10146,7 +10153,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="22.2" customHeight="1">
+    <row r="10" spans="1:11">
       <c r="A10" s="25" t="s">
         <v>79</v>
       </c>
@@ -10178,7 +10185,7 @@
         <v>8.0851875000000004E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="22.2" customHeight="1">
+    <row r="11" spans="1:11">
       <c r="A11" s="25" t="s">
         <v>10</v>
       </c>
@@ -10210,7 +10217,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="22.2" customHeight="1">
+    <row r="12" spans="1:11">
       <c r="A12" s="25" t="s">
         <v>13</v>
       </c>
@@ -10245,7 +10252,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="22.2" customHeight="1">
+    <row r="13" spans="1:11">
       <c r="A13" s="25" t="s">
         <v>14</v>
       </c>
@@ -10277,7 +10284,7 @@
         <v>9.2851200000000009E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:11" ht="22.2" customHeight="1">
+    <row r="14" spans="1:11">
       <c r="A14" s="25" t="s">
         <v>16</v>
       </c>
@@ -10309,7 +10316,7 @@
         <v>9.2851200000000009E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:11" ht="22.2" customHeight="1">
+    <row r="15" spans="1:11">
       <c r="A15" s="25" t="s">
         <v>17</v>
       </c>
@@ -10341,7 +10348,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="16" spans="1:11" ht="22.2" customHeight="1">
+    <row r="16" spans="1:11" ht="43.5">
       <c r="A16" s="25" t="s">
         <v>83</v>
       </c>
@@ -10373,7 +10380,7 @@
         <v>1.6E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:13" ht="22.2" customHeight="1">
+    <row r="17" spans="1:13">
       <c r="A17" s="25" t="s">
         <v>20</v>
       </c>
@@ -10405,7 +10412,7 @@
         <v>5.5E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:13" ht="22.2" customHeight="1">
+    <row r="18" spans="1:13">
       <c r="A18" s="25" t="s">
         <v>21</v>
       </c>
@@ -10437,7 +10444,7 @@
         <v>1.1368E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:13" ht="22.2" customHeight="1">
+    <row r="19" spans="1:13">
       <c r="A19" s="25" t="s">
         <v>96</v>
       </c>
@@ -10470,7 +10477,7 @@
       </c>
       <c r="K19" s="2"/>
     </row>
-    <row r="20" spans="1:13" ht="22.2" customHeight="1">
+    <row r="20" spans="1:13" ht="29">
       <c r="A20" s="30" t="s">
         <v>80</v>
       </c>
@@ -10503,7 +10510,7 @@
       </c>
       <c r="K20" s="2"/>
     </row>
-    <row r="21" spans="1:13" ht="22.2" customHeight="1">
+    <row r="21" spans="1:13">
       <c r="A21" s="34" t="s">
         <v>86</v>
       </c>
@@ -10536,9 +10543,9 @@
       </c>
       <c r="K21" s="2"/>
     </row>
-    <row r="22" spans="1:13" ht="22.2" customHeight="1">
+    <row r="22" spans="1:13">
       <c r="A22" s="34" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B22" s="25" t="s">
         <v>84</v>
@@ -10569,14 +10576,14 @@
       </c>
       <c r="K22" s="2"/>
     </row>
-    <row r="23" spans="1:13" ht="22.2" customHeight="1">
+    <row r="23" spans="1:13">
       <c r="A23" s="38" t="s">
         <v>109</v>
       </c>
       <c r="B23" s="35" t="s">
         <v>84</v>
       </c>
-      <c r="C23" s="61" t="s">
+      <c r="C23" s="60" t="s">
         <v>104</v>
       </c>
       <c r="D23" s="36" t="s">
@@ -10602,14 +10609,14 @@
       </c>
       <c r="K23" s="2"/>
     </row>
-    <row r="24" spans="1:13" ht="22.2" customHeight="1">
+    <row r="24" spans="1:13">
       <c r="A24" s="38" t="s">
         <v>108</v>
       </c>
       <c r="B24" s="35" t="s">
         <v>84</v>
       </c>
-      <c r="C24" s="61" t="s">
+      <c r="C24" s="60" t="s">
         <v>110</v>
       </c>
       <c r="D24" s="36" t="s">
@@ -10623,14 +10630,14 @@
       <c r="J24" s="37"/>
       <c r="K24" s="2"/>
     </row>
-    <row r="25" spans="1:13" ht="22.2" customHeight="1">
+    <row r="25" spans="1:13">
       <c r="A25" s="38" t="s">
         <v>107</v>
       </c>
       <c r="B25" s="35" t="s">
         <v>84</v>
       </c>
-      <c r="C25" s="61" t="s">
+      <c r="C25" s="60" t="s">
         <v>105</v>
       </c>
       <c r="D25" s="36" t="s">
@@ -10656,7 +10663,7 @@
       </c>
       <c r="K25" s="2"/>
     </row>
-    <row r="26" spans="1:13" ht="22.2" customHeight="1">
+    <row r="26" spans="1:13">
       <c r="A26" s="30" t="s">
         <v>26</v>
       </c>
@@ -10689,7 +10696,7 @@
       </c>
       <c r="K26" s="2"/>
     </row>
-    <row r="27" spans="1:13" ht="22.2" customHeight="1">
+    <row r="27" spans="1:13">
       <c r="A27" s="30" t="s">
         <v>27</v>
       </c>
@@ -10722,7 +10729,7 @@
       </c>
       <c r="K27" s="2"/>
     </row>
-    <row r="28" spans="1:13" ht="22.2" customHeight="1" thickBot="1">
+    <row r="28" spans="1:13" ht="15" thickBot="1">
       <c r="A28" s="30" t="s">
         <v>29</v>
       </c>
@@ -10730,7 +10737,7 @@
         <v>84</v>
       </c>
       <c r="C28" s="31" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D28" s="20" t="s">
         <v>15</v>
@@ -10755,7 +10762,7 @@
       </c>
       <c r="K28" s="2"/>
     </row>
-    <row r="29" spans="1:13" ht="22.2" customHeight="1" thickBot="1">
+    <row r="29" spans="1:13" ht="15" thickBot="1">
       <c r="A29" s="39" t="s">
         <v>118</v>
       </c>
@@ -10789,7 +10796,7 @@
       </c>
       <c r="K29" s="2"/>
     </row>
-    <row r="30" spans="1:13" ht="22.2" customHeight="1" thickBot="1">
+    <row r="30" spans="1:13" ht="15" thickBot="1">
       <c r="A30" s="39" t="s">
         <v>121</v>
       </c>
@@ -10822,7 +10829,7 @@
       </c>
       <c r="K30" s="2"/>
     </row>
-    <row r="31" spans="1:13" ht="22.2" customHeight="1" thickBot="1">
+    <row r="31" spans="1:13" ht="58.5" thickBot="1">
       <c r="A31" s="39" t="s">
         <v>124</v>
       </c>
@@ -10856,7 +10863,7 @@
       </c>
       <c r="K31" s="2"/>
     </row>
-    <row r="32" spans="1:13" ht="22.2" customHeight="1">
+    <row r="32" spans="1:13">
       <c r="A32" s="30" t="s">
         <v>30</v>
       </c>
@@ -10891,7 +10898,7 @@
       <c r="L32" s="4"/>
       <c r="M32" s="4"/>
     </row>
-    <row r="33" spans="1:13" ht="22.2" customHeight="1">
+    <row r="33" spans="1:13">
       <c r="A33" s="30" t="s">
         <v>31</v>
       </c>
@@ -10918,7 +10925,7 @@
       <c r="L33" s="4"/>
       <c r="M33" s="4"/>
     </row>
-    <row r="34" spans="1:13" ht="22.2" customHeight="1">
+    <row r="34" spans="1:13">
       <c r="A34" s="30" t="s">
         <v>33</v>
       </c>
@@ -10953,7 +10960,7 @@
       <c r="L34" s="4"/>
       <c r="M34" s="4"/>
     </row>
-    <row r="35" spans="1:13" ht="22.2" customHeight="1">
+    <row r="35" spans="1:13">
       <c r="A35" s="25" t="s">
         <v>35</v>
       </c>
@@ -10985,7 +10992,7 @@
         <v>8.2655999999999993E-2</v>
       </c>
     </row>
-    <row r="36" spans="1:13" ht="22.2" customHeight="1">
+    <row r="36" spans="1:13">
       <c r="A36" s="25" t="s">
         <v>36</v>
       </c>
@@ -11017,7 +11024,7 @@
         <v>5.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="37" spans="1:13" ht="22.2" customHeight="1">
+    <row r="37" spans="1:13">
       <c r="A37" s="25" t="s">
         <v>38</v>
       </c>
@@ -11049,7 +11056,7 @@
         <v>2.7047999999999999E-2</v>
       </c>
     </row>
-    <row r="38" spans="1:13" ht="22.2" customHeight="1">
+    <row r="38" spans="1:13">
       <c r="A38" s="25" t="s">
         <v>39</v>
       </c>
@@ -11081,7 +11088,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="39" spans="1:13" ht="22.2" customHeight="1">
+    <row r="39" spans="1:13">
       <c r="A39" s="25" t="s">
         <v>41</v>
       </c>
@@ -11113,7 +11120,7 @@
         <v>3.6801E-2</v>
       </c>
     </row>
-    <row r="40" spans="1:13" ht="22.2" customHeight="1">
+    <row r="40" spans="1:13">
       <c r="A40" s="25" t="s">
         <v>42</v>
       </c>
@@ -11145,7 +11152,7 @@
         <v>9.4207075000000001E-2</v>
       </c>
     </row>
-    <row r="41" spans="1:13" ht="22.2" customHeight="1">
+    <row r="41" spans="1:13">
       <c r="A41" s="25" t="s">
         <v>43</v>
       </c>
@@ -11177,17 +11184,17 @@
         <v>0.104</v>
       </c>
     </row>
-    <row r="42" spans="1:13" ht="16.2" customHeight="1">
+    <row r="42" spans="1:13">
       <c r="D42"/>
     </row>
-    <row r="43" spans="1:13" ht="16.2" customHeight="1">
+    <row r="43" spans="1:13" ht="23">
       <c r="A43" s="11" t="s">
         <v>62</v>
       </c>
       <c r="B43" s="11"/>
       <c r="D43"/>
     </row>
-    <row r="44" spans="1:13" ht="16.2" customHeight="1">
+    <row r="44" spans="1:13">
       <c r="A44" s="1" t="s">
         <v>0</v>
       </c>
@@ -11217,7 +11224,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="45" spans="1:13" ht="16.2" customHeight="1">
+    <row r="45" spans="1:13">
       <c r="A45" s="30" t="s">
         <v>48</v>
       </c>
@@ -11244,7 +11251,7 @@
       </c>
       <c r="K45" s="4"/>
     </row>
-    <row r="46" spans="1:13" ht="16.2" customHeight="1">
+    <row r="46" spans="1:13">
       <c r="A46" s="30" t="s">
         <v>49</v>
       </c>
@@ -11275,7 +11282,7 @@
       </c>
       <c r="K46" s="4"/>
     </row>
-    <row r="47" spans="1:13" ht="16.2" customHeight="1">
+    <row r="47" spans="1:13">
       <c r="A47" s="30" t="s">
         <v>50</v>
       </c>
@@ -11306,7 +11313,7 @@
       </c>
       <c r="K47" s="4"/>
     </row>
-    <row r="48" spans="1:13" ht="16.2" customHeight="1">
+    <row r="48" spans="1:13" ht="29">
       <c r="A48" s="30" t="s">
         <v>82</v>
       </c>
@@ -11335,7 +11342,7 @@
       </c>
       <c r="K48" s="4"/>
     </row>
-    <row r="49" spans="1:11" ht="16.2" customHeight="1">
+    <row r="49" spans="1:11">
       <c r="A49" s="30" t="s">
         <v>51</v>
       </c>
@@ -11367,7 +11374,7 @@
       </c>
       <c r="K49" s="4"/>
     </row>
-    <row r="50" spans="1:11" ht="16.2" customHeight="1">
+    <row r="50" spans="1:11">
       <c r="A50" s="30" t="s">
         <v>131</v>
       </c>
@@ -11399,7 +11406,7 @@
       </c>
       <c r="K50" s="4"/>
     </row>
-    <row r="51" spans="1:11" ht="16.2" customHeight="1">
+    <row r="51" spans="1:11">
       <c r="A51" s="30" t="s">
         <v>52</v>
       </c>
@@ -11431,7 +11438,7 @@
       </c>
       <c r="K51" s="4"/>
     </row>
-    <row r="52" spans="1:11" ht="16.2" customHeight="1">
+    <row r="52" spans="1:11">
       <c r="A52" s="30" t="s">
         <v>53</v>
       </c>
@@ -11465,7 +11472,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="53" spans="1:11" ht="16.2" customHeight="1">
+    <row r="53" spans="1:11">
       <c r="A53" s="30" t="s">
         <v>54</v>
       </c>
@@ -11497,7 +11504,7 @@
       </c>
       <c r="K53" s="4"/>
     </row>
-    <row r="54" spans="1:11" ht="16.2" customHeight="1">
+    <row r="54" spans="1:11">
       <c r="A54" s="30" t="s">
         <v>55</v>
       </c>
@@ -11528,7 +11535,7 @@
       </c>
       <c r="K54" s="4"/>
     </row>
-    <row r="55" spans="1:11" ht="16.2" customHeight="1">
+    <row r="55" spans="1:11">
       <c r="A55" s="30" t="s">
         <v>56</v>
       </c>
@@ -11559,7 +11566,7 @@
       </c>
       <c r="K55" s="4"/>
     </row>
-    <row r="56" spans="1:11" ht="16.2" customHeight="1">
+    <row r="56" spans="1:11" ht="29">
       <c r="A56" s="30" t="s">
         <v>81</v>
       </c>
@@ -11588,7 +11595,7 @@
       </c>
       <c r="K56" s="4"/>
     </row>
-    <row r="57" spans="1:11" ht="16.2" customHeight="1">
+    <row r="57" spans="1:11">
       <c r="A57" s="30" t="s">
         <v>57</v>
       </c>
@@ -11619,7 +11626,7 @@
       </c>
       <c r="K57" s="4"/>
     </row>
-    <row r="58" spans="1:11" ht="16.2" customHeight="1">
+    <row r="58" spans="1:11">
       <c r="A58" s="30" t="s">
         <v>58</v>
       </c>
@@ -11650,7 +11657,7 @@
       </c>
       <c r="K58" s="4"/>
     </row>
-    <row r="59" spans="1:11" ht="16.2" customHeight="1">
+    <row r="59" spans="1:11">
       <c r="A59" s="30" t="s">
         <v>60</v>
       </c>
@@ -11682,7 +11689,7 @@
       </c>
       <c r="K59" s="4"/>
     </row>
-    <row r="60" spans="1:11" ht="16.2" customHeight="1">
+    <row r="60" spans="1:11">
       <c r="A60" s="30" t="s">
         <v>59</v>
       </c>
@@ -11714,7 +11721,7 @@
       </c>
       <c r="K60" s="4"/>
     </row>
-    <row r="61" spans="1:11" ht="16.2" customHeight="1">
+    <row r="61" spans="1:11">
       <c r="A61" s="30" t="s">
         <v>61</v>
       </c>
@@ -11749,7 +11756,7 @@
       </c>
       <c r="K61" s="4"/>
     </row>
-    <row r="62" spans="1:11" ht="16.2" customHeight="1">
+    <row r="62" spans="1:11">
       <c r="E62" s="2"/>
       <c r="F62" s="2"/>
       <c r="G62" s="2"/>
@@ -11757,7 +11764,7 @@
       <c r="I62" s="2"/>
       <c r="J62" s="7"/>
     </row>
-    <row r="63" spans="1:11" ht="16.2" customHeight="1">
+    <row r="63" spans="1:11">
       <c r="E63" s="2"/>
       <c r="F63" s="2"/>
       <c r="G63" s="2"/>
@@ -11765,13 +11772,13 @@
       <c r="I63" s="2"/>
       <c r="J63" s="7"/>
     </row>
-    <row r="64" spans="1:11" ht="16.2" customHeight="1">
+    <row r="64" spans="1:11" ht="23.5">
       <c r="A64" s="10" t="s">
         <v>73</v>
       </c>
       <c r="B64" s="10"/>
     </row>
-    <row r="65" spans="1:10" ht="16.2" customHeight="1">
+    <row r="65" spans="1:10">
       <c r="A65" s="12" t="s">
         <v>0</v>
       </c>
@@ -11801,12 +11808,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="66" spans="1:10" ht="16.2" customHeight="1">
+    <row r="66" spans="1:10" ht="15.5">
       <c r="A66" s="48" t="s">
         <v>155</v>
       </c>
       <c r="B66" s="19"/>
-      <c r="C66" s="48" t="s">
+      <c r="C66" s="65" t="s">
         <v>156</v>
       </c>
       <c r="D66" s="20" t="s">
@@ -11831,12 +11838,12 @@
         <v>0.14799999999999999</v>
       </c>
     </row>
-    <row r="67" spans="1:10" ht="16.2" customHeight="1">
+    <row r="67" spans="1:10" ht="15.5">
       <c r="A67" s="48" t="s">
         <v>157</v>
       </c>
       <c r="B67" s="19"/>
-      <c r="C67" s="48" t="s">
+      <c r="C67" s="65" t="s">
         <v>156</v>
       </c>
       <c r="D67" s="20" t="s">
@@ -11848,25 +11855,25 @@
       <c r="F67" s="19">
         <v>24</v>
       </c>
-      <c r="G67" s="62">
+      <c r="G67" s="58">
         <v>58</v>
       </c>
-      <c r="H67" s="62">
+      <c r="H67" s="58">
         <v>43.5</v>
       </c>
-      <c r="I67" s="62">
+      <c r="I67" s="58">
         <v>58.5</v>
       </c>
-      <c r="J67" s="63">
+      <c r="J67" s="59">
         <v>0.14799999999999999</v>
       </c>
     </row>
-    <row r="68" spans="1:10" ht="16.2" customHeight="1">
+    <row r="68" spans="1:10" ht="15.5">
       <c r="A68" s="48" t="s">
         <v>158</v>
       </c>
       <c r="B68" s="19"/>
-      <c r="C68" s="48" t="s">
+      <c r="C68" s="65" t="s">
         <v>159</v>
       </c>
       <c r="D68" s="20" t="s">
@@ -11878,41 +11885,41 @@
       <c r="F68" s="19">
         <v>8.8000000000000007</v>
       </c>
-      <c r="G68" s="64">
+      <c r="G68" s="61">
         <v>31</v>
       </c>
-      <c r="H68" s="64">
+      <c r="H68" s="61">
         <v>39</v>
       </c>
-      <c r="I68" s="64">
+      <c r="I68" s="61">
         <v>42.5</v>
       </c>
-      <c r="J68" s="65">
+      <c r="J68" s="62">
         <v>5.5E-2</v>
       </c>
     </row>
-    <row r="69" spans="1:10" ht="16.2" customHeight="1">
+    <row r="69" spans="1:10" ht="16">
       <c r="A69" s="48" t="s">
         <v>150</v>
       </c>
       <c r="B69" s="50"/>
-      <c r="C69" s="48" t="s">
+      <c r="C69" s="65" t="s">
         <v>151</v>
       </c>
       <c r="D69" s="20"/>
       <c r="E69" s="19"/>
       <c r="F69" s="19"/>
-      <c r="G69" s="66"/>
-      <c r="H69" s="66"/>
-      <c r="I69" s="66"/>
-      <c r="J69" s="67"/>
+      <c r="G69" s="61"/>
+      <c r="H69" s="61"/>
+      <c r="I69" s="61"/>
+      <c r="J69" s="63"/>
     </row>
-    <row r="70" spans="1:10" ht="16.2" customHeight="1">
+    <row r="70" spans="1:10">
       <c r="A70" s="48" t="s">
         <v>152</v>
       </c>
       <c r="B70" s="50"/>
-      <c r="C70" s="48" t="s">
+      <c r="C70" s="65" t="s">
         <v>151</v>
       </c>
       <c r="D70" s="20"/>
@@ -11923,12 +11930,12 @@
       <c r="I70" s="19"/>
       <c r="J70" s="21"/>
     </row>
-    <row r="71" spans="1:10" ht="16.2" customHeight="1">
+    <row r="71" spans="1:10">
       <c r="A71" s="48" t="s">
         <v>147</v>
       </c>
       <c r="B71" s="49"/>
-      <c r="C71" s="60" t="s">
+      <c r="C71" s="66" t="s">
         <v>148</v>
       </c>
       <c r="D71" s="20" t="s">
@@ -11945,12 +11952,12 @@
       <c r="I71" s="19"/>
       <c r="J71" s="21"/>
     </row>
-    <row r="72" spans="1:10" ht="16.2" customHeight="1">
+    <row r="72" spans="1:10">
       <c r="A72" s="48" t="s">
         <v>149</v>
       </c>
       <c r="B72" s="49"/>
-      <c r="C72" s="60" t="s">
+      <c r="C72" s="66" t="s">
         <v>148</v>
       </c>
       <c r="D72" s="20"/>
@@ -11961,12 +11968,12 @@
       <c r="I72" s="19"/>
       <c r="J72" s="21"/>
     </row>
-    <row r="73" spans="1:10" ht="16.2" customHeight="1">
+    <row r="73" spans="1:10">
       <c r="A73" s="50" t="s">
         <v>153</v>
       </c>
       <c r="B73" s="19"/>
-      <c r="C73" s="48" t="s">
+      <c r="C73" s="65" t="s">
         <v>154</v>
       </c>
       <c r="D73" s="20" t="s">
@@ -11991,12 +11998,12 @@
         <v>2.816625E-2</v>
       </c>
     </row>
-    <row r="74" spans="1:10" ht="16.2" customHeight="1">
+    <row r="74" spans="1:10">
       <c r="A74" s="48" t="s">
         <v>143</v>
       </c>
       <c r="B74" s="48"/>
-      <c r="C74" s="48" t="s">
+      <c r="C74" s="65" t="s">
         <v>144</v>
       </c>
       <c r="D74" s="20" t="s">
@@ -12013,12 +12020,12 @@
       <c r="I74" s="19"/>
       <c r="J74" s="21"/>
     </row>
-    <row r="75" spans="1:10" ht="16.2" customHeight="1">
+    <row r="75" spans="1:10" ht="15.5">
       <c r="A75" s="48" t="s">
         <v>145</v>
       </c>
       <c r="B75" s="48"/>
-      <c r="C75" s="48" t="s">
+      <c r="C75" s="65" t="s">
         <v>146</v>
       </c>
       <c r="D75" s="20" t="s">
@@ -12030,25 +12037,25 @@
       <c r="F75" s="19">
         <v>16.600000000000001</v>
       </c>
-      <c r="G75" s="70">
+      <c r="G75" s="61">
         <v>40.5</v>
       </c>
-      <c r="H75" s="70">
+      <c r="H75" s="61">
         <v>33.5</v>
       </c>
-      <c r="I75" s="70">
+      <c r="I75" s="61">
         <v>30</v>
       </c>
-      <c r="J75" s="71">
+      <c r="J75" s="64">
         <v>0.41</v>
       </c>
     </row>
-    <row r="76" spans="1:10" ht="16.2" customHeight="1">
+    <row r="76" spans="1:10" ht="29">
       <c r="A76" s="30" t="s">
         <v>142</v>
       </c>
       <c r="B76" s="30"/>
-      <c r="C76" s="47" t="s">
+      <c r="C76" s="29" t="s">
         <v>141</v>
       </c>
       <c r="D76" s="20" t="s">
@@ -12060,30 +12067,30 @@
       <c r="F76" s="19">
         <v>27</v>
       </c>
-      <c r="G76" s="68">
+      <c r="G76" s="61">
         <v>80</v>
       </c>
-      <c r="H76" s="68">
+      <c r="H76" s="61">
         <v>31.5</v>
       </c>
-      <c r="I76" s="68">
+      <c r="I76" s="61">
         <v>53.5</v>
       </c>
-      <c r="J76" s="69">
+      <c r="J76" s="62">
         <v>0.13500000000000001</v>
       </c>
     </row>
-    <row r="77" spans="1:10" ht="16.2" customHeight="1">
+    <row r="77" spans="1:10">
       <c r="A77" s="4"/>
       <c r="B77" s="4"/>
     </row>
-    <row r="78" spans="1:10" ht="16.2" customHeight="1">
+    <row r="78" spans="1:10" ht="23.5">
       <c r="A78" s="10" t="s">
         <v>78</v>
       </c>
       <c r="B78" s="10"/>
     </row>
-    <row r="79" spans="1:10" ht="16.2" customHeight="1">
+    <row r="79" spans="1:10">
       <c r="A79" s="12" t="s">
         <v>0</v>
       </c>
@@ -12113,7 +12120,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="80" spans="1:10" s="5" customFormat="1" ht="16.2" customHeight="1">
+    <row r="80" spans="1:10" s="5" customFormat="1" ht="43.5">
       <c r="A80" s="51" t="s">
         <v>165</v>
       </c>
@@ -12143,7 +12150,7 @@
         <v>2.7E-2</v>
       </c>
     </row>
-    <row r="81" spans="1:10" s="5" customFormat="1" ht="16.2" customHeight="1">
+    <row r="81" spans="1:10" s="5" customFormat="1">
       <c r="A81" s="30" t="s">
         <v>166</v>
       </c>
@@ -12173,7 +12180,7 @@
         <v>3.6999999999999998E-2</v>
       </c>
     </row>
-    <row r="82" spans="1:10" s="5" customFormat="1" ht="16.2" customHeight="1">
+    <row r="82" spans="1:10" s="5" customFormat="1">
       <c r="A82" s="30" t="s">
         <v>75</v>
       </c>
@@ -12203,7 +12210,7 @@
         <v>2.6244E-2</v>
       </c>
     </row>
-    <row r="83" spans="1:10" s="5" customFormat="1" ht="16.2" customHeight="1">
+    <row r="83" spans="1:10" s="5" customFormat="1">
       <c r="A83" s="30" t="s">
         <v>76</v>
       </c>
@@ -12233,7 +12240,7 @@
         <v>3.6999999999999998E-2</v>
       </c>
     </row>
-    <row r="84" spans="1:10" s="5" customFormat="1" ht="16.2" customHeight="1">
+    <row r="84" spans="1:10" s="5" customFormat="1" ht="43.5">
       <c r="A84" s="30" t="s">
         <v>39</v>
       </c>
@@ -12263,13 +12270,13 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="85" spans="1:10" s="5" customFormat="1" ht="16.2" customHeight="1">
+    <row r="85" spans="1:10" s="5" customFormat="1" ht="29">
       <c r="A85" s="52" t="s">
         <v>162</v>
       </c>
       <c r="B85" s="30"/>
       <c r="C85" s="29" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="D85" s="25" t="s">
         <v>70</v>
@@ -12293,7 +12300,7 @@
         <v>1.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="86" spans="1:10" s="5" customFormat="1" ht="16.2" customHeight="1">
+    <row r="86" spans="1:10" s="5" customFormat="1">
       <c r="A86" s="52" t="s">
         <v>163</v>
       </c>
@@ -12319,9 +12326,9 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Case Size.xlsx
+++ b/Case Size.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maa00\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DBA2D4D-71C3-4711-A3B4-48ADEF69E0A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4487DCBF-FD93-41C8-8682-90771EABB61B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="170">
   <si>
     <t>Category</t>
   </si>
@@ -422,201 +422,209 @@
     </r>
   </si>
   <si>
+    <t>100 GMS</t>
+  </si>
+  <si>
+    <t>48 pack contaning 10 pcs of Cup Dhoop each</t>
+  </si>
+  <si>
+    <t>100 ML Bottle, 72 Bottles in Master Carton</t>
+  </si>
+  <si>
+    <t>1 pack Contain - 10 pcs of Tea light Candles, 12 pcs packed in 1 Outer Carton, 6 Outer Cartons in 1 Master Carton</t>
+  </si>
+  <si>
+    <t>90 gm scented tin smudge candle, wrapped with label sticker. Such 72 pcs packed inside master carton.</t>
+  </si>
+  <si>
+    <t>8 Sticks in a packet,25 packet in a box</t>
+  </si>
+  <si>
+    <t>100 GMS in a packet, 6 packets in a box</t>
+  </si>
+  <si>
+    <t>7 CHAKRA HEXA GIFT PACK</t>
+  </si>
+  <si>
+    <t>7 Packet in an outer packet</t>
+  </si>
+  <si>
+    <t>48 pcs</t>
+  </si>
+  <si>
+    <t>WHITE SAGE CLEANSING COLLECTION GIFT PACK</t>
+  </si>
+  <si>
+    <t>48 sets</t>
+  </si>
+  <si>
+    <t>6 assorated packets in one gift box, such 48 boxes packed inside master carton.</t>
+  </si>
+  <si>
+    <t>YOG CHAKRA GIFT PACK</t>
+  </si>
+  <si>
+    <t>4 Disc in one pack- 2 doz in one inner corrogated box</t>
+  </si>
+  <si>
+    <t>4 Balls in one pack - 2 doz in one inner corrogated box</t>
+  </si>
+  <si>
+    <t>6 Pouches in one pack. 10  sticks in one pouch</t>
+  </si>
+  <si>
+    <t>Paper hexa shape 50grams in a golden pouch with wooden spoon. 12 Hexa Qatari Incense Powder in one Display Box</t>
+  </si>
+  <si>
+    <t>15 gms in one pack, 6 Fragrances  x 2 in one dispenser outer</t>
+  </si>
+  <si>
+    <t>Manifestation candle 125 grms</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Glass Jar 125 grams Candle </t>
+  </si>
+  <si>
+    <t>10 Sticks in one pack with Crystal and Cards with Affirmation. 1 doz in one Outer</t>
+  </si>
+  <si>
+    <t>15 Grams in a packet,  12 Packs (1 dozen) in a box, 288 Packs (24 dozen) in a master carton</t>
+  </si>
+  <si>
+    <t>Planned to be discontinued</t>
+  </si>
+  <si>
+    <t>ENERGY CLEANSING KIT-  1) Palo Santo Room Spray. - 100ml , 2) Sacred Element - Organic Cones -5- 6 pcs 3) 3) Organic Resins -  10- 15 gsm 4) Organic Herbs -  25-30 gms. 5) Coal Tables for burning - 1 set 6. Terra clay</t>
+  </si>
+  <si>
+    <t>Product - 10 Sticks in a pack, and 12 pack in one dispenser</t>
+  </si>
+  <si>
+    <t>Product - 8 Sticks in a pack, and 12 pack in one dispenser</t>
+  </si>
+  <si>
+    <t>3 sticks in a pack, 6 PACK in one dispenser</t>
+  </si>
+  <si>
+    <t>5 cones in a pack.. 12 pack in one dispenser</t>
+  </si>
+  <si>
+    <t>White Abhir, Gulal, Kumkum, Haldi, Camphor Tablets, Moli, Pooja Supari, Akhata, Agarbatti, Agarbatti Wooden Stand, Janvi Jod, Goddess Photo, Vastra (Pooja Cloth) &amp; Dhoop.</t>
+  </si>
+  <si>
+    <t>Pooja Samagri Kit</t>
+  </si>
+  <si>
+    <t>Aradhana Pooja Oil Pack 900ml</t>
+  </si>
+  <si>
+    <t>1 Bottle x 900 ml, 20Pcs in 1 master carton</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aradhana Pooja Oil Pack 450Ml </t>
+  </si>
+  <si>
+    <t>1 Bottle x 450 ml, 40Pcs in 1 master carton</t>
+  </si>
+  <si>
+    <t>HEM Aradhana Camphor - 100g</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Camphor - 100g</t>
+  </si>
+  <si>
+    <t>HEM Aradhana Bhimseni Camphor</t>
+  </si>
+  <si>
+    <t>HEM Aradhana Pure Cow Ghee Diya 100 pcs</t>
+  </si>
+  <si>
+    <t>100 pcs Diya in a box, 4 doz in 1 Master Carton</t>
+  </si>
+  <si>
+    <t>HEM Aradhana Pure Ghee Diya 100 pcs</t>
+  </si>
+  <si>
+    <t>HEM Aradhana Gangajal</t>
+  </si>
+  <si>
+    <t>Gangajal, 24 pc in box</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Soham Sambrani Cup Dhoop </t>
+  </si>
+  <si>
+    <t>12 pcs in 1 box, 12 dozen in 1 Master Carton</t>
+  </si>
+  <si>
+    <t>Pama Sambrani Cup Dhoop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Madhur Guggal Cup Dhhop </t>
+  </si>
+  <si>
+    <t>12 pcs in 1 box, 4 dozen in 1 Master Carton</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spell Candle pack of 20 N </t>
+  </si>
+  <si>
+    <t>Votive Shot Glass Candles 40G</t>
+  </si>
+  <si>
+    <t>1 Candle = 40 gms,     48 Pcs (4 Dozen in 1 master carton)</t>
+  </si>
+  <si>
+    <t>7 Chakra  Tea Light Fragrance  Candle</t>
+  </si>
+  <si>
+    <t>GLASS JAR  CANDLE 185 GMS</t>
+  </si>
+  <si>
+    <t>125 gms Scented Candle</t>
+  </si>
+  <si>
+    <t>6 hexa pack in packet</t>
+  </si>
+  <si>
+    <t>7 Diffrenet types of Stones in one pack.,12 packs in 1 Outer Carton,6 Outer Cartons in one Master Carton</t>
+  </si>
+  <si>
+    <t>20 Sticks in a packet, 6 packet in a box, 2 boxes make 1 Dozen, 25 dozen in 1 master carton</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100 gm in a packet, 12 packet in 1 dozen,,,24 dozen in 1 master carton </t>
+  </si>
+  <si>
+    <t>25 gm in a packet, 12 packets in 1 dozen,24 dozen in master carton</t>
+  </si>
+  <si>
+    <t>20 Sticks in a packet, 6 packet in a box,2 boxes make 1 Dozen, 25 dozen in 1 master carton</t>
+  </si>
+  <si>
+    <t>12 pcs packed inside the display box.,8 display box packed inside master carton</t>
+  </si>
+  <si>
+    <t>Gift Pack Contain single pc of Yog Chakra 100ml room freshener, 15gm Masala incense stick,Yog Chakra cone &amp;Wooden incense holder</t>
+  </si>
+  <si>
+    <t>1 pack Contain -7 pcs of Tea light Candles.,12 pcs packed in 1 Outer Carton.,6 Outer Cartons in 1 Master Carton</t>
+  </si>
+  <si>
+    <t>1 pack Contain - 10 pcs of Tea light Candles.,12 pcs packed in 1 Outer Carton.,6 Outer Cartons in 1 Master Carton</t>
+  </si>
+  <si>
+    <t>20 candles unsencted ,Extended Burn Time: Each 4-inch tall unscented candle burns continuously for up to 2 hours.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>DHOOP</t>
+  </si>
+  <si>
     <r>
-      <t>DHOOP</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF3D2020"/>
-        <rFont val="Aptos Display"/>
-        <scheme val="major"/>
-      </rPr>
-      <t>    25 GMS</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>DHOOP</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF3D2020"/>
-        <rFont val="Aptos Display"/>
-        <scheme val="major"/>
-      </rPr>
-      <t>   60 GRMS</t>
-    </r>
-  </si>
-  <si>
-    <t>25 GMS in a packet,12 packet in a box</t>
-  </si>
-  <si>
-    <t>100 GMS</t>
-  </si>
-  <si>
-    <t>48 pack contaning 10 pcs of Cup Dhoop each</t>
-  </si>
-  <si>
-    <t>100 ML Bottle, 72 Bottles in Master Carton</t>
-  </si>
-  <si>
-    <t>1 pack Contain - 10 pcs of Tea light Candles, 12 pcs packed in 1 Outer Carton, 6 Outer Cartons in 1 Master Carton</t>
-  </si>
-  <si>
-    <t>90 gm scented tin smudge candle, wrapped with label sticker. Such 72 pcs packed inside master carton.</t>
-  </si>
-  <si>
-    <t>8 Sticks in a packet,25 packet in a box</t>
-  </si>
-  <si>
-    <t>100 GMS in a packet, 6 packets in a box</t>
-  </si>
-  <si>
-    <t>7 CHAKRA HEXA GIFT PACK</t>
-  </si>
-  <si>
-    <t>7 Packet in an outer packet</t>
-  </si>
-  <si>
-    <t>48 pcs</t>
-  </si>
-  <si>
-    <t>WHITE SAGE CLEANSING COLLECTION GIFT PACK</t>
-  </si>
-  <si>
-    <t>48 sets</t>
-  </si>
-  <si>
-    <t>6 assorated packets in one gift box, such 48 boxes packed inside master carton.</t>
-  </si>
-  <si>
-    <t>YOG CHAKRA GIFT PACK</t>
-  </si>
-  <si>
-    <t>4 Disc in one pack- 2 doz in one inner corrogated box</t>
-  </si>
-  <si>
-    <t>4 Balls in one pack - 2 doz in one inner corrogated box</t>
-  </si>
-  <si>
-    <t>6 Pouches in one pack. 10  sticks in one pouch</t>
-  </si>
-  <si>
-    <t>Paper hexa shape 50grams in a golden pouch with wooden spoon. 12 Hexa Qatari Incense Powder in one Display Box</t>
-  </si>
-  <si>
-    <t>15 gms in one pack, 6 Fragrances  x 2 in one dispenser outer</t>
-  </si>
-  <si>
-    <t>Manifestation candle 125 grms</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Glass Jar 125 grams Candle </t>
-  </si>
-  <si>
-    <t>10 Sticks in one pack with Crystal and Cards with Affirmation. 1 doz in one Outer</t>
-  </si>
-  <si>
-    <t>15 Grams in a packet,  12 Packs (1 dozen) in a box, 288 Packs (24 dozen) in a master carton</t>
-  </si>
-  <si>
-    <t>Planned to be discontinued</t>
-  </si>
-  <si>
-    <t>ENERGY CLEANSING KIT-  1) Palo Santo Room Spray. - 100ml , 2) Sacred Element - Organic Cones -5- 6 pcs 3) 3) Organic Resins -  10- 15 gsm 4) Organic Herbs -  25-30 gms. 5) Coal Tables for burning - 1 set 6. Terra clay</t>
-  </si>
-  <si>
-    <t>Product - 10 Sticks in a pack, and 12 pack in one dispenser</t>
-  </si>
-  <si>
-    <t>Product - 8 Sticks in a pack, and 12 pack in one dispenser</t>
-  </si>
-  <si>
-    <t>3 sticks in a pack, 6 PACK in one dispenser</t>
-  </si>
-  <si>
-    <t>5 cones in a pack.. 12 pack in one dispenser</t>
-  </si>
-  <si>
-    <t>White Abhir, Gulal, Kumkum, Haldi, Camphor Tablets, Moli, Pooja Supari, Akhata, Agarbatti, Agarbatti Wooden Stand, Janvi Jod, Goddess Photo, Vastra (Pooja Cloth) &amp; Dhoop.</t>
-  </si>
-  <si>
-    <t>Pooja Samagri Kit</t>
-  </si>
-  <si>
-    <t>Aradhana Pooja Oil Pack 900ml</t>
-  </si>
-  <si>
-    <t>1 Bottle x 900 ml, 20Pcs in 1 master carton</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aradhana Pooja Oil Pack 450Ml </t>
-  </si>
-  <si>
-    <t>1 Bottle x 450 ml, 40Pcs in 1 master carton</t>
-  </si>
-  <si>
-    <t>HEM Aradhana Camphor - 100g</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Camphor - 100g</t>
-  </si>
-  <si>
-    <t>HEM Aradhana Bhimseni Camphor</t>
-  </si>
-  <si>
-    <t>HEM Aradhana Pure Cow Ghee Diya 100 pcs</t>
-  </si>
-  <si>
-    <t>100 pcs Diya in a box, 4 doz in 1 Master Carton</t>
-  </si>
-  <si>
-    <t>HEM Aradhana Pure Ghee Diya 100 pcs</t>
-  </si>
-  <si>
-    <t>HEM Aradhana Gangajal</t>
-  </si>
-  <si>
-    <t>Gangajal, 24 pc in box</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Soham Sambrani Cup Dhoop </t>
-  </si>
-  <si>
-    <t>12 pcs in 1 box, 12 dozen in 1 Master Carton</t>
-  </si>
-  <si>
-    <t>Pama Sambrani Cup Dhoop</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Madhur Guggal Cup Dhhop </t>
-  </si>
-  <si>
-    <t>12 pcs in 1 box, 4 dozen in 1 Master Carton</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spell Candle pack of 20 N </t>
-  </si>
-  <si>
-    <t>Votive Shot Glass Candles 40G</t>
-  </si>
-  <si>
-    <t>1 Candle = 40 gms,     48 Pcs (4 Dozen in 1 master carton)</t>
-  </si>
-  <si>
-    <t>7 Chakra  Tea Light Fragrance  Candle</t>
-  </si>
-  <si>
-    <t>GLASS JAR  CANDLE 185 GMS</t>
-  </si>
-  <si>
-    <t>125 gms Scented Candle</t>
-  </si>
-  <si>
-    <r>
-      <t>Regular CONE</t>
+      <t>CONE</t>
     </r>
     <r>
       <rPr>
@@ -627,39 +635,6 @@
       </rPr>
       <t> </t>
     </r>
-  </si>
-  <si>
-    <t>6 hexa pack in packet</t>
-  </si>
-  <si>
-    <t>7 Diffrenet types of Stones in one pack.,12 packs in 1 Outer Carton,6 Outer Cartons in one Master Carton</t>
-  </si>
-  <si>
-    <t>20 Sticks in a packet, 6 packet in a box, 2 boxes make 1 Dozen, 25 dozen in 1 master carton</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100 gm in a packet, 12 packet in 1 dozen,,,24 dozen in 1 master carton </t>
-  </si>
-  <si>
-    <t>25 gm in a packet, 12 packets in 1 dozen,24 dozen in master carton</t>
-  </si>
-  <si>
-    <t>20 Sticks in a packet, 6 packet in a box,2 boxes make 1 Dozen, 25 dozen in 1 master carton</t>
-  </si>
-  <si>
-    <t>12 pcs packed inside the display box.,8 display box packed inside master carton</t>
-  </si>
-  <si>
-    <t>Gift Pack Contain single pc of Yog Chakra 100ml room freshener, 15gm Masala incense stick,Yog Chakra cone &amp;Wooden incense holder</t>
-  </si>
-  <si>
-    <t>1 pack Contain -7 pcs of Tea light Candles.,12 pcs packed in 1 Outer Carton.,6 Outer Cartons in 1 Master Carton</t>
-  </si>
-  <si>
-    <t>1 pack Contain - 10 pcs of Tea light Candles.,12 pcs packed in 1 Outer Carton.,6 Outer Cartons in 1 Master Carton</t>
-  </si>
-  <si>
-    <t>20 candles unsencted ,Extended Burn Time: Each 4-inch tall unscented candle burns continuously for up to 2 hours.</t>
   </si>
 </sst>
 </file>
@@ -9738,7 +9713,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L87"/>
+  <dimension ref="A1:L86"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="69.1796875" style="4" customWidth="1"/>
@@ -9749,7 +9724,7 @@
     <col min="6" max="6" width="9.7265625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="10.6328125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="9.54296875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="5.7265625" style="5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="39.6328125" style="5" customWidth="1"/>
     <col min="10" max="10" width="19.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -9764,7 +9739,9 @@
       <c r="F1" s="9"/>
       <c r="G1" s="9"/>
       <c r="H1" s="9"/>
-      <c r="I1" s="11"/>
+      <c r="I1" s="11" t="s">
+        <v>167</v>
+      </c>
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="28" t="s">
@@ -9800,7 +9777,7 @@
         <v>45</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="C3" s="10" t="s">
         <v>18</v>
@@ -9829,7 +9806,7 @@
         <v>45</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="C4" s="10" t="s">
         <v>19</v>
@@ -9858,7 +9835,7 @@
         <v>45</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="C5" s="10" t="s">
         <v>11</v>
@@ -9887,7 +9864,7 @@
         <v>45</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="C6" s="10" t="s">
         <v>9</v>
@@ -10151,7 +10128,7 @@
         <v>17</v>
       </c>
       <c r="B15" s="17" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="C15" s="10" t="s">
         <v>18</v>
@@ -10180,7 +10157,7 @@
         <v>83</v>
       </c>
       <c r="B16" s="17" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="C16" s="10" t="s">
         <v>40</v>
@@ -10297,7 +10274,7 @@
         <v>80</v>
       </c>
       <c r="B20" s="18" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="C20" s="10" t="s">
         <v>22</v>
@@ -10354,7 +10331,7 @@
     </row>
     <row r="22" spans="1:12">
       <c r="A22" s="29" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="B22" s="18" t="s">
         <v>95</v>
@@ -10384,7 +10361,7 @@
     </row>
     <row r="23" spans="1:12">
       <c r="A23" s="30" t="s">
-        <v>103</v>
+        <v>168</v>
       </c>
       <c r="B23" s="24" t="s">
         <v>98</v>
@@ -10414,139 +10391,152 @@
     </row>
     <row r="24" spans="1:12">
       <c r="A24" s="30" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B24" s="24" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="C24" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="D24" s="10"/>
-      <c r="E24" s="10"/>
-      <c r="F24" s="10"/>
-      <c r="G24" s="10"/>
-      <c r="H24" s="10"/>
-      <c r="I24" s="16"/>
+        <v>25</v>
+      </c>
+      <c r="D24" s="10">
+        <v>27</v>
+      </c>
+      <c r="E24" s="10">
+        <v>25.3</v>
+      </c>
+      <c r="F24" s="10">
+        <v>61.5</v>
+      </c>
+      <c r="G24" s="10">
+        <v>46</v>
+      </c>
+      <c r="H24" s="10">
+        <v>35</v>
+      </c>
+      <c r="I24" s="16">
+        <v>9.9015000000000006E-2</v>
+      </c>
       <c r="J24" s="2"/>
     </row>
     <row r="25" spans="1:12">
-      <c r="A25" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="B25" s="24" t="s">
-        <v>99</v>
+      <c r="A25" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="B25" s="18" t="s">
+        <v>97</v>
       </c>
       <c r="C25" s="10" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="D25" s="10">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="E25" s="10">
-        <v>25.3</v>
+        <v>19</v>
       </c>
       <c r="F25" s="10">
-        <v>61.5</v>
+        <v>42.5</v>
       </c>
       <c r="G25" s="10">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="H25" s="10">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="I25" s="16">
-        <v>9.9015000000000006E-2</v>
+        <v>6.6640000000000005E-2</v>
       </c>
       <c r="J25" s="2"/>
     </row>
     <row r="26" spans="1:12">
       <c r="A26" s="15" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B26" s="18" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C26" s="10" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="D26" s="10">
-        <v>20</v>
+        <v>12.75</v>
       </c>
       <c r="E26" s="10">
-        <v>19</v>
+        <v>11.2</v>
       </c>
       <c r="F26" s="10">
-        <v>42.5</v>
+        <v>37.5</v>
       </c>
       <c r="G26" s="10">
-        <v>32</v>
+        <v>28.2</v>
       </c>
       <c r="H26" s="10">
-        <v>49</v>
+        <v>34.799999999999997</v>
       </c>
       <c r="I26" s="16">
-        <v>6.6640000000000005E-2</v>
+        <v>3.6801E-2</v>
       </c>
       <c r="J26" s="2"/>
     </row>
-    <row r="27" spans="1:12">
+    <row r="27" spans="1:12" ht="15" thickBot="1">
       <c r="A27" s="15" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B27" s="18" t="s">
-        <v>100</v>
+        <v>156</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="D27" s="10">
-        <v>12.75</v>
+        <v>13.8</v>
       </c>
       <c r="E27" s="10">
-        <v>11.2</v>
+        <v>12.8</v>
       </c>
       <c r="F27" s="10">
-        <v>37.5</v>
+        <v>58.5</v>
       </c>
       <c r="G27" s="10">
-        <v>28.2</v>
+        <v>31</v>
       </c>
       <c r="H27" s="10">
-        <v>34.799999999999997</v>
+        <v>51.2</v>
       </c>
       <c r="I27" s="16">
-        <v>3.6801E-2</v>
+        <v>9.2851200000000009E-2</v>
       </c>
       <c r="J27" s="2"/>
     </row>
     <row r="28" spans="1:12" ht="15" thickBot="1">
-      <c r="A28" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="B28" s="18" t="s">
-        <v>160</v>
+      <c r="A28" s="31" t="s">
+        <v>109</v>
+      </c>
+      <c r="B28" s="19" t="s">
+        <v>110</v>
       </c>
       <c r="C28" s="10" t="s">
-        <v>15</v>
+        <v>111</v>
       </c>
       <c r="D28" s="10">
-        <v>13.8</v>
+        <v>16.3</v>
       </c>
       <c r="E28" s="10">
-        <v>12.8</v>
+        <v>15.1</v>
       </c>
       <c r="F28" s="10">
-        <v>58.5</v>
+        <v>42</v>
       </c>
       <c r="G28" s="10">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="H28" s="10">
-        <v>51.2</v>
+        <v>53</v>
       </c>
       <c r="I28" s="16">
-        <v>9.2851200000000009E-2</v>
+        <f t="shared" ref="I28" si="0">+F28*G28*H28/1000000</f>
+        <v>8.0135999999999999E-2</v>
       </c>
       <c r="J28" s="2"/>
     </row>
@@ -10554,386 +10544,367 @@
       <c r="A29" s="31" t="s">
         <v>112</v>
       </c>
-      <c r="B29" s="19" t="s">
+      <c r="B29" s="18" t="s">
+        <v>114</v>
+      </c>
+      <c r="C29" s="10" t="s">
         <v>113</v>
       </c>
-      <c r="C29" s="10" t="s">
-        <v>114</v>
-      </c>
       <c r="D29" s="10">
-        <v>16.3</v>
+        <v>15.3</v>
       </c>
       <c r="E29" s="10">
-        <v>15.1</v>
+        <v>14.3</v>
       </c>
       <c r="F29" s="10">
-        <v>42</v>
+        <v>42.5</v>
       </c>
       <c r="G29" s="10">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="H29" s="10">
-        <v>53</v>
+        <v>54.5</v>
       </c>
       <c r="I29" s="16">
-        <f t="shared" ref="I29" si="0">+F29*G29*H29/1000000</f>
-        <v>8.0135999999999999E-2</v>
+        <v>9.2766407999999995E-2</v>
       </c>
       <c r="J29" s="2"/>
     </row>
-    <row r="30" spans="1:12" ht="15" thickBot="1">
+    <row r="30" spans="1:12" ht="29.5" thickBot="1">
       <c r="A30" s="31" t="s">
         <v>115</v>
       </c>
-      <c r="B30" s="18" t="s">
-        <v>117</v>
+      <c r="B30" s="19" t="s">
+        <v>163</v>
       </c>
       <c r="C30" s="10" t="s">
-        <v>116</v>
+        <v>77</v>
       </c>
       <c r="D30" s="10">
-        <v>15.3</v>
+        <v>11.5</v>
       </c>
       <c r="E30" s="10">
-        <v>14.3</v>
+        <v>10.9</v>
       </c>
       <c r="F30" s="10">
-        <v>42.5</v>
+        <v>46</v>
       </c>
       <c r="G30" s="10">
-        <v>40</v>
+        <v>40.5</v>
       </c>
       <c r="H30" s="10">
-        <v>54.5</v>
+        <v>47</v>
       </c>
       <c r="I30" s="16">
-        <v>9.2766407999999995E-2</v>
+        <f>F30*G30*H30/1000000</f>
+        <v>8.7561E-2</v>
       </c>
       <c r="J30" s="2"/>
     </row>
-    <row r="31" spans="1:12" ht="29.5" thickBot="1">
-      <c r="A31" s="31" t="s">
-        <v>118</v>
-      </c>
-      <c r="B31" s="19" t="s">
-        <v>167</v>
+    <row r="31" spans="1:12">
+      <c r="A31" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="B31" s="18" t="s">
+        <v>95</v>
       </c>
       <c r="C31" s="10" t="s">
-        <v>77</v>
+        <v>11</v>
       </c>
       <c r="D31" s="10">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="E31" s="10">
-        <v>10.9</v>
+        <v>12.4</v>
       </c>
       <c r="F31" s="10">
-        <v>46</v>
+        <v>47.5</v>
       </c>
       <c r="G31" s="10">
-        <v>40.5</v>
+        <v>44.3</v>
       </c>
       <c r="H31" s="10">
-        <v>47</v>
+        <v>32.5</v>
       </c>
       <c r="I31" s="16">
-        <f>F31*G31*H31/1000000</f>
-        <v>8.7561E-2</v>
-      </c>
-      <c r="J31" s="2"/>
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="J31" s="3"/>
+      <c r="K31" s="3"/>
+      <c r="L31" s="3"/>
     </row>
     <row r="32" spans="1:12">
       <c r="A32" s="15" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B32" s="18" t="s">
-        <v>95</v>
+        <v>160</v>
       </c>
       <c r="C32" s="10" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="D32" s="10">
-        <v>13.5</v>
+        <v>15.3</v>
       </c>
       <c r="E32" s="10">
-        <v>12.4</v>
-      </c>
-      <c r="F32" s="10">
-        <v>47.5</v>
-      </c>
-      <c r="G32" s="10">
-        <v>44.3</v>
-      </c>
-      <c r="H32" s="10">
-        <v>32.5</v>
-      </c>
-      <c r="I32" s="16">
-        <v>7.0000000000000007E-2</v>
-      </c>
+        <v>13.95</v>
+      </c>
+      <c r="F32" s="10"/>
+      <c r="G32" s="10"/>
+      <c r="H32" s="10"/>
+      <c r="I32" s="16"/>
       <c r="J32" s="3"/>
       <c r="K32" s="3"/>
       <c r="L32" s="3"/>
     </row>
     <row r="33" spans="1:12">
       <c r="A33" s="15" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B33" s="18" t="s">
-        <v>164</v>
+        <v>102</v>
       </c>
       <c r="C33" s="10" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D33" s="10">
-        <v>15.3</v>
+        <v>11</v>
       </c>
       <c r="E33" s="10">
-        <v>13.95</v>
-      </c>
-      <c r="F33" s="10"/>
-      <c r="G33" s="10"/>
-      <c r="H33" s="10"/>
-      <c r="I33" s="16"/>
+        <v>10</v>
+      </c>
+      <c r="F33" s="10">
+        <v>41.5</v>
+      </c>
+      <c r="G33" s="10">
+        <v>27.5</v>
+      </c>
+      <c r="H33" s="10">
+        <v>21</v>
+      </c>
+      <c r="I33" s="16">
+        <v>2.3966250000000001E-2</v>
+      </c>
       <c r="J33" s="3"/>
       <c r="K33" s="3"/>
       <c r="L33" s="3"/>
     </row>
     <row r="34" spans="1:12">
       <c r="A34" s="15" t="s">
-        <v>33</v>
-      </c>
-      <c r="B34" s="18" t="s">
-        <v>105</v>
+        <v>35</v>
+      </c>
+      <c r="B34" s="17" t="s">
+        <v>94</v>
       </c>
       <c r="C34" s="10" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="D34" s="10">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E34" s="10">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F34" s="10">
-        <v>41.5</v>
+        <v>63</v>
       </c>
       <c r="G34" s="10">
-        <v>27.5</v>
+        <v>32</v>
       </c>
       <c r="H34" s="10">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="I34" s="16">
-        <v>2.3966250000000001E-2</v>
-      </c>
-      <c r="J34" s="3"/>
-      <c r="K34" s="3"/>
-      <c r="L34" s="3"/>
+        <v>8.2655999999999993E-2</v>
+      </c>
     </row>
     <row r="35" spans="1:12">
       <c r="A35" s="15" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B35" s="17" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="C35" s="10" t="s">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="D35" s="10">
-        <v>15</v>
+        <v>10.5</v>
       </c>
       <c r="E35" s="10">
-        <v>14</v>
+        <v>9.6999999999999993</v>
       </c>
       <c r="F35" s="10">
-        <v>63</v>
+        <v>37.5</v>
       </c>
       <c r="G35" s="10">
-        <v>32</v>
+        <v>30.5</v>
       </c>
       <c r="H35" s="10">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="I35" s="16">
-        <v>8.2655999999999993E-2</v>
+        <v>5.2999999999999999E-2</v>
       </c>
     </row>
     <row r="36" spans="1:12">
       <c r="A36" s="15" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B36" s="17" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C36" s="10" t="s">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="D36" s="10">
-        <v>10.5</v>
+        <v>10.72</v>
       </c>
       <c r="E36" s="10">
-        <v>9.6999999999999993</v>
+        <v>9.7200000000000006</v>
       </c>
       <c r="F36" s="10">
-        <v>37.5</v>
+        <v>28</v>
       </c>
       <c r="G36" s="10">
-        <v>30.5</v>
+        <v>28</v>
       </c>
       <c r="H36" s="10">
-        <v>46</v>
+        <v>34.5</v>
       </c>
       <c r="I36" s="16">
-        <v>5.2999999999999999E-2</v>
+        <v>2.7047999999999999E-2</v>
       </c>
     </row>
     <row r="37" spans="1:12">
       <c r="A37" s="15" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B37" s="17" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C37" s="10" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="D37" s="10">
-        <v>10.72</v>
+        <v>13</v>
       </c>
       <c r="E37" s="10">
-        <v>9.7200000000000006</v>
+        <v>11</v>
       </c>
       <c r="F37" s="10">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="G37" s="10">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="H37" s="10">
-        <v>34.5</v>
+        <v>39</v>
       </c>
       <c r="I37" s="16">
-        <v>2.7047999999999999E-2</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="38" spans="1:12">
       <c r="A38" s="15" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B38" s="17" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C38" s="10" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="D38" s="10">
-        <v>13</v>
+        <v>11.4</v>
       </c>
       <c r="E38" s="10">
         <v>11</v>
       </c>
       <c r="F38" s="10">
-        <v>35</v>
+        <v>37.5</v>
       </c>
       <c r="G38" s="10">
-        <v>22</v>
+        <v>28.2</v>
       </c>
       <c r="H38" s="10">
-        <v>39</v>
+        <v>34.799999999999997</v>
       </c>
       <c r="I38" s="16">
-        <v>0.03</v>
+        <v>3.6801E-2</v>
       </c>
     </row>
     <row r="39" spans="1:12">
       <c r="A39" s="15" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B39" s="17" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C39" s="10" t="s">
-        <v>18</v>
+        <v>44</v>
       </c>
       <c r="D39" s="10">
-        <v>11.4</v>
+        <v>23</v>
       </c>
       <c r="E39" s="10">
-        <v>11</v>
+        <v>21.5</v>
       </c>
       <c r="F39" s="10">
-        <v>37.5</v>
+        <v>41.5</v>
       </c>
       <c r="G39" s="10">
-        <v>28.2</v>
+        <v>41.5</v>
       </c>
       <c r="H39" s="10">
-        <v>34.799999999999997</v>
+        <v>54.7</v>
       </c>
       <c r="I39" s="16">
-        <v>3.6801E-2</v>
+        <v>9.4207075000000001E-2</v>
       </c>
     </row>
     <row r="40" spans="1:12">
       <c r="A40" s="15" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B40" s="17" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C40" s="10" t="s">
-        <v>44</v>
+        <v>19</v>
       </c>
       <c r="D40" s="10">
+        <v>24</v>
+      </c>
+      <c r="E40" s="10">
         <v>23</v>
       </c>
-      <c r="E40" s="10">
-        <v>21.5</v>
-      </c>
       <c r="F40" s="10">
-        <v>41.5</v>
+        <v>51.5</v>
       </c>
       <c r="G40" s="10">
-        <v>41.5</v>
+        <v>33.5</v>
       </c>
       <c r="H40" s="10">
-        <v>54.7</v>
+        <v>60</v>
       </c>
       <c r="I40" s="16">
-        <v>9.4207075000000001E-2</v>
+        <v>0.104</v>
       </c>
     </row>
     <row r="41" spans="1:12">
-      <c r="A41" s="15" t="s">
-        <v>43</v>
-      </c>
-      <c r="B41" s="17" t="s">
-        <v>111</v>
-      </c>
-      <c r="C41" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="D41" s="10">
-        <v>24</v>
-      </c>
-      <c r="E41" s="10">
-        <v>23</v>
-      </c>
-      <c r="F41" s="10">
-        <v>51.5</v>
-      </c>
-      <c r="G41" s="10">
-        <v>33.5</v>
-      </c>
-      <c r="H41" s="10">
-        <v>60</v>
-      </c>
-      <c r="I41" s="16">
-        <v>0.104</v>
-      </c>
+      <c r="C41" s="10"/>
+      <c r="D41" s="10"/>
+      <c r="E41" s="10"/>
+      <c r="F41" s="10"/>
+      <c r="G41" s="10"/>
+      <c r="H41" s="10"/>
+      <c r="I41" s="16"/>
     </row>
-    <row r="42" spans="1:12">
+    <row r="42" spans="1:12" ht="23">
+      <c r="A42" s="32" t="s">
+        <v>62</v>
+      </c>
       <c r="C42" s="10"/>
       <c r="D42" s="10"/>
       <c r="E42" s="10"/>
@@ -10942,260 +10913,281 @@
       <c r="H42" s="10"/>
       <c r="I42" s="16"/>
     </row>
-    <row r="43" spans="1:12" ht="23">
-      <c r="A43" s="32" t="s">
-        <v>62</v>
-      </c>
-      <c r="C43" s="10"/>
-      <c r="D43" s="10"/>
-      <c r="E43" s="10"/>
-      <c r="F43" s="10"/>
-      <c r="G43" s="10"/>
-      <c r="H43" s="10"/>
-      <c r="I43" s="16"/>
+    <row r="43" spans="1:12">
+      <c r="A43" s="33" t="s">
+        <v>0</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C43" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="D43" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="E43" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="F43" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="G43" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="H43" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="I43" s="16" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="44" spans="1:12">
-      <c r="A44" s="33" t="s">
-        <v>0</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>1</v>
+      <c r="A44" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="B44" s="18" t="s">
+        <v>116</v>
       </c>
       <c r="C44" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="D44" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="E44" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="F44" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="G44" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="H44" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="I44" s="16" t="s">
-        <v>7</v>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="D44" s="10"/>
+      <c r="E44" s="10"/>
+      <c r="F44" s="10">
+        <v>50.9</v>
+      </c>
+      <c r="G44" s="10">
+        <v>39.6</v>
+      </c>
+      <c r="H44" s="10">
+        <v>60</v>
+      </c>
+      <c r="I44" s="16">
+        <v>0.12093840000000002</v>
+      </c>
+      <c r="J44" s="3"/>
     </row>
     <row r="45" spans="1:12">
       <c r="A45" s="15" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B45" s="18" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C45" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="D45" s="10"/>
-      <c r="E45" s="10"/>
+      <c r="D45" s="10">
+        <v>27</v>
+      </c>
+      <c r="E45" s="10">
+        <v>24</v>
+      </c>
       <c r="F45" s="10">
-        <v>50.9</v>
+        <v>55</v>
       </c>
       <c r="G45" s="10">
-        <v>39.6</v>
+        <v>33</v>
       </c>
       <c r="H45" s="10">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="I45" s="16">
-        <v>0.12093840000000002</v>
+        <v>0.12705</v>
       </c>
       <c r="J45" s="3"/>
     </row>
     <row r="46" spans="1:12">
       <c r="A46" s="15" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B46" s="18" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C46" s="10" t="s">
-        <v>32</v>
+        <v>63</v>
       </c>
       <c r="D46" s="10">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E46" s="10">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F46" s="10">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="G46" s="10">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="H46" s="10">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="I46" s="16">
-        <v>0.12705</v>
+        <v>0.11015999999999999</v>
       </c>
       <c r="J46" s="3"/>
     </row>
     <row r="47" spans="1:12">
       <c r="A47" s="15" t="s">
-        <v>50</v>
+        <v>82</v>
       </c>
       <c r="B47" s="18" t="s">
-        <v>121</v>
-      </c>
-      <c r="C47" s="10" t="s">
-        <v>63</v>
-      </c>
+        <v>119</v>
+      </c>
+      <c r="C47" s="10"/>
       <c r="D47" s="10">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="E47" s="10">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="F47" s="10">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="G47" s="10">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="H47" s="10">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="I47" s="16">
-        <v>0.11015999999999999</v>
+        <v>7.0223999999999995E-2</v>
       </c>
       <c r="J47" s="3"/>
     </row>
     <row r="48" spans="1:12">
       <c r="A48" s="15" t="s">
-        <v>82</v>
+        <v>51</v>
       </c>
       <c r="B48" s="18" t="s">
-        <v>122</v>
-      </c>
-      <c r="C48" s="10"/>
+        <v>120</v>
+      </c>
+      <c r="C48" s="10" t="s">
+        <v>19</v>
+      </c>
       <c r="D48" s="10">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E48" s="10">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F48" s="10">
-        <v>38</v>
+        <v>46.5</v>
       </c>
       <c r="G48" s="10">
-        <v>56</v>
+        <v>36.5</v>
       </c>
       <c r="H48" s="10">
-        <v>33</v>
+        <v>55</v>
       </c>
       <c r="I48" s="16">
-        <v>7.0223999999999995E-2</v>
+        <f>(F48*G48*H48)/1000000</f>
+        <v>9.3348749999999994E-2</v>
       </c>
       <c r="J48" s="3"/>
     </row>
     <row r="49" spans="1:10">
       <c r="A49" s="15" t="s">
-        <v>51</v>
+        <v>121</v>
       </c>
       <c r="B49" s="18" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C49" s="10" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="D49" s="10">
-        <v>7</v>
+        <v>9.5</v>
       </c>
       <c r="E49" s="10">
-        <v>5</v>
+        <v>9.3000000000000007</v>
       </c>
       <c r="F49" s="10">
-        <v>46.5</v>
+        <v>36</v>
       </c>
       <c r="G49" s="10">
-        <v>36.5</v>
+        <v>28</v>
       </c>
       <c r="H49" s="10">
-        <v>55</v>
+        <v>33.5</v>
       </c>
       <c r="I49" s="16">
         <f>(F49*G49*H49)/1000000</f>
-        <v>9.3348749999999994E-2</v>
+        <v>3.3767999999999999E-2</v>
       </c>
       <c r="J49" s="3"/>
     </row>
     <row r="50" spans="1:10">
       <c r="A50" s="15" t="s">
-        <v>124</v>
+        <v>52</v>
       </c>
       <c r="B50" s="18" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C50" s="10" t="s">
-        <v>28</v>
+        <v>63</v>
       </c>
       <c r="D50" s="10">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="E50" s="10">
-        <v>9.3000000000000007</v>
+        <v>5</v>
       </c>
       <c r="F50" s="10">
-        <v>36</v>
+        <v>46.5</v>
       </c>
       <c r="G50" s="10">
-        <v>28</v>
+        <v>36.5</v>
       </c>
       <c r="H50" s="10">
-        <v>33.5</v>
+        <v>55</v>
       </c>
       <c r="I50" s="16">
         <f>(F50*G50*H50)/1000000</f>
-        <v>3.3767999999999999E-2</v>
+        <v>9.3348749999999994E-2</v>
       </c>
       <c r="J50" s="3"/>
     </row>
     <row r="51" spans="1:10">
       <c r="A51" s="15" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B51" s="18" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C51" s="10" t="s">
-        <v>63</v>
+        <v>11</v>
       </c>
       <c r="D51" s="10">
-        <v>7</v>
+        <v>10.3</v>
       </c>
       <c r="E51" s="10">
-        <v>5</v>
+        <v>9.6</v>
       </c>
       <c r="F51" s="10">
-        <v>46.5</v>
+        <v>49</v>
       </c>
       <c r="G51" s="10">
-        <v>36.5</v>
+        <v>27</v>
       </c>
       <c r="H51" s="10">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="I51" s="16">
         <f>(F51*G51*H51)/1000000</f>
-        <v>9.3348749999999994E-2</v>
-      </c>
-      <c r="J51" s="3"/>
+        <v>5.9534999999999998E-2</v>
+      </c>
+      <c r="J51" s="3" t="s">
+        <v>125</v>
+      </c>
     </row>
     <row r="52" spans="1:10">
       <c r="A52" s="15" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B52" s="18" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="C52" s="10" t="s">
         <v>11</v>
@@ -11216,138 +11208,135 @@
         <v>45</v>
       </c>
       <c r="I52" s="16">
-        <f>(F52*G52*H52)/1000000</f>
+        <f t="shared" ref="I52" si="1">(F52*G52*H52)/1000000</f>
         <v>5.9534999999999998E-2</v>
       </c>
-      <c r="J52" s="3" t="s">
-        <v>128</v>
-      </c>
+      <c r="J52" s="3"/>
     </row>
     <row r="53" spans="1:10">
       <c r="A53" s="15" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B53" s="18" t="s">
-        <v>127</v>
+        <v>104</v>
       </c>
       <c r="C53" s="10" t="s">
-        <v>11</v>
+        <v>64</v>
       </c>
       <c r="D53" s="10">
-        <v>10.3</v>
+        <v>10.72</v>
       </c>
       <c r="E53" s="10">
-        <v>9.6</v>
+        <v>9.7200000000000006</v>
       </c>
       <c r="F53" s="10">
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="G53" s="10">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H53" s="10">
-        <v>45</v>
+        <v>34.5</v>
       </c>
       <c r="I53" s="16">
-        <f t="shared" ref="I53" si="1">(F53*G53*H53)/1000000</f>
-        <v>5.9534999999999998E-2</v>
+        <v>2.7047999999999999E-2</v>
       </c>
       <c r="J53" s="3"/>
     </row>
     <row r="54" spans="1:10">
       <c r="A54" s="15" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B54" s="18" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="C54" s="10" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D54" s="10">
-        <v>10.72</v>
+        <v>12.75</v>
       </c>
       <c r="E54" s="10">
-        <v>9.7200000000000006</v>
+        <v>11.2</v>
       </c>
       <c r="F54" s="10">
-        <v>28</v>
+        <v>37.5</v>
       </c>
       <c r="G54" s="10">
-        <v>28</v>
+        <v>28.2</v>
       </c>
       <c r="H54" s="10">
-        <v>34.5</v>
+        <v>34.799999999999997</v>
       </c>
       <c r="I54" s="16">
-        <v>2.7047999999999999E-2</v>
+        <v>3.6801E-2</v>
       </c>
       <c r="J54" s="3"/>
     </row>
-    <row r="55" spans="1:10">
+    <row r="55" spans="1:10" ht="29">
       <c r="A55" s="15" t="s">
-        <v>56</v>
+        <v>81</v>
       </c>
       <c r="B55" s="18" t="s">
-        <v>100</v>
-      </c>
-      <c r="C55" s="10" t="s">
-        <v>65</v>
-      </c>
+        <v>126</v>
+      </c>
+      <c r="C55" s="10"/>
       <c r="D55" s="10">
-        <v>12.75</v>
+        <v>16</v>
       </c>
       <c r="E55" s="10">
-        <v>11.2</v>
+        <v>15</v>
       </c>
       <c r="F55" s="10">
-        <v>37.5</v>
+        <v>22</v>
       </c>
       <c r="G55" s="10">
-        <v>28.2</v>
+        <v>7.8</v>
       </c>
       <c r="H55" s="10">
-        <v>34.799999999999997</v>
+        <v>21</v>
       </c>
       <c r="I55" s="16">
-        <v>3.6801E-2</v>
+        <v>9.3348749999999994E-2</v>
       </c>
       <c r="J55" s="3"/>
     </row>
-    <row r="56" spans="1:10" ht="29">
+    <row r="56" spans="1:10">
       <c r="A56" s="15" t="s">
-        <v>81</v>
+        <v>57</v>
       </c>
       <c r="B56" s="18" t="s">
-        <v>129</v>
-      </c>
-      <c r="C56" s="10"/>
+        <v>127</v>
+      </c>
+      <c r="C56" s="10" t="s">
+        <v>32</v>
+      </c>
       <c r="D56" s="10">
-        <v>16</v>
+        <v>10.3</v>
       </c>
       <c r="E56" s="10">
-        <v>15</v>
+        <v>9.6</v>
       </c>
       <c r="F56" s="10">
-        <v>22</v>
+        <v>21.8</v>
       </c>
       <c r="G56" s="10">
-        <v>7.8</v>
+        <v>5.6</v>
       </c>
       <c r="H56" s="10">
-        <v>21</v>
+        <v>14.1</v>
       </c>
       <c r="I56" s="16">
-        <v>9.3348749999999994E-2</v>
+        <v>9.4E-2</v>
       </c>
       <c r="J56" s="3"/>
     </row>
     <row r="57" spans="1:10">
       <c r="A57" s="15" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B57" s="18" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C57" s="10" t="s">
         <v>32</v>
@@ -11374,129 +11363,108 @@
     </row>
     <row r="58" spans="1:10">
       <c r="A58" s="15" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B58" s="18" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C58" s="10" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="D58" s="10">
-        <v>10.3</v>
+        <v>15.6</v>
       </c>
       <c r="E58" s="10">
-        <v>9.6</v>
+        <v>14.6</v>
       </c>
       <c r="F58" s="10">
-        <v>21.8</v>
+        <v>54</v>
       </c>
       <c r="G58" s="10">
-        <v>5.6</v>
+        <v>30</v>
       </c>
       <c r="H58" s="10">
-        <v>14.1</v>
+        <v>44.5</v>
       </c>
       <c r="I58" s="16">
-        <v>9.4E-2</v>
+        <f t="shared" ref="I58:I59" si="2">(F58*G58*H58)/1000000</f>
+        <v>7.2090000000000001E-2</v>
       </c>
       <c r="J58" s="3"/>
     </row>
     <row r="59" spans="1:10">
       <c r="A59" s="15" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B59" s="18" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C59" s="10" t="s">
-        <v>47</v>
+        <v>66</v>
       </c>
       <c r="D59" s="10">
-        <v>15.6</v>
+        <v>20</v>
       </c>
       <c r="E59" s="10">
-        <v>14.6</v>
+        <v>19.2</v>
       </c>
       <c r="F59" s="10">
-        <v>54</v>
+        <v>48.5</v>
       </c>
       <c r="G59" s="10">
-        <v>30</v>
+        <v>40.5</v>
       </c>
       <c r="H59" s="10">
-        <v>44.5</v>
+        <v>42</v>
       </c>
       <c r="I59" s="16">
-        <f t="shared" ref="I59:I60" si="2">(F59*G59*H59)/1000000</f>
-        <v>7.2090000000000001E-2</v>
+        <f t="shared" si="2"/>
+        <v>8.2498500000000002E-2</v>
       </c>
       <c r="J59" s="3"/>
     </row>
     <row r="60" spans="1:10">
       <c r="A60" s="15" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B60" s="18" t="s">
-        <v>133</v>
+        <v>118</v>
       </c>
       <c r="C60" s="10" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D60" s="10">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="E60" s="10">
-        <v>19.2</v>
+        <v>28</v>
       </c>
       <c r="F60" s="10">
-        <v>48.5</v>
+        <f>12*4</f>
+        <v>48</v>
       </c>
       <c r="G60" s="10">
-        <v>40.5</v>
+        <f>25.5*2</f>
+        <v>51</v>
       </c>
       <c r="H60" s="10">
-        <v>42</v>
+        <f>2.5*18</f>
+        <v>45</v>
       </c>
       <c r="I60" s="16">
-        <f t="shared" si="2"/>
-        <v>8.2498500000000002E-2</v>
+        <f>(F60*G60*H60)/1000000</f>
+        <v>0.11015999999999999</v>
       </c>
       <c r="J60" s="3"/>
     </row>
     <row r="61" spans="1:10">
-      <c r="A61" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="B61" s="18" t="s">
-        <v>121</v>
-      </c>
-      <c r="C61" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="D61" s="10">
-        <v>30</v>
-      </c>
-      <c r="E61" s="10">
-        <v>28</v>
-      </c>
-      <c r="F61" s="10">
-        <f>12*4</f>
-        <v>48</v>
-      </c>
-      <c r="G61" s="10">
-        <f>25.5*2</f>
-        <v>51</v>
-      </c>
-      <c r="H61" s="10">
-        <f>2.5*18</f>
-        <v>45</v>
-      </c>
-      <c r="I61" s="16">
-        <f>(F61*G61*H61)/1000000</f>
-        <v>0.11015999999999999</v>
-      </c>
-      <c r="J61" s="3"/>
+      <c r="C61" s="10"/>
+      <c r="D61" s="10"/>
+      <c r="E61" s="10"/>
+      <c r="F61" s="10"/>
+      <c r="G61" s="10"/>
+      <c r="H61" s="10"/>
+      <c r="I61" s="16"/>
     </row>
     <row r="62" spans="1:10">
       <c r="C62" s="10"/>
@@ -11507,7 +11475,10 @@
       <c r="H62" s="10"/>
       <c r="I62" s="16"/>
     </row>
-    <row r="63" spans="1:10">
+    <row r="63" spans="1:10" ht="23.5">
+      <c r="A63" s="34" t="s">
+        <v>73</v>
+      </c>
       <c r="C63" s="10"/>
       <c r="D63" s="10"/>
       <c r="E63" s="10"/>
@@ -11516,53 +11487,70 @@
       <c r="H63" s="10"/>
       <c r="I63" s="16"/>
     </row>
-    <row r="64" spans="1:10" ht="23.5">
-      <c r="A64" s="34" t="s">
-        <v>73</v>
-      </c>
-      <c r="C64" s="10"/>
-      <c r="D64" s="10"/>
-      <c r="E64" s="10"/>
-      <c r="F64" s="10"/>
-      <c r="G64" s="10"/>
-      <c r="H64" s="10"/>
-      <c r="I64" s="16"/>
+    <row r="64" spans="1:10">
+      <c r="A64" s="35" t="s">
+        <v>0</v>
+      </c>
+      <c r="B64" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C64" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="D64" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="E64" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="F64" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="G64" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="H64" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="I64" s="16" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="65" spans="1:9">
-      <c r="A65" s="35" t="s">
-        <v>0</v>
-      </c>
-      <c r="B65" s="8" t="s">
-        <v>1</v>
+      <c r="A65" s="36" t="s">
+        <v>145</v>
+      </c>
+      <c r="B65" s="25" t="s">
+        <v>146</v>
       </c>
       <c r="C65" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="D65" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="E65" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="F65" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="G65" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="H65" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="I65" s="16" t="s">
-        <v>7</v>
+        <v>71</v>
+      </c>
+      <c r="D65" s="10">
+        <v>25</v>
+      </c>
+      <c r="E65" s="10">
+        <v>24</v>
+      </c>
+      <c r="F65" s="10">
+        <v>58</v>
+      </c>
+      <c r="G65" s="10">
+        <v>43.5</v>
+      </c>
+      <c r="H65" s="10">
+        <v>58.5</v>
+      </c>
+      <c r="I65" s="16">
+        <v>0.14799999999999999</v>
       </c>
     </row>
     <row r="66" spans="1:9">
       <c r="A66" s="36" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B66" s="25" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="C66" s="10" t="s">
         <v>71</v>
@@ -11588,68 +11576,54 @@
     </row>
     <row r="67" spans="1:9">
       <c r="A67" s="36" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B67" s="25" t="s">
         <v>149</v>
       </c>
       <c r="C67" s="10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D67" s="10">
-        <v>25</v>
+        <v>9.6</v>
       </c>
       <c r="E67" s="10">
-        <v>24</v>
+        <v>8.8000000000000007</v>
       </c>
       <c r="F67" s="10">
-        <v>58</v>
+        <v>31</v>
       </c>
       <c r="G67" s="10">
-        <v>43.5</v>
+        <v>39</v>
       </c>
       <c r="H67" s="10">
-        <v>58.5</v>
+        <v>42.5</v>
       </c>
       <c r="I67" s="16">
-        <v>0.14799999999999999</v>
+        <v>5.5E-2</v>
       </c>
     </row>
     <row r="68" spans="1:9">
       <c r="A68" s="36" t="s">
-        <v>151</v>
+        <v>140</v>
       </c>
       <c r="B68" s="25" t="s">
-        <v>152</v>
-      </c>
-      <c r="C68" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="D68" s="10">
-        <v>9.6</v>
-      </c>
-      <c r="E68" s="10">
-        <v>8.8000000000000007</v>
-      </c>
-      <c r="F68" s="10">
-        <v>31</v>
-      </c>
-      <c r="G68" s="10">
-        <v>39</v>
-      </c>
-      <c r="H68" s="10">
-        <v>42.5</v>
-      </c>
-      <c r="I68" s="16">
-        <v>5.5E-2</v>
-      </c>
+        <v>141</v>
+      </c>
+      <c r="C68" s="10"/>
+      <c r="D68" s="10"/>
+      <c r="E68" s="10"/>
+      <c r="F68" s="10"/>
+      <c r="G68" s="10"/>
+      <c r="H68" s="10"/>
+      <c r="I68" s="16"/>
     </row>
     <row r="69" spans="1:9">
       <c r="A69" s="36" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B69" s="25" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C69" s="10"/>
       <c r="D69" s="10"/>
@@ -11661,14 +11635,20 @@
     </row>
     <row r="70" spans="1:9">
       <c r="A70" s="36" t="s">
-        <v>145</v>
-      </c>
-      <c r="B70" s="25" t="s">
-        <v>144</v>
-      </c>
-      <c r="C70" s="10"/>
-      <c r="D70" s="10"/>
-      <c r="E70" s="10"/>
+        <v>137</v>
+      </c>
+      <c r="B70" s="26" t="s">
+        <v>138</v>
+      </c>
+      <c r="C70" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="D70" s="10">
+        <v>15.2</v>
+      </c>
+      <c r="E70" s="10">
+        <v>14.2</v>
+      </c>
       <c r="F70" s="10"/>
       <c r="G70" s="10"/>
       <c r="H70" s="10"/>
@@ -11676,149 +11656,140 @@
     </row>
     <row r="71" spans="1:9">
       <c r="A71" s="36" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B71" s="26" t="s">
-        <v>141</v>
-      </c>
-      <c r="C71" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="D71" s="10">
-        <v>15.2</v>
-      </c>
-      <c r="E71" s="10">
-        <v>14.2</v>
-      </c>
+        <v>138</v>
+      </c>
+      <c r="C71" s="10"/>
+      <c r="D71" s="10"/>
+      <c r="E71" s="10"/>
       <c r="F71" s="10"/>
       <c r="G71" s="10"/>
       <c r="H71" s="10"/>
       <c r="I71" s="16"/>
     </row>
     <row r="72" spans="1:9">
-      <c r="A72" s="36" t="s">
-        <v>142</v>
-      </c>
-      <c r="B72" s="26" t="s">
-        <v>141</v>
-      </c>
-      <c r="C72" s="10"/>
-      <c r="D72" s="10"/>
-      <c r="E72" s="10"/>
-      <c r="F72" s="10"/>
-      <c r="G72" s="10"/>
-      <c r="H72" s="10"/>
-      <c r="I72" s="16"/>
+      <c r="A72" s="17" t="s">
+        <v>143</v>
+      </c>
+      <c r="B72" s="25" t="s">
+        <v>144</v>
+      </c>
+      <c r="C72" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="D72" s="10">
+        <v>17.079999999999998</v>
+      </c>
+      <c r="E72" s="10">
+        <v>16.5</v>
+      </c>
+      <c r="F72" s="10">
+        <v>37</v>
+      </c>
+      <c r="G72" s="10">
+        <v>17.5</v>
+      </c>
+      <c r="H72" s="10">
+        <v>43.5</v>
+      </c>
+      <c r="I72" s="16">
+        <v>2.816625E-2</v>
+      </c>
     </row>
     <row r="73" spans="1:9">
-      <c r="A73" s="17" t="s">
-        <v>146</v>
+      <c r="A73" s="36" t="s">
+        <v>133</v>
       </c>
       <c r="B73" s="25" t="s">
-        <v>147</v>
+        <v>134</v>
       </c>
       <c r="C73" s="10" t="s">
-        <v>28</v>
+        <v>68</v>
       </c>
       <c r="D73" s="10">
-        <v>17.079999999999998</v>
+        <v>18.86</v>
       </c>
       <c r="E73" s="10">
-        <v>16.5</v>
-      </c>
-      <c r="F73" s="10">
-        <v>37</v>
-      </c>
-      <c r="G73" s="10">
-        <v>17.5</v>
-      </c>
-      <c r="H73" s="10">
-        <v>43.5</v>
-      </c>
-      <c r="I73" s="16">
-        <v>2.816625E-2</v>
-      </c>
+        <v>17.239999999999998</v>
+      </c>
+      <c r="F73" s="10"/>
+      <c r="G73" s="10"/>
+      <c r="H73" s="10"/>
+      <c r="I73" s="16"/>
     </row>
     <row r="74" spans="1:9">
       <c r="A74" s="36" t="s">
+        <v>135</v>
+      </c>
+      <c r="B74" s="25" t="s">
         <v>136</v>
       </c>
-      <c r="B74" s="25" t="s">
-        <v>137</v>
-      </c>
       <c r="C74" s="10" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D74" s="10">
-        <v>18.86</v>
+        <v>17.600000000000001</v>
       </c>
       <c r="E74" s="10">
-        <v>17.239999999999998</v>
-      </c>
-      <c r="F74" s="10"/>
-      <c r="G74" s="10"/>
-      <c r="H74" s="10"/>
-      <c r="I74" s="16"/>
+        <v>16.600000000000001</v>
+      </c>
+      <c r="F74" s="10">
+        <v>40.5</v>
+      </c>
+      <c r="G74" s="10">
+        <v>33.5</v>
+      </c>
+      <c r="H74" s="10">
+        <v>30</v>
+      </c>
+      <c r="I74" s="16">
+        <v>0.41</v>
+      </c>
     </row>
-    <row r="75" spans="1:9">
-      <c r="A75" s="36" t="s">
-        <v>138</v>
-      </c>
-      <c r="B75" s="25" t="s">
-        <v>139</v>
+    <row r="75" spans="1:9" ht="29">
+      <c r="A75" s="15" t="s">
+        <v>132</v>
+      </c>
+      <c r="B75" s="17" t="s">
+        <v>131</v>
       </c>
       <c r="C75" s="10" t="s">
-        <v>67</v>
+        <v>18</v>
       </c>
       <c r="D75" s="10">
-        <v>17.600000000000001</v>
+        <v>28.5</v>
       </c>
       <c r="E75" s="10">
-        <v>16.600000000000001</v>
+        <v>27</v>
       </c>
       <c r="F75" s="10">
-        <v>40.5</v>
+        <v>80</v>
       </c>
       <c r="G75" s="10">
-        <v>33.5</v>
+        <v>31.5</v>
       </c>
       <c r="H75" s="10">
-        <v>30</v>
+        <v>53.5</v>
       </c>
       <c r="I75" s="16">
-        <v>0.41</v>
+        <v>0.13500000000000001</v>
       </c>
     </row>
-    <row r="76" spans="1:9" ht="29">
-      <c r="A76" s="15" t="s">
-        <v>135</v>
-      </c>
-      <c r="B76" s="17" t="s">
-        <v>134</v>
-      </c>
-      <c r="C76" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="D76" s="10">
-        <v>28.5</v>
-      </c>
-      <c r="E76" s="10">
-        <v>27</v>
-      </c>
-      <c r="F76" s="10">
-        <v>80</v>
-      </c>
-      <c r="G76" s="10">
-        <v>31.5</v>
-      </c>
-      <c r="H76" s="10">
-        <v>53.5</v>
-      </c>
-      <c r="I76" s="16">
-        <v>0.13500000000000001</v>
-      </c>
+    <row r="76" spans="1:9">
+      <c r="C76" s="10"/>
+      <c r="D76" s="10"/>
+      <c r="E76" s="10"/>
+      <c r="F76" s="10"/>
+      <c r="G76" s="10"/>
+      <c r="H76" s="10"/>
+      <c r="I76" s="16"/>
     </row>
-    <row r="77" spans="1:9">
+    <row r="77" spans="1:9" ht="23.5">
+      <c r="A77" s="34" t="s">
+        <v>78</v>
+      </c>
       <c r="C77" s="10"/>
       <c r="D77" s="10"/>
       <c r="E77" s="10"/>
@@ -11827,246 +11798,234 @@
       <c r="H77" s="10"/>
       <c r="I77" s="16"/>
     </row>
-    <row r="78" spans="1:9" ht="23.5">
-      <c r="A78" s="34" t="s">
-        <v>78</v>
-      </c>
-      <c r="C78" s="10"/>
-      <c r="D78" s="10"/>
-      <c r="E78" s="10"/>
-      <c r="F78" s="10"/>
-      <c r="G78" s="10"/>
-      <c r="H78" s="10"/>
-      <c r="I78" s="16"/>
+    <row r="78" spans="1:9">
+      <c r="A78" s="35" t="s">
+        <v>0</v>
+      </c>
+      <c r="B78" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C78" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="D78" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="E78" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="F78" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="G78" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="H78" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="I78" s="16" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="79" spans="1:9">
-      <c r="A79" s="35" t="s">
-        <v>0</v>
-      </c>
-      <c r="B79" s="6" t="s">
-        <v>1</v>
+    <row r="79" spans="1:9" s="4" customFormat="1">
+      <c r="A79" s="17" t="s">
+        <v>153</v>
+      </c>
+      <c r="B79" s="21" t="s">
+        <v>164</v>
       </c>
       <c r="C79" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="D79" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="E79" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="F79" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="G79" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="H79" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="I79" s="16" t="s">
-        <v>7</v>
+        <v>40</v>
+      </c>
+      <c r="D79" s="10">
+        <v>11.8</v>
+      </c>
+      <c r="E79" s="10">
+        <v>11.6</v>
+      </c>
+      <c r="F79" s="10">
+        <v>28.4</v>
+      </c>
+      <c r="G79" s="10">
+        <v>31.6</v>
+      </c>
+      <c r="H79" s="10">
+        <v>30</v>
+      </c>
+      <c r="I79" s="16">
+        <v>2.7E-2</v>
       </c>
     </row>
     <row r="80" spans="1:9" s="4" customFormat="1">
-      <c r="A80" s="17" t="s">
-        <v>156</v>
+      <c r="A80" s="15" t="s">
+        <v>154</v>
       </c>
       <c r="B80" s="21" t="s">
-        <v>168</v>
+        <v>100</v>
       </c>
       <c r="C80" s="10" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="D80" s="10">
-        <v>11.8</v>
+        <v>12.75</v>
       </c>
       <c r="E80" s="10">
-        <v>11.6</v>
+        <v>11.2</v>
       </c>
       <c r="F80" s="10">
-        <v>28.4</v>
+        <v>37.5</v>
       </c>
       <c r="G80" s="10">
-        <v>31.6</v>
+        <v>28.2</v>
       </c>
       <c r="H80" s="10">
-        <v>30</v>
+        <v>34.799999999999997</v>
       </c>
       <c r="I80" s="16">
-        <v>2.7E-2</v>
+        <v>3.6999999999999998E-2</v>
       </c>
     </row>
     <row r="81" spans="1:9" s="4" customFormat="1">
       <c r="A81" s="15" t="s">
-        <v>157</v>
-      </c>
-      <c r="B81" s="21" t="s">
-        <v>100</v>
+        <v>75</v>
+      </c>
+      <c r="B81" s="17" t="s">
+        <v>155</v>
       </c>
       <c r="C81" s="10" t="s">
-        <v>28</v>
+        <v>77</v>
       </c>
       <c r="D81" s="10">
-        <v>12.75</v>
+        <v>12</v>
       </c>
       <c r="E81" s="10">
-        <v>11.2</v>
+        <v>11.23</v>
       </c>
       <c r="F81" s="10">
-        <v>37.5</v>
+        <v>36</v>
       </c>
       <c r="G81" s="10">
-        <v>28.2</v>
+        <v>27</v>
       </c>
       <c r="H81" s="10">
-        <v>34.799999999999997</v>
+        <v>27</v>
       </c>
       <c r="I81" s="16">
-        <v>3.6999999999999998E-2</v>
+        <v>2.6244E-2</v>
       </c>
     </row>
     <row r="82" spans="1:9" s="4" customFormat="1">
       <c r="A82" s="15" t="s">
-        <v>75</v>
-      </c>
-      <c r="B82" s="17" t="s">
-        <v>158</v>
+        <v>76</v>
+      </c>
+      <c r="B82" s="21" t="s">
+        <v>106</v>
       </c>
       <c r="C82" s="10" t="s">
-        <v>77</v>
+        <v>18</v>
       </c>
       <c r="D82" s="10">
-        <v>12</v>
+        <v>12.75</v>
       </c>
       <c r="E82" s="10">
-        <v>11.23</v>
+        <v>11.2</v>
       </c>
       <c r="F82" s="10">
-        <v>36</v>
+        <v>37.5</v>
       </c>
       <c r="G82" s="10">
-        <v>27</v>
+        <v>28.2</v>
       </c>
       <c r="H82" s="10">
-        <v>27</v>
+        <v>34.799999999999997</v>
       </c>
       <c r="I82" s="16">
-        <v>2.6244E-2</v>
+        <v>3.6999999999999998E-2</v>
       </c>
     </row>
     <row r="83" spans="1:9" s="4" customFormat="1">
       <c r="A83" s="15" t="s">
-        <v>76</v>
+        <v>39</v>
       </c>
       <c r="B83" s="21" t="s">
-        <v>109</v>
+        <v>165</v>
       </c>
       <c r="C83" s="10" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="D83" s="10">
-        <v>12.75</v>
+        <v>11</v>
       </c>
       <c r="E83" s="10">
-        <v>11.2</v>
+        <v>13</v>
       </c>
       <c r="F83" s="10">
-        <v>37.5</v>
+        <v>35</v>
       </c>
       <c r="G83" s="10">
-        <v>28.2</v>
+        <v>22</v>
       </c>
       <c r="H83" s="10">
-        <v>34.799999999999997</v>
+        <v>39</v>
       </c>
       <c r="I83" s="16">
-        <v>3.6999999999999998E-2</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="84" spans="1:9" s="4" customFormat="1">
       <c r="A84" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="B84" s="21" t="s">
-        <v>169</v>
+        <v>150</v>
+      </c>
+      <c r="B84" s="17" t="s">
+        <v>166</v>
       </c>
       <c r="C84" s="10" t="s">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="D84" s="10">
-        <v>11</v>
+        <v>9.5440000000000005</v>
       </c>
       <c r="E84" s="10">
-        <v>13</v>
+        <v>8.5440000000000005</v>
       </c>
       <c r="F84" s="10">
-        <v>35</v>
+        <v>44.8</v>
       </c>
       <c r="G84" s="10">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="H84" s="10">
-        <v>39</v>
+        <v>10</v>
       </c>
       <c r="I84" s="16">
-        <v>0.03</v>
+        <v>1.2999999999999999E-2</v>
       </c>
     </row>
     <row r="85" spans="1:9" s="4" customFormat="1">
       <c r="A85" s="15" t="s">
-        <v>153</v>
-      </c>
-      <c r="B85" s="17" t="s">
-        <v>170</v>
+        <v>151</v>
+      </c>
+      <c r="B85" s="22" t="s">
+        <v>152</v>
       </c>
       <c r="C85" s="10" t="s">
         <v>70</v>
       </c>
-      <c r="D85" s="10">
-        <v>9.5440000000000005</v>
-      </c>
-      <c r="E85" s="10">
-        <v>8.5440000000000005</v>
-      </c>
-      <c r="F85" s="10">
-        <v>44.8</v>
-      </c>
-      <c r="G85" s="10">
-        <v>30</v>
-      </c>
-      <c r="H85" s="10">
-        <v>10</v>
-      </c>
-      <c r="I85" s="16">
-        <v>1.2999999999999999E-2</v>
-      </c>
+      <c r="D85" s="10"/>
+      <c r="E85" s="10"/>
+      <c r="F85" s="10"/>
+      <c r="G85" s="10"/>
+      <c r="H85" s="10"/>
+      <c r="I85" s="16"/>
     </row>
-    <row r="86" spans="1:9" s="4" customFormat="1">
-      <c r="A86" s="15" t="s">
-        <v>154</v>
-      </c>
-      <c r="B86" s="22" t="s">
-        <v>155</v>
-      </c>
-      <c r="C86" s="10" t="s">
-        <v>70</v>
-      </c>
+    <row r="86" spans="1:9">
+      <c r="C86" s="10"/>
       <c r="D86" s="10"/>
       <c r="E86" s="10"/>
       <c r="F86" s="10"/>
       <c r="G86" s="10"/>
       <c r="H86" s="10"/>
       <c r="I86" s="16"/>
-    </row>
-    <row r="87" spans="1:9">
-      <c r="C87" s="10"/>
-      <c r="D87" s="10"/>
-      <c r="E87" s="10"/>
-      <c r="F87" s="10"/>
-      <c r="G87" s="10"/>
-      <c r="H87" s="10"/>
-      <c r="I87" s="16"/>
     </row>
   </sheetData>
   <phoneticPr fontId="30" type="noConversion"/>

--- a/Case Size.xlsx
+++ b/Case Size.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maa00\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4487DCBF-FD93-41C8-8682-90771EABB61B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7922D8D3-3F22-49A2-871B-F764EE8D0619}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="163">
   <si>
     <t>Category</t>
   </si>
@@ -346,20 +346,6 @@
     <t>7 CHAKRA STONE</t>
   </si>
   <si>
-    <r>
-      <t>4 in 1 Assorted CONE</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="7"/>
-        <color rgb="FF3D2020"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t> </t>
-    </r>
-  </si>
-  <si>
     <t>10 Sticks in a packet, 6 packets in a box,  2 boxes make 1 Dozen</t>
   </si>
   <si>
@@ -408,20 +394,6 @@
     <t>185 gm scented tin smudge candle, wrapped with label sticker. Such 24 pcs packed inside master carton.</t>
   </si>
   <si>
-    <r>
-      <t>Soham DHOOP</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF3D2020"/>
-        <rFont val="Aptos Display"/>
-        <scheme val="major"/>
-      </rPr>
-      <t>  STICK</t>
-    </r>
-  </si>
-  <si>
     <t>100 GMS</t>
   </si>
   <si>
@@ -512,55 +484,22 @@
     <t>White Abhir, Gulal, Kumkum, Haldi, Camphor Tablets, Moli, Pooja Supari, Akhata, Agarbatti, Agarbatti Wooden Stand, Janvi Jod, Goddess Photo, Vastra (Pooja Cloth) &amp; Dhoop.</t>
   </si>
   <si>
-    <t>Pooja Samagri Kit</t>
-  </si>
-  <si>
-    <t>Aradhana Pooja Oil Pack 900ml</t>
-  </si>
-  <si>
     <t>1 Bottle x 900 ml, 20Pcs in 1 master carton</t>
   </si>
   <si>
-    <t xml:space="preserve">Aradhana Pooja Oil Pack 450Ml </t>
-  </si>
-  <si>
     <t>1 Bottle x 450 ml, 40Pcs in 1 master carton</t>
   </si>
   <si>
-    <t>HEM Aradhana Camphor - 100g</t>
-  </si>
-  <si>
     <t xml:space="preserve"> Camphor - 100g</t>
   </si>
   <si>
-    <t>HEM Aradhana Bhimseni Camphor</t>
-  </si>
-  <si>
-    <t>HEM Aradhana Pure Cow Ghee Diya 100 pcs</t>
-  </si>
-  <si>
     <t>100 pcs Diya in a box, 4 doz in 1 Master Carton</t>
   </si>
   <si>
-    <t>HEM Aradhana Pure Ghee Diya 100 pcs</t>
-  </si>
-  <si>
-    <t>HEM Aradhana Gangajal</t>
-  </si>
-  <si>
     <t>Gangajal, 24 pc in box</t>
   </si>
   <si>
-    <t xml:space="preserve">Soham Sambrani Cup Dhoop </t>
-  </si>
-  <si>
     <t>12 pcs in 1 box, 12 dozen in 1 Master Carton</t>
-  </si>
-  <si>
-    <t>Pama Sambrani Cup Dhoop</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Madhur Guggal Cup Dhhop </t>
   </si>
   <si>
     <t>12 pcs in 1 box, 4 dozen in 1 Master Carton</t>
@@ -636,6 +575,24 @@
       <t> </t>
     </r>
   </si>
+  <si>
+    <t>Cup Dhoop</t>
+  </si>
+  <si>
+    <t>Ghee Diya</t>
+  </si>
+  <si>
+    <t>HEM Camphor</t>
+  </si>
+  <si>
+    <t>HEM Gangajal</t>
+  </si>
+  <si>
+    <t>Pooja Oil</t>
+  </si>
+  <si>
+    <t>Pooja Samagri</t>
+  </si>
 </sst>
 </file>
 
@@ -644,7 +601,7 @@
   <numFmts count="1">
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="36">
+  <fonts count="35">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -852,12 +809,6 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Aptos Display"/>
-      <scheme val="major"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3D2020"/>
       <name val="Aptos Display"/>
       <scheme val="major"/>
     </font>
@@ -6017,20 +5968,20 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="134" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="134" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="134" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -6089,7 +6040,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="135" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="135" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="135" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -6129,9 +6080,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="25" borderId="135" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="135" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -9716,7 +9664,7 @@
   <dimension ref="A1:L86"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="69.1796875" style="4" customWidth="1"/>
+    <col min="1" max="1" width="87.36328125" style="4" customWidth="1"/>
     <col min="2" max="2" width="108.7265625" style="23" customWidth="1"/>
     <col min="3" max="3" width="21.36328125" style="2" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.08984375" bestFit="1" customWidth="1"/>
@@ -9740,7 +9688,7 @@
       <c r="G1" s="9"/>
       <c r="H1" s="9"/>
       <c r="I1" s="11" t="s">
-        <v>167</v>
+        <v>154</v>
       </c>
     </row>
     <row r="2" spans="1:10">
@@ -9777,7 +9725,7 @@
         <v>45</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>158</v>
+        <v>145</v>
       </c>
       <c r="C3" s="10" t="s">
         <v>18</v>
@@ -9806,7 +9754,7 @@
         <v>45</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>161</v>
+        <v>148</v>
       </c>
       <c r="C4" s="10" t="s">
         <v>19</v>
@@ -9835,7 +9783,7 @@
         <v>45</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>161</v>
+        <v>148</v>
       </c>
       <c r="C5" s="10" t="s">
         <v>11</v>
@@ -9864,7 +9812,7 @@
         <v>45</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>161</v>
+        <v>148</v>
       </c>
       <c r="C6" s="10" t="s">
         <v>9</v>
@@ -9893,7 +9841,7 @@
         <v>46</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C7" s="10" t="s">
         <v>18</v>
@@ -9922,7 +9870,7 @@
         <v>46</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C8" s="10" t="s">
         <v>47</v>
@@ -9951,7 +9899,7 @@
         <v>46</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C9" s="10" t="s">
         <v>19</v>
@@ -9980,7 +9928,7 @@
         <v>79</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C10" s="10" t="s">
         <v>9</v>
@@ -10009,7 +9957,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="17" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C11" s="10" t="s">
         <v>11</v>
@@ -10038,7 +9986,7 @@
         <v>13</v>
       </c>
       <c r="B12" s="17" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C12" s="10" t="s">
         <v>11</v>
@@ -10062,7 +10010,7 @@
         <v>12</v>
       </c>
       <c r="J12" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -10070,7 +10018,7 @@
         <v>14</v>
       </c>
       <c r="B13" s="17" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C13" s="10" t="s">
         <v>15</v>
@@ -10099,7 +10047,7 @@
         <v>16</v>
       </c>
       <c r="B14" s="17" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C14" s="10" t="s">
         <v>15</v>
@@ -10128,7 +10076,7 @@
         <v>17</v>
       </c>
       <c r="B15" s="17" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="C15" s="10" t="s">
         <v>18</v>
@@ -10157,7 +10105,7 @@
         <v>83</v>
       </c>
       <c r="B16" s="17" t="s">
-        <v>157</v>
+        <v>144</v>
       </c>
       <c r="C16" s="10" t="s">
         <v>40</v>
@@ -10186,7 +10134,7 @@
         <v>20</v>
       </c>
       <c r="B17" s="17" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C17" s="10" t="s">
         <v>19</v>
@@ -10215,7 +10163,7 @@
         <v>21</v>
       </c>
       <c r="B18" s="17" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C18" s="10" t="s">
         <v>19</v>
@@ -10241,10 +10189,10 @@
     </row>
     <row r="19" spans="1:12">
       <c r="A19" s="15" t="s">
+        <v>91</v>
+      </c>
+      <c r="B19" s="17" t="s">
         <v>92</v>
-      </c>
-      <c r="B19" s="17" t="s">
-        <v>93</v>
       </c>
       <c r="C19" s="10" t="s">
         <v>18</v>
@@ -10274,7 +10222,7 @@
         <v>80</v>
       </c>
       <c r="B20" s="18" t="s">
-        <v>162</v>
+        <v>149</v>
       </c>
       <c r="C20" s="10" t="s">
         <v>22</v>
@@ -10301,10 +10249,10 @@
     </row>
     <row r="21" spans="1:12">
       <c r="A21" s="29" t="s">
-        <v>84</v>
+        <v>156</v>
       </c>
       <c r="B21" s="18" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C21" s="10" t="s">
         <v>23</v>
@@ -10331,10 +10279,10 @@
     </row>
     <row r="22" spans="1:12">
       <c r="A22" s="29" t="s">
-        <v>169</v>
+        <v>156</v>
       </c>
       <c r="B22" s="18" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C22" s="10" t="s">
         <v>24</v>
@@ -10361,10 +10309,10 @@
     </row>
     <row r="23" spans="1:12">
       <c r="A23" s="30" t="s">
-        <v>168</v>
+        <v>155</v>
       </c>
       <c r="B23" s="24" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C23" s="10" t="s">
         <v>11</v>
@@ -10391,10 +10339,10 @@
     </row>
     <row r="24" spans="1:12">
       <c r="A24" s="30" t="s">
-        <v>101</v>
+        <v>155</v>
       </c>
       <c r="B24" s="24" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C24" s="10" t="s">
         <v>25</v>
@@ -10424,7 +10372,7 @@
         <v>26</v>
       </c>
       <c r="B25" s="18" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C25" s="10" t="s">
         <v>19</v>
@@ -10454,7 +10402,7 @@
         <v>27</v>
       </c>
       <c r="B26" s="18" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C26" s="10" t="s">
         <v>28</v>
@@ -10484,7 +10432,7 @@
         <v>29</v>
       </c>
       <c r="B27" s="18" t="s">
-        <v>156</v>
+        <v>143</v>
       </c>
       <c r="C27" s="10" t="s">
         <v>15</v>
@@ -10511,13 +10459,13 @@
     </row>
     <row r="28" spans="1:12" ht="15" thickBot="1">
       <c r="A28" s="31" t="s">
+        <v>107</v>
+      </c>
+      <c r="B28" s="19" t="s">
+        <v>108</v>
+      </c>
+      <c r="C28" s="10" t="s">
         <v>109</v>
-      </c>
-      <c r="B28" s="19" t="s">
-        <v>110</v>
-      </c>
-      <c r="C28" s="10" t="s">
-        <v>111</v>
       </c>
       <c r="D28" s="10">
         <v>16.3</v>
@@ -10542,13 +10490,13 @@
     </row>
     <row r="29" spans="1:12" ht="15" thickBot="1">
       <c r="A29" s="31" t="s">
+        <v>110</v>
+      </c>
+      <c r="B29" s="18" t="s">
         <v>112</v>
       </c>
-      <c r="B29" s="18" t="s">
-        <v>114</v>
-      </c>
       <c r="C29" s="10" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D29" s="10">
         <v>15.3</v>
@@ -10570,12 +10518,12 @@
       </c>
       <c r="J29" s="2"/>
     </row>
-    <row r="30" spans="1:12" ht="29.5" thickBot="1">
+    <row r="30" spans="1:12" ht="14" customHeight="1" thickBot="1">
       <c r="A30" s="31" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B30" s="19" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
       <c r="C30" s="10" t="s">
         <v>77</v>
@@ -10606,7 +10554,7 @@
         <v>30</v>
       </c>
       <c r="B31" s="18" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C31" s="10" t="s">
         <v>11</v>
@@ -10638,7 +10586,7 @@
         <v>31</v>
       </c>
       <c r="B32" s="18" t="s">
-        <v>160</v>
+        <v>147</v>
       </c>
       <c r="C32" s="10" t="s">
         <v>32</v>
@@ -10662,7 +10610,7 @@
         <v>33</v>
       </c>
       <c r="B33" s="18" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C33" s="10" t="s">
         <v>34</v>
@@ -10694,7 +10642,7 @@
         <v>35</v>
       </c>
       <c r="B34" s="17" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C34" s="10" t="s">
         <v>11</v>
@@ -10723,7 +10671,7 @@
         <v>36</v>
       </c>
       <c r="B35" s="17" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C35" s="10" t="s">
         <v>37</v>
@@ -10752,7 +10700,7 @@
         <v>38</v>
       </c>
       <c r="B36" s="17" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C36" s="10" t="s">
         <v>18</v>
@@ -10781,7 +10729,7 @@
         <v>39</v>
       </c>
       <c r="B37" s="17" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C37" s="10" t="s">
         <v>40</v>
@@ -10810,7 +10758,7 @@
         <v>41</v>
       </c>
       <c r="B38" s="17" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C38" s="10" t="s">
         <v>18</v>
@@ -10839,7 +10787,7 @@
         <v>42</v>
       </c>
       <c r="B39" s="17" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C39" s="10" t="s">
         <v>44</v>
@@ -10868,7 +10816,7 @@
         <v>43</v>
       </c>
       <c r="B40" s="17" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C40" s="10" t="s">
         <v>19</v>
@@ -10947,7 +10895,7 @@
         <v>48</v>
       </c>
       <c r="B44" s="18" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C44" s="10" t="s">
         <v>32</v>
@@ -10973,7 +10921,7 @@
         <v>49</v>
       </c>
       <c r="B45" s="18" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C45" s="10" t="s">
         <v>32</v>
@@ -11003,7 +10951,7 @@
         <v>50</v>
       </c>
       <c r="B46" s="18" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C46" s="10" t="s">
         <v>63</v>
@@ -11033,7 +10981,7 @@
         <v>82</v>
       </c>
       <c r="B47" s="18" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C47" s="10"/>
       <c r="D47" s="10">
@@ -11061,7 +11009,7 @@
         <v>51</v>
       </c>
       <c r="B48" s="18" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C48" s="10" t="s">
         <v>19</v>
@@ -11089,10 +11037,10 @@
     </row>
     <row r="49" spans="1:10">
       <c r="A49" s="15" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B49" s="18" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C49" s="10" t="s">
         <v>28</v>
@@ -11123,7 +11071,7 @@
         <v>52</v>
       </c>
       <c r="B50" s="18" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C50" s="10" t="s">
         <v>63</v>
@@ -11154,7 +11102,7 @@
         <v>53</v>
       </c>
       <c r="B51" s="18" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C51" s="10" t="s">
         <v>11</v>
@@ -11179,7 +11127,7 @@
         <v>5.9534999999999998E-2</v>
       </c>
       <c r="J51" s="3" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="52" spans="1:10">
@@ -11187,7 +11135,7 @@
         <v>54</v>
       </c>
       <c r="B52" s="18" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C52" s="10" t="s">
         <v>11</v>
@@ -11218,7 +11166,7 @@
         <v>55</v>
       </c>
       <c r="B53" s="18" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C53" s="10" t="s">
         <v>64</v>
@@ -11243,12 +11191,12 @@
       </c>
       <c r="J53" s="3"/>
     </row>
-    <row r="54" spans="1:10">
+    <row r="54" spans="1:10" ht="14" customHeight="1">
       <c r="A54" s="15" t="s">
         <v>56</v>
       </c>
       <c r="B54" s="18" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C54" s="10" t="s">
         <v>65</v>
@@ -11273,12 +11221,12 @@
       </c>
       <c r="J54" s="3"/>
     </row>
-    <row r="55" spans="1:10" ht="29">
+    <row r="55" spans="1:10" ht="16" customHeight="1">
       <c r="A55" s="15" t="s">
         <v>81</v>
       </c>
       <c r="B55" s="18" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C55" s="10"/>
       <c r="D55" s="10">
@@ -11306,7 +11254,7 @@
         <v>57</v>
       </c>
       <c r="B56" s="18" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C56" s="10" t="s">
         <v>32</v>
@@ -11336,7 +11284,7 @@
         <v>58</v>
       </c>
       <c r="B57" s="18" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C57" s="10" t="s">
         <v>32</v>
@@ -11366,7 +11314,7 @@
         <v>60</v>
       </c>
       <c r="B58" s="18" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C58" s="10" t="s">
         <v>47</v>
@@ -11397,7 +11345,7 @@
         <v>59</v>
       </c>
       <c r="B59" s="18" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C59" s="10" t="s">
         <v>66</v>
@@ -11428,7 +11376,7 @@
         <v>61</v>
       </c>
       <c r="B60" s="18" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C60" s="10" t="s">
         <v>63</v>
@@ -11517,11 +11465,11 @@
       </c>
     </row>
     <row r="65" spans="1:9">
-      <c r="A65" s="36" t="s">
-        <v>145</v>
+      <c r="A65" s="15" t="s">
+        <v>157</v>
       </c>
       <c r="B65" s="25" t="s">
-        <v>146</v>
+        <v>135</v>
       </c>
       <c r="C65" s="10" t="s">
         <v>71</v>
@@ -11546,11 +11494,11 @@
       </c>
     </row>
     <row r="66" spans="1:9">
-      <c r="A66" s="36" t="s">
-        <v>147</v>
+      <c r="A66" s="15" t="s">
+        <v>157</v>
       </c>
       <c r="B66" s="25" t="s">
-        <v>146</v>
+        <v>135</v>
       </c>
       <c r="C66" s="10" t="s">
         <v>71</v>
@@ -11575,11 +11523,11 @@
       </c>
     </row>
     <row r="67" spans="1:9">
-      <c r="A67" s="36" t="s">
-        <v>148</v>
+      <c r="A67" s="15" t="s">
+        <v>157</v>
       </c>
       <c r="B67" s="25" t="s">
-        <v>149</v>
+        <v>136</v>
       </c>
       <c r="C67" s="10" t="s">
         <v>72</v>
@@ -11604,11 +11552,11 @@
       </c>
     </row>
     <row r="68" spans="1:9">
-      <c r="A68" s="36" t="s">
-        <v>140</v>
+      <c r="A68" s="15" t="s">
+        <v>158</v>
       </c>
       <c r="B68" s="25" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="C68" s="10"/>
       <c r="D68" s="10"/>
@@ -11619,11 +11567,11 @@
       <c r="I68" s="16"/>
     </row>
     <row r="69" spans="1:9">
-      <c r="A69" s="36" t="s">
-        <v>142</v>
+      <c r="A69" s="15" t="s">
+        <v>158</v>
       </c>
       <c r="B69" s="25" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="C69" s="10"/>
       <c r="D69" s="10"/>
@@ -11634,11 +11582,11 @@
       <c r="I69" s="16"/>
     </row>
     <row r="70" spans="1:9">
-      <c r="A70" s="36" t="s">
-        <v>137</v>
+      <c r="A70" s="15" t="s">
+        <v>159</v>
       </c>
       <c r="B70" s="26" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="C70" s="10" t="s">
         <v>69</v>
@@ -11655,11 +11603,11 @@
       <c r="I70" s="16"/>
     </row>
     <row r="71" spans="1:9">
-      <c r="A71" s="36" t="s">
-        <v>139</v>
+      <c r="A71" s="15" t="s">
+        <v>159</v>
       </c>
       <c r="B71" s="26" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="C71" s="10"/>
       <c r="D71" s="10"/>
@@ -11670,11 +11618,11 @@
       <c r="I71" s="16"/>
     </row>
     <row r="72" spans="1:9">
-      <c r="A72" s="17" t="s">
-        <v>143</v>
+      <c r="A72" s="15" t="s">
+        <v>160</v>
       </c>
       <c r="B72" s="25" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="C72" s="10" t="s">
         <v>28</v>
@@ -11699,11 +11647,11 @@
       </c>
     </row>
     <row r="73" spans="1:9">
-      <c r="A73" s="36" t="s">
-        <v>133</v>
+      <c r="A73" s="15" t="s">
+        <v>161</v>
       </c>
       <c r="B73" s="25" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C73" s="10" t="s">
         <v>68</v>
@@ -11720,11 +11668,11 @@
       <c r="I73" s="16"/>
     </row>
     <row r="74" spans="1:9">
-      <c r="A74" s="36" t="s">
-        <v>135</v>
+      <c r="A74" s="15" t="s">
+        <v>161</v>
       </c>
       <c r="B74" s="25" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="C74" s="10" t="s">
         <v>67</v>
@@ -11750,10 +11698,10 @@
     </row>
     <row r="75" spans="1:9" ht="29">
       <c r="A75" s="15" t="s">
-        <v>132</v>
+        <v>162</v>
       </c>
       <c r="B75" s="17" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C75" s="10" t="s">
         <v>18</v>
@@ -11829,10 +11777,10 @@
     </row>
     <row r="79" spans="1:9" s="4" customFormat="1">
       <c r="A79" s="17" t="s">
-        <v>153</v>
+        <v>140</v>
       </c>
       <c r="B79" s="21" t="s">
-        <v>164</v>
+        <v>151</v>
       </c>
       <c r="C79" s="10" t="s">
         <v>40</v>
@@ -11858,10 +11806,10 @@
     </row>
     <row r="80" spans="1:9" s="4" customFormat="1">
       <c r="A80" s="15" t="s">
-        <v>154</v>
+        <v>141</v>
       </c>
       <c r="B80" s="21" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C80" s="10" t="s">
         <v>28</v>
@@ -11890,7 +11838,7 @@
         <v>75</v>
       </c>
       <c r="B81" s="17" t="s">
-        <v>155</v>
+        <v>142</v>
       </c>
       <c r="C81" s="10" t="s">
         <v>77</v>
@@ -11919,7 +11867,7 @@
         <v>76</v>
       </c>
       <c r="B82" s="21" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C82" s="10" t="s">
         <v>18</v>
@@ -11948,7 +11896,7 @@
         <v>39</v>
       </c>
       <c r="B83" s="21" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="C83" s="10" t="s">
         <v>40</v>
@@ -11974,10 +11922,10 @@
     </row>
     <row r="84" spans="1:9" s="4" customFormat="1">
       <c r="A84" s="15" t="s">
-        <v>150</v>
+        <v>137</v>
       </c>
       <c r="B84" s="17" t="s">
-        <v>166</v>
+        <v>153</v>
       </c>
       <c r="C84" s="10" t="s">
         <v>70</v>
@@ -12003,10 +11951,10 @@
     </row>
     <row r="85" spans="1:9" s="4" customFormat="1">
       <c r="A85" s="15" t="s">
-        <v>151</v>
+        <v>138</v>
       </c>
       <c r="B85" s="22" t="s">
-        <v>152</v>
+        <v>139</v>
       </c>
       <c r="C85" s="10" t="s">
         <v>70</v>
